--- a/Arbs/Arbsheet updated.xlsx
+++ b/Arbs/Arbsheet updated.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel desk\Arbsheet\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\Arbs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B5566-2A6A-4961-81E9-673F2B9DF725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3487CC69-7ABF-448E-83AB-D5B298C2D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3232,6 +3232,26 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="21" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="19" fillId="21" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3244,6 +3264,12 @@
     <xf numFmtId="16" fontId="0" fillId="25" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3253,17 +3279,11 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3280,16 +3300,16 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3394,25 +3414,10 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3428,6 +3433,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3454,12 +3474,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3475,29 +3489,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="21" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3505,14 +3501,18 @@
     <xf numFmtId="0" fontId="25" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="19" fillId="21" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -3521,27 +3521,7 @@
     <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="33">
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9" tint="-0.499984740745262"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="30">
     <dxf>
       <font>
         <color theme="9" tint="-0.499984740745262"/>
@@ -4360,60 +4340,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="12">
-        <item m="1" x="8"/>
-        <item m="1" x="10"/>
-        <item m="1" x="4"/>
-        <item m="1" x="6"/>
-        <item m="1" x="3"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="5"/>
-        <item n="01.11.2024" x="0"/>
-        <item n="01.12.2024" x="1"/>
-        <item n="01.01.2025" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O2:O5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -4839,6 +4765,60 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="12">
+        <item m="1" x="8"/>
+        <item m="1" x="10"/>
+        <item m="1" x="4"/>
+        <item m="1" x="6"/>
+        <item m="1" x="3"/>
+        <item m="1" x="9"/>
+        <item m="1" x="7"/>
+        <item m="1" x="5"/>
+        <item n="01.11.2024" x="0"/>
+        <item n="01.12.2024" x="1"/>
+        <item n="01.01.2025" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5110,7 +5090,7 @@
     <col min="2" max="2" width="28.7109375" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="7.42578125" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="23.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.5703125" hidden="1" customWidth="1"/>
     <col min="6" max="8" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23.5703125" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" customWidth="1"/>
@@ -5163,28 +5143,28 @@
       <c r="M3" s="155"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="448" t="s">
+      <c r="A4" s="457" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="155"/>
-      <c r="C4" s="444" t="s">
+      <c r="C4" s="454" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="446"/>
-      <c r="F4" s="444" t="s">
+      <c r="D4" s="456"/>
+      <c r="F4" s="454" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="445"/>
-      <c r="H4" s="446"/>
-      <c r="J4" s="444" t="s">
+      <c r="G4" s="455"/>
+      <c r="H4" s="456"/>
+      <c r="J4" s="454" t="s">
         <v>133</v>
       </c>
-      <c r="K4" s="445"/>
-      <c r="L4" s="446"/>
+      <c r="K4" s="455"/>
+      <c r="L4" s="456"/>
       <c r="M4" s="155"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="448"/>
+      <c r="A5" s="457"/>
       <c r="B5" s="199" t="s">
         <v>134</v>
       </c>
@@ -9339,28 +9319,28 @@
       <c r="M99" s="155"/>
     </row>
     <row r="100" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="447" t="s">
+      <c r="A100" s="458" t="s">
         <v>138</v>
       </c>
       <c r="B100" s="155"/>
-      <c r="C100" s="451"/>
-      <c r="D100" s="452"/>
+      <c r="C100" s="459"/>
+      <c r="D100" s="460"/>
       <c r="E100" s="139"/>
-      <c r="F100" s="453" t="s">
+      <c r="F100" s="461" t="s">
         <v>132</v>
       </c>
-      <c r="G100" s="454"/>
-      <c r="H100" s="455"/>
+      <c r="G100" s="462"/>
+      <c r="H100" s="463"/>
       <c r="I100" s="139"/>
-      <c r="J100" s="453" t="s">
+      <c r="J100" s="461" t="s">
         <v>133</v>
       </c>
-      <c r="K100" s="454"/>
-      <c r="L100" s="455"/>
+      <c r="K100" s="462"/>
+      <c r="L100" s="463"/>
       <c r="M100" s="155"/>
     </row>
     <row r="101" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="447"/>
+      <c r="A101" s="458"/>
       <c r="B101" s="199" t="s">
         <v>134</v>
       </c>
@@ -9437,8 +9417,8 @@
         <v>139</v>
       </c>
       <c r="B103" s="168"/>
-      <c r="C103" s="442"/>
-      <c r="D103" s="443"/>
+      <c r="C103" s="450"/>
+      <c r="D103" s="451"/>
       <c r="E103" s="10"/>
       <c r="F103" s="159">
         <f ca="1">F123+F104-F105</f>
@@ -9472,8 +9452,8 @@
       <c r="B104" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C104" s="442"/>
-      <c r="D104" s="443"/>
+      <c r="C104" s="450"/>
+      <c r="D104" s="451"/>
       <c r="E104" s="177" t="s">
         <v>131</v>
       </c>
@@ -9511,8 +9491,8 @@
       <c r="B105" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C105" s="442"/>
-      <c r="D105" s="443"/>
+      <c r="C105" s="450"/>
+      <c r="D105" s="451"/>
       <c r="E105" s="177" t="s">
         <v>130</v>
       </c>
@@ -9550,8 +9530,8 @@
       <c r="B106" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C106" s="442"/>
-      <c r="D106" s="443"/>
+      <c r="C106" s="450"/>
+      <c r="D106" s="451"/>
       <c r="E106" s="6" t="s">
         <v>55</v>
       </c>
@@ -9589,8 +9569,8 @@
       <c r="B107" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C107" s="442"/>
-      <c r="D107" s="443"/>
+      <c r="C107" s="450"/>
+      <c r="D107" s="451"/>
       <c r="E107" s="6" t="s">
         <v>56</v>
       </c>
@@ -9628,8 +9608,8 @@
       <c r="B108" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C108" s="442"/>
-      <c r="D108" s="443"/>
+      <c r="C108" s="450"/>
+      <c r="D108" s="451"/>
       <c r="E108" s="6" t="s">
         <v>57</v>
       </c>
@@ -9667,8 +9647,8 @@
       <c r="B109" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C109" s="442"/>
-      <c r="D109" s="443"/>
+      <c r="C109" s="450"/>
+      <c r="D109" s="451"/>
       <c r="E109" s="6" t="s">
         <v>58</v>
       </c>
@@ -9706,8 +9686,8 @@
       <c r="B110" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C110" s="442"/>
-      <c r="D110" s="443"/>
+      <c r="C110" s="450"/>
+      <c r="D110" s="451"/>
       <c r="E110" s="6" t="s">
         <v>127</v>
       </c>
@@ -9745,8 +9725,8 @@
       <c r="B111" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C111" s="442"/>
-      <c r="D111" s="443"/>
+      <c r="C111" s="450"/>
+      <c r="D111" s="451"/>
       <c r="E111" s="6" t="s">
         <v>128</v>
       </c>
@@ -9784,8 +9764,8 @@
       <c r="B112" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="442"/>
-      <c r="D112" s="443"/>
+      <c r="C112" s="450"/>
+      <c r="D112" s="451"/>
       <c r="E112" s="6" t="s">
         <v>83</v>
       </c>
@@ -9823,8 +9803,8 @@
       <c r="B113" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C113" s="442"/>
-      <c r="D113" s="443"/>
+      <c r="C113" s="450"/>
+      <c r="D113" s="451"/>
       <c r="E113" s="6" t="s">
         <v>59</v>
       </c>
@@ -9862,8 +9842,8 @@
       <c r="B114" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C114" s="442"/>
-      <c r="D114" s="443"/>
+      <c r="C114" s="450"/>
+      <c r="D114" s="451"/>
       <c r="E114" s="6" t="s">
         <v>60</v>
       </c>
@@ -9901,8 +9881,8 @@
       <c r="B115" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C115" s="442"/>
-      <c r="D115" s="443"/>
+      <c r="C115" s="450"/>
+      <c r="D115" s="451"/>
       <c r="E115" s="6" t="s">
         <v>61</v>
       </c>
@@ -9940,8 +9920,8 @@
       <c r="B116" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C116" s="442"/>
-      <c r="D116" s="443"/>
+      <c r="C116" s="450"/>
+      <c r="D116" s="451"/>
       <c r="E116" s="6" t="s">
         <v>62</v>
       </c>
@@ -9979,8 +9959,8 @@
       <c r="B117" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C117" s="442"/>
-      <c r="D117" s="443"/>
+      <c r="C117" s="450"/>
+      <c r="D117" s="451"/>
       <c r="E117" s="6" t="s">
         <v>63</v>
       </c>
@@ -10018,8 +9998,8 @@
       <c r="B118" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C118" s="442"/>
-      <c r="D118" s="443"/>
+      <c r="C118" s="450"/>
+      <c r="D118" s="451"/>
       <c r="E118" s="6" t="s">
         <v>64</v>
       </c>
@@ -10057,8 +10037,8 @@
       <c r="B119" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C119" s="442"/>
-      <c r="D119" s="443"/>
+      <c r="C119" s="450"/>
+      <c r="D119" s="451"/>
       <c r="E119" s="6" t="s">
         <v>65</v>
       </c>
@@ -10096,8 +10076,8 @@
       <c r="B120" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C120" s="442"/>
-      <c r="D120" s="443"/>
+      <c r="C120" s="450"/>
+      <c r="D120" s="451"/>
       <c r="E120" s="6" t="s">
         <v>66</v>
       </c>
@@ -10135,8 +10115,8 @@
       <c r="B121" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C121" s="442"/>
-      <c r="D121" s="443"/>
+      <c r="C121" s="450"/>
+      <c r="D121" s="451"/>
       <c r="E121" s="6" t="s">
         <v>102</v>
       </c>
@@ -10174,8 +10154,8 @@
       <c r="B122" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="442"/>
-      <c r="D122" s="443"/>
+      <c r="C122" s="450"/>
+      <c r="D122" s="451"/>
       <c r="E122" s="6" t="s">
         <v>103</v>
       </c>
@@ -10213,8 +10193,8 @@
       <c r="B123" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="442"/>
-      <c r="D123" s="443"/>
+      <c r="C123" s="450"/>
+      <c r="D123" s="451"/>
       <c r="E123" s="6" t="s">
         <v>115</v>
       </c>
@@ -10252,8 +10232,8 @@
       <c r="B124" s="257" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="442"/>
-      <c r="D124" s="443"/>
+      <c r="C124" s="450"/>
+      <c r="D124" s="451"/>
       <c r="E124" s="6" t="s">
         <v>129</v>
       </c>
@@ -10326,8 +10306,8 @@
       <c r="B126" s="169" t="s">
         <v>131</v>
       </c>
-      <c r="C126" s="442"/>
-      <c r="D126" s="456"/>
+      <c r="C126" s="450"/>
+      <c r="D126" s="466"/>
       <c r="E126" s="177" t="s">
         <v>131</v>
       </c>
@@ -10364,8 +10344,8 @@
       <c r="B127" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C127" s="442"/>
-      <c r="D127" s="456"/>
+      <c r="C127" s="450"/>
+      <c r="D127" s="466"/>
       <c r="E127" s="177" t="s">
         <v>130</v>
       </c>
@@ -10404,8 +10384,8 @@
       <c r="B128" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C128" s="442"/>
-      <c r="D128" s="456"/>
+      <c r="C128" s="450"/>
+      <c r="D128" s="466"/>
       <c r="E128" s="232" t="s">
         <v>55</v>
       </c>
@@ -10443,8 +10423,8 @@
       <c r="B129" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C129" s="442"/>
-      <c r="D129" s="456"/>
+      <c r="C129" s="450"/>
+      <c r="D129" s="466"/>
       <c r="E129" s="177" t="s">
         <v>56</v>
       </c>
@@ -10482,8 +10462,8 @@
       <c r="B130" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C130" s="442"/>
-      <c r="D130" s="456"/>
+      <c r="C130" s="450"/>
+      <c r="D130" s="466"/>
       <c r="E130" s="177" t="s">
         <v>57</v>
       </c>
@@ -10521,8 +10501,8 @@
       <c r="B131" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C131" s="442"/>
-      <c r="D131" s="456"/>
+      <c r="C131" s="450"/>
+      <c r="D131" s="466"/>
       <c r="E131" s="177" t="s">
         <v>58</v>
       </c>
@@ -10560,8 +10540,8 @@
       <c r="B132" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C132" s="442"/>
-      <c r="D132" s="456"/>
+      <c r="C132" s="450"/>
+      <c r="D132" s="466"/>
       <c r="E132" s="177" t="s">
         <v>127</v>
       </c>
@@ -10599,8 +10579,8 @@
       <c r="B133" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C133" s="442"/>
-      <c r="D133" s="456"/>
+      <c r="C133" s="450"/>
+      <c r="D133" s="466"/>
       <c r="E133" s="177" t="s">
         <v>128</v>
       </c>
@@ -10638,8 +10618,8 @@
       <c r="B134" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C134" s="442"/>
-      <c r="D134" s="456"/>
+      <c r="C134" s="450"/>
+      <c r="D134" s="466"/>
       <c r="E134" s="177" t="s">
         <v>83</v>
       </c>
@@ -10677,8 +10657,8 @@
       <c r="B135" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C135" s="442"/>
-      <c r="D135" s="456"/>
+      <c r="C135" s="450"/>
+      <c r="D135" s="466"/>
       <c r="E135" s="177" t="s">
         <v>59</v>
       </c>
@@ -10716,8 +10696,8 @@
       <c r="B136" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C136" s="442"/>
-      <c r="D136" s="456"/>
+      <c r="C136" s="450"/>
+      <c r="D136" s="466"/>
       <c r="E136" s="177" t="s">
         <v>60</v>
       </c>
@@ -10755,8 +10735,8 @@
       <c r="B137" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C137" s="442"/>
-      <c r="D137" s="456"/>
+      <c r="C137" s="450"/>
+      <c r="D137" s="466"/>
       <c r="E137" s="177" t="s">
         <v>61</v>
       </c>
@@ -10794,8 +10774,8 @@
       <c r="B138" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C138" s="442"/>
-      <c r="D138" s="456"/>
+      <c r="C138" s="450"/>
+      <c r="D138" s="466"/>
       <c r="E138" s="177" t="s">
         <v>62</v>
       </c>
@@ -10833,8 +10813,8 @@
       <c r="B139" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C139" s="442"/>
-      <c r="D139" s="456"/>
+      <c r="C139" s="450"/>
+      <c r="D139" s="466"/>
       <c r="E139" s="177" t="s">
         <v>63</v>
       </c>
@@ -10872,8 +10852,8 @@
       <c r="B140" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C140" s="442"/>
-      <c r="D140" s="456"/>
+      <c r="C140" s="450"/>
+      <c r="D140" s="466"/>
       <c r="E140" s="177" t="s">
         <v>64</v>
       </c>
@@ -10911,8 +10891,8 @@
       <c r="B141" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C141" s="442"/>
-      <c r="D141" s="456"/>
+      <c r="C141" s="450"/>
+      <c r="D141" s="466"/>
       <c r="E141" s="177" t="s">
         <v>65</v>
       </c>
@@ -10950,8 +10930,8 @@
       <c r="B142" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C142" s="442"/>
-      <c r="D142" s="456"/>
+      <c r="C142" s="450"/>
+      <c r="D142" s="466"/>
       <c r="E142" s="177" t="s">
         <v>66</v>
       </c>
@@ -10989,8 +10969,8 @@
       <c r="B143" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C143" s="442"/>
-      <c r="D143" s="456"/>
+      <c r="C143" s="450"/>
+      <c r="D143" s="466"/>
       <c r="E143" s="177" t="s">
         <v>102</v>
       </c>
@@ -11028,8 +11008,8 @@
       <c r="B144" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C144" s="442"/>
-      <c r="D144" s="456"/>
+      <c r="C144" s="450"/>
+      <c r="D144" s="466"/>
       <c r="E144" s="177" t="s">
         <v>103</v>
       </c>
@@ -11067,8 +11047,8 @@
       <c r="B145" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C145" s="442"/>
-      <c r="D145" s="456"/>
+      <c r="C145" s="450"/>
+      <c r="D145" s="466"/>
       <c r="E145" s="177" t="s">
         <v>115</v>
       </c>
@@ -11106,8 +11086,8 @@
       <c r="B146" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C146" s="457"/>
-      <c r="D146" s="458"/>
+      <c r="C146" s="464"/>
+      <c r="D146" s="467"/>
       <c r="E146" s="233" t="s">
         <v>129</v>
       </c>
@@ -11172,28 +11152,28 @@
       <c r="U148" s="436"/>
     </row>
     <row r="149" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="448" t="s">
+      <c r="A149" s="457" t="s">
         <v>141</v>
       </c>
       <c r="B149" s="155"/>
-      <c r="C149" s="449"/>
-      <c r="D149" s="450"/>
+      <c r="C149" s="452"/>
+      <c r="D149" s="453"/>
       <c r="E149" s="157"/>
-      <c r="F149" s="444" t="s">
+      <c r="F149" s="454" t="s">
         <v>132</v>
       </c>
-      <c r="G149" s="445"/>
-      <c r="H149" s="446"/>
+      <c r="G149" s="455"/>
+      <c r="H149" s="456"/>
       <c r="I149" s="157"/>
-      <c r="J149" s="444" t="s">
+      <c r="J149" s="454" t="s">
         <v>133</v>
       </c>
-      <c r="K149" s="445"/>
-      <c r="L149" s="446"/>
+      <c r="K149" s="455"/>
+      <c r="L149" s="456"/>
       <c r="M149" s="155"/>
     </row>
     <row r="150" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="448"/>
+      <c r="A150" s="457"/>
       <c r="B150" s="199" t="s">
         <v>134</v>
       </c>
@@ -11235,8 +11215,8 @@
       <c r="B151" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="C151" s="440"/>
-      <c r="D151" s="441"/>
+      <c r="C151" s="448"/>
+      <c r="D151" s="449"/>
       <c r="E151" s="6"/>
       <c r="F151" s="158">
         <f ca="1">'Loading Arrival'!B26</f>
@@ -11273,8 +11253,8 @@
         <v>235</v>
       </c>
       <c r="B152" s="168"/>
-      <c r="C152" s="442"/>
-      <c r="D152" s="443"/>
+      <c r="C152" s="450"/>
+      <c r="D152" s="451"/>
       <c r="E152" s="10"/>
       <c r="F152" s="159">
         <f ca="1">F172+F153-F154</f>
@@ -11311,8 +11291,8 @@
       <c r="B153" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C153" s="442"/>
-      <c r="D153" s="443"/>
+      <c r="C153" s="450"/>
+      <c r="D153" s="451"/>
       <c r="E153" s="177" t="s">
         <v>131</v>
       </c>
@@ -11353,8 +11333,8 @@
       <c r="B154" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C154" s="442"/>
-      <c r="D154" s="443"/>
+      <c r="C154" s="450"/>
+      <c r="D154" s="451"/>
       <c r="E154" s="177" t="s">
         <v>130</v>
       </c>
@@ -11392,8 +11372,8 @@
       <c r="B155" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C155" s="442"/>
-      <c r="D155" s="443"/>
+      <c r="C155" s="450"/>
+      <c r="D155" s="451"/>
       <c r="E155" s="6" t="s">
         <v>55</v>
       </c>
@@ -11431,8 +11411,8 @@
       <c r="B156" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C156" s="442"/>
-      <c r="D156" s="443"/>
+      <c r="C156" s="450"/>
+      <c r="D156" s="451"/>
       <c r="E156" s="6" t="s">
         <v>56</v>
       </c>
@@ -11470,8 +11450,8 @@
       <c r="B157" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C157" s="442"/>
-      <c r="D157" s="443"/>
+      <c r="C157" s="450"/>
+      <c r="D157" s="451"/>
       <c r="E157" s="6" t="s">
         <v>57</v>
       </c>
@@ -11509,8 +11489,8 @@
       <c r="B158" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C158" s="442"/>
-      <c r="D158" s="443"/>
+      <c r="C158" s="450"/>
+      <c r="D158" s="451"/>
       <c r="E158" s="6" t="s">
         <v>58</v>
       </c>
@@ -11548,8 +11528,8 @@
       <c r="B159" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C159" s="442"/>
-      <c r="D159" s="443"/>
+      <c r="C159" s="450"/>
+      <c r="D159" s="451"/>
       <c r="E159" s="6" t="s">
         <v>127</v>
       </c>
@@ -11587,8 +11567,8 @@
       <c r="B160" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C160" s="442"/>
-      <c r="D160" s="443"/>
+      <c r="C160" s="450"/>
+      <c r="D160" s="451"/>
       <c r="E160" s="6" t="s">
         <v>128</v>
       </c>
@@ -11626,8 +11606,8 @@
       <c r="B161" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C161" s="442"/>
-      <c r="D161" s="443"/>
+      <c r="C161" s="450"/>
+      <c r="D161" s="451"/>
       <c r="E161" s="6" t="s">
         <v>83</v>
       </c>
@@ -11665,8 +11645,8 @@
       <c r="B162" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C162" s="442"/>
-      <c r="D162" s="443"/>
+      <c r="C162" s="450"/>
+      <c r="D162" s="451"/>
       <c r="E162" s="6" t="s">
         <v>59</v>
       </c>
@@ -11704,8 +11684,8 @@
       <c r="B163" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C163" s="442"/>
-      <c r="D163" s="443"/>
+      <c r="C163" s="450"/>
+      <c r="D163" s="451"/>
       <c r="E163" s="6" t="s">
         <v>60</v>
       </c>
@@ -11743,8 +11723,8 @@
       <c r="B164" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C164" s="442"/>
-      <c r="D164" s="443"/>
+      <c r="C164" s="450"/>
+      <c r="D164" s="451"/>
       <c r="E164" s="6" t="s">
         <v>61</v>
       </c>
@@ -11782,8 +11762,8 @@
       <c r="B165" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C165" s="442"/>
-      <c r="D165" s="443"/>
+      <c r="C165" s="450"/>
+      <c r="D165" s="451"/>
       <c r="E165" s="6" t="s">
         <v>62</v>
       </c>
@@ -11821,8 +11801,8 @@
       <c r="B166" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C166" s="442"/>
-      <c r="D166" s="443"/>
+      <c r="C166" s="450"/>
+      <c r="D166" s="451"/>
       <c r="E166" s="6" t="s">
         <v>63</v>
       </c>
@@ -11860,8 +11840,8 @@
       <c r="B167" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C167" s="442"/>
-      <c r="D167" s="443"/>
+      <c r="C167" s="450"/>
+      <c r="D167" s="451"/>
       <c r="E167" s="6" t="s">
         <v>64</v>
       </c>
@@ -11899,8 +11879,8 @@
       <c r="B168" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C168" s="442"/>
-      <c r="D168" s="443"/>
+      <c r="C168" s="450"/>
+      <c r="D168" s="451"/>
       <c r="E168" s="6" t="s">
         <v>65</v>
       </c>
@@ -11938,8 +11918,8 @@
       <c r="B169" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C169" s="442"/>
-      <c r="D169" s="443"/>
+      <c r="C169" s="450"/>
+      <c r="D169" s="451"/>
       <c r="E169" s="6" t="s">
         <v>66</v>
       </c>
@@ -11977,8 +11957,8 @@
       <c r="B170" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C170" s="442"/>
-      <c r="D170" s="443"/>
+      <c r="C170" s="450"/>
+      <c r="D170" s="451"/>
       <c r="E170" s="6" t="s">
         <v>102</v>
       </c>
@@ -12016,8 +11996,8 @@
       <c r="B171" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C171" s="442"/>
-      <c r="D171" s="443"/>
+      <c r="C171" s="450"/>
+      <c r="D171" s="451"/>
       <c r="E171" s="6" t="s">
         <v>103</v>
       </c>
@@ -12055,8 +12035,8 @@
       <c r="B172" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C172" s="442"/>
-      <c r="D172" s="443"/>
+      <c r="C172" s="450"/>
+      <c r="D172" s="451"/>
       <c r="E172" s="6" t="s">
         <v>115</v>
       </c>
@@ -12094,8 +12074,8 @@
       <c r="B173" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C173" s="442"/>
-      <c r="D173" s="443"/>
+      <c r="C173" s="450"/>
+      <c r="D173" s="451"/>
       <c r="E173" s="6" t="s">
         <v>129</v>
       </c>
@@ -12145,28 +12125,28 @@
       <c r="M174" s="155"/>
     </row>
     <row r="175" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="447" t="s">
+      <c r="A175" s="458" t="s">
         <v>142</v>
       </c>
       <c r="B175" s="155"/>
-      <c r="C175" s="451"/>
-      <c r="D175" s="452"/>
+      <c r="C175" s="459"/>
+      <c r="D175" s="460"/>
       <c r="E175" s="214"/>
-      <c r="F175" s="453" t="s">
+      <c r="F175" s="461" t="s">
         <v>132</v>
       </c>
-      <c r="G175" s="454"/>
-      <c r="H175" s="455"/>
+      <c r="G175" s="462"/>
+      <c r="H175" s="463"/>
       <c r="I175" s="214"/>
-      <c r="J175" s="453" t="s">
+      <c r="J175" s="461" t="s">
         <v>133</v>
       </c>
-      <c r="K175" s="454"/>
-      <c r="L175" s="455"/>
+      <c r="K175" s="462"/>
+      <c r="L175" s="463"/>
       <c r="M175" s="155"/>
     </row>
     <row r="176" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="447"/>
+      <c r="A176" s="458"/>
       <c r="B176" s="199" t="s">
         <v>134</v>
       </c>
@@ -12208,8 +12188,8 @@
       <c r="B177" s="154" t="s">
         <v>134</v>
       </c>
-      <c r="C177" s="440"/>
-      <c r="D177" s="441"/>
+      <c r="C177" s="448"/>
+      <c r="D177" s="449"/>
       <c r="E177" s="6"/>
       <c r="F177" s="252">
         <f ca="1">'Loading Arrival'!B44</f>
@@ -12246,8 +12226,8 @@
         <v>139</v>
       </c>
       <c r="B178" s="168"/>
-      <c r="C178" s="442"/>
-      <c r="D178" s="443"/>
+      <c r="C178" s="450"/>
+      <c r="D178" s="451"/>
       <c r="E178" s="10"/>
       <c r="F178" s="159">
         <f ca="1">F198+F179-F180</f>
@@ -12281,8 +12261,8 @@
       <c r="B179" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C179" s="442"/>
-      <c r="D179" s="443"/>
+      <c r="C179" s="450"/>
+      <c r="D179" s="451"/>
       <c r="E179" s="177" t="s">
         <v>131</v>
       </c>
@@ -12320,8 +12300,8 @@
       <c r="B180" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C180" s="442"/>
-      <c r="D180" s="443"/>
+      <c r="C180" s="450"/>
+      <c r="D180" s="451"/>
       <c r="E180" s="177" t="s">
         <v>130</v>
       </c>
@@ -12359,8 +12339,8 @@
       <c r="B181" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C181" s="442"/>
-      <c r="D181" s="443"/>
+      <c r="C181" s="450"/>
+      <c r="D181" s="451"/>
       <c r="E181" s="6" t="s">
         <v>55</v>
       </c>
@@ -12397,8 +12377,8 @@
       <c r="B182" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C182" s="442"/>
-      <c r="D182" s="443"/>
+      <c r="C182" s="450"/>
+      <c r="D182" s="451"/>
       <c r="E182" s="6" t="s">
         <v>56</v>
       </c>
@@ -12435,8 +12415,8 @@
       <c r="B183" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C183" s="442"/>
-      <c r="D183" s="443"/>
+      <c r="C183" s="450"/>
+      <c r="D183" s="451"/>
       <c r="E183" s="6" t="s">
         <v>57</v>
       </c>
@@ -12473,8 +12453,8 @@
       <c r="B184" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C184" s="442"/>
-      <c r="D184" s="443"/>
+      <c r="C184" s="450"/>
+      <c r="D184" s="451"/>
       <c r="E184" s="6" t="s">
         <v>58</v>
       </c>
@@ -12511,8 +12491,8 @@
       <c r="B185" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C185" s="442"/>
-      <c r="D185" s="443"/>
+      <c r="C185" s="450"/>
+      <c r="D185" s="451"/>
       <c r="E185" s="6" t="s">
         <v>127</v>
       </c>
@@ -12549,8 +12529,8 @@
       <c r="B186" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C186" s="442"/>
-      <c r="D186" s="443"/>
+      <c r="C186" s="450"/>
+      <c r="D186" s="451"/>
       <c r="E186" s="6" t="s">
         <v>128</v>
       </c>
@@ -12587,8 +12567,8 @@
       <c r="B187" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C187" s="442"/>
-      <c r="D187" s="443"/>
+      <c r="C187" s="450"/>
+      <c r="D187" s="451"/>
       <c r="E187" s="6" t="s">
         <v>83</v>
       </c>
@@ -12625,8 +12605,8 @@
       <c r="B188" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C188" s="442"/>
-      <c r="D188" s="443"/>
+      <c r="C188" s="450"/>
+      <c r="D188" s="451"/>
       <c r="E188" s="6" t="s">
         <v>59</v>
       </c>
@@ -12663,8 +12643,8 @@
       <c r="B189" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C189" s="442"/>
-      <c r="D189" s="443"/>
+      <c r="C189" s="450"/>
+      <c r="D189" s="451"/>
       <c r="E189" s="6" t="s">
         <v>60</v>
       </c>
@@ -12701,8 +12681,8 @@
       <c r="B190" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C190" s="442"/>
-      <c r="D190" s="443"/>
+      <c r="C190" s="450"/>
+      <c r="D190" s="451"/>
       <c r="E190" s="6" t="s">
         <v>61</v>
       </c>
@@ -12739,8 +12719,8 @@
       <c r="B191" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C191" s="442"/>
-      <c r="D191" s="443"/>
+      <c r="C191" s="450"/>
+      <c r="D191" s="451"/>
       <c r="E191" s="6" t="s">
         <v>62</v>
       </c>
@@ -12777,8 +12757,8 @@
       <c r="B192" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C192" s="442"/>
-      <c r="D192" s="443"/>
+      <c r="C192" s="450"/>
+      <c r="D192" s="451"/>
       <c r="E192" s="6" t="s">
         <v>63</v>
       </c>
@@ -12815,8 +12795,8 @@
       <c r="B193" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C193" s="442"/>
-      <c r="D193" s="443"/>
+      <c r="C193" s="450"/>
+      <c r="D193" s="451"/>
       <c r="E193" s="6" t="s">
         <v>64</v>
       </c>
@@ -12853,8 +12833,8 @@
       <c r="B194" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C194" s="442"/>
-      <c r="D194" s="443"/>
+      <c r="C194" s="450"/>
+      <c r="D194" s="451"/>
       <c r="E194" s="6" t="s">
         <v>65</v>
       </c>
@@ -12891,8 +12871,8 @@
       <c r="B195" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C195" s="442"/>
-      <c r="D195" s="443"/>
+      <c r="C195" s="450"/>
+      <c r="D195" s="451"/>
       <c r="E195" s="6" t="s">
         <v>66</v>
       </c>
@@ -12929,8 +12909,8 @@
       <c r="B196" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C196" s="442"/>
-      <c r="D196" s="443"/>
+      <c r="C196" s="450"/>
+      <c r="D196" s="451"/>
       <c r="E196" s="6" t="s">
         <v>102</v>
       </c>
@@ -12967,8 +12947,8 @@
       <c r="B197" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C197" s="442"/>
-      <c r="D197" s="443"/>
+      <c r="C197" s="450"/>
+      <c r="D197" s="451"/>
       <c r="E197" s="6" t="s">
         <v>103</v>
       </c>
@@ -13005,8 +12985,8 @@
       <c r="B198" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C198" s="442"/>
-      <c r="D198" s="443"/>
+      <c r="C198" s="450"/>
+      <c r="D198" s="451"/>
       <c r="E198" s="6" t="s">
         <v>115</v>
       </c>
@@ -13043,8 +13023,8 @@
       <c r="B199" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C199" s="457"/>
-      <c r="D199" s="459"/>
+      <c r="C199" s="464"/>
+      <c r="D199" s="465"/>
       <c r="E199" s="105" t="s">
         <v>129</v>
       </c>
@@ -13126,20 +13106,20 @@
     <row r="204" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="155"/>
       <c r="B204" s="155"/>
-      <c r="C204" s="449"/>
-      <c r="D204" s="450"/>
+      <c r="C204" s="452"/>
+      <c r="D204" s="453"/>
       <c r="E204" s="157"/>
-      <c r="F204" s="444" t="s">
+      <c r="F204" s="454" t="s">
         <v>132</v>
       </c>
-      <c r="G204" s="445"/>
-      <c r="H204" s="446"/>
+      <c r="G204" s="455"/>
+      <c r="H204" s="456"/>
       <c r="I204" s="157"/>
-      <c r="J204" s="444" t="s">
+      <c r="J204" s="454" t="s">
         <v>133</v>
       </c>
-      <c r="K204" s="445"/>
-      <c r="L204" s="446"/>
+      <c r="K204" s="455"/>
+      <c r="L204" s="456"/>
       <c r="M204" s="155"/>
     </row>
     <row r="205" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -13147,8 +13127,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="B205" s="171"/>
-      <c r="C205" s="449"/>
-      <c r="D205" s="450">
+      <c r="C205" s="452"/>
+      <c r="D205" s="453">
         <f>D227+D208-D209</f>
         <v>0</v>
       </c>
@@ -13253,8 +13233,8 @@
       <c r="B208" s="167" t="s">
         <v>131</v>
       </c>
-      <c r="C208" s="440"/>
-      <c r="D208" s="441"/>
+      <c r="C208" s="448"/>
+      <c r="D208" s="449"/>
       <c r="E208" s="177" t="s">
         <v>131</v>
       </c>
@@ -13293,8 +13273,8 @@
       <c r="B209" s="172" t="s">
         <v>130</v>
       </c>
-      <c r="C209" s="442"/>
-      <c r="D209" s="443"/>
+      <c r="C209" s="450"/>
+      <c r="D209" s="451"/>
       <c r="E209" s="177" t="s">
         <v>130</v>
       </c>
@@ -13332,8 +13312,8 @@
       <c r="B210" s="155" t="s">
         <v>55</v>
       </c>
-      <c r="C210" s="440"/>
-      <c r="D210" s="441"/>
+      <c r="C210" s="448"/>
+      <c r="D210" s="449"/>
       <c r="E210" s="6" t="s">
         <v>55</v>
       </c>
@@ -13371,8 +13351,8 @@
       <c r="B211" s="155" t="s">
         <v>56</v>
       </c>
-      <c r="C211" s="442"/>
-      <c r="D211" s="443"/>
+      <c r="C211" s="450"/>
+      <c r="D211" s="451"/>
       <c r="E211" t="s">
         <v>56</v>
       </c>
@@ -13410,8 +13390,8 @@
       <c r="B212" s="155" t="s">
         <v>57</v>
       </c>
-      <c r="C212" s="442"/>
-      <c r="D212" s="443"/>
+      <c r="C212" s="450"/>
+      <c r="D212" s="451"/>
       <c r="E212" t="s">
         <v>57</v>
       </c>
@@ -13449,8 +13429,8 @@
       <c r="B213" s="155" t="s">
         <v>58</v>
       </c>
-      <c r="C213" s="442"/>
-      <c r="D213" s="443"/>
+      <c r="C213" s="450"/>
+      <c r="D213" s="451"/>
       <c r="E213" t="s">
         <v>58</v>
       </c>
@@ -13488,8 +13468,8 @@
       <c r="B214" s="155" t="s">
         <v>127</v>
       </c>
-      <c r="C214" s="442"/>
-      <c r="D214" s="443"/>
+      <c r="C214" s="450"/>
+      <c r="D214" s="451"/>
       <c r="E214" t="s">
         <v>127</v>
       </c>
@@ -13526,8 +13506,8 @@
       <c r="B215" s="155" t="s">
         <v>128</v>
       </c>
-      <c r="C215" s="442"/>
-      <c r="D215" s="443"/>
+      <c r="C215" s="450"/>
+      <c r="D215" s="451"/>
       <c r="E215" t="s">
         <v>128</v>
       </c>
@@ -13564,8 +13544,8 @@
       <c r="B216" s="155" t="s">
         <v>83</v>
       </c>
-      <c r="C216" s="442"/>
-      <c r="D216" s="443"/>
+      <c r="C216" s="450"/>
+      <c r="D216" s="451"/>
       <c r="E216" t="s">
         <v>83</v>
       </c>
@@ -13602,8 +13582,8 @@
       <c r="B217" s="155" t="s">
         <v>59</v>
       </c>
-      <c r="C217" s="442"/>
-      <c r="D217" s="443"/>
+      <c r="C217" s="450"/>
+      <c r="D217" s="451"/>
       <c r="E217" t="s">
         <v>59</v>
       </c>
@@ -13640,8 +13620,8 @@
       <c r="B218" s="155" t="s">
         <v>60</v>
       </c>
-      <c r="C218" s="442"/>
-      <c r="D218" s="443"/>
+      <c r="C218" s="450"/>
+      <c r="D218" s="451"/>
       <c r="E218" t="s">
         <v>60</v>
       </c>
@@ -13678,8 +13658,8 @@
       <c r="B219" s="155" t="s">
         <v>61</v>
       </c>
-      <c r="C219" s="442"/>
-      <c r="D219" s="443"/>
+      <c r="C219" s="450"/>
+      <c r="D219" s="451"/>
       <c r="E219" t="s">
         <v>61</v>
       </c>
@@ -13716,8 +13696,8 @@
       <c r="B220" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="C220" s="442"/>
-      <c r="D220" s="443"/>
+      <c r="C220" s="450"/>
+      <c r="D220" s="451"/>
       <c r="E220" t="s">
         <v>62</v>
       </c>
@@ -13754,8 +13734,8 @@
       <c r="B221" s="155" t="s">
         <v>63</v>
       </c>
-      <c r="C221" s="442"/>
-      <c r="D221" s="443"/>
+      <c r="C221" s="450"/>
+      <c r="D221" s="451"/>
       <c r="E221" t="s">
         <v>63</v>
       </c>
@@ -13792,8 +13772,8 @@
       <c r="B222" s="155" t="s">
         <v>64</v>
       </c>
-      <c r="C222" s="442"/>
-      <c r="D222" s="443"/>
+      <c r="C222" s="450"/>
+      <c r="D222" s="451"/>
       <c r="E222" t="s">
         <v>64</v>
       </c>
@@ -13830,8 +13810,8 @@
       <c r="B223" s="155" t="s">
         <v>65</v>
       </c>
-      <c r="C223" s="442"/>
-      <c r="D223" s="443"/>
+      <c r="C223" s="450"/>
+      <c r="D223" s="451"/>
       <c r="E223" t="s">
         <v>65</v>
       </c>
@@ -13868,8 +13848,8 @@
       <c r="B224" s="155" t="s">
         <v>66</v>
       </c>
-      <c r="C224" s="442"/>
-      <c r="D224" s="443"/>
+      <c r="C224" s="450"/>
+      <c r="D224" s="451"/>
       <c r="E224" t="s">
         <v>66</v>
       </c>
@@ -13906,8 +13886,8 @@
       <c r="B225" s="155" t="s">
         <v>102</v>
       </c>
-      <c r="C225" s="442"/>
-      <c r="D225" s="443"/>
+      <c r="C225" s="450"/>
+      <c r="D225" s="451"/>
       <c r="E225" t="s">
         <v>102</v>
       </c>
@@ -13944,8 +13924,8 @@
       <c r="B226" s="155" t="s">
         <v>103</v>
       </c>
-      <c r="C226" s="442"/>
-      <c r="D226" s="443"/>
+      <c r="C226" s="450"/>
+      <c r="D226" s="451"/>
       <c r="E226" t="s">
         <v>103</v>
       </c>
@@ -13982,8 +13962,8 @@
       <c r="B227" s="155" t="s">
         <v>115</v>
       </c>
-      <c r="C227" s="442"/>
-      <c r="D227" s="443"/>
+      <c r="C227" s="450"/>
+      <c r="D227" s="451"/>
       <c r="E227" t="s">
         <v>115</v>
       </c>
@@ -14020,8 +14000,8 @@
       <c r="B228" s="155" t="s">
         <v>129</v>
       </c>
-      <c r="C228" s="442"/>
-      <c r="D228" s="443"/>
+      <c r="C228" s="450"/>
+      <c r="D228" s="451"/>
       <c r="E228" t="s">
         <v>129</v>
       </c>
@@ -14095,28 +14075,28 @@
       <c r="M231" s="155"/>
     </row>
     <row r="232" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="448" t="s">
+      <c r="A232" s="457" t="s">
         <v>214</v>
       </c>
       <c r="B232" s="155"/>
-      <c r="C232" s="449"/>
-      <c r="D232" s="450"/>
+      <c r="C232" s="452"/>
+      <c r="D232" s="453"/>
       <c r="E232" s="157"/>
-      <c r="F232" s="444" t="s">
+      <c r="F232" s="454" t="s">
         <v>132</v>
       </c>
-      <c r="G232" s="445"/>
-      <c r="H232" s="446"/>
+      <c r="G232" s="455"/>
+      <c r="H232" s="456"/>
       <c r="I232" s="157"/>
-      <c r="J232" s="444" t="s">
+      <c r="J232" s="454" t="s">
         <v>133</v>
       </c>
-      <c r="K232" s="445"/>
-      <c r="L232" s="446"/>
+      <c r="K232" s="455"/>
+      <c r="L232" s="456"/>
       <c r="M232" s="155"/>
     </row>
     <row r="233" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="448"/>
+      <c r="A233" s="457"/>
       <c r="B233" s="199" t="s">
         <v>187</v>
       </c>
@@ -14154,8 +14134,8 @@
       <c r="M233" s="155"/>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C234" s="440"/>
-      <c r="D234" s="441"/>
+      <c r="C234" s="448"/>
+      <c r="D234" s="449"/>
       <c r="F234" s="158">
         <f ca="1">'Loading Arrival'!G9</f>
         <v>45918</v>
@@ -14191,8 +14171,8 @@
         <v>231</v>
       </c>
       <c r="B235" s="168"/>
-      <c r="C235" s="442"/>
-      <c r="D235" s="443"/>
+      <c r="C235" s="450"/>
+      <c r="D235" s="451"/>
       <c r="F235" s="159">
         <f ca="1">F255+F236-F237</f>
         <v>-53.505408333333307</v>
@@ -14225,8 +14205,8 @@
       <c r="B236" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C236" s="442"/>
-      <c r="D236" s="443"/>
+      <c r="C236" s="450"/>
+      <c r="D236" s="451"/>
       <c r="E236" s="177" t="s">
         <v>131</v>
       </c>
@@ -14264,8 +14244,8 @@
       <c r="B237" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C237" s="442"/>
-      <c r="D237" s="443"/>
+      <c r="C237" s="450"/>
+      <c r="D237" s="451"/>
       <c r="E237" s="177" t="s">
         <v>130</v>
       </c>
@@ -14303,8 +14283,8 @@
       <c r="B238" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C238" s="442"/>
-      <c r="D238" s="443"/>
+      <c r="C238" s="450"/>
+      <c r="D238" s="451"/>
       <c r="E238" s="6" t="s">
         <v>55</v>
       </c>
@@ -14342,8 +14322,8 @@
       <c r="B239" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C239" s="442"/>
-      <c r="D239" s="443"/>
+      <c r="C239" s="450"/>
+      <c r="D239" s="451"/>
       <c r="E239" t="s">
         <v>56</v>
       </c>
@@ -14381,8 +14361,8 @@
       <c r="B240" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C240" s="442"/>
-      <c r="D240" s="443"/>
+      <c r="C240" s="450"/>
+      <c r="D240" s="451"/>
       <c r="E240" t="s">
         <v>57</v>
       </c>
@@ -14420,8 +14400,8 @@
       <c r="B241" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C241" s="442"/>
-      <c r="D241" s="443"/>
+      <c r="C241" s="450"/>
+      <c r="D241" s="451"/>
       <c r="E241" t="s">
         <v>58</v>
       </c>
@@ -14459,8 +14439,8 @@
       <c r="B242" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C242" s="442"/>
-      <c r="D242" s="443"/>
+      <c r="C242" s="450"/>
+      <c r="D242" s="451"/>
       <c r="E242" t="s">
         <v>127</v>
       </c>
@@ -14498,8 +14478,8 @@
       <c r="B243" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C243" s="442"/>
-      <c r="D243" s="443"/>
+      <c r="C243" s="450"/>
+      <c r="D243" s="451"/>
       <c r="E243" t="s">
         <v>128</v>
       </c>
@@ -14537,8 +14517,8 @@
       <c r="B244" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C244" s="442"/>
-      <c r="D244" s="443"/>
+      <c r="C244" s="450"/>
+      <c r="D244" s="451"/>
       <c r="E244" t="s">
         <v>83</v>
       </c>
@@ -14576,8 +14556,8 @@
       <c r="B245" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C245" s="442"/>
-      <c r="D245" s="443"/>
+      <c r="C245" s="450"/>
+      <c r="D245" s="451"/>
       <c r="E245" t="s">
         <v>59</v>
       </c>
@@ -14615,8 +14595,8 @@
       <c r="B246" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C246" s="442"/>
-      <c r="D246" s="443"/>
+      <c r="C246" s="450"/>
+      <c r="D246" s="451"/>
       <c r="E246" t="s">
         <v>60</v>
       </c>
@@ -14654,8 +14634,8 @@
       <c r="B247" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C247" s="442"/>
-      <c r="D247" s="443"/>
+      <c r="C247" s="450"/>
+      <c r="D247" s="451"/>
       <c r="E247" t="s">
         <v>61</v>
       </c>
@@ -14693,8 +14673,8 @@
       <c r="B248" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C248" s="442"/>
-      <c r="D248" s="443"/>
+      <c r="C248" s="450"/>
+      <c r="D248" s="451"/>
       <c r="E248" t="s">
         <v>62</v>
       </c>
@@ -14732,8 +14712,8 @@
       <c r="B249" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C249" s="442"/>
-      <c r="D249" s="443"/>
+      <c r="C249" s="450"/>
+      <c r="D249" s="451"/>
       <c r="E249" t="s">
         <v>63</v>
       </c>
@@ -14771,8 +14751,8 @@
       <c r="B250" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C250" s="442"/>
-      <c r="D250" s="443"/>
+      <c r="C250" s="450"/>
+      <c r="D250" s="451"/>
       <c r="E250" t="s">
         <v>64</v>
       </c>
@@ -14810,8 +14790,8 @@
       <c r="B251" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C251" s="442"/>
-      <c r="D251" s="443"/>
+      <c r="C251" s="450"/>
+      <c r="D251" s="451"/>
       <c r="E251" t="s">
         <v>65</v>
       </c>
@@ -14849,8 +14829,8 @@
       <c r="B252" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C252" s="442"/>
-      <c r="D252" s="443"/>
+      <c r="C252" s="450"/>
+      <c r="D252" s="451"/>
       <c r="E252" t="s">
         <v>66</v>
       </c>
@@ -14888,8 +14868,8 @@
       <c r="B253" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C253" s="442"/>
-      <c r="D253" s="443"/>
+      <c r="C253" s="450"/>
+      <c r="D253" s="451"/>
       <c r="E253" t="s">
         <v>102</v>
       </c>
@@ -14927,8 +14907,8 @@
       <c r="B254" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C254" s="442"/>
-      <c r="D254" s="443"/>
+      <c r="C254" s="450"/>
+      <c r="D254" s="451"/>
       <c r="E254" t="s">
         <v>103</v>
       </c>
@@ -14966,8 +14946,8 @@
       <c r="B255" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C255" s="442"/>
-      <c r="D255" s="443"/>
+      <c r="C255" s="450"/>
+      <c r="D255" s="451"/>
       <c r="E255" t="s">
         <v>115</v>
       </c>
@@ -15005,8 +14985,8 @@
       <c r="B256" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C256" s="442"/>
-      <c r="D256" s="443"/>
+      <c r="C256" s="450"/>
+      <c r="D256" s="451"/>
       <c r="E256" t="s">
         <v>129</v>
       </c>
@@ -15058,8 +15038,8 @@
     <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="155"/>
       <c r="B258" s="155"/>
-      <c r="C258" s="440"/>
-      <c r="D258" s="441"/>
+      <c r="C258" s="448"/>
+      <c r="D258" s="449"/>
       <c r="F258" s="158">
         <f ca="1">F234</f>
         <v>45918</v>
@@ -15095,8 +15075,8 @@
         <v>232</v>
       </c>
       <c r="B259" s="168"/>
-      <c r="C259" s="442"/>
-      <c r="D259" s="443"/>
+      <c r="C259" s="450"/>
+      <c r="D259" s="451"/>
       <c r="F259" s="159">
         <f ca="1">F279+F260-F261</f>
         <v>-12.710598256550956</v>
@@ -15129,8 +15109,8 @@
       <c r="B260" s="169" t="s">
         <v>136</v>
       </c>
-      <c r="C260" s="442"/>
-      <c r="D260" s="443"/>
+      <c r="C260" s="450"/>
+      <c r="D260" s="451"/>
       <c r="E260" s="177" t="s">
         <v>131</v>
       </c>
@@ -15168,8 +15148,8 @@
       <c r="B261" s="170" t="s">
         <v>135</v>
       </c>
-      <c r="C261" s="442"/>
-      <c r="D261" s="443"/>
+      <c r="C261" s="450"/>
+      <c r="D261" s="451"/>
       <c r="E261" s="177" t="s">
         <v>130</v>
       </c>
@@ -15207,8 +15187,8 @@
       <c r="B262" s="255" t="s">
         <v>55</v>
       </c>
-      <c r="C262" s="442"/>
-      <c r="D262" s="443"/>
+      <c r="C262" s="450"/>
+      <c r="D262" s="451"/>
       <c r="E262" s="6" t="s">
         <v>55</v>
       </c>
@@ -15245,8 +15225,8 @@
       <c r="B263" s="256" t="s">
         <v>56</v>
       </c>
-      <c r="C263" s="442"/>
-      <c r="D263" s="443"/>
+      <c r="C263" s="450"/>
+      <c r="D263" s="451"/>
       <c r="E263" t="s">
         <v>56</v>
       </c>
@@ -15283,8 +15263,8 @@
       <c r="B264" s="256" t="s">
         <v>57</v>
       </c>
-      <c r="C264" s="442"/>
-      <c r="D264" s="443"/>
+      <c r="C264" s="450"/>
+      <c r="D264" s="451"/>
       <c r="E264" t="s">
         <v>57</v>
       </c>
@@ -15321,8 +15301,8 @@
       <c r="B265" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="C265" s="442"/>
-      <c r="D265" s="443"/>
+      <c r="C265" s="450"/>
+      <c r="D265" s="451"/>
       <c r="E265" t="s">
         <v>58</v>
       </c>
@@ -15359,8 +15339,8 @@
       <c r="B266" s="256" t="s">
         <v>127</v>
       </c>
-      <c r="C266" s="442"/>
-      <c r="D266" s="443"/>
+      <c r="C266" s="450"/>
+      <c r="D266" s="451"/>
       <c r="E266" t="s">
         <v>127</v>
       </c>
@@ -15397,8 +15377,8 @@
       <c r="B267" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C267" s="442"/>
-      <c r="D267" s="443"/>
+      <c r="C267" s="450"/>
+      <c r="D267" s="451"/>
       <c r="E267" t="s">
         <v>128</v>
       </c>
@@ -15435,8 +15415,8 @@
       <c r="B268" s="256" t="s">
         <v>83</v>
       </c>
-      <c r="C268" s="442"/>
-      <c r="D268" s="443"/>
+      <c r="C268" s="450"/>
+      <c r="D268" s="451"/>
       <c r="E268" t="s">
         <v>83</v>
       </c>
@@ -15473,8 +15453,8 @@
       <c r="B269" s="256" t="s">
         <v>59</v>
       </c>
-      <c r="C269" s="442"/>
-      <c r="D269" s="443"/>
+      <c r="C269" s="450"/>
+      <c r="D269" s="451"/>
       <c r="E269" t="s">
         <v>59</v>
       </c>
@@ -15511,8 +15491,8 @@
       <c r="B270" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="C270" s="442"/>
-      <c r="D270" s="443"/>
+      <c r="C270" s="450"/>
+      <c r="D270" s="451"/>
       <c r="E270" t="s">
         <v>60</v>
       </c>
@@ -15549,8 +15529,8 @@
       <c r="B271" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="C271" s="442"/>
-      <c r="D271" s="443"/>
+      <c r="C271" s="450"/>
+      <c r="D271" s="451"/>
       <c r="E271" t="s">
         <v>61</v>
       </c>
@@ -15587,8 +15567,8 @@
       <c r="B272" s="256" t="s">
         <v>62</v>
       </c>
-      <c r="C272" s="442"/>
-      <c r="D272" s="443"/>
+      <c r="C272" s="450"/>
+      <c r="D272" s="451"/>
       <c r="E272" t="s">
         <v>62</v>
       </c>
@@ -15625,8 +15605,8 @@
       <c r="B273" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="C273" s="442"/>
-      <c r="D273" s="443"/>
+      <c r="C273" s="450"/>
+      <c r="D273" s="451"/>
       <c r="E273" t="s">
         <v>63</v>
       </c>
@@ -15663,8 +15643,8 @@
       <c r="B274" s="256" t="s">
         <v>64</v>
       </c>
-      <c r="C274" s="442"/>
-      <c r="D274" s="443"/>
+      <c r="C274" s="450"/>
+      <c r="D274" s="451"/>
       <c r="E274" t="s">
         <v>64</v>
       </c>
@@ -15701,8 +15681,8 @@
       <c r="B275" s="256" t="s">
         <v>65</v>
       </c>
-      <c r="C275" s="442"/>
-      <c r="D275" s="443"/>
+      <c r="C275" s="450"/>
+      <c r="D275" s="451"/>
       <c r="E275" t="s">
         <v>65</v>
       </c>
@@ -15739,8 +15719,8 @@
       <c r="B276" s="256" t="s">
         <v>66</v>
       </c>
-      <c r="C276" s="442"/>
-      <c r="D276" s="443"/>
+      <c r="C276" s="450"/>
+      <c r="D276" s="451"/>
       <c r="E276" t="s">
         <v>66</v>
       </c>
@@ -15777,8 +15757,8 @@
       <c r="B277" s="256" t="s">
         <v>102</v>
       </c>
-      <c r="C277" s="442"/>
-      <c r="D277" s="443"/>
+      <c r="C277" s="450"/>
+      <c r="D277" s="451"/>
       <c r="E277" t="s">
         <v>102</v>
       </c>
@@ -15815,8 +15795,8 @@
       <c r="B278" s="256" t="s">
         <v>103</v>
       </c>
-      <c r="C278" s="442"/>
-      <c r="D278" s="443"/>
+      <c r="C278" s="450"/>
+      <c r="D278" s="451"/>
       <c r="E278" t="s">
         <v>103</v>
       </c>
@@ -15853,8 +15833,8 @@
       <c r="B279" s="256" t="s">
         <v>115</v>
       </c>
-      <c r="C279" s="442"/>
-      <c r="D279" s="443"/>
+      <c r="C279" s="450"/>
+      <c r="D279" s="451"/>
       <c r="E279" t="s">
         <v>115</v>
       </c>
@@ -15891,8 +15871,8 @@
       <c r="B280" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C280" s="442"/>
-      <c r="D280" s="443"/>
+      <c r="C280" s="450"/>
+      <c r="D280" s="451"/>
       <c r="E280" t="s">
         <v>129</v>
       </c>
@@ -15942,22 +15922,6 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="32">
-    <mergeCell ref="C234:D256"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="F204:H204"/>
-    <mergeCell ref="J204:L204"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="C232:D232"/>
-    <mergeCell ref="F232:H232"/>
-    <mergeCell ref="J232:L232"/>
-    <mergeCell ref="C210:D228"/>
-    <mergeCell ref="C208:D209"/>
-    <mergeCell ref="C205:D205"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:H175"/>
-    <mergeCell ref="J175:L175"/>
-    <mergeCell ref="C177:D199"/>
     <mergeCell ref="C258:D280"/>
     <mergeCell ref="J149:L149"/>
     <mergeCell ref="C151:D173"/>
@@ -15974,112 +15938,128 @@
     <mergeCell ref="J100:L100"/>
     <mergeCell ref="C103:D124"/>
     <mergeCell ref="C126:D146"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:H175"/>
+    <mergeCell ref="J175:L175"/>
+    <mergeCell ref="C177:D199"/>
+    <mergeCell ref="C234:D256"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="F204:H204"/>
+    <mergeCell ref="J204:L204"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="C232:D232"/>
+    <mergeCell ref="F232:H232"/>
+    <mergeCell ref="J232:L232"/>
+    <mergeCell ref="C210:D228"/>
+    <mergeCell ref="C208:D209"/>
+    <mergeCell ref="C205:D205"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:L7 C29:L29">
-    <cfRule type="cellIs" dxfId="32" priority="31" operator="between">
+    <cfRule type="cellIs" dxfId="29" priority="31" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="32" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="32" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="33" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="27" priority="33" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C54:L54 C76:L76">
-    <cfRule type="cellIs" dxfId="29" priority="28" operator="between">
+    <cfRule type="cellIs" dxfId="26" priority="28" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="29" operator="lessThan">
+    <cfRule type="cellIs" dxfId="25" priority="29" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="30" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="24" priority="30" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E103:L103 E125:L125">
-    <cfRule type="cellIs" dxfId="26" priority="25" operator="between">
+    <cfRule type="cellIs" dxfId="23" priority="25" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="26" operator="lessThan">
+    <cfRule type="cellIs" dxfId="22" priority="26" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="27" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="21" priority="27" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E152:L152">
-    <cfRule type="cellIs" dxfId="23" priority="19" operator="between">
+    <cfRule type="cellIs" dxfId="20" priority="19" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="20" operator="lessThan">
+    <cfRule type="cellIs" dxfId="19" priority="20" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="21" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="18" priority="21" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E178:L178">
-    <cfRule type="cellIs" dxfId="20" priority="16" operator="between">
+    <cfRule type="cellIs" dxfId="17" priority="16" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="17" operator="lessThan">
+    <cfRule type="cellIs" dxfId="16" priority="17" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="18" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="15" priority="18" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F207:L207">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="between">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="lessThan">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="15" priority="9" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F235:L235">
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="between">
+    <cfRule type="cellIs" dxfId="11" priority="4" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="10" priority="5" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="9" priority="6" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F259:L259">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="between">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I205:I206 E205:E207">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="between">
+    <cfRule type="cellIs" dxfId="5" priority="10" operator="between">
       <formula>-2.5</formula>
       <formula>0.01</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="lessThan">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="lessThan">
       <formula>-2.5</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="12" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="greaterThan">
       <formula>-0.01</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16153,10 +16133,10 @@
         <f ca="1">E2-B2</f>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I2" s="510" t="s">
+      <c r="I2" s="518" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="511" t="s">
+      <c r="J2" s="519" t="s">
         <v>46</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -16192,8 +16172,8 @@
         <f t="shared" ref="F3:F66" ca="1" si="0">E3-B3</f>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I3" s="510"/>
-      <c r="J3" s="512"/>
+      <c r="I3" s="518"/>
+      <c r="J3" s="520"/>
       <c r="K3" s="5" t="s">
         <v>106</v>
       </c>
@@ -16227,8 +16207,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I4" s="510"/>
-      <c r="J4" s="512"/>
+      <c r="I4" s="518"/>
+      <c r="J4" s="520"/>
       <c r="K4" s="114" t="s">
         <v>107</v>
       </c>
@@ -16262,8 +16242,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I5" s="510"/>
-      <c r="J5" s="512"/>
+      <c r="I5" s="518"/>
+      <c r="J5" s="520"/>
       <c r="K5" s="3" t="s">
         <v>108</v>
       </c>
@@ -16297,8 +16277,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I6" s="510"/>
-      <c r="J6" s="512"/>
+      <c r="I6" s="518"/>
+      <c r="J6" s="520"/>
       <c r="K6" s="5" t="s">
         <v>106</v>
       </c>
@@ -16332,8 +16312,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I7" s="510"/>
-      <c r="J7" s="512"/>
+      <c r="I7" s="518"/>
+      <c r="J7" s="520"/>
       <c r="K7" s="7" t="s">
         <v>107</v>
       </c>
@@ -16367,8 +16347,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I8" s="510"/>
-      <c r="J8" s="512"/>
+      <c r="I8" s="518"/>
+      <c r="J8" s="520"/>
       <c r="K8" s="3" t="s">
         <v>109</v>
       </c>
@@ -16402,8 +16382,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I9" s="510"/>
-      <c r="J9" s="512"/>
+      <c r="I9" s="518"/>
+      <c r="J9" s="520"/>
       <c r="K9" s="5" t="s">
         <v>106</v>
       </c>
@@ -16437,8 +16417,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I10" s="510"/>
-      <c r="J10" s="513"/>
+      <c r="I10" s="518"/>
+      <c r="J10" s="521"/>
       <c r="K10" s="114" t="s">
         <v>107</v>
       </c>
@@ -16472,7 +16452,7 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I11" s="510"/>
+      <c r="I11" s="518"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -16499,8 +16479,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I12" s="510"/>
-      <c r="J12" s="507" t="s">
+      <c r="I12" s="518"/>
+      <c r="J12" s="515" t="s">
         <v>110</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -16536,8 +16516,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I13" s="510"/>
-      <c r="J13" s="508"/>
+      <c r="I13" s="518"/>
+      <c r="J13" s="516"/>
       <c r="K13" s="5" t="s">
         <v>106</v>
       </c>
@@ -16571,8 +16551,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I14" s="510"/>
-      <c r="J14" s="508"/>
+      <c r="I14" s="518"/>
+      <c r="J14" s="516"/>
       <c r="K14" s="118" t="s">
         <v>107</v>
       </c>
@@ -16606,8 +16586,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I15" s="510"/>
-      <c r="J15" s="508"/>
+      <c r="I15" s="518"/>
+      <c r="J15" s="516"/>
       <c r="K15" s="3" t="s">
         <v>108</v>
       </c>
@@ -16644,8 +16624,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I16" s="510"/>
-      <c r="J16" s="508"/>
+      <c r="I16" s="518"/>
+      <c r="J16" s="516"/>
       <c r="K16" s="5" t="s">
         <v>106</v>
       </c>
@@ -16683,8 +16663,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I17" s="510"/>
-      <c r="J17" s="508"/>
+      <c r="I17" s="518"/>
+      <c r="J17" s="516"/>
       <c r="K17" s="114" t="s">
         <v>107</v>
       </c>
@@ -16721,8 +16701,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I18" s="510"/>
-      <c r="J18" s="508"/>
+      <c r="I18" s="518"/>
+      <c r="J18" s="516"/>
       <c r="K18" s="5" t="s">
         <v>109</v>
       </c>
@@ -16756,8 +16736,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I19" s="510"/>
-      <c r="J19" s="508"/>
+      <c r="I19" s="518"/>
+      <c r="J19" s="516"/>
       <c r="K19" s="5" t="s">
         <v>106</v>
       </c>
@@ -16791,8 +16771,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I20" s="510"/>
-      <c r="J20" s="509"/>
+      <c r="I20" s="518"/>
+      <c r="J20" s="517"/>
       <c r="K20" s="114" t="s">
         <v>107</v>
       </c>
@@ -16852,10 +16832,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I22" s="506" t="s">
+      <c r="I22" s="514" t="s">
         <v>112</v>
       </c>
-      <c r="J22" s="507" t="s">
+      <c r="J22" s="515" t="s">
         <v>110</v>
       </c>
       <c r="K22" s="3" t="s">
@@ -16891,8 +16871,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I23" s="506"/>
-      <c r="J23" s="508"/>
+      <c r="I23" s="514"/>
+      <c r="J23" s="516"/>
       <c r="K23" s="5" t="s">
         <v>106</v>
       </c>
@@ -16926,8 +16906,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I24" s="506"/>
-      <c r="J24" s="508"/>
+      <c r="I24" s="514"/>
+      <c r="J24" s="516"/>
       <c r="K24" s="118" t="s">
         <v>107</v>
       </c>
@@ -16961,8 +16941,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I25" s="506"/>
-      <c r="J25" s="508"/>
+      <c r="I25" s="514"/>
+      <c r="J25" s="516"/>
       <c r="K25" s="3" t="s">
         <v>108</v>
       </c>
@@ -16996,8 +16976,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I26" s="506"/>
-      <c r="J26" s="508"/>
+      <c r="I26" s="514"/>
+      <c r="J26" s="516"/>
       <c r="K26" s="5" t="s">
         <v>106</v>
       </c>
@@ -17031,8 +17011,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I27" s="506"/>
-      <c r="J27" s="508"/>
+      <c r="I27" s="514"/>
+      <c r="J27" s="516"/>
       <c r="K27" s="114" t="s">
         <v>107</v>
       </c>
@@ -17066,8 +17046,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I28" s="506"/>
-      <c r="J28" s="508"/>
+      <c r="I28" s="514"/>
+      <c r="J28" s="516"/>
       <c r="K28" s="5" t="s">
         <v>109</v>
       </c>
@@ -17101,8 +17081,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I29" s="506"/>
-      <c r="J29" s="508"/>
+      <c r="I29" s="514"/>
+      <c r="J29" s="516"/>
       <c r="K29" s="5" t="s">
         <v>106</v>
       </c>
@@ -17136,8 +17116,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I30" s="506"/>
-      <c r="J30" s="509"/>
+      <c r="I30" s="514"/>
+      <c r="J30" s="517"/>
       <c r="K30" s="114" t="s">
         <v>107</v>
       </c>
@@ -17197,10 +17177,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I32" s="506" t="s">
+      <c r="I32" s="514" t="s">
         <v>113</v>
       </c>
-      <c r="J32" s="507" t="s">
+      <c r="J32" s="515" t="s">
         <v>110</v>
       </c>
       <c r="K32" s="3" t="s">
@@ -17236,8 +17216,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I33" s="506"/>
-      <c r="J33" s="508"/>
+      <c r="I33" s="514"/>
+      <c r="J33" s="516"/>
       <c r="K33" s="5" t="s">
         <v>106</v>
       </c>
@@ -17271,8 +17251,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I34" s="506"/>
-      <c r="J34" s="508"/>
+      <c r="I34" s="514"/>
+      <c r="J34" s="516"/>
       <c r="K34" s="118" t="s">
         <v>107</v>
       </c>
@@ -17306,8 +17286,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I35" s="506"/>
-      <c r="J35" s="508"/>
+      <c r="I35" s="514"/>
+      <c r="J35" s="516"/>
       <c r="K35" s="3" t="s">
         <v>108</v>
       </c>
@@ -17341,8 +17321,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I36" s="506"/>
-      <c r="J36" s="508"/>
+      <c r="I36" s="514"/>
+      <c r="J36" s="516"/>
       <c r="K36" s="5" t="s">
         <v>106</v>
       </c>
@@ -17376,8 +17356,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I37" s="506"/>
-      <c r="J37" s="508"/>
+      <c r="I37" s="514"/>
+      <c r="J37" s="516"/>
       <c r="K37" s="114" t="s">
         <v>107</v>
       </c>
@@ -17411,8 +17391,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I38" s="506"/>
-      <c r="J38" s="508"/>
+      <c r="I38" s="514"/>
+      <c r="J38" s="516"/>
       <c r="K38" s="5" t="s">
         <v>109</v>
       </c>
@@ -17446,8 +17426,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I39" s="506"/>
-      <c r="J39" s="508"/>
+      <c r="I39" s="514"/>
+      <c r="J39" s="516"/>
       <c r="K39" s="5" t="s">
         <v>106</v>
       </c>
@@ -17481,8 +17461,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I40" s="506"/>
-      <c r="J40" s="509"/>
+      <c r="I40" s="514"/>
+      <c r="J40" s="517"/>
       <c r="K40" s="114" t="s">
         <v>107</v>
       </c>
@@ -17542,10 +17522,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I42" s="506" t="s">
+      <c r="I42" s="514" t="s">
         <v>114</v>
       </c>
-      <c r="J42" s="507" t="s">
+      <c r="J42" s="515" t="s">
         <v>110</v>
       </c>
       <c r="K42" s="3" t="s">
@@ -17581,8 +17561,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I43" s="506"/>
-      <c r="J43" s="508"/>
+      <c r="I43" s="514"/>
+      <c r="J43" s="516"/>
       <c r="K43" s="5" t="s">
         <v>106</v>
       </c>
@@ -17616,8 +17596,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I44" s="506"/>
-      <c r="J44" s="508"/>
+      <c r="I44" s="514"/>
+      <c r="J44" s="516"/>
       <c r="K44" s="118" t="s">
         <v>107</v>
       </c>
@@ -17651,8 +17631,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I45" s="506"/>
-      <c r="J45" s="508"/>
+      <c r="I45" s="514"/>
+      <c r="J45" s="516"/>
       <c r="K45" s="3" t="s">
         <v>108</v>
       </c>
@@ -17686,8 +17666,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I46" s="506"/>
-      <c r="J46" s="508"/>
+      <c r="I46" s="514"/>
+      <c r="J46" s="516"/>
       <c r="K46" s="5" t="s">
         <v>106</v>
       </c>
@@ -17721,8 +17701,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I47" s="506"/>
-      <c r="J47" s="508"/>
+      <c r="I47" s="514"/>
+      <c r="J47" s="516"/>
       <c r="K47" s="114" t="s">
         <v>107</v>
       </c>
@@ -17756,8 +17736,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I48" s="506"/>
-      <c r="J48" s="508"/>
+      <c r="I48" s="514"/>
+      <c r="J48" s="516"/>
       <c r="K48" s="5" t="s">
         <v>109</v>
       </c>
@@ -17791,8 +17771,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I49" s="506"/>
-      <c r="J49" s="508"/>
+      <c r="I49" s="514"/>
+      <c r="J49" s="516"/>
       <c r="K49" s="5" t="s">
         <v>106</v>
       </c>
@@ -17826,8 +17806,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I50" s="506"/>
-      <c r="J50" s="509"/>
+      <c r="I50" s="514"/>
+      <c r="J50" s="517"/>
       <c r="K50" s="114" t="s">
         <v>107</v>
       </c>
@@ -17887,10 +17867,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I52" s="506" t="s">
+      <c r="I52" s="514" t="s">
         <v>222</v>
       </c>
-      <c r="J52" s="507" t="s">
+      <c r="J52" s="515" t="s">
         <v>110</v>
       </c>
       <c r="K52" s="3" t="s">
@@ -17926,8 +17906,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I53" s="506"/>
-      <c r="J53" s="508"/>
+      <c r="I53" s="514"/>
+      <c r="J53" s="516"/>
       <c r="K53" s="5" t="s">
         <v>106</v>
       </c>
@@ -17961,8 +17941,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I54" s="506"/>
-      <c r="J54" s="508"/>
+      <c r="I54" s="514"/>
+      <c r="J54" s="516"/>
       <c r="K54" s="118" t="s">
         <v>107</v>
       </c>
@@ -17996,8 +17976,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I55" s="506"/>
-      <c r="J55" s="508"/>
+      <c r="I55" s="514"/>
+      <c r="J55" s="516"/>
       <c r="K55" s="3" t="s">
         <v>108</v>
       </c>
@@ -18031,8 +18011,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I56" s="506"/>
-      <c r="J56" s="508"/>
+      <c r="I56" s="514"/>
+      <c r="J56" s="516"/>
       <c r="K56" s="5" t="s">
         <v>106</v>
       </c>
@@ -18066,8 +18046,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I57" s="506"/>
-      <c r="J57" s="508"/>
+      <c r="I57" s="514"/>
+      <c r="J57" s="516"/>
       <c r="K57" s="114" t="s">
         <v>107</v>
       </c>
@@ -18101,8 +18081,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I58" s="506"/>
-      <c r="J58" s="508"/>
+      <c r="I58" s="514"/>
+      <c r="J58" s="516"/>
       <c r="K58" s="5" t="s">
         <v>109</v>
       </c>
@@ -18136,8 +18116,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I59" s="506"/>
-      <c r="J59" s="508"/>
+      <c r="I59" s="514"/>
+      <c r="J59" s="516"/>
       <c r="K59" s="5" t="s">
         <v>106</v>
       </c>
@@ -18171,8 +18151,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I60" s="506"/>
-      <c r="J60" s="509"/>
+      <c r="I60" s="514"/>
+      <c r="J60" s="517"/>
       <c r="K60" s="114" t="s">
         <v>107</v>
       </c>
@@ -18409,10 +18389,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A2), MONTH(A2), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H2" s="510" t="s">
+      <c r="H2" s="518" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="511" t="s">
+      <c r="I2" s="519" t="s">
         <v>46</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -18444,8 +18424,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A3), MONTH(A3), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H3" s="510"/>
-      <c r="I3" s="512"/>
+      <c r="H3" s="518"/>
+      <c r="I3" s="520"/>
       <c r="J3" s="5" t="s">
         <v>106</v>
       </c>
@@ -18475,8 +18455,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A4), MONTH(A4), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H4" s="510"/>
-      <c r="I4" s="512"/>
+      <c r="H4" s="518"/>
+      <c r="I4" s="520"/>
       <c r="J4" s="114" t="s">
         <v>107</v>
       </c>
@@ -18506,8 +18486,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A5), MONTH(A5), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H5" s="510"/>
-      <c r="I5" s="512"/>
+      <c r="H5" s="518"/>
+      <c r="I5" s="520"/>
       <c r="J5" s="3" t="s">
         <v>108</v>
       </c>
@@ -18537,8 +18517,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A6), MONTH(A6), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H6" s="510"/>
-      <c r="I6" s="512"/>
+      <c r="H6" s="518"/>
+      <c r="I6" s="520"/>
       <c r="J6" s="5" t="s">
         <v>106</v>
       </c>
@@ -18568,8 +18548,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A7), MONTH(A7), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H7" s="510"/>
-      <c r="I7" s="512"/>
+      <c r="H7" s="518"/>
+      <c r="I7" s="520"/>
       <c r="J7" s="7" t="s">
         <v>107</v>
       </c>
@@ -18599,8 +18579,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A8), MONTH(A8), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H8" s="510"/>
-      <c r="I8" s="512"/>
+      <c r="H8" s="518"/>
+      <c r="I8" s="520"/>
       <c r="J8" s="3" t="s">
         <v>109</v>
       </c>
@@ -18630,8 +18610,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A9), MONTH(A9), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H9" s="510"/>
-      <c r="I9" s="512"/>
+      <c r="H9" s="518"/>
+      <c r="I9" s="520"/>
       <c r="J9" s="5" t="s">
         <v>106</v>
       </c>
@@ -18661,8 +18641,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A10), MONTH(A10), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H10" s="510"/>
-      <c r="I10" s="513"/>
+      <c r="H10" s="518"/>
+      <c r="I10" s="521"/>
       <c r="J10" s="114" t="s">
         <v>107</v>
       </c>
@@ -18692,7 +18672,7 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A11), MONTH(A11), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H11" s="510"/>
+      <c r="H11" s="518"/>
       <c r="Q11" t="s">
         <v>153</v>
       </c>
@@ -18718,8 +18698,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A12), MONTH(A12), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H12" s="510"/>
-      <c r="I12" s="507" t="s">
+      <c r="H12" s="518"/>
+      <c r="I12" s="515" t="s">
         <v>110</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -18757,8 +18737,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A13), MONTH(A13), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H13" s="510"/>
-      <c r="I13" s="508"/>
+      <c r="H13" s="518"/>
+      <c r="I13" s="516"/>
       <c r="J13" s="5" t="s">
         <v>106</v>
       </c>
@@ -18791,8 +18771,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A14), MONTH(A14), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H14" s="510"/>
-      <c r="I14" s="508"/>
+      <c r="H14" s="518"/>
+      <c r="I14" s="516"/>
       <c r="J14" s="118" t="s">
         <v>107</v>
       </c>
@@ -18822,8 +18802,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A15), MONTH(A15), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H15" s="510"/>
-      <c r="I15" s="508"/>
+      <c r="H15" s="518"/>
+      <c r="I15" s="516"/>
       <c r="J15" s="3" t="s">
         <v>108</v>
       </c>
@@ -18853,8 +18833,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A16), MONTH(A16), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H16" s="510"/>
-      <c r="I16" s="508"/>
+      <c r="H16" s="518"/>
+      <c r="I16" s="516"/>
       <c r="J16" s="5" t="s">
         <v>106</v>
       </c>
@@ -18884,8 +18864,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A17), MONTH(A17), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H17" s="510"/>
-      <c r="I17" s="508"/>
+      <c r="H17" s="518"/>
+      <c r="I17" s="516"/>
       <c r="J17" s="114" t="s">
         <v>107</v>
       </c>
@@ -18918,8 +18898,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A18), MONTH(A18), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H18" s="510"/>
-      <c r="I18" s="508"/>
+      <c r="H18" s="518"/>
+      <c r="I18" s="516"/>
       <c r="J18" s="5" t="s">
         <v>109</v>
       </c>
@@ -18949,8 +18929,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A19), MONTH(A19), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H19" s="510"/>
-      <c r="I19" s="508"/>
+      <c r="H19" s="518"/>
+      <c r="I19" s="516"/>
       <c r="J19" s="5" t="s">
         <v>106</v>
       </c>
@@ -18980,8 +18960,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A20), MONTH(A20), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H20" s="510"/>
-      <c r="I20" s="509"/>
+      <c r="H20" s="518"/>
+      <c r="I20" s="517"/>
       <c r="J20" s="114" t="s">
         <v>107</v>
       </c>
@@ -19033,10 +19013,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A22), MONTH(A22), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H22" s="506" t="s">
+      <c r="H22" s="514" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="507" t="s">
+      <c r="I22" s="515" t="s">
         <v>110</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -19068,8 +19048,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A23), MONTH(A23), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H23" s="506"/>
-      <c r="I23" s="508"/>
+      <c r="H23" s="514"/>
+      <c r="I23" s="516"/>
       <c r="J23" s="5" t="s">
         <v>106</v>
       </c>
@@ -19099,8 +19079,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A24), MONTH(A24), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H24" s="506"/>
-      <c r="I24" s="508"/>
+      <c r="H24" s="514"/>
+      <c r="I24" s="516"/>
       <c r="J24" s="118" t="s">
         <v>107</v>
       </c>
@@ -19130,8 +19110,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A25), MONTH(A25), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H25" s="506"/>
-      <c r="I25" s="508"/>
+      <c r="H25" s="514"/>
+      <c r="I25" s="516"/>
       <c r="J25" s="3" t="s">
         <v>108</v>
       </c>
@@ -19161,8 +19141,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A26), MONTH(A26), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H26" s="506"/>
-      <c r="I26" s="508"/>
+      <c r="H26" s="514"/>
+      <c r="I26" s="516"/>
       <c r="J26" s="5" t="s">
         <v>106</v>
       </c>
@@ -19192,8 +19172,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A27), MONTH(A27), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H27" s="506"/>
-      <c r="I27" s="508"/>
+      <c r="H27" s="514"/>
+      <c r="I27" s="516"/>
       <c r="J27" s="114" t="s">
         <v>107</v>
       </c>
@@ -19223,8 +19203,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A28), MONTH(A28), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H28" s="506"/>
-      <c r="I28" s="508"/>
+      <c r="H28" s="514"/>
+      <c r="I28" s="516"/>
       <c r="J28" s="5" t="s">
         <v>109</v>
       </c>
@@ -19254,8 +19234,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A29), MONTH(A29), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H29" s="506"/>
-      <c r="I29" s="508"/>
+      <c r="H29" s="514"/>
+      <c r="I29" s="516"/>
       <c r="J29" s="5" t="s">
         <v>106</v>
       </c>
@@ -19285,8 +19265,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A30), MONTH(A30), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H30" s="506"/>
-      <c r="I30" s="509"/>
+      <c r="H30" s="514"/>
+      <c r="I30" s="517"/>
       <c r="J30" s="114" t="s">
         <v>107</v>
       </c>
@@ -19338,10 +19318,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A32), MONTH(A32), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H32" s="506" t="s">
+      <c r="H32" s="514" t="s">
         <v>113</v>
       </c>
-      <c r="I32" s="507" t="s">
+      <c r="I32" s="515" t="s">
         <v>110</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -19373,8 +19353,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A33), MONTH(A33), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H33" s="506"/>
-      <c r="I33" s="508"/>
+      <c r="H33" s="514"/>
+      <c r="I33" s="516"/>
       <c r="J33" s="5" t="s">
         <v>106</v>
       </c>
@@ -19404,8 +19384,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A34), MONTH(A34), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H34" s="506"/>
-      <c r="I34" s="508"/>
+      <c r="H34" s="514"/>
+      <c r="I34" s="516"/>
       <c r="J34" s="118" t="s">
         <v>107</v>
       </c>
@@ -19435,8 +19415,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A35), MONTH(A35), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H35" s="506"/>
-      <c r="I35" s="508"/>
+      <c r="H35" s="514"/>
+      <c r="I35" s="516"/>
       <c r="J35" s="3" t="s">
         <v>108</v>
       </c>
@@ -19466,8 +19446,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A36), MONTH(A36), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H36" s="506"/>
-      <c r="I36" s="508"/>
+      <c r="H36" s="514"/>
+      <c r="I36" s="516"/>
       <c r="J36" s="5" t="s">
         <v>106</v>
       </c>
@@ -19497,8 +19477,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A37), MONTH(A37), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H37" s="506"/>
-      <c r="I37" s="508"/>
+      <c r="H37" s="514"/>
+      <c r="I37" s="516"/>
       <c r="J37" s="114" t="s">
         <v>107</v>
       </c>
@@ -19528,8 +19508,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A38), MONTH(A38), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H38" s="506"/>
-      <c r="I38" s="508"/>
+      <c r="H38" s="514"/>
+      <c r="I38" s="516"/>
       <c r="J38" s="5" t="s">
         <v>109</v>
       </c>
@@ -19559,8 +19539,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A39), MONTH(A39), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H39" s="506"/>
-      <c r="I39" s="508"/>
+      <c r="H39" s="514"/>
+      <c r="I39" s="516"/>
       <c r="J39" s="5" t="s">
         <v>106</v>
       </c>
@@ -19590,8 +19570,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A40), MONTH(A40), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H40" s="506"/>
-      <c r="I40" s="509"/>
+      <c r="H40" s="514"/>
+      <c r="I40" s="517"/>
       <c r="J40" s="114" t="s">
         <v>107</v>
       </c>
@@ -19643,10 +19623,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A42), MONTH(A42), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H42" s="506" t="s">
+      <c r="H42" s="514" t="s">
         <v>114</v>
       </c>
-      <c r="I42" s="507" t="s">
+      <c r="I42" s="515" t="s">
         <v>110</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -19678,8 +19658,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A43), MONTH(A43), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H43" s="506"/>
-      <c r="I43" s="508"/>
+      <c r="H43" s="514"/>
+      <c r="I43" s="516"/>
       <c r="J43" s="5" t="s">
         <v>106</v>
       </c>
@@ -19709,8 +19689,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A44), MONTH(A44), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H44" s="506"/>
-      <c r="I44" s="508"/>
+      <c r="H44" s="514"/>
+      <c r="I44" s="516"/>
       <c r="J44" s="118" t="s">
         <v>107</v>
       </c>
@@ -19740,8 +19720,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A45), MONTH(A45), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H45" s="506"/>
-      <c r="I45" s="508"/>
+      <c r="H45" s="514"/>
+      <c r="I45" s="516"/>
       <c r="J45" s="3" t="s">
         <v>108</v>
       </c>
@@ -19771,8 +19751,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A46), MONTH(A46), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H46" s="506"/>
-      <c r="I46" s="508"/>
+      <c r="H46" s="514"/>
+      <c r="I46" s="516"/>
       <c r="J46" s="5" t="s">
         <v>106</v>
       </c>
@@ -19802,8 +19782,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A47), MONTH(A47), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H47" s="506"/>
-      <c r="I47" s="508"/>
+      <c r="H47" s="514"/>
+      <c r="I47" s="516"/>
       <c r="J47" s="114" t="s">
         <v>107</v>
       </c>
@@ -19833,8 +19813,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A48), MONTH(A48), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H48" s="506"/>
-      <c r="I48" s="508"/>
+      <c r="H48" s="514"/>
+      <c r="I48" s="516"/>
       <c r="J48" s="5" t="s">
         <v>109</v>
       </c>
@@ -19864,8 +19844,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A49), MONTH(A49), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H49" s="506"/>
-      <c r="I49" s="508"/>
+      <c r="H49" s="514"/>
+      <c r="I49" s="516"/>
       <c r="J49" s="5" t="s">
         <v>106</v>
       </c>
@@ -19895,8 +19875,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A50), MONTH(A50), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H50" s="506"/>
-      <c r="I50" s="509"/>
+      <c r="H50" s="514"/>
+      <c r="I50" s="517"/>
       <c r="J50" s="114" t="s">
         <v>107</v>
       </c>
@@ -19948,10 +19928,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A52), MONTH(A52), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H52" s="506" t="s">
+      <c r="H52" s="514" t="s">
         <v>222</v>
       </c>
-      <c r="I52" s="507" t="s">
+      <c r="I52" s="515" t="s">
         <v>110</v>
       </c>
       <c r="J52" s="3" t="s">
@@ -19983,8 +19963,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A53), MONTH(A53), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H53" s="506"/>
-      <c r="I53" s="508"/>
+      <c r="H53" s="514"/>
+      <c r="I53" s="516"/>
       <c r="J53" s="5" t="s">
         <v>106</v>
       </c>
@@ -20014,8 +19994,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A54), MONTH(A54), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H54" s="506"/>
-      <c r="I54" s="508"/>
+      <c r="H54" s="514"/>
+      <c r="I54" s="516"/>
       <c r="J54" s="118" t="s">
         <v>107</v>
       </c>
@@ -20045,8 +20025,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A55), MONTH(A55), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H55" s="506"/>
-      <c r="I55" s="508"/>
+      <c r="H55" s="514"/>
+      <c r="I55" s="516"/>
       <c r="J55" s="3" t="s">
         <v>108</v>
       </c>
@@ -20076,8 +20056,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A56), MONTH(A56), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H56" s="506"/>
-      <c r="I56" s="508"/>
+      <c r="H56" s="514"/>
+      <c r="I56" s="516"/>
       <c r="J56" s="5" t="s">
         <v>106</v>
       </c>
@@ -20107,8 +20087,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A57), MONTH(A57), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H57" s="506"/>
-      <c r="I57" s="508"/>
+      <c r="H57" s="514"/>
+      <c r="I57" s="516"/>
       <c r="J57" s="114" t="s">
         <v>107</v>
       </c>
@@ -20138,8 +20118,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A58), MONTH(A58), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H58" s="506"/>
-      <c r="I58" s="508"/>
+      <c r="H58" s="514"/>
+      <c r="I58" s="516"/>
       <c r="J58" s="5" t="s">
         <v>109</v>
       </c>
@@ -20169,8 +20149,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A59), MONTH(A59), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H59" s="506"/>
-      <c r="I59" s="508"/>
+      <c r="H59" s="514"/>
+      <c r="I59" s="516"/>
       <c r="J59" s="5" t="s">
         <v>106</v>
       </c>
@@ -20200,8 +20180,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A60), MONTH(A60), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H60" s="506"/>
-      <c r="I60" s="509"/>
+      <c r="H60" s="514"/>
+      <c r="I60" s="517"/>
       <c r="J60" s="114" t="s">
         <v>107</v>
       </c>
@@ -24248,7 +24228,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="525">
+      <c r="A57" s="440">
         <v>2026</v>
       </c>
       <c r="B57" s="299">
@@ -24258,7 +24238,7 @@
         <v>357.33333333333331</v>
       </c>
       <c r="D57" s="300"/>
-      <c r="E57" s="525">
+      <c r="E57" s="440">
         <v>2026</v>
       </c>
       <c r="F57" s="302">
@@ -24267,25 +24247,25 @@
       <c r="G57" s="301">
         <v>375.5625</v>
       </c>
-      <c r="H57" s="525">
+      <c r="H57" s="440">
         <v>2026</v>
       </c>
       <c r="I57" s="302">
         <v>18.479166666666668</v>
       </c>
-      <c r="J57" s="526">
+      <c r="J57" s="441">
         <v>417.20833333333337</v>
       </c>
-      <c r="K57" s="525">
+      <c r="K57" s="440">
         <v>2026</v>
       </c>
       <c r="L57" s="302">
         <v>14.229166666666666</v>
       </c>
-      <c r="M57" s="526">
+      <c r="M57" s="441">
         <v>398.72916666666669</v>
       </c>
-      <c r="N57" s="525">
+      <c r="N57" s="440">
         <v>2026</v>
       </c>
       <c r="O57" s="302">
@@ -24294,13 +24274,13 @@
       <c r="P57" s="302">
         <v>405.1875</v>
       </c>
-      <c r="Q57" s="525">
+      <c r="Q57" s="440">
         <v>2026</v>
       </c>
       <c r="R57" s="302">
         <v>1.25</v>
       </c>
-      <c r="S57" s="527">
+      <c r="S57" s="442">
         <v>432.46492045454539</v>
       </c>
     </row>
@@ -26281,72 +26261,72 @@
   <sheetData>
     <row r="2" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="372"/>
-      <c r="B2" s="514">
+      <c r="B2" s="533">
         <v>45895</v>
       </c>
-      <c r="C2" s="514"/>
+      <c r="C2" s="533"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="F3" s="373"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="515" t="s">
+      <c r="B4" s="534" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="515"/>
+      <c r="C4" s="534"/>
       <c r="R4" s="364"/>
     </row>
     <row r="5" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="516" t="s">
+      <c r="B5" s="522" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="517"/>
+      <c r="C5" s="523"/>
       <c r="D5" s="374"/>
-      <c r="E5" s="516" t="s">
+      <c r="E5" s="522" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="518"/>
+      <c r="F5" s="524"/>
       <c r="G5" s="374"/>
-      <c r="H5" s="516" t="s">
+      <c r="H5" s="522" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="517"/>
-      <c r="K5" s="516" t="s">
+      <c r="I5" s="523"/>
+      <c r="K5" s="522" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="517"/>
-      <c r="N5" s="516" t="s">
+      <c r="L5" s="523"/>
+      <c r="N5" s="522" t="s">
         <v>174</v>
       </c>
-      <c r="O5" s="517"/>
-      <c r="Q5" s="516" t="s">
+      <c r="O5" s="523"/>
+      <c r="Q5" s="522" t="s">
         <v>175</v>
       </c>
-      <c r="R5" s="517"/>
-      <c r="T5" s="516" t="s">
+      <c r="R5" s="523"/>
+      <c r="T5" s="522" t="s">
         <v>176</v>
       </c>
-      <c r="U5" s="517"/>
-      <c r="W5" s="516" t="s">
+      <c r="U5" s="523"/>
+      <c r="W5" s="522" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="517"/>
-      <c r="Z5" s="516" t="s">
+      <c r="X5" s="523"/>
+      <c r="Z5" s="522" t="s">
         <v>178</v>
       </c>
-      <c r="AA5" s="517"/>
-      <c r="AC5" s="516" t="s">
+      <c r="AA5" s="523"/>
+      <c r="AC5" s="522" t="s">
         <v>179</v>
       </c>
-      <c r="AD5" s="517"/>
-      <c r="AF5" s="516" t="s">
+      <c r="AD5" s="523"/>
+      <c r="AF5" s="522" t="s">
         <v>239</v>
       </c>
-      <c r="AG5" s="517"/>
-      <c r="AI5" s="516" t="s">
+      <c r="AG5" s="523"/>
+      <c r="AI5" s="522" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="517"/>
+      <c r="AJ5" s="523"/>
     </row>
     <row r="6" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="375">
@@ -26526,10 +26506,10 @@
         <v>-6.67</v>
       </c>
       <c r="D8" s="374"/>
-      <c r="E8" s="516" t="s">
+      <c r="E8" s="522" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="518"/>
+      <c r="F8" s="524"/>
       <c r="G8" s="374"/>
       <c r="H8" s="378">
         <f t="shared" si="0"/>
@@ -27348,231 +27328,231 @@
       </c>
     </row>
     <row r="18" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="516" t="s">
+      <c r="B18" s="522" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="518"/>
+      <c r="C18" s="524"/>
       <c r="D18" s="374"/>
       <c r="E18" s="401"/>
       <c r="F18" s="401"/>
       <c r="G18" s="374"/>
-      <c r="H18" s="516" t="s">
+      <c r="H18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="518"/>
-      <c r="K18" s="516" t="s">
+      <c r="I18" s="524"/>
+      <c r="K18" s="522" t="s">
         <v>185</v>
       </c>
-      <c r="L18" s="518"/>
-      <c r="N18" s="516" t="s">
+      <c r="L18" s="524"/>
+      <c r="N18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="518"/>
-      <c r="Q18" s="516" t="s">
+      <c r="O18" s="524"/>
+      <c r="Q18" s="522" t="s">
         <v>185</v>
       </c>
-      <c r="R18" s="518"/>
-      <c r="T18" s="516" t="s">
+      <c r="R18" s="524"/>
+      <c r="T18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="U18" s="518"/>
-      <c r="W18" s="516" t="s">
+      <c r="U18" s="524"/>
+      <c r="W18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="X18" s="518"/>
-      <c r="Z18" s="516" t="s">
+      <c r="X18" s="524"/>
+      <c r="Z18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AA18" s="518"/>
-      <c r="AC18" s="516" t="s">
+      <c r="AA18" s="524"/>
+      <c r="AC18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AD18" s="518"/>
-      <c r="AF18" s="516" t="s">
+      <c r="AD18" s="524"/>
+      <c r="AF18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AG18" s="518"/>
-      <c r="AI18" s="516" t="s">
+      <c r="AG18" s="524"/>
+      <c r="AI18" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AJ18" s="518"/>
+      <c r="AJ18" s="524"/>
     </row>
     <row r="19" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="519">
+      <c r="B19" s="525">
         <v>336</v>
       </c>
-      <c r="C19" s="520"/>
+      <c r="C19" s="526"/>
       <c r="D19" s="374"/>
       <c r="E19" s="374"/>
       <c r="F19" s="401"/>
       <c r="G19" s="374"/>
-      <c r="H19" s="519"/>
-      <c r="I19" s="521"/>
-      <c r="K19" s="522">
+      <c r="H19" s="525"/>
+      <c r="I19" s="532"/>
+      <c r="K19" s="527">
         <v>941</v>
       </c>
-      <c r="L19" s="523"/>
+      <c r="L19" s="528"/>
       <c r="M19" s="374"/>
-      <c r="N19" s="522">
+      <c r="N19" s="527">
         <v>417</v>
       </c>
-      <c r="O19" s="523"/>
+      <c r="O19" s="528"/>
       <c r="P19" s="374"/>
-      <c r="Q19" s="522">
+      <c r="Q19" s="527">
         <v>1610</v>
       </c>
-      <c r="R19" s="523"/>
+      <c r="R19" s="528"/>
       <c r="S19" s="374"/>
-      <c r="T19" s="519">
+      <c r="T19" s="525">
         <v>480</v>
       </c>
-      <c r="U19" s="520"/>
+      <c r="U19" s="526"/>
       <c r="V19" s="374"/>
-      <c r="W19" s="519">
+      <c r="W19" s="525">
         <v>342</v>
       </c>
-      <c r="X19" s="520"/>
+      <c r="X19" s="526"/>
       <c r="Y19" s="374"/>
-      <c r="Z19" s="519">
+      <c r="Z19" s="525">
         <v>59</v>
       </c>
-      <c r="AA19" s="520"/>
+      <c r="AA19" s="526"/>
       <c r="AB19" s="374"/>
-      <c r="AC19" s="519">
+      <c r="AC19" s="525">
         <v>143</v>
       </c>
-      <c r="AD19" s="520"/>
+      <c r="AD19" s="526"/>
       <c r="AE19" s="374"/>
-      <c r="AF19" s="519">
+      <c r="AF19" s="525">
         <v>111</v>
       </c>
-      <c r="AG19" s="520"/>
-      <c r="AI19" s="519">
+      <c r="AG19" s="526"/>
+      <c r="AI19" s="525">
         <v>371</v>
       </c>
-      <c r="AJ19" s="520"/>
+      <c r="AJ19" s="526"/>
     </row>
     <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="516" t="s">
+      <c r="B20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="518"/>
+      <c r="C20" s="524"/>
       <c r="D20" s="374"/>
       <c r="E20" s="374"/>
       <c r="F20" s="401"/>
       <c r="G20" s="374"/>
-      <c r="H20" s="516" t="s">
+      <c r="H20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="518"/>
+      <c r="I20" s="524"/>
       <c r="J20" s="374"/>
-      <c r="K20" s="516" t="s">
+      <c r="K20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="L20" s="518"/>
+      <c r="L20" s="524"/>
       <c r="M20" s="374"/>
-      <c r="N20" s="516" t="s">
+      <c r="N20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="O20" s="518"/>
+      <c r="O20" s="524"/>
       <c r="P20" s="374"/>
-      <c r="Q20" s="516" t="s">
+      <c r="Q20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="R20" s="518"/>
+      <c r="R20" s="524"/>
       <c r="S20" s="374"/>
-      <c r="T20" s="516" t="s">
+      <c r="T20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="U20" s="518"/>
+      <c r="U20" s="524"/>
       <c r="V20" s="374"/>
-      <c r="W20" s="516" t="s">
+      <c r="W20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="X20" s="518"/>
+      <c r="X20" s="524"/>
       <c r="Y20" s="374"/>
-      <c r="Z20" s="516" t="s">
+      <c r="Z20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AA20" s="518"/>
+      <c r="AA20" s="524"/>
       <c r="AB20" s="374"/>
-      <c r="AC20" s="516" t="s">
+      <c r="AC20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AD20" s="518"/>
+      <c r="AD20" s="524"/>
       <c r="AE20" s="374"/>
-      <c r="AF20" s="516" t="s">
+      <c r="AF20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AG20" s="518"/>
-      <c r="AI20" s="516" t="s">
+      <c r="AG20" s="524"/>
+      <c r="AI20" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AJ20" s="518"/>
+      <c r="AJ20" s="524"/>
     </row>
     <row r="21" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="522">
+      <c r="B21" s="527">
         <f>B19-B70</f>
         <v>175</v>
       </c>
-      <c r="C21" s="523"/>
+      <c r="C21" s="528"/>
       <c r="D21" s="374"/>
       <c r="F21" s="401"/>
       <c r="G21" s="374"/>
-      <c r="H21" s="522"/>
-      <c r="I21" s="523"/>
+      <c r="H21" s="527"/>
+      <c r="I21" s="528"/>
       <c r="J21" s="374"/>
-      <c r="K21" s="522">
+      <c r="K21" s="527">
         <f>K19-E70</f>
         <v>833</v>
       </c>
-      <c r="L21" s="523"/>
+      <c r="L21" s="528"/>
       <c r="M21" s="374"/>
-      <c r="N21" s="522">
+      <c r="N21" s="527">
         <f>N19-H70</f>
         <v>327</v>
       </c>
-      <c r="O21" s="523"/>
+      <c r="O21" s="528"/>
       <c r="P21" s="374"/>
-      <c r="Q21" s="522">
+      <c r="Q21" s="527">
         <f>Q19-K70</f>
         <v>440</v>
       </c>
-      <c r="R21" s="520"/>
+      <c r="R21" s="526"/>
       <c r="S21" s="374"/>
-      <c r="T21" s="519">
+      <c r="T21" s="525">
         <f>T19-N70</f>
         <v>-20</v>
       </c>
-      <c r="U21" s="520"/>
+      <c r="U21" s="526"/>
       <c r="V21" s="374"/>
-      <c r="W21" s="519">
+      <c r="W21" s="525">
         <f>W19-Q70</f>
         <v>47</v>
       </c>
-      <c r="X21" s="520"/>
+      <c r="X21" s="526"/>
       <c r="Y21" s="374"/>
-      <c r="Z21" s="519">
+      <c r="Z21" s="525">
         <f>Z19-T70</f>
         <v>58</v>
       </c>
-      <c r="AA21" s="520"/>
+      <c r="AA21" s="526"/>
       <c r="AB21" s="374"/>
-      <c r="AC21" s="519">
+      <c r="AC21" s="525">
         <f>AC19-W70</f>
         <v>111</v>
       </c>
-      <c r="AD21" s="520"/>
-      <c r="AF21" s="519">
+      <c r="AD21" s="526"/>
+      <c r="AF21" s="525">
         <f>AF19-Z70</f>
         <v>6</v>
       </c>
-      <c r="AG21" s="520"/>
-      <c r="AI21" s="519">
+      <c r="AG21" s="526"/>
+      <c r="AI21" s="525">
         <f>AI19-AC70</f>
         <v>281</v>
       </c>
-      <c r="AJ21" s="520"/>
+      <c r="AJ21" s="526"/>
     </row>
     <row r="22" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AZ22" s="374"/>
@@ -27588,60 +27568,60 @@
       <c r="BJ22" s="374"/>
     </row>
     <row r="23" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="516" t="s">
+      <c r="B23" s="522" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="517"/>
+      <c r="C23" s="523"/>
       <c r="D23" s="374"/>
-      <c r="E23" s="516" t="s">
+      <c r="E23" s="522" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="518"/>
+      <c r="F23" s="524"/>
       <c r="G23" s="374"/>
-      <c r="H23" s="516" t="s">
+      <c r="H23" s="522" t="s">
         <v>189</v>
       </c>
-      <c r="I23" s="517"/>
+      <c r="I23" s="523"/>
       <c r="J23" s="374"/>
-      <c r="K23" s="516" t="s">
+      <c r="K23" s="522" t="s">
         <v>190</v>
       </c>
-      <c r="L23" s="517"/>
+      <c r="L23" s="523"/>
       <c r="M23" s="374"/>
-      <c r="N23" s="516" t="s">
+      <c r="N23" s="522" t="s">
         <v>191</v>
       </c>
-      <c r="O23" s="517"/>
+      <c r="O23" s="523"/>
       <c r="P23" s="374"/>
-      <c r="Q23" s="516" t="s">
+      <c r="Q23" s="522" t="s">
         <v>192</v>
       </c>
-      <c r="R23" s="517"/>
+      <c r="R23" s="523"/>
       <c r="S23" s="374"/>
-      <c r="T23" s="516" t="s">
+      <c r="T23" s="522" t="s">
         <v>193</v>
       </c>
-      <c r="U23" s="517"/>
+      <c r="U23" s="523"/>
       <c r="V23" s="374"/>
-      <c r="W23" s="516" t="s">
+      <c r="W23" s="522" t="s">
         <v>194</v>
       </c>
-      <c r="X23" s="517"/>
+      <c r="X23" s="523"/>
       <c r="Y23" s="374"/>
-      <c r="Z23" s="516" t="s">
+      <c r="Z23" s="522" t="s">
         <v>195</v>
       </c>
-      <c r="AA23" s="517"/>
+      <c r="AA23" s="523"/>
       <c r="AB23" s="374"/>
-      <c r="AC23" s="516" t="s">
+      <c r="AC23" s="522" t="s">
         <v>196</v>
       </c>
-      <c r="AD23" s="517"/>
+      <c r="AD23" s="523"/>
       <c r="AE23" s="374"/>
-      <c r="AF23" s="516" t="s">
+      <c r="AF23" s="522" t="s">
         <v>197</v>
       </c>
-      <c r="AG23" s="517"/>
+      <c r="AG23" s="523"/>
       <c r="AZ23" s="374"/>
       <c r="BA23" s="374"/>
       <c r="BB23" s="374"/>
@@ -28343,7 +28323,7 @@
         <f t="shared" si="24"/>
         <v>46078</v>
       </c>
-      <c r="I30" s="528">
+      <c r="I30" s="443">
         <v>-2.54</v>
       </c>
       <c r="J30" s="374"/>
@@ -28566,7 +28546,7 @@
         <f t="shared" si="24"/>
         <v>46137</v>
       </c>
-      <c r="I32" s="528">
+      <c r="I32" s="443">
         <v>-2.44</v>
       </c>
       <c r="J32" s="374"/>
@@ -28940,219 +28920,219 @@
       <c r="BJ35" s="374"/>
     </row>
     <row r="36" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="516" t="s">
+      <c r="B36" s="522" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="518"/>
+      <c r="C36" s="524"/>
       <c r="D36" s="374"/>
-      <c r="E36" s="516" t="s">
+      <c r="E36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="518"/>
+      <c r="F36" s="524"/>
       <c r="G36" s="374"/>
-      <c r="H36" s="516" t="s">
+      <c r="H36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="518"/>
+      <c r="I36" s="524"/>
       <c r="J36" s="374"/>
-      <c r="K36" s="516" t="s">
+      <c r="K36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="L36" s="518"/>
+      <c r="L36" s="524"/>
       <c r="M36" s="374"/>
-      <c r="N36" s="516" t="s">
+      <c r="N36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="O36" s="518"/>
+      <c r="O36" s="524"/>
       <c r="P36" s="374"/>
-      <c r="Q36" s="516" t="s">
+      <c r="Q36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="518"/>
+      <c r="R36" s="524"/>
       <c r="S36" s="374"/>
-      <c r="T36" s="516" t="s">
+      <c r="T36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="U36" s="518"/>
+      <c r="U36" s="524"/>
       <c r="V36" s="374"/>
-      <c r="W36" s="516" t="s">
+      <c r="W36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="X36" s="518"/>
+      <c r="X36" s="524"/>
       <c r="Y36" s="374"/>
-      <c r="Z36" s="516" t="s">
+      <c r="Z36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AA36" s="518"/>
+      <c r="AA36" s="524"/>
       <c r="AB36" s="374"/>
-      <c r="AC36" s="516" t="s">
+      <c r="AC36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AD36" s="518"/>
+      <c r="AD36" s="524"/>
       <c r="AE36" s="374"/>
-      <c r="AF36" s="516" t="s">
+      <c r="AF36" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AG36" s="518"/>
+      <c r="AG36" s="524"/>
     </row>
     <row r="37" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="522">
+      <c r="B37" s="527">
         <v>1150</v>
       </c>
-      <c r="C37" s="523"/>
+      <c r="C37" s="528"/>
       <c r="D37" s="374"/>
-      <c r="E37" s="522">
+      <c r="E37" s="527">
         <v>764</v>
       </c>
-      <c r="F37" s="523"/>
+      <c r="F37" s="528"/>
       <c r="G37" s="374"/>
-      <c r="H37" s="522">
+      <c r="H37" s="527">
         <v>115</v>
       </c>
-      <c r="I37" s="523"/>
+      <c r="I37" s="528"/>
       <c r="J37" s="374"/>
-      <c r="K37" s="519">
+      <c r="K37" s="525">
         <v>96</v>
       </c>
-      <c r="L37" s="520"/>
+      <c r="L37" s="526"/>
       <c r="M37" s="374"/>
-      <c r="N37" s="519"/>
-      <c r="O37" s="520"/>
+      <c r="N37" s="525"/>
+      <c r="O37" s="526"/>
       <c r="P37" s="374"/>
-      <c r="Q37" s="519">
+      <c r="Q37" s="525">
         <v>35</v>
       </c>
-      <c r="R37" s="520"/>
+      <c r="R37" s="526"/>
       <c r="S37" s="374"/>
-      <c r="T37" s="519">
+      <c r="T37" s="525">
         <v>0</v>
       </c>
-      <c r="U37" s="520"/>
+      <c r="U37" s="526"/>
       <c r="V37" s="374"/>
-      <c r="W37" s="519"/>
-      <c r="X37" s="520"/>
+      <c r="W37" s="525"/>
+      <c r="X37" s="526"/>
       <c r="Y37" s="374"/>
-      <c r="Z37" s="519">
+      <c r="Z37" s="525">
         <v>50</v>
       </c>
-      <c r="AA37" s="520"/>
+      <c r="AA37" s="526"/>
       <c r="AB37" s="374"/>
-      <c r="AC37" s="519"/>
-      <c r="AD37" s="520"/>
+      <c r="AC37" s="525"/>
+      <c r="AD37" s="526"/>
       <c r="AE37" s="374"/>
-      <c r="AF37" s="519"/>
-      <c r="AG37" s="520"/>
+      <c r="AF37" s="525"/>
+      <c r="AG37" s="526"/>
     </row>
     <row r="38" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="516" t="s">
+      <c r="B38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="518"/>
+      <c r="C38" s="524"/>
       <c r="D38" s="374"/>
-      <c r="E38" s="516" t="s">
+      <c r="E38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="518"/>
+      <c r="F38" s="524"/>
       <c r="G38" s="374"/>
-      <c r="H38" s="516" t="s">
+      <c r="H38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="518"/>
+      <c r="I38" s="524"/>
       <c r="J38" s="374"/>
-      <c r="K38" s="516" t="s">
+      <c r="K38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="L38" s="518"/>
+      <c r="L38" s="524"/>
       <c r="M38" s="374"/>
-      <c r="N38" s="516" t="s">
+      <c r="N38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="O38" s="518"/>
+      <c r="O38" s="524"/>
       <c r="P38" s="374"/>
-      <c r="Q38" s="516" t="s">
+      <c r="Q38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="R38" s="518"/>
+      <c r="R38" s="524"/>
       <c r="S38" s="374"/>
-      <c r="T38" s="516" t="s">
+      <c r="T38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="U38" s="518"/>
+      <c r="U38" s="524"/>
       <c r="V38" s="374"/>
-      <c r="W38" s="516" t="s">
+      <c r="W38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="X38" s="518"/>
+      <c r="X38" s="524"/>
       <c r="Y38" s="374"/>
-      <c r="Z38" s="516" t="s">
+      <c r="Z38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AA38" s="518"/>
+      <c r="AA38" s="524"/>
       <c r="AB38" s="374"/>
-      <c r="AC38" s="516" t="s">
+      <c r="AC38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AD38" s="518"/>
+      <c r="AD38" s="524"/>
       <c r="AE38" s="374"/>
-      <c r="AF38" s="516" t="s">
+      <c r="AF38" s="522" t="s">
         <v>186</v>
       </c>
-      <c r="AG38" s="518"/>
+      <c r="AG38" s="524"/>
     </row>
     <row r="39" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="522">
+      <c r="B39" s="527">
         <f>B37-B62</f>
         <v>436</v>
       </c>
-      <c r="C39" s="523"/>
+      <c r="C39" s="528"/>
       <c r="D39" s="374"/>
-      <c r="E39" s="522">
+      <c r="E39" s="527">
         <f>E37-E62</f>
         <v>379</v>
       </c>
-      <c r="F39" s="523"/>
+      <c r="F39" s="528"/>
       <c r="G39" s="374"/>
-      <c r="H39" s="522">
+      <c r="H39" s="527">
         <f>H37-H62</f>
         <v>115</v>
       </c>
-      <c r="I39" s="523"/>
+      <c r="I39" s="528"/>
       <c r="J39" s="374"/>
-      <c r="K39" s="519">
+      <c r="K39" s="525">
         <f>K37-K62</f>
         <v>57</v>
       </c>
-      <c r="L39" s="520"/>
+      <c r="L39" s="526"/>
       <c r="M39" s="374"/>
-      <c r="N39" s="519"/>
-      <c r="O39" s="520"/>
+      <c r="N39" s="525"/>
+      <c r="O39" s="526"/>
       <c r="P39" s="374"/>
-      <c r="Q39" s="519">
+      <c r="Q39" s="525">
         <f>Q37-Q62</f>
         <v>-167</v>
       </c>
-      <c r="R39" s="520"/>
+      <c r="R39" s="526"/>
       <c r="S39" s="374"/>
-      <c r="T39" s="519">
+      <c r="T39" s="525">
         <f>T37-T62</f>
         <v>-187</v>
       </c>
-      <c r="U39" s="520"/>
+      <c r="U39" s="526"/>
       <c r="V39" s="374"/>
-      <c r="W39" s="519"/>
-      <c r="X39" s="520"/>
+      <c r="W39" s="525"/>
+      <c r="X39" s="526"/>
       <c r="Y39" s="374"/>
-      <c r="Z39" s="519">
+      <c r="Z39" s="525">
         <f>Z37-Z62</f>
         <v>0</v>
       </c>
-      <c r="AA39" s="520"/>
+      <c r="AA39" s="526"/>
       <c r="AB39" s="374"/>
-      <c r="AC39" s="519"/>
-      <c r="AD39" s="520"/>
+      <c r="AC39" s="525"/>
+      <c r="AD39" s="526"/>
       <c r="AE39" s="374"/>
-      <c r="AF39" s="519"/>
-      <c r="AG39" s="520"/>
+      <c r="AF39" s="525"/>
+      <c r="AG39" s="526"/>
     </row>
     <row r="40" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B40" s="411"/>
@@ -29189,10 +29169,10 @@
       <c r="AG40" s="374"/>
     </row>
     <row r="41" spans="2:62" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="524" t="s">
+      <c r="B41" s="531" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="524"/>
+      <c r="C41" s="531"/>
       <c r="D41" s="374"/>
       <c r="E41" s="374"/>
       <c r="F41" s="374"/>
@@ -29224,59 +29204,59 @@
       <c r="AG41" s="374"/>
     </row>
     <row r="42" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="516" t="s">
+      <c r="B42" s="522" t="s">
         <v>170</v>
       </c>
-      <c r="C42" s="517"/>
+      <c r="C42" s="523"/>
       <c r="D42" s="374"/>
-      <c r="E42" s="516" t="s">
+      <c r="E42" s="522" t="s">
         <v>173</v>
       </c>
-      <c r="F42" s="517"/>
+      <c r="F42" s="523"/>
       <c r="G42" s="374"/>
-      <c r="H42" s="516" t="s">
+      <c r="H42" s="522" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="517"/>
+      <c r="I42" s="523"/>
       <c r="J42" s="374"/>
-      <c r="K42" s="516" t="s">
+      <c r="K42" s="522" t="s">
         <v>175</v>
       </c>
-      <c r="L42" s="517"/>
+      <c r="L42" s="523"/>
       <c r="M42" s="374"/>
-      <c r="N42" s="516" t="s">
+      <c r="N42" s="522" t="s">
         <v>176</v>
       </c>
-      <c r="O42" s="517"/>
+      <c r="O42" s="523"/>
       <c r="P42" s="374"/>
-      <c r="Q42" s="516" t="s">
+      <c r="Q42" s="522" t="s">
         <v>177</v>
       </c>
-      <c r="R42" s="517"/>
-      <c r="T42" s="516" t="s">
+      <c r="R42" s="523"/>
+      <c r="T42" s="522" t="s">
         <v>178</v>
       </c>
-      <c r="U42" s="517"/>
+      <c r="U42" s="523"/>
       <c r="V42" s="374"/>
-      <c r="W42" s="516" t="s">
+      <c r="W42" s="522" t="s">
         <v>179</v>
       </c>
-      <c r="X42" s="517"/>
+      <c r="X42" s="523"/>
       <c r="Y42" s="374"/>
       <c r="Z42" s="529" t="s">
         <v>239</v>
       </c>
       <c r="AA42" s="530"/>
       <c r="AB42" s="374"/>
-      <c r="AC42" s="516" t="s">
+      <c r="AC42" s="522" t="s">
         <v>180</v>
       </c>
-      <c r="AD42" s="517"/>
+      <c r="AD42" s="523"/>
       <c r="AE42" s="374"/>
-      <c r="AF42" s="516" t="s">
+      <c r="AF42" s="522" t="s">
         <v>197</v>
       </c>
-      <c r="AG42" s="517"/>
+      <c r="AG42" s="523"/>
     </row>
     <row r="43" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="378">
@@ -29286,7 +29266,7 @@
       <c r="C43" s="376">
         <v>-6.51</v>
       </c>
-      <c r="D43" s="531"/>
+      <c r="D43" s="444"/>
       <c r="E43" s="378">
         <f>B6</f>
         <v>45893</v>
@@ -29294,7 +29274,7 @@
       <c r="F43" s="376">
         <v>4.1900000000000004</v>
       </c>
-      <c r="G43" s="531"/>
+      <c r="G43" s="444"/>
       <c r="H43" s="413" t="str">
         <f>E24</f>
         <v>Aug/Sep</v>
@@ -29302,7 +29282,7 @@
       <c r="I43" s="376">
         <v>1.75</v>
       </c>
-      <c r="J43" s="531"/>
+      <c r="J43" s="444"/>
       <c r="K43" s="378">
         <f>B6</f>
         <v>45893</v>
@@ -29310,7 +29290,7 @@
       <c r="L43" s="376">
         <v>8.75</v>
       </c>
-      <c r="M43" s="531"/>
+      <c r="M43" s="444"/>
       <c r="N43" s="413" t="str">
         <f>E24</f>
         <v>Aug/Sep</v>
@@ -29318,7 +29298,7 @@
       <c r="O43" s="376">
         <v>0.5</v>
       </c>
-      <c r="P43" s="531"/>
+      <c r="P43" s="444"/>
       <c r="Q43" s="413" t="str">
         <f>E24</f>
         <v>Aug/Sep</v>
@@ -29334,7 +29314,7 @@
       <c r="U43" s="376">
         <v>28.91</v>
       </c>
-      <c r="V43" s="531"/>
+      <c r="V43" s="444"/>
       <c r="W43" s="378">
         <f>B6</f>
         <v>45893</v>
@@ -29342,7 +29322,7 @@
       <c r="X43" s="376">
         <v>5.75</v>
       </c>
-      <c r="Y43" s="531"/>
+      <c r="Y43" s="444"/>
       <c r="Z43" s="378">
         <f>B24</f>
         <v>45893</v>
@@ -29350,7 +29330,7 @@
       <c r="AA43" s="376">
         <v>-5.61</v>
       </c>
-      <c r="AB43" s="531"/>
+      <c r="AB43" s="444"/>
       <c r="AC43" s="379" t="str">
         <f>E24</f>
         <v>Aug/Sep</v>
@@ -29358,7 +29338,7 @@
       <c r="AD43" s="376">
         <v>3</v>
       </c>
-      <c r="AE43" s="531"/>
+      <c r="AE43" s="444"/>
       <c r="AF43" s="378">
         <f>B24</f>
         <v>45893</v>
@@ -29376,7 +29356,7 @@
       <c r="C44" s="382">
         <v>-6.55</v>
       </c>
-      <c r="D44" s="531"/>
+      <c r="D44" s="444"/>
       <c r="E44" s="388">
         <f>B7</f>
         <v>45924</v>
@@ -29384,15 +29364,15 @@
       <c r="F44" s="382">
         <v>4.3499999999999996</v>
       </c>
-      <c r="G44" s="531"/>
-      <c r="H44" s="532" t="str">
+      <c r="G44" s="444"/>
+      <c r="H44" s="445" t="str">
         <f>E25</f>
         <v>Sep/Oct</v>
       </c>
       <c r="I44" s="382">
         <v>4.75</v>
       </c>
-      <c r="J44" s="531"/>
+      <c r="J44" s="444"/>
       <c r="K44" s="388">
         <f>B7</f>
         <v>45924</v>
@@ -29400,16 +29380,16 @@
       <c r="L44" s="382">
         <v>9.1</v>
       </c>
-      <c r="M44" s="531"/>
-      <c r="N44" s="532" t="str">
+      <c r="M44" s="444"/>
+      <c r="N44" s="445" t="str">
         <f>E25</f>
         <v>Sep/Oct</v>
       </c>
       <c r="O44" s="382">
         <v>1.5</v>
       </c>
-      <c r="P44" s="531"/>
-      <c r="Q44" s="532" t="str">
+      <c r="P44" s="444"/>
+      <c r="Q44" s="445" t="str">
         <f>E25</f>
         <v>Sep/Oct</v>
       </c>
@@ -29424,7 +29404,7 @@
       <c r="U44" s="382">
         <v>30.16</v>
       </c>
-      <c r="V44" s="531"/>
+      <c r="V44" s="444"/>
       <c r="W44" s="388">
         <f>B7</f>
         <v>45924</v>
@@ -29432,7 +29412,7 @@
       <c r="X44" s="382">
         <v>10.5</v>
       </c>
-      <c r="Y44" s="531"/>
+      <c r="Y44" s="444"/>
       <c r="Z44" s="388">
         <f t="shared" ref="Z44:Z45" si="29">B25</f>
         <v>45924</v>
@@ -29440,7 +29420,7 @@
       <c r="AA44" s="382">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="AB44" s="531"/>
+      <c r="AB44" s="444"/>
       <c r="AC44" s="393" t="str">
         <f t="shared" ref="AC44:AC48" si="30">E25</f>
         <v>Sep/Oct</v>
@@ -29448,7 +29428,7 @@
       <c r="AD44" s="382">
         <v>4</v>
       </c>
-      <c r="AE44" s="531"/>
+      <c r="AE44" s="444"/>
       <c r="AF44" s="388">
         <f t="shared" ref="AF44:AF49" si="31">B25</f>
         <v>45924</v>
@@ -29465,7 +29445,7 @@
       <c r="C45" s="376">
         <v>-6.74</v>
       </c>
-      <c r="D45" s="531"/>
+      <c r="D45" s="444"/>
       <c r="E45" s="378">
         <f>B8</f>
         <v>45954</v>
@@ -29473,7 +29453,7 @@
       <c r="F45" s="376">
         <v>4.05</v>
       </c>
-      <c r="G45" s="531"/>
+      <c r="G45" s="444"/>
       <c r="H45" s="413" t="str">
         <f>E26</f>
         <v>Oct/Nov</v>
@@ -29481,7 +29461,7 @@
       <c r="I45" s="376">
         <v>3.75</v>
       </c>
-      <c r="J45" s="531"/>
+      <c r="J45" s="444"/>
       <c r="K45" s="378">
         <f>B8</f>
         <v>45954</v>
@@ -29489,7 +29469,7 @@
       <c r="L45" s="376">
         <v>9.31</v>
       </c>
-      <c r="M45" s="531"/>
+      <c r="M45" s="444"/>
       <c r="N45" s="413" t="str">
         <f>E26</f>
         <v>Oct/Nov</v>
@@ -29497,7 +29477,7 @@
       <c r="O45" s="376">
         <v>2.75</v>
       </c>
-      <c r="P45" s="531"/>
+      <c r="P45" s="444"/>
       <c r="Q45" s="413" t="str">
         <f>E26</f>
         <v>Oct/Nov</v>
@@ -29513,7 +29493,7 @@
       <c r="U45" s="376">
         <v>33.409999999999997</v>
       </c>
-      <c r="V45" s="531"/>
+      <c r="V45" s="444"/>
       <c r="W45" s="378">
         <f>B8</f>
         <v>45954</v>
@@ -29521,7 +29501,7 @@
       <c r="X45" s="376">
         <v>13.75</v>
       </c>
-      <c r="Y45" s="531"/>
+      <c r="Y45" s="444"/>
       <c r="Z45" s="378">
         <f t="shared" si="29"/>
         <v>45954</v>
@@ -29529,7 +29509,7 @@
       <c r="AA45" s="376">
         <v>-4.57</v>
       </c>
-      <c r="AB45" s="531"/>
+      <c r="AB45" s="444"/>
       <c r="AC45" s="379" t="str">
         <f t="shared" si="30"/>
         <v>Oct/Nov</v>
@@ -29537,7 +29517,7 @@
       <c r="AD45" s="376">
         <v>4.5</v>
       </c>
-      <c r="AE45" s="531"/>
+      <c r="AE45" s="444"/>
       <c r="AF45" s="378">
         <f t="shared" si="31"/>
         <v>45954</v>
@@ -29555,7 +29535,7 @@
       <c r="C46" s="382">
         <v>-7.15</v>
       </c>
-      <c r="D46" s="531"/>
+      <c r="D46" s="444"/>
       <c r="E46" s="393" t="str">
         <f>B15</f>
         <v>Q4-25</v>
@@ -29563,7 +29543,7 @@
       <c r="F46" s="382">
         <v>3.76</v>
       </c>
-      <c r="G46" s="531"/>
+      <c r="G46" s="444"/>
       <c r="H46" s="393" t="str">
         <f>E33</f>
         <v>Q4/Q126</v>
@@ -29571,7 +29551,7 @@
       <c r="I46" s="382">
         <v>6.83</v>
       </c>
-      <c r="J46" s="531"/>
+      <c r="J46" s="444"/>
       <c r="K46" s="393" t="str">
         <f>B15</f>
         <v>Q4-25</v>
@@ -29579,7 +29559,7 @@
       <c r="L46" s="382">
         <v>9.1300000000000008</v>
       </c>
-      <c r="M46" s="531"/>
+      <c r="M46" s="444"/>
       <c r="N46" s="393" t="str">
         <f t="shared" ref="N46:N48" si="32">E33</f>
         <v>Q4/Q126</v>
@@ -29587,7 +29567,7 @@
       <c r="O46" s="382">
         <v>6.83</v>
       </c>
-      <c r="P46" s="531"/>
+      <c r="P46" s="444"/>
       <c r="Q46" s="393" t="str">
         <f t="shared" ref="Q46:Q48" si="33">E33</f>
         <v>Q4/Q126</v>
@@ -29603,7 +29583,7 @@
       <c r="U46" s="382">
         <v>34.159999999999997</v>
       </c>
-      <c r="V46" s="531"/>
+      <c r="V46" s="444"/>
       <c r="W46" s="394" t="str">
         <f>B15</f>
         <v>Q4-25</v>
@@ -29611,7 +29591,7 @@
       <c r="X46" s="382">
         <v>14.67</v>
       </c>
-      <c r="Y46" s="531"/>
+      <c r="Y46" s="444"/>
       <c r="Z46" s="388" t="str">
         <f>B33</f>
         <v>Q4-25</v>
@@ -29619,7 +29599,7 @@
       <c r="AA46" s="382">
         <v>-4.74</v>
       </c>
-      <c r="AB46" s="531"/>
+      <c r="AB46" s="444"/>
       <c r="AC46" s="393" t="str">
         <f t="shared" si="30"/>
         <v>Nov/Dec</v>
@@ -29627,7 +29607,7 @@
       <c r="AD46" s="382">
         <v>3.5</v>
       </c>
-      <c r="AE46" s="531"/>
+      <c r="AE46" s="444"/>
       <c r="AF46" s="388">
         <f t="shared" si="31"/>
         <v>45985</v>
@@ -29642,10 +29622,10 @@
         <f>B16</f>
         <v>Q1-26</v>
       </c>
-      <c r="C47" s="528">
+      <c r="C47" s="443">
         <v>-7.85</v>
       </c>
-      <c r="D47" s="531"/>
+      <c r="D47" s="444"/>
       <c r="E47" s="380" t="str">
         <f>B16</f>
         <v>Q1-26</v>
@@ -29653,7 +29633,7 @@
       <c r="F47" s="376">
         <v>3</v>
       </c>
-      <c r="G47" s="531"/>
+      <c r="G47" s="444"/>
       <c r="H47" s="379" t="str">
         <f>E34</f>
         <v>Q1/Q2</v>
@@ -29661,7 +29641,7 @@
       <c r="I47" s="376">
         <v>4.33</v>
       </c>
-      <c r="J47" s="531"/>
+      <c r="J47" s="444"/>
       <c r="K47" s="380" t="str">
         <f>B16</f>
         <v>Q1-26</v>
@@ -29669,60 +29649,60 @@
       <c r="L47" s="376">
         <v>8.3699999999999992</v>
       </c>
-      <c r="M47" s="531"/>
+      <c r="M47" s="444"/>
       <c r="N47" s="379" t="str">
         <f t="shared" si="32"/>
         <v>Q1/Q2</v>
       </c>
-      <c r="O47" s="528">
+      <c r="O47" s="443">
         <v>5.5</v>
       </c>
-      <c r="P47" s="531"/>
+      <c r="P47" s="444"/>
       <c r="Q47" s="400" t="str">
         <f t="shared" si="33"/>
         <v>Q1/Q2</v>
       </c>
-      <c r="R47" s="528">
+      <c r="R47" s="443">
         <v>2.92</v>
       </c>
       <c r="S47" s="155"/>
-      <c r="T47" s="533" t="str">
+      <c r="T47" s="446" t="str">
         <f>B16</f>
         <v>Q1-26</v>
       </c>
-      <c r="U47" s="528">
+      <c r="U47" s="443">
         <v>34.159999999999997</v>
       </c>
-      <c r="V47" s="531"/>
-      <c r="W47" s="533" t="str">
+      <c r="V47" s="444"/>
+      <c r="W47" s="446" t="str">
         <f>B16</f>
         <v>Q1-26</v>
       </c>
-      <c r="X47" s="528">
+      <c r="X47" s="443">
         <v>15.33</v>
       </c>
-      <c r="Y47" s="531"/>
+      <c r="Y47" s="444"/>
       <c r="Z47" s="407" t="str">
         <f>B34</f>
         <v>Q1-26</v>
       </c>
-      <c r="AA47" s="528">
+      <c r="AA47" s="443">
         <v>-5.34</v>
       </c>
-      <c r="AB47" s="531"/>
+      <c r="AB47" s="444"/>
       <c r="AC47" s="379" t="str">
         <f t="shared" si="30"/>
         <v>Dec/Jan</v>
       </c>
-      <c r="AD47" s="528">
+      <c r="AD47" s="443">
         <v>1.75</v>
       </c>
-      <c r="AE47" s="531"/>
+      <c r="AE47" s="444"/>
       <c r="AF47" s="378">
         <f t="shared" si="31"/>
         <v>46015</v>
       </c>
-      <c r="AG47" s="528">
+      <c r="AG47" s="443">
         <f>AG46-AD46</f>
         <v>371.25</v>
       </c>
@@ -29735,7 +29715,7 @@
       <c r="C48" s="382">
         <v>-7.8</v>
       </c>
-      <c r="D48" s="531"/>
+      <c r="D48" s="444"/>
       <c r="E48" s="393" t="str">
         <f>B17</f>
         <v>Q2-26</v>
@@ -29743,7 +29723,7 @@
       <c r="F48" s="382">
         <v>2.46</v>
       </c>
-      <c r="G48" s="531"/>
+      <c r="G48" s="444"/>
       <c r="H48" s="393" t="str">
         <f>E35</f>
         <v>Q2/Q3</v>
@@ -29751,7 +29731,7 @@
       <c r="I48" s="382">
         <v>4.42</v>
       </c>
-      <c r="J48" s="531"/>
+      <c r="J48" s="444"/>
       <c r="K48" s="393" t="str">
         <f>B17</f>
         <v>Q2-26</v>
@@ -29759,7 +29739,7 @@
       <c r="L48" s="382">
         <v>7.65</v>
       </c>
-      <c r="M48" s="531"/>
+      <c r="M48" s="444"/>
       <c r="N48" s="393" t="str">
         <f t="shared" si="32"/>
         <v>Q2/Q3</v>
@@ -29767,7 +29747,7 @@
       <c r="O48" s="382">
         <v>5.5</v>
       </c>
-      <c r="P48" s="531"/>
+      <c r="P48" s="444"/>
       <c r="Q48" s="393" t="str">
         <f t="shared" si="33"/>
         <v>Q2/Q3</v>
@@ -29783,7 +29763,7 @@
       <c r="U48" s="382">
         <v>32.99</v>
       </c>
-      <c r="V48" s="531"/>
+      <c r="V48" s="444"/>
       <c r="W48" s="394" t="str">
         <f>B17</f>
         <v>Q2-26</v>
@@ -29791,7 +29771,7 @@
       <c r="X48" s="382">
         <v>13</v>
       </c>
-      <c r="Y48" s="531"/>
+      <c r="Y48" s="444"/>
       <c r="Z48" s="388" t="str">
         <f>K35</f>
         <v>Q2-26</v>
@@ -29799,7 +29779,7 @@
       <c r="AA48" s="382">
         <v>-5.65</v>
       </c>
-      <c r="AB48" s="531"/>
+      <c r="AB48" s="444"/>
       <c r="AC48" s="393" t="str">
         <f t="shared" si="30"/>
         <v>Jan/Feb</v>
@@ -29807,7 +29787,7 @@
       <c r="AD48" s="382">
         <v>1.25</v>
       </c>
-      <c r="AE48" s="531"/>
+      <c r="AE48" s="444"/>
       <c r="AF48" s="388">
         <f t="shared" si="31"/>
         <v>46047</v>
@@ -29818,59 +29798,59 @@
       </c>
     </row>
     <row r="49" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="516" t="s">
+      <c r="B49" s="522" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="518"/>
-      <c r="D49" s="531"/>
-      <c r="E49" s="516" t="s">
+      <c r="C49" s="524"/>
+      <c r="D49" s="444"/>
+      <c r="E49" s="522" t="s">
         <v>185</v>
       </c>
-      <c r="F49" s="518"/>
+      <c r="F49" s="524"/>
       <c r="G49" s="374"/>
-      <c r="H49" s="516" t="s">
+      <c r="H49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="I49" s="518"/>
+      <c r="I49" s="524"/>
       <c r="J49" s="374"/>
-      <c r="K49" s="516" t="s">
+      <c r="K49" s="522" t="s">
         <v>185</v>
       </c>
-      <c r="L49" s="518"/>
-      <c r="M49" s="531"/>
-      <c r="N49" s="516" t="s">
+      <c r="L49" s="524"/>
+      <c r="M49" s="444"/>
+      <c r="N49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="O49" s="518"/>
-      <c r="P49" s="531"/>
-      <c r="Q49" s="516" t="s">
+      <c r="O49" s="524"/>
+      <c r="P49" s="444"/>
+      <c r="Q49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="R49" s="518"/>
+      <c r="R49" s="524"/>
       <c r="S49" s="155"/>
-      <c r="T49" s="516" t="s">
+      <c r="T49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="U49" s="518"/>
-      <c r="V49" s="531"/>
-      <c r="W49" s="516" t="s">
+      <c r="U49" s="524"/>
+      <c r="V49" s="444"/>
+      <c r="W49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="X49" s="518"/>
-      <c r="Y49" s="531"/>
-      <c r="Z49" s="516" t="s">
+      <c r="X49" s="524"/>
+      <c r="Y49" s="444"/>
+      <c r="Z49" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AA49" s="518"/>
-      <c r="AB49" s="531"/>
-      <c r="AC49" s="533" t="str">
+      <c r="AA49" s="524"/>
+      <c r="AB49" s="444"/>
+      <c r="AC49" s="446" t="str">
         <f>E33</f>
         <v>Q4/Q126</v>
       </c>
       <c r="AD49" s="376">
         <v>6.5</v>
       </c>
-      <c r="AE49" s="531"/>
+      <c r="AE49" s="444"/>
       <c r="AF49" s="378">
         <f t="shared" si="31"/>
         <v>46078</v>
@@ -29881,34 +29861,34 @@
       </c>
     </row>
     <row r="50" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="519"/>
-      <c r="C50" s="520"/>
+      <c r="B50" s="525"/>
+      <c r="C50" s="526"/>
       <c r="D50" s="364"/>
-      <c r="E50" s="519"/>
-      <c r="F50" s="520"/>
+      <c r="E50" s="525"/>
+      <c r="F50" s="526"/>
       <c r="G50" s="374"/>
-      <c r="H50" s="522"/>
-      <c r="I50" s="523"/>
+      <c r="H50" s="527"/>
+      <c r="I50" s="528"/>
       <c r="J50" s="374"/>
-      <c r="K50" s="519"/>
-      <c r="L50" s="520"/>
+      <c r="K50" s="525"/>
+      <c r="L50" s="526"/>
       <c r="M50" s="374"/>
-      <c r="N50" s="519"/>
-      <c r="O50" s="520"/>
+      <c r="N50" s="525"/>
+      <c r="O50" s="526"/>
       <c r="P50" s="374"/>
-      <c r="Q50" s="519"/>
-      <c r="R50" s="520"/>
+      <c r="Q50" s="525"/>
+      <c r="R50" s="526"/>
       <c r="S50" s="374"/>
-      <c r="T50" s="519"/>
-      <c r="U50" s="520"/>
+      <c r="T50" s="525"/>
+      <c r="U50" s="526"/>
       <c r="V50" s="374"/>
-      <c r="W50" s="519"/>
-      <c r="X50" s="520"/>
+      <c r="W50" s="525"/>
+      <c r="X50" s="526"/>
       <c r="Y50" s="374"/>
-      <c r="Z50" s="519"/>
-      <c r="AA50" s="520"/>
+      <c r="Z50" s="525"/>
+      <c r="AA50" s="526"/>
       <c r="AB50" s="374"/>
-      <c r="AC50" s="533" t="str">
+      <c r="AC50" s="446" t="str">
         <f t="shared" ref="AC50:AC51" si="34">E34</f>
         <v>Q1/Q2</v>
       </c>
@@ -29952,7 +29932,7 @@
       <c r="Z51" s="412"/>
       <c r="AA51" s="412"/>
       <c r="AB51" s="412"/>
-      <c r="AC51" s="533" t="str">
+      <c r="AC51" s="446" t="str">
         <f t="shared" si="34"/>
         <v>Q2/Q3</v>
       </c>
@@ -29960,8 +29940,8 @@
         <v>4.42</v>
       </c>
       <c r="AE51" s="412"/>
-      <c r="AF51" s="533"/>
-      <c r="AG51" s="528"/>
+      <c r="AF51" s="446"/>
+      <c r="AG51" s="443"/>
     </row>
     <row r="52" spans="2:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B52" s="412"/>
@@ -29991,15 +29971,15 @@
       <c r="Z52" s="412"/>
       <c r="AA52" s="412"/>
       <c r="AB52" s="412"/>
-      <c r="AC52" s="516" t="s">
+      <c r="AC52" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AD52" s="518"/>
+      <c r="AD52" s="524"/>
       <c r="AE52" s="412"/>
-      <c r="AF52" s="516" t="s">
+      <c r="AF52" s="522" t="s">
         <v>184</v>
       </c>
-      <c r="AG52" s="518"/>
+      <c r="AG52" s="524"/>
     </row>
     <row r="53" spans="2:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="412"/>
@@ -30028,8 +30008,8 @@
       <c r="Z53" s="412"/>
       <c r="AA53" s="412"/>
       <c r="AB53" s="374"/>
-      <c r="AC53" s="519"/>
-      <c r="AD53" s="520"/>
+      <c r="AC53" s="525"/>
+      <c r="AD53" s="526"/>
       <c r="AE53" s="374"/>
       <c r="AF53" s="438"/>
       <c r="AG53" s="439"/>
@@ -30103,7 +30083,7 @@
       <c r="AB56" s="412"/>
       <c r="AC56" s="412"/>
       <c r="AD56" s="374"/>
-      <c r="AI56" s="534"/>
+      <c r="AI56" s="447"/>
     </row>
     <row r="57" spans="2:35" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="415"/>
@@ -30134,157 +30114,157 @@
       </c>
     </row>
     <row r="60" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="516" t="s">
+      <c r="B60" s="522" t="s">
         <v>209</v>
       </c>
-      <c r="C60" s="517"/>
+      <c r="C60" s="523"/>
       <c r="D60" s="374"/>
-      <c r="E60" s="516" t="s">
+      <c r="E60" s="522" t="s">
         <v>210</v>
       </c>
-      <c r="F60" s="518"/>
+      <c r="F60" s="524"/>
       <c r="G60" s="374"/>
-      <c r="H60" s="516" t="s">
+      <c r="H60" s="522" t="s">
         <v>211</v>
       </c>
-      <c r="I60" s="517"/>
+      <c r="I60" s="523"/>
       <c r="J60" s="374"/>
-      <c r="K60" s="516" t="s">
+      <c r="K60" s="522" t="s">
         <v>190</v>
       </c>
-      <c r="L60" s="517"/>
+      <c r="L60" s="523"/>
       <c r="M60" s="374"/>
-      <c r="N60" s="516" t="s">
+      <c r="N60" s="522" t="s">
         <v>191</v>
       </c>
-      <c r="O60" s="517"/>
+      <c r="O60" s="523"/>
       <c r="P60" s="374"/>
-      <c r="Q60" s="516" t="s">
+      <c r="Q60" s="522" t="s">
         <v>192</v>
       </c>
-      <c r="R60" s="517"/>
+      <c r="R60" s="523"/>
       <c r="S60" s="374"/>
-      <c r="T60" s="516" t="s">
+      <c r="T60" s="522" t="s">
         <v>193</v>
       </c>
-      <c r="U60" s="517"/>
+      <c r="U60" s="523"/>
       <c r="V60" s="374"/>
-      <c r="W60" s="516" t="s">
+      <c r="W60" s="522" t="s">
         <v>194</v>
       </c>
-      <c r="X60" s="517"/>
+      <c r="X60" s="523"/>
       <c r="Y60" s="374"/>
-      <c r="Z60" s="516" t="s">
+      <c r="Z60" s="522" t="s">
         <v>195</v>
       </c>
-      <c r="AA60" s="517"/>
+      <c r="AA60" s="523"/>
       <c r="AB60" s="374"/>
-      <c r="AC60" s="516" t="s">
+      <c r="AC60" s="522" t="s">
         <v>196</v>
       </c>
-      <c r="AD60" s="517"/>
+      <c r="AD60" s="523"/>
       <c r="AF60" s="374">
         <v>66.680000000000007</v>
       </c>
     </row>
     <row r="61" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="516" t="s">
+      <c r="B61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="C61" s="518"/>
+      <c r="C61" s="524"/>
       <c r="D61" s="374"/>
-      <c r="E61" s="516" t="s">
+      <c r="E61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="518"/>
+      <c r="F61" s="524"/>
       <c r="G61" s="374"/>
-      <c r="H61" s="516" t="s">
+      <c r="H61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="I61" s="518"/>
+      <c r="I61" s="524"/>
       <c r="J61" s="374"/>
-      <c r="K61" s="516" t="s">
+      <c r="K61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="L61" s="518"/>
+      <c r="L61" s="524"/>
       <c r="M61" s="374"/>
-      <c r="N61" s="516" t="s">
+      <c r="N61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="O61" s="518"/>
+      <c r="O61" s="524"/>
       <c r="P61" s="374"/>
-      <c r="Q61" s="516" t="s">
+      <c r="Q61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="R61" s="518"/>
+      <c r="R61" s="524"/>
       <c r="S61" s="374"/>
-      <c r="T61" s="516" t="s">
+      <c r="T61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="U61" s="518"/>
+      <c r="U61" s="524"/>
       <c r="V61" s="374"/>
-      <c r="W61" s="516" t="s">
+      <c r="W61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="X61" s="518"/>
+      <c r="X61" s="524"/>
       <c r="Y61" s="374"/>
-      <c r="Z61" s="516" t="s">
+      <c r="Z61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="AA61" s="518"/>
+      <c r="AA61" s="524"/>
       <c r="AB61" s="374"/>
-      <c r="AC61" s="516" t="s">
+      <c r="AC61" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="AD61" s="518"/>
+      <c r="AD61" s="524"/>
       <c r="AF61" s="364">
         <v>66.260000000000005</v>
       </c>
     </row>
     <row r="62" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="522">
+      <c r="B62" s="527">
         <v>714</v>
       </c>
-      <c r="C62" s="523"/>
+      <c r="C62" s="528"/>
       <c r="D62" s="374"/>
-      <c r="E62" s="522">
+      <c r="E62" s="527">
         <v>385</v>
       </c>
-      <c r="F62" s="523"/>
+      <c r="F62" s="528"/>
       <c r="G62" s="374"/>
-      <c r="H62" s="522">
+      <c r="H62" s="527">
         <v>0</v>
       </c>
-      <c r="I62" s="523"/>
+      <c r="I62" s="528"/>
       <c r="J62" s="374"/>
-      <c r="K62" s="519">
+      <c r="K62" s="525">
         <v>39</v>
       </c>
-      <c r="L62" s="520"/>
+      <c r="L62" s="526"/>
       <c r="M62" s="374"/>
-      <c r="N62" s="519"/>
-      <c r="O62" s="520"/>
+      <c r="N62" s="525"/>
+      <c r="O62" s="526"/>
       <c r="P62" s="374"/>
-      <c r="Q62" s="519">
+      <c r="Q62" s="525">
         <v>202</v>
       </c>
-      <c r="R62" s="520"/>
+      <c r="R62" s="526"/>
       <c r="S62" s="374"/>
-      <c r="T62" s="519">
+      <c r="T62" s="525">
         <v>187</v>
       </c>
-      <c r="U62" s="520"/>
+      <c r="U62" s="526"/>
       <c r="V62" s="374"/>
-      <c r="W62" s="519"/>
-      <c r="X62" s="520"/>
+      <c r="W62" s="525"/>
+      <c r="X62" s="526"/>
       <c r="Y62" s="374"/>
-      <c r="Z62" s="519">
+      <c r="Z62" s="525">
         <v>50</v>
       </c>
-      <c r="AA62" s="520"/>
+      <c r="AA62" s="526"/>
       <c r="AB62" s="374"/>
-      <c r="AC62" s="519"/>
-      <c r="AD62" s="520"/>
+      <c r="AC62" s="525"/>
+      <c r="AD62" s="526"/>
       <c r="AE62" s="374"/>
       <c r="AF62" s="374">
         <v>66</v>
@@ -30382,279 +30362,192 @@
       </c>
     </row>
     <row r="68" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="516" t="s">
+      <c r="B68" s="522" t="s">
         <v>170</v>
       </c>
-      <c r="C68" s="517"/>
-      <c r="E68" s="516" t="s">
+      <c r="C68" s="523"/>
+      <c r="E68" s="522" t="s">
         <v>173</v>
       </c>
-      <c r="F68" s="517"/>
-      <c r="H68" s="516" t="s">
+      <c r="F68" s="523"/>
+      <c r="H68" s="522" t="s">
         <v>174</v>
       </c>
-      <c r="I68" s="517"/>
-      <c r="K68" s="516" t="s">
+      <c r="I68" s="523"/>
+      <c r="K68" s="522" t="s">
         <v>175</v>
       </c>
-      <c r="L68" s="517"/>
-      <c r="N68" s="516" t="s">
+      <c r="L68" s="523"/>
+      <c r="N68" s="522" t="s">
         <v>176</v>
       </c>
-      <c r="O68" s="517"/>
-      <c r="Q68" s="516" t="s">
+      <c r="O68" s="523"/>
+      <c r="Q68" s="522" t="s">
         <v>177</v>
       </c>
-      <c r="R68" s="517"/>
-      <c r="T68" s="516" t="s">
+      <c r="R68" s="523"/>
+      <c r="T68" s="522" t="s">
         <v>178</v>
       </c>
-      <c r="U68" s="517"/>
-      <c r="W68" s="516" t="s">
+      <c r="U68" s="523"/>
+      <c r="W68" s="522" t="s">
         <v>179</v>
       </c>
-      <c r="X68" s="517"/>
-      <c r="Z68" s="516" t="s">
+      <c r="X68" s="523"/>
+      <c r="Z68" s="522" t="s">
         <v>239</v>
       </c>
-      <c r="AA68" s="517"/>
-      <c r="AC68" s="516" t="s">
+      <c r="AA68" s="523"/>
+      <c r="AC68" s="522" t="s">
         <v>180</v>
       </c>
-      <c r="AD68" s="517"/>
+      <c r="AD68" s="523"/>
     </row>
     <row r="69" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="516" t="s">
+      <c r="B69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="C69" s="517"/>
-      <c r="E69" s="516" t="s">
+      <c r="C69" s="523"/>
+      <c r="E69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="F69" s="518"/>
-      <c r="H69" s="516" t="s">
+      <c r="F69" s="524"/>
+      <c r="H69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="I69" s="518"/>
-      <c r="K69" s="516" t="s">
+      <c r="I69" s="524"/>
+      <c r="K69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="L69" s="518"/>
-      <c r="N69" s="516" t="s">
+      <c r="L69" s="524"/>
+      <c r="N69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="O69" s="518"/>
-      <c r="Q69" s="516" t="s">
+      <c r="O69" s="524"/>
+      <c r="Q69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="R69" s="518"/>
-      <c r="T69" s="516" t="s">
+      <c r="R69" s="524"/>
+      <c r="T69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="U69" s="518"/>
-      <c r="W69" s="516" t="s">
+      <c r="U69" s="524"/>
+      <c r="W69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="X69" s="518"/>
-      <c r="Z69" s="516" t="s">
+      <c r="X69" s="524"/>
+      <c r="Z69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="AA69" s="518"/>
-      <c r="AC69" s="516" t="s">
+      <c r="AA69" s="524"/>
+      <c r="AC69" s="522" t="s">
         <v>212</v>
       </c>
-      <c r="AD69" s="518"/>
+      <c r="AD69" s="524"/>
     </row>
     <row r="70" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="519">
+      <c r="B70" s="525">
         <v>161</v>
       </c>
-      <c r="C70" s="520"/>
+      <c r="C70" s="526"/>
       <c r="D70" s="374"/>
-      <c r="E70" s="522">
+      <c r="E70" s="527">
         <v>108</v>
       </c>
-      <c r="F70" s="523"/>
+      <c r="F70" s="528"/>
       <c r="G70" s="374"/>
-      <c r="H70" s="522">
+      <c r="H70" s="527">
         <v>90</v>
       </c>
-      <c r="I70" s="523"/>
+      <c r="I70" s="528"/>
       <c r="J70" s="374"/>
-      <c r="K70" s="522">
+      <c r="K70" s="527">
         <v>1170</v>
       </c>
-      <c r="L70" s="523"/>
+      <c r="L70" s="528"/>
       <c r="M70" s="374"/>
-      <c r="N70" s="519">
+      <c r="N70" s="525">
         <v>500</v>
       </c>
-      <c r="O70" s="520"/>
+      <c r="O70" s="526"/>
       <c r="P70" s="374"/>
-      <c r="Q70" s="519">
+      <c r="Q70" s="525">
         <v>295</v>
       </c>
-      <c r="R70" s="520"/>
+      <c r="R70" s="526"/>
       <c r="S70" s="374"/>
-      <c r="T70" s="519">
+      <c r="T70" s="525">
         <v>1</v>
       </c>
-      <c r="U70" s="520"/>
+      <c r="U70" s="526"/>
       <c r="V70" s="374"/>
-      <c r="W70" s="519">
+      <c r="W70" s="525">
         <v>32</v>
       </c>
-      <c r="X70" s="520"/>
+      <c r="X70" s="526"/>
       <c r="Y70" s="374"/>
-      <c r="Z70" s="519">
+      <c r="Z70" s="525">
         <v>105</v>
       </c>
-      <c r="AA70" s="520"/>
-      <c r="AC70" s="519">
+      <c r="AA70" s="526"/>
+      <c r="AC70" s="525">
         <v>90</v>
       </c>
-      <c r="AD70" s="520"/>
+      <c r="AD70" s="526"/>
     </row>
     <row r="86" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M86" s="364"/>
     </row>
   </sheetData>
   <mergeCells count="207">
-    <mergeCell ref="AC68:AD68"/>
-    <mergeCell ref="AC69:AD69"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="AI20:AJ20"/>
-    <mergeCell ref="AI21:AJ21"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="Z50:AA50"/>
-    <mergeCell ref="AF52:AG52"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="Q69:R69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="Z70:AA70"/>
-    <mergeCell ref="AC70:AD70"/>
-    <mergeCell ref="W69:X69"/>
-    <mergeCell ref="Z69:AA69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="W70:X70"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="Q68:R68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="W68:X68"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="AC61:AD61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="Q62:R62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="W62:X62"/>
-    <mergeCell ref="Z62:AA62"/>
-    <mergeCell ref="AC62:AD62"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="Q61:R61"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="W61:X61"/>
-    <mergeCell ref="Z61:AA61"/>
-    <mergeCell ref="AC52:AD52"/>
-    <mergeCell ref="AC53:AD53"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="W60:X60"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="AC60:AD60"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AC42:AD42"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AF39:AG39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AF38:AG38"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="AF37:AG37"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="AC36:AD36"/>
-    <mergeCell ref="AF36:AG36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="AF5:AG5"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="N18:O18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="T18:U18"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="Z18:AA18"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="AC5:AD5"/>
+    <mergeCell ref="AC18:AD18"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AF20:AG20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="B38:C38"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="H38:I38"/>
@@ -30679,54 +30572,141 @@
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="N21:O21"/>
     <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AF20:AG20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="AF5:AG5"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="N18:O18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="T18:U18"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="Z18:AA18"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="T5:U5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Z5:AA5"/>
-    <mergeCell ref="AC5:AD5"/>
-    <mergeCell ref="AC18:AD18"/>
-    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AF36:AG36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AF38:AG38"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AF39:AG39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="W60:X60"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="W61:X61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="Q62:R62"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="W62:X62"/>
+    <mergeCell ref="Z62:AA62"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="Q68:R68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="W68:X68"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="AC70:AD70"/>
+    <mergeCell ref="W69:X69"/>
+    <mergeCell ref="Z69:AA69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="AC68:AD68"/>
+    <mergeCell ref="AC69:AD69"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="AI20:AJ20"/>
+    <mergeCell ref="AI21:AJ21"/>
+    <mergeCell ref="AF42:AG42"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="Z50:AA50"/>
+    <mergeCell ref="AF52:AG52"/>
+    <mergeCell ref="AC61:AD61"/>
+    <mergeCell ref="AC62:AD62"/>
+    <mergeCell ref="AC52:AD52"/>
+    <mergeCell ref="AC53:AD53"/>
+    <mergeCell ref="AC60:AD60"/>
+    <mergeCell ref="Z42:AA42"/>
+    <mergeCell ref="AC42:AD42"/>
   </mergeCells>
   <conditionalFormatting sqref="F9">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
@@ -30763,15 +30743,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="460" t="s">
+      <c r="A1" s="468" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="460"/>
-      <c r="C1" s="460"/>
-      <c r="J1" s="461" t="s">
+      <c r="B1" s="468"/>
+      <c r="C1" s="468"/>
+      <c r="J1" s="469" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="461"/>
+      <c r="K1" s="469"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="136"/>
@@ -30943,10 +30923,10 @@
         <v>45</v>
       </c>
       <c r="B10" s="142"/>
-      <c r="J10" s="461" t="s">
+      <c r="J10" s="469" t="s">
         <v>125</v>
       </c>
-      <c r="K10" s="461"/>
+      <c r="K10" s="469"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -31183,11 +31163,11 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="460" t="s">
+      <c r="A20" s="468" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="460"/>
-      <c r="C20" s="460"/>
+      <c r="B20" s="468"/>
+      <c r="C20" s="468"/>
       <c r="J20" s="2">
         <f ca="1">'Loading Arrival'!B35</f>
         <v>45923</v>
@@ -31711,18 +31691,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="477" t="s">
+      <c r="A1" s="485" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="478"/>
-      <c r="C1" s="478"/>
-      <c r="D1" s="479"/>
-      <c r="F1" s="462" t="s">
+      <c r="B1" s="486"/>
+      <c r="C1" s="486"/>
+      <c r="D1" s="487"/>
+      <c r="F1" s="470" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="463"/>
-      <c r="H1" s="463"/>
-      <c r="I1" s="464"/>
+      <c r="G1" s="471"/>
+      <c r="H1" s="471"/>
+      <c r="I1" s="472"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="32"/>
@@ -31747,7 +31727,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="489" t="s">
+      <c r="A3" s="497" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="23">
@@ -31762,7 +31742,7 @@
         <f ca="1">C3+14</f>
         <v>45938</v>
       </c>
-      <c r="F3" s="465" t="s">
+      <c r="F3" s="473" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="418">
@@ -31779,7 +31759,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="489"/>
+      <c r="A4" s="497"/>
       <c r="B4" s="26">
         <f ca="1">B5-B3</f>
         <v>21</v>
@@ -31792,7 +31772,7 @@
         <f ca="1">D5-D3</f>
         <v>24</v>
       </c>
-      <c r="F4" s="466"/>
+      <c r="F4" s="474"/>
       <c r="G4" s="421">
         <f ca="1">G5-G3</f>
         <v>28</v>
@@ -31807,7 +31787,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="489"/>
+      <c r="A5" s="497"/>
       <c r="B5" s="29">
         <f ca="1">EOMONTH(B3,0)+1</f>
         <v>45931</v>
@@ -31820,7 +31800,7 @@
         <f ca="1">EOMONTH(D3,0)+1</f>
         <v>45962</v>
       </c>
-      <c r="F5" s="466"/>
+      <c r="F5" s="474"/>
       <c r="G5" s="424">
         <f ca="1">EOMONTH(G3,0)+1</f>
         <v>45931</v>
@@ -31835,7 +31815,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="489"/>
+      <c r="A6" s="497"/>
       <c r="B6" s="26">
         <f ca="1">IF(45-B4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),45-B4)</f>
         <v>24</v>
@@ -31848,7 +31828,7 @@
         <f ca="1">IF(45-D4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),45-D4)</f>
         <v>21</v>
       </c>
-      <c r="F6" s="466"/>
+      <c r="F6" s="474"/>
       <c r="G6" s="421">
         <f ca="1">IF(15-G4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),15-G4)</f>
         <v>-13</v>
@@ -31863,7 +31843,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="489"/>
+      <c r="A7" s="497"/>
       <c r="B7" s="29">
         <f ca="1">B5+B6</f>
         <v>45955</v>
@@ -31876,7 +31856,7 @@
         <f ca="1">D5+D6</f>
         <v>45983</v>
       </c>
-      <c r="F7" s="466"/>
+      <c r="F7" s="474"/>
       <c r="G7" s="424">
         <f ca="1">G5+G6</f>
         <v>45918</v>
@@ -31891,7 +31871,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="489"/>
+      <c r="A8" s="497"/>
       <c r="B8" s="26">
         <f ca="1">IF(45-B4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),45-B4-B6,0)</f>
         <v>0</v>
@@ -31904,7 +31884,7 @@
         <f ca="1">IF(45-D4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),45-D4-D6,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="466"/>
+      <c r="F8" s="474"/>
       <c r="G8" s="421">
         <f ca="1">IF(15-G4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),15-G4-G6,0)</f>
         <v>0</v>
@@ -31919,7 +31899,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="490"/>
+      <c r="A9" s="498"/>
       <c r="B9" s="29">
         <f ca="1">B7+B8</f>
         <v>45955</v>
@@ -31932,7 +31912,7 @@
         <f ca="1">D7+D8</f>
         <v>45983</v>
       </c>
-      <c r="F9" s="467"/>
+      <c r="F9" s="475"/>
       <c r="G9" s="427">
         <f ca="1">G7+G8</f>
         <v>45918</v>
@@ -31959,7 +31939,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="491" t="s">
+      <c r="A11" s="499" t="s">
         <v>50</v>
       </c>
       <c r="B11" s="51">
@@ -31976,7 +31956,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="492"/>
+      <c r="A12" s="500"/>
       <c r="B12" s="54">
         <f ca="1">B13-B11</f>
         <v>28</v>
@@ -31991,7 +31971,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="492"/>
+      <c r="A13" s="500"/>
       <c r="B13" s="57">
         <f ca="1">EOMONTH(B11,0)+1</f>
         <v>45931</v>
@@ -32006,7 +31986,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="492"/>
+      <c r="A14" s="500"/>
       <c r="B14" s="54">
         <f ca="1">IF(27-B12&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),27-B12)</f>
         <v>-1</v>
@@ -32021,7 +32001,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="492"/>
+      <c r="A15" s="500"/>
       <c r="B15" s="57">
         <f ca="1">B13+B14</f>
         <v>45930</v>
@@ -32037,7 +32017,7 @@
       <c r="H15" s="364"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="492"/>
+      <c r="A16" s="500"/>
       <c r="B16" s="54">
         <f ca="1">IF(27-B12&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),30-B12-B14,0)</f>
         <v>0</v>
@@ -32052,7 +32032,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="493"/>
+      <c r="A17" s="501"/>
       <c r="B17" s="60">
         <f ca="1">B15+B16</f>
         <v>45930</v>
@@ -32067,12 +32047,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="480" t="s">
+      <c r="A18" s="488" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="481"/>
-      <c r="C18" s="481"/>
-      <c r="D18" s="482"/>
+      <c r="B18" s="489"/>
+      <c r="C18" s="489"/>
+      <c r="D18" s="490"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="63"/>
@@ -32087,7 +32067,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="468" t="s">
+      <c r="A20" s="476" t="s">
         <v>50</v>
       </c>
       <c r="B20" s="67">
@@ -32104,7 +32084,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="469"/>
+      <c r="A21" s="477"/>
       <c r="B21" s="70">
         <f ca="1">B22-B20</f>
         <v>28</v>
@@ -32119,7 +32099,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="469"/>
+      <c r="A22" s="477"/>
       <c r="B22" s="71">
         <f ca="1">EOMONTH(B20,0)+1</f>
         <v>45931</v>
@@ -32134,7 +32114,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="469"/>
+      <c r="A23" s="477"/>
       <c r="B23" s="70">
         <f ca="1">IF(19-B21&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),19-B21)</f>
         <v>-9</v>
@@ -32149,7 +32129,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="469"/>
+      <c r="A24" s="477"/>
       <c r="B24" s="71">
         <f ca="1">B22+B23</f>
         <v>45922</v>
@@ -32164,7 +32144,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="469"/>
+      <c r="A25" s="477"/>
       <c r="B25" s="70">
         <f ca="1">IF(19-B21&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),19-B21-B23,0)</f>
         <v>0</v>
@@ -32179,7 +32159,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="470"/>
+      <c r="A26" s="478"/>
       <c r="B26" s="72">
         <f ca="1">B24+B25</f>
         <v>45922</v>
@@ -32194,12 +32174,12 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="483" t="s">
+      <c r="A27" s="491" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="484"/>
-      <c r="C27" s="484"/>
-      <c r="D27" s="485"/>
+      <c r="B27" s="492"/>
+      <c r="C27" s="492"/>
+      <c r="D27" s="493"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="73"/>
@@ -32214,7 +32194,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="471" t="s">
+      <c r="A29" s="479" t="s">
         <v>50</v>
       </c>
       <c r="B29" s="17">
@@ -32231,7 +32211,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="472"/>
+      <c r="A30" s="480"/>
       <c r="B30" s="11">
         <f ca="1">B31-B29</f>
         <v>28</v>
@@ -32246,7 +32226,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="472"/>
+      <c r="A31" s="480"/>
       <c r="B31" s="14">
         <f ca="1">EOMONTH(B29,0)+1</f>
         <v>45931</v>
@@ -32261,7 +32241,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="472"/>
+      <c r="A32" s="480"/>
       <c r="B32" s="11">
         <f ca="1">IF(20-B30&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),20-B30)</f>
         <v>-8</v>
@@ -32276,7 +32256,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="472"/>
+      <c r="A33" s="480"/>
       <c r="B33" s="14">
         <f ca="1">B31+B32</f>
         <v>45923</v>
@@ -32291,7 +32271,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="472"/>
+      <c r="A34" s="480"/>
       <c r="B34" s="11">
         <f ca="1">IF(20-B30&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),20-B30-B32,0)</f>
         <v>0</v>
@@ -32306,7 +32286,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="473"/>
+      <c r="A35" s="481"/>
       <c r="B35" s="20">
         <f ca="1">B33+B34</f>
         <v>45923</v>
@@ -32321,12 +32301,12 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="486" t="s">
+      <c r="A36" s="494" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="487"/>
-      <c r="C36" s="487"/>
-      <c r="D36" s="488"/>
+      <c r="B36" s="495"/>
+      <c r="C36" s="495"/>
+      <c r="D36" s="496"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="83"/>
@@ -32341,7 +32321,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="474" t="s">
+      <c r="A38" s="482" t="s">
         <v>50</v>
       </c>
       <c r="B38" s="77">
@@ -32358,7 +32338,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="475"/>
+      <c r="A39" s="483"/>
       <c r="B39" s="80">
         <f ca="1">B40-B38</f>
         <v>12</v>
@@ -32373,7 +32353,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="475"/>
+      <c r="A40" s="483"/>
       <c r="B40" s="81">
         <f ca="1">IF(EOMONTH(B38,0)+1-B38&gt;12,B38+12,EOMONTH(B38,0)+1)</f>
         <v>45915</v>
@@ -32388,7 +32368,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="475"/>
+      <c r="A41" s="483"/>
       <c r="B41" s="80">
         <f ca="1">IF(12-B39&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),12-B39)</f>
         <v>0</v>
@@ -32403,7 +32383,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="475"/>
+      <c r="A42" s="483"/>
       <c r="B42" s="81">
         <f ca="1">B40+B41</f>
         <v>45915</v>
@@ -32418,7 +32398,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="475"/>
+      <c r="A43" s="483"/>
       <c r="B43" s="80">
         <f ca="1">IF(12-B39&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),20-B39-B41,0)</f>
         <v>0</v>
@@ -32433,7 +32413,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="476"/>
+      <c r="A44" s="484"/>
       <c r="B44" s="82">
         <f ca="1">B42+B43</f>
         <v>45915</v>
@@ -32497,74 +32477,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="494" t="s">
+      <c r="E3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="495"/>
-      <c r="G3" s="494" t="s">
+      <c r="F3" s="513"/>
+      <c r="G3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="495"/>
-      <c r="I3" s="494" t="s">
+      <c r="H3" s="513"/>
+      <c r="I3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="495"/>
-      <c r="P3" s="494" t="s">
+      <c r="J3" s="513"/>
+      <c r="P3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="495"/>
-      <c r="R3" s="494" t="s">
+      <c r="Q3" s="513"/>
+      <c r="R3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="495"/>
-      <c r="T3" s="494" t="s">
+      <c r="S3" s="513"/>
+      <c r="T3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="495"/>
+      <c r="U3" s="513"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="496" t="s">
+      <c r="A4" s="510" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="497"/>
-      <c r="C4" s="497"/>
-      <c r="D4" s="497"/>
-      <c r="E4" s="498">
+      <c r="B4" s="511"/>
+      <c r="C4" s="511"/>
+      <c r="D4" s="511"/>
+      <c r="E4" s="509">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="499"/>
-      <c r="G4" s="500">
+      <c r="F4" s="503"/>
+      <c r="G4" s="502">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="499"/>
-      <c r="I4" s="500">
+      <c r="H4" s="503"/>
+      <c r="I4" s="502">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="499"/>
-      <c r="L4" s="496" t="s">
+      <c r="J4" s="503"/>
+      <c r="L4" s="510" t="s">
         <v>216</v>
       </c>
-      <c r="M4" s="497"/>
-      <c r="N4" s="497"/>
-      <c r="O4" s="497"/>
-      <c r="P4" s="498">
+      <c r="M4" s="511"/>
+      <c r="N4" s="511"/>
+      <c r="O4" s="511"/>
+      <c r="P4" s="509">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="499"/>
-      <c r="R4" s="500">
+      <c r="Q4" s="503"/>
+      <c r="R4" s="502">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="499"/>
-      <c r="T4" s="500">
+      <c r="S4" s="503"/>
+      <c r="T4" s="502">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="499"/>
+      <c r="U4" s="503"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -33847,45 +33827,56 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="501">
+      <c r="E25" s="504">
         <f ca="1">'Loading Arrival'!G9</f>
         <v>45918</v>
       </c>
-      <c r="F25" s="502"/>
-      <c r="G25" s="503">
+      <c r="F25" s="505"/>
+      <c r="G25" s="506">
         <f ca="1">'Loading Arrival'!H9</f>
         <v>45932</v>
       </c>
-      <c r="H25" s="504"/>
-      <c r="I25" s="505">
+      <c r="H25" s="507"/>
+      <c r="I25" s="508">
         <f ca="1">'Loading Arrival'!I9</f>
         <v>45946</v>
       </c>
-      <c r="J25" s="502"/>
+      <c r="J25" s="505"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="501">
+      <c r="P25" s="504">
         <f ca="1">E25</f>
         <v>45918</v>
       </c>
-      <c r="Q25" s="502"/>
-      <c r="R25" s="503">
+      <c r="Q25" s="505"/>
+      <c r="R25" s="506">
         <f ca="1">G25</f>
         <v>45932</v>
       </c>
-      <c r="S25" s="504"/>
-      <c r="T25" s="505">
+      <c r="S25" s="507"/>
+      <c r="T25" s="508">
         <f ca="1">I25</f>
         <v>45946</v>
       </c>
-      <c r="U25" s="502"/>
+      <c r="U25" s="505"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -33895,17 +33886,6 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33938,38 +33918,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="494" t="s">
+      <c r="E3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="495"/>
-      <c r="G3" s="494" t="s">
+      <c r="F3" s="513"/>
+      <c r="G3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="495"/>
-      <c r="N3" s="494" t="s">
+      <c r="H3" s="513"/>
+      <c r="N3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="495"/>
-      <c r="P3" s="494" t="s">
+      <c r="O3" s="513"/>
+      <c r="P3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="495"/>
-      <c r="R3" s="494" t="s">
+      <c r="Q3" s="513"/>
+      <c r="R3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="495"/>
-      <c r="Y3" s="494" t="s">
+      <c r="S3" s="513"/>
+      <c r="Y3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="495"/>
-      <c r="AA3" s="494" t="s">
+      <c r="Z3" s="513"/>
+      <c r="AA3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="AB3" s="495"/>
-      <c r="AC3" s="494" t="s">
+      <c r="AB3" s="513"/>
+      <c r="AC3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="495"/>
+      <c r="AD3" s="513"/>
     </row>
     <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="341" t="s">
@@ -35918,61 +35898,69 @@
       <c r="B27" s="108"/>
       <c r="C27" s="105"/>
       <c r="D27" s="105"/>
-      <c r="E27" s="501">
+      <c r="E27" s="504">
         <f ca="1">'Loading Arrival'!B9</f>
         <v>45955</v>
       </c>
-      <c r="F27" s="502"/>
-      <c r="G27" s="501">
+      <c r="F27" s="505"/>
+      <c r="G27" s="504">
         <f ca="1">'Loading Arrival'!C9</f>
         <v>45969</v>
       </c>
-      <c r="H27" s="502"/>
+      <c r="H27" s="505"/>
       <c r="J27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K27" s="108"/>
       <c r="L27" s="105"/>
       <c r="M27" s="105"/>
-      <c r="N27" s="501">
+      <c r="N27" s="504">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="O27" s="502"/>
-      <c r="P27" s="503">
+      <c r="O27" s="505"/>
+      <c r="P27" s="506">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="Q27" s="504"/>
-      <c r="R27" s="505">
+      <c r="Q27" s="507"/>
+      <c r="R27" s="508">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="S27" s="502"/>
+      <c r="S27" s="505"/>
       <c r="U27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V27" s="108"/>
       <c r="W27" s="105"/>
       <c r="X27" s="105"/>
-      <c r="Y27" s="501">
+      <c r="Y27" s="504">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="Z27" s="502"/>
-      <c r="AA27" s="503">
+      <c r="Z27" s="505"/>
+      <c r="AA27" s="506">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="AB27" s="504"/>
-      <c r="AC27" s="505">
+      <c r="AB27" s="507"/>
+      <c r="AC27" s="508">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="AD27" s="502"/>
+      <c r="AD27" s="505"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Y27:Z27"/>
+    <mergeCell ref="AA27:AB27"/>
+    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="N27:O27"/>
+    <mergeCell ref="P27:Q27"/>
+    <mergeCell ref="R27:S27"/>
     <mergeCell ref="Y3:Z3"/>
     <mergeCell ref="AA3:AB3"/>
     <mergeCell ref="AC3:AD3"/>
@@ -35981,14 +35969,6 @@
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="R3:S3"/>
-    <mergeCell ref="Y27:Z27"/>
-    <mergeCell ref="AA27:AB27"/>
-    <mergeCell ref="AC27:AD27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="N27:O27"/>
-    <mergeCell ref="P27:Q27"/>
-    <mergeCell ref="R27:S27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -36027,74 +36007,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="494" t="s">
+      <c r="E3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="495"/>
-      <c r="G3" s="494" t="s">
+      <c r="F3" s="513"/>
+      <c r="G3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="495"/>
-      <c r="I3" s="494" t="s">
+      <c r="H3" s="513"/>
+      <c r="I3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="495"/>
-      <c r="P3" s="494" t="s">
+      <c r="J3" s="513"/>
+      <c r="P3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="495"/>
-      <c r="R3" s="494" t="s">
+      <c r="Q3" s="513"/>
+      <c r="R3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="495"/>
-      <c r="T3" s="494" t="s">
+      <c r="S3" s="513"/>
+      <c r="T3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="495"/>
+      <c r="U3" s="513"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="496" t="s">
+      <c r="A4" s="510" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="497"/>
-      <c r="C4" s="497"/>
-      <c r="D4" s="497"/>
-      <c r="E4" s="498">
+      <c r="B4" s="511"/>
+      <c r="C4" s="511"/>
+      <c r="D4" s="511"/>
+      <c r="E4" s="509">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="499"/>
-      <c r="G4" s="500">
+      <c r="F4" s="503"/>
+      <c r="G4" s="502">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="499"/>
-      <c r="I4" s="500">
+      <c r="H4" s="503"/>
+      <c r="I4" s="502">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="499"/>
-      <c r="L4" s="496" t="s">
+      <c r="J4" s="503"/>
+      <c r="L4" s="510" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="497"/>
-      <c r="N4" s="497"/>
-      <c r="O4" s="497"/>
-      <c r="P4" s="498">
+      <c r="M4" s="511"/>
+      <c r="N4" s="511"/>
+      <c r="O4" s="511"/>
+      <c r="P4" s="509">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="499"/>
-      <c r="R4" s="500">
+      <c r="Q4" s="503"/>
+      <c r="R4" s="502">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="499"/>
-      <c r="T4" s="500">
+      <c r="S4" s="503"/>
+      <c r="T4" s="502">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="499"/>
+      <c r="U4" s="503"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -37377,51 +37357,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="501">
+      <c r="E25" s="504">
         <f ca="1">'Loading Arrival'!B35</f>
         <v>45923</v>
       </c>
-      <c r="F25" s="502"/>
-      <c r="G25" s="503">
+      <c r="F25" s="505"/>
+      <c r="G25" s="506">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="504"/>
-      <c r="I25" s="505">
+      <c r="H25" s="507"/>
+      <c r="I25" s="508">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="502"/>
+      <c r="J25" s="505"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="501">
+      <c r="P25" s="504">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="502"/>
-      <c r="R25" s="503">
+      <c r="Q25" s="505"/>
+      <c r="R25" s="506">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="504"/>
-      <c r="T25" s="505">
+      <c r="S25" s="507"/>
+      <c r="T25" s="508">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="502"/>
+      <c r="U25" s="505"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -37430,12 +37410,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -37474,74 +37454,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="494" t="s">
+      <c r="E3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="495"/>
-      <c r="G3" s="494" t="s">
+      <c r="F3" s="513"/>
+      <c r="G3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="495"/>
-      <c r="I3" s="494" t="s">
+      <c r="H3" s="513"/>
+      <c r="I3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="495"/>
-      <c r="P3" s="494" t="s">
+      <c r="J3" s="513"/>
+      <c r="P3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="495"/>
-      <c r="R3" s="494" t="s">
+      <c r="Q3" s="513"/>
+      <c r="R3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="495"/>
-      <c r="T3" s="494" t="s">
+      <c r="S3" s="513"/>
+      <c r="T3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="495"/>
+      <c r="U3" s="513"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="496" t="s">
+      <c r="A4" s="510" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="497"/>
-      <c r="C4" s="497"/>
-      <c r="D4" s="497"/>
-      <c r="E4" s="498">
+      <c r="B4" s="511"/>
+      <c r="C4" s="511"/>
+      <c r="D4" s="511"/>
+      <c r="E4" s="509">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="499"/>
-      <c r="G4" s="500">
+      <c r="F4" s="503"/>
+      <c r="G4" s="502">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="499"/>
-      <c r="I4" s="500">
+      <c r="H4" s="503"/>
+      <c r="I4" s="502">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="499"/>
-      <c r="L4" s="496" t="s">
+      <c r="J4" s="503"/>
+      <c r="L4" s="510" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="497"/>
-      <c r="N4" s="497"/>
-      <c r="O4" s="497"/>
-      <c r="P4" s="498">
+      <c r="M4" s="511"/>
+      <c r="N4" s="511"/>
+      <c r="O4" s="511"/>
+      <c r="P4" s="509">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="499"/>
-      <c r="R4" s="500">
+      <c r="Q4" s="503"/>
+      <c r="R4" s="502">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="499"/>
-      <c r="T4" s="500">
+      <c r="S4" s="503"/>
+      <c r="T4" s="502">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="499"/>
+      <c r="U4" s="503"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -38824,51 +38804,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="501">
+      <c r="E25" s="504">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="502"/>
-      <c r="G25" s="503">
+      <c r="F25" s="505"/>
+      <c r="G25" s="506">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="504"/>
-      <c r="I25" s="505">
+      <c r="H25" s="507"/>
+      <c r="I25" s="508">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="502"/>
+      <c r="J25" s="505"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="501">
+      <c r="P25" s="504">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="502"/>
-      <c r="R25" s="503">
+      <c r="Q25" s="505"/>
+      <c r="R25" s="506">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="504"/>
-      <c r="T25" s="505">
+      <c r="S25" s="507"/>
+      <c r="T25" s="508">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="502"/>
+      <c r="U25" s="505"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -38877,12 +38857,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -38921,74 +38901,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="494" t="s">
+      <c r="E3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="495"/>
-      <c r="G3" s="494" t="s">
+      <c r="F3" s="513"/>
+      <c r="G3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="495"/>
-      <c r="I3" s="494" t="s">
+      <c r="H3" s="513"/>
+      <c r="I3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="495"/>
-      <c r="P3" s="494" t="s">
+      <c r="J3" s="513"/>
+      <c r="P3" s="512" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="495"/>
-      <c r="R3" s="494" t="s">
+      <c r="Q3" s="513"/>
+      <c r="R3" s="512" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="495"/>
-      <c r="T3" s="494" t="s">
+      <c r="S3" s="513"/>
+      <c r="T3" s="512" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="495"/>
+      <c r="U3" s="513"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="496" t="s">
+      <c r="A4" s="510" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="497"/>
-      <c r="C4" s="497"/>
-      <c r="D4" s="497"/>
-      <c r="E4" s="498">
+      <c r="B4" s="511"/>
+      <c r="C4" s="511"/>
+      <c r="D4" s="511"/>
+      <c r="E4" s="509">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="499"/>
-      <c r="G4" s="500">
+      <c r="F4" s="503"/>
+      <c r="G4" s="502">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="499"/>
-      <c r="I4" s="500">
+      <c r="H4" s="503"/>
+      <c r="I4" s="502">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="499"/>
-      <c r="L4" s="496" t="s">
+      <c r="J4" s="503"/>
+      <c r="L4" s="510" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="497"/>
-      <c r="N4" s="497"/>
-      <c r="O4" s="497"/>
-      <c r="P4" s="498">
+      <c r="M4" s="511"/>
+      <c r="N4" s="511"/>
+      <c r="O4" s="511"/>
+      <c r="P4" s="509">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="499"/>
-      <c r="R4" s="500">
+      <c r="Q4" s="503"/>
+      <c r="R4" s="502">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="499"/>
-      <c r="T4" s="500">
+      <c r="S4" s="503"/>
+      <c r="T4" s="502">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="499"/>
+      <c r="U4" s="503"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -40271,51 +40251,50 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="501">
+      <c r="E25" s="504">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="502"/>
-      <c r="G25" s="503">
+      <c r="F25" s="505"/>
+      <c r="G25" s="506">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="504"/>
-      <c r="I25" s="505">
+      <c r="H25" s="507"/>
+      <c r="I25" s="508">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="502"/>
+      <c r="J25" s="505"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="501">
+      <c r="P25" s="504">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="502"/>
-      <c r="R25" s="503">
+      <c r="Q25" s="505"/>
+      <c r="R25" s="506">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="504"/>
-      <c r="T25" s="505">
+      <c r="S25" s="507"/>
+      <c r="T25" s="508">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="502"/>
+      <c r="U25" s="505"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -40325,11 +40304,12 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Arbs/Arbsheet updated.xlsx
+++ b/Arbs/Arbsheet updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\Arbs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3487CC69-7ABF-448E-83AB-D5B298C2D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8961388F-9A59-47C3-BB8F-A22179F2636C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3264,12 +3264,6 @@
     <xf numFmtId="16" fontId="0" fillId="25" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3279,11 +3273,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3300,16 +3300,16 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3414,10 +3414,25 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3433,21 +3448,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3474,6 +3474,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3489,28 +3495,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="106" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4340,6 +4340,60 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="12">
+        <item m="1" x="8"/>
+        <item m="1" x="10"/>
+        <item m="1" x="4"/>
+        <item m="1" x="6"/>
+        <item m="1" x="3"/>
+        <item m="1" x="9"/>
+        <item m="1" x="7"/>
+        <item m="1" x="5"/>
+        <item n="01.11.2024" x="0"/>
+        <item n="01.12.2024" x="1"/>
+        <item n="01.01.2025" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O2:O5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -4765,60 +4819,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="12">
-        <item m="1" x="8"/>
-        <item m="1" x="10"/>
-        <item m="1" x="4"/>
-        <item m="1" x="6"/>
-        <item m="1" x="3"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="5"/>
-        <item n="01.11.2024" x="0"/>
-        <item n="01.12.2024" x="1"/>
-        <item n="01.01.2025" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5143,28 +5143,28 @@
       <c r="M3" s="155"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="457" t="s">
+      <c r="A4" s="456" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="155"/>
-      <c r="C4" s="454" t="s">
+      <c r="C4" s="452" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="456"/>
-      <c r="F4" s="454" t="s">
+      <c r="D4" s="454"/>
+      <c r="F4" s="452" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="455"/>
-      <c r="H4" s="456"/>
-      <c r="J4" s="454" t="s">
+      <c r="G4" s="453"/>
+      <c r="H4" s="454"/>
+      <c r="J4" s="452" t="s">
         <v>133</v>
       </c>
-      <c r="K4" s="455"/>
-      <c r="L4" s="456"/>
+      <c r="K4" s="453"/>
+      <c r="L4" s="454"/>
       <c r="M4" s="155"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="457"/>
+      <c r="A5" s="456"/>
       <c r="B5" s="199" t="s">
         <v>134</v>
       </c>
@@ -9319,7 +9319,7 @@
       <c r="M99" s="155"/>
     </row>
     <row r="100" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="458" t="s">
+      <c r="A100" s="455" t="s">
         <v>138</v>
       </c>
       <c r="B100" s="155"/>
@@ -9340,7 +9340,7 @@
       <c r="M100" s="155"/>
     </row>
     <row r="101" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="458"/>
+      <c r="A101" s="455"/>
       <c r="B101" s="199" t="s">
         <v>134</v>
       </c>
@@ -10307,7 +10307,7 @@
         <v>131</v>
       </c>
       <c r="C126" s="450"/>
-      <c r="D126" s="466"/>
+      <c r="D126" s="464"/>
       <c r="E126" s="177" t="s">
         <v>131</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>135</v>
       </c>
       <c r="C127" s="450"/>
-      <c r="D127" s="466"/>
+      <c r="D127" s="464"/>
       <c r="E127" s="177" t="s">
         <v>130</v>
       </c>
@@ -10385,7 +10385,7 @@
         <v>55</v>
       </c>
       <c r="C128" s="450"/>
-      <c r="D128" s="466"/>
+      <c r="D128" s="464"/>
       <c r="E128" s="232" t="s">
         <v>55</v>
       </c>
@@ -10424,7 +10424,7 @@
         <v>56</v>
       </c>
       <c r="C129" s="450"/>
-      <c r="D129" s="466"/>
+      <c r="D129" s="464"/>
       <c r="E129" s="177" t="s">
         <v>56</v>
       </c>
@@ -10463,7 +10463,7 @@
         <v>57</v>
       </c>
       <c r="C130" s="450"/>
-      <c r="D130" s="466"/>
+      <c r="D130" s="464"/>
       <c r="E130" s="177" t="s">
         <v>57</v>
       </c>
@@ -10502,7 +10502,7 @@
         <v>58</v>
       </c>
       <c r="C131" s="450"/>
-      <c r="D131" s="466"/>
+      <c r="D131" s="464"/>
       <c r="E131" s="177" t="s">
         <v>58</v>
       </c>
@@ -10541,7 +10541,7 @@
         <v>127</v>
       </c>
       <c r="C132" s="450"/>
-      <c r="D132" s="466"/>
+      <c r="D132" s="464"/>
       <c r="E132" s="177" t="s">
         <v>127</v>
       </c>
@@ -10580,7 +10580,7 @@
         <v>128</v>
       </c>
       <c r="C133" s="450"/>
-      <c r="D133" s="466"/>
+      <c r="D133" s="464"/>
       <c r="E133" s="177" t="s">
         <v>128</v>
       </c>
@@ -10619,7 +10619,7 @@
         <v>83</v>
       </c>
       <c r="C134" s="450"/>
-      <c r="D134" s="466"/>
+      <c r="D134" s="464"/>
       <c r="E134" s="177" t="s">
         <v>83</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>59</v>
       </c>
       <c r="C135" s="450"/>
-      <c r="D135" s="466"/>
+      <c r="D135" s="464"/>
       <c r="E135" s="177" t="s">
         <v>59</v>
       </c>
@@ -10697,7 +10697,7 @@
         <v>60</v>
       </c>
       <c r="C136" s="450"/>
-      <c r="D136" s="466"/>
+      <c r="D136" s="464"/>
       <c r="E136" s="177" t="s">
         <v>60</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>61</v>
       </c>
       <c r="C137" s="450"/>
-      <c r="D137" s="466"/>
+      <c r="D137" s="464"/>
       <c r="E137" s="177" t="s">
         <v>61</v>
       </c>
@@ -10775,7 +10775,7 @@
         <v>62</v>
       </c>
       <c r="C138" s="450"/>
-      <c r="D138" s="466"/>
+      <c r="D138" s="464"/>
       <c r="E138" s="177" t="s">
         <v>62</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>63</v>
       </c>
       <c r="C139" s="450"/>
-      <c r="D139" s="466"/>
+      <c r="D139" s="464"/>
       <c r="E139" s="177" t="s">
         <v>63</v>
       </c>
@@ -10853,7 +10853,7 @@
         <v>64</v>
       </c>
       <c r="C140" s="450"/>
-      <c r="D140" s="466"/>
+      <c r="D140" s="464"/>
       <c r="E140" s="177" t="s">
         <v>64</v>
       </c>
@@ -10892,7 +10892,7 @@
         <v>65</v>
       </c>
       <c r="C141" s="450"/>
-      <c r="D141" s="466"/>
+      <c r="D141" s="464"/>
       <c r="E141" s="177" t="s">
         <v>65</v>
       </c>
@@ -10931,7 +10931,7 @@
         <v>66</v>
       </c>
       <c r="C142" s="450"/>
-      <c r="D142" s="466"/>
+      <c r="D142" s="464"/>
       <c r="E142" s="177" t="s">
         <v>66</v>
       </c>
@@ -10970,7 +10970,7 @@
         <v>102</v>
       </c>
       <c r="C143" s="450"/>
-      <c r="D143" s="466"/>
+      <c r="D143" s="464"/>
       <c r="E143" s="177" t="s">
         <v>102</v>
       </c>
@@ -11009,7 +11009,7 @@
         <v>103</v>
       </c>
       <c r="C144" s="450"/>
-      <c r="D144" s="466"/>
+      <c r="D144" s="464"/>
       <c r="E144" s="177" t="s">
         <v>103</v>
       </c>
@@ -11048,7 +11048,7 @@
         <v>115</v>
       </c>
       <c r="C145" s="450"/>
-      <c r="D145" s="466"/>
+      <c r="D145" s="464"/>
       <c r="E145" s="177" t="s">
         <v>115</v>
       </c>
@@ -11086,8 +11086,8 @@
       <c r="B146" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C146" s="464"/>
-      <c r="D146" s="467"/>
+      <c r="C146" s="465"/>
+      <c r="D146" s="466"/>
       <c r="E146" s="233" t="s">
         <v>129</v>
       </c>
@@ -11152,28 +11152,28 @@
       <c r="U148" s="436"/>
     </row>
     <row r="149" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="457" t="s">
+      <c r="A149" s="456" t="s">
         <v>141</v>
       </c>
       <c r="B149" s="155"/>
-      <c r="C149" s="452"/>
-      <c r="D149" s="453"/>
+      <c r="C149" s="457"/>
+      <c r="D149" s="458"/>
       <c r="E149" s="157"/>
-      <c r="F149" s="454" t="s">
+      <c r="F149" s="452" t="s">
         <v>132</v>
       </c>
-      <c r="G149" s="455"/>
-      <c r="H149" s="456"/>
+      <c r="G149" s="453"/>
+      <c r="H149" s="454"/>
       <c r="I149" s="157"/>
-      <c r="J149" s="454" t="s">
+      <c r="J149" s="452" t="s">
         <v>133</v>
       </c>
-      <c r="K149" s="455"/>
-      <c r="L149" s="456"/>
+      <c r="K149" s="453"/>
+      <c r="L149" s="454"/>
       <c r="M149" s="155"/>
     </row>
     <row r="150" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="457"/>
+      <c r="A150" s="456"/>
       <c r="B150" s="199" t="s">
         <v>134</v>
       </c>
@@ -12125,7 +12125,7 @@
       <c r="M174" s="155"/>
     </row>
     <row r="175" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="458" t="s">
+      <c r="A175" s="455" t="s">
         <v>142</v>
       </c>
       <c r="B175" s="155"/>
@@ -12146,7 +12146,7 @@
       <c r="M175" s="155"/>
     </row>
     <row r="176" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="458"/>
+      <c r="A176" s="455"/>
       <c r="B176" s="199" t="s">
         <v>134</v>
       </c>
@@ -13023,8 +13023,8 @@
       <c r="B199" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C199" s="464"/>
-      <c r="D199" s="465"/>
+      <c r="C199" s="465"/>
+      <c r="D199" s="467"/>
       <c r="E199" s="105" t="s">
         <v>129</v>
       </c>
@@ -13106,20 +13106,20 @@
     <row r="204" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="155"/>
       <c r="B204" s="155"/>
-      <c r="C204" s="452"/>
-      <c r="D204" s="453"/>
+      <c r="C204" s="457"/>
+      <c r="D204" s="458"/>
       <c r="E204" s="157"/>
-      <c r="F204" s="454" t="s">
+      <c r="F204" s="452" t="s">
         <v>132</v>
       </c>
-      <c r="G204" s="455"/>
-      <c r="H204" s="456"/>
+      <c r="G204" s="453"/>
+      <c r="H204" s="454"/>
       <c r="I204" s="157"/>
-      <c r="J204" s="454" t="s">
+      <c r="J204" s="452" t="s">
         <v>133</v>
       </c>
-      <c r="K204" s="455"/>
-      <c r="L204" s="456"/>
+      <c r="K204" s="453"/>
+      <c r="L204" s="454"/>
       <c r="M204" s="155"/>
     </row>
     <row r="205" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -13127,8 +13127,8 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="B205" s="171"/>
-      <c r="C205" s="452"/>
-      <c r="D205" s="453">
+      <c r="C205" s="457"/>
+      <c r="D205" s="458">
         <f>D227+D208-D209</f>
         <v>0</v>
       </c>
@@ -14075,28 +14075,28 @@
       <c r="M231" s="155"/>
     </row>
     <row r="232" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="457" t="s">
+      <c r="A232" s="456" t="s">
         <v>214</v>
       </c>
       <c r="B232" s="155"/>
-      <c r="C232" s="452"/>
-      <c r="D232" s="453"/>
+      <c r="C232" s="457"/>
+      <c r="D232" s="458"/>
       <c r="E232" s="157"/>
-      <c r="F232" s="454" t="s">
+      <c r="F232" s="452" t="s">
         <v>132</v>
       </c>
-      <c r="G232" s="455"/>
-      <c r="H232" s="456"/>
+      <c r="G232" s="453"/>
+      <c r="H232" s="454"/>
       <c r="I232" s="157"/>
-      <c r="J232" s="454" t="s">
+      <c r="J232" s="452" t="s">
         <v>133</v>
       </c>
-      <c r="K232" s="455"/>
-      <c r="L232" s="456"/>
+      <c r="K232" s="453"/>
+      <c r="L232" s="454"/>
       <c r="M232" s="155"/>
     </row>
     <row r="233" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="457"/>
+      <c r="A233" s="456"/>
       <c r="B233" s="199" t="s">
         <v>187</v>
       </c>
@@ -15922,6 +15922,22 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="32">
+    <mergeCell ref="C234:D256"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="F204:H204"/>
+    <mergeCell ref="J204:L204"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="C232:D232"/>
+    <mergeCell ref="F232:H232"/>
+    <mergeCell ref="J232:L232"/>
+    <mergeCell ref="C210:D228"/>
+    <mergeCell ref="C208:D209"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:H175"/>
+    <mergeCell ref="J175:L175"/>
+    <mergeCell ref="C177:D199"/>
     <mergeCell ref="C258:D280"/>
     <mergeCell ref="J149:L149"/>
     <mergeCell ref="C151:D173"/>
@@ -15938,22 +15954,6 @@
     <mergeCell ref="J100:L100"/>
     <mergeCell ref="C103:D124"/>
     <mergeCell ref="C126:D146"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:H175"/>
-    <mergeCell ref="J175:L175"/>
-    <mergeCell ref="C177:D199"/>
-    <mergeCell ref="C234:D256"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="F204:H204"/>
-    <mergeCell ref="J204:L204"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="C232:D232"/>
-    <mergeCell ref="F232:H232"/>
-    <mergeCell ref="J232:L232"/>
-    <mergeCell ref="C210:D228"/>
-    <mergeCell ref="C208:D209"/>
-    <mergeCell ref="C205:D205"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:L7 C29:L29">
     <cfRule type="cellIs" dxfId="29" priority="31" operator="between">
@@ -26261,72 +26261,72 @@
   <sheetData>
     <row r="2" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="372"/>
-      <c r="B2" s="533">
+      <c r="B2" s="522">
         <v>45895</v>
       </c>
-      <c r="C2" s="533"/>
+      <c r="C2" s="522"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="F3" s="373"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="534" t="s">
+      <c r="B4" s="523" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="534"/>
+      <c r="C4" s="523"/>
       <c r="R4" s="364"/>
     </row>
     <row r="5" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="522" t="s">
+      <c r="B5" s="524" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="523"/>
+      <c r="C5" s="525"/>
       <c r="D5" s="374"/>
-      <c r="E5" s="522" t="s">
+      <c r="E5" s="524" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="524"/>
+      <c r="F5" s="526"/>
       <c r="G5" s="374"/>
-      <c r="H5" s="522" t="s">
+      <c r="H5" s="524" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="523"/>
-      <c r="K5" s="522" t="s">
+      <c r="I5" s="525"/>
+      <c r="K5" s="524" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="523"/>
-      <c r="N5" s="522" t="s">
+      <c r="L5" s="525"/>
+      <c r="N5" s="524" t="s">
         <v>174</v>
       </c>
-      <c r="O5" s="523"/>
-      <c r="Q5" s="522" t="s">
+      <c r="O5" s="525"/>
+      <c r="Q5" s="524" t="s">
         <v>175</v>
       </c>
-      <c r="R5" s="523"/>
-      <c r="T5" s="522" t="s">
+      <c r="R5" s="525"/>
+      <c r="T5" s="524" t="s">
         <v>176</v>
       </c>
-      <c r="U5" s="523"/>
-      <c r="W5" s="522" t="s">
+      <c r="U5" s="525"/>
+      <c r="W5" s="524" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="523"/>
-      <c r="Z5" s="522" t="s">
+      <c r="X5" s="525"/>
+      <c r="Z5" s="524" t="s">
         <v>178</v>
       </c>
-      <c r="AA5" s="523"/>
-      <c r="AC5" s="522" t="s">
+      <c r="AA5" s="525"/>
+      <c r="AC5" s="524" t="s">
         <v>179</v>
       </c>
-      <c r="AD5" s="523"/>
-      <c r="AF5" s="522" t="s">
+      <c r="AD5" s="525"/>
+      <c r="AF5" s="524" t="s">
         <v>239</v>
       </c>
-      <c r="AG5" s="523"/>
-      <c r="AI5" s="522" t="s">
+      <c r="AG5" s="525"/>
+      <c r="AI5" s="524" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="523"/>
+      <c r="AJ5" s="525"/>
     </row>
     <row r="6" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="375">
@@ -26506,10 +26506,10 @@
         <v>-6.67</v>
       </c>
       <c r="D8" s="374"/>
-      <c r="E8" s="522" t="s">
+      <c r="E8" s="524" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="524"/>
+      <c r="F8" s="526"/>
       <c r="G8" s="374"/>
       <c r="H8" s="378">
         <f t="shared" si="0"/>
@@ -27328,231 +27328,231 @@
       </c>
     </row>
     <row r="18" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="522" t="s">
+      <c r="B18" s="524" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="524"/>
+      <c r="C18" s="526"/>
       <c r="D18" s="374"/>
       <c r="E18" s="401"/>
       <c r="F18" s="401"/>
       <c r="G18" s="374"/>
-      <c r="H18" s="522" t="s">
+      <c r="H18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="524"/>
-      <c r="K18" s="522" t="s">
+      <c r="I18" s="526"/>
+      <c r="K18" s="524" t="s">
         <v>185</v>
       </c>
-      <c r="L18" s="524"/>
-      <c r="N18" s="522" t="s">
+      <c r="L18" s="526"/>
+      <c r="N18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="524"/>
-      <c r="Q18" s="522" t="s">
+      <c r="O18" s="526"/>
+      <c r="Q18" s="524" t="s">
         <v>185</v>
       </c>
-      <c r="R18" s="524"/>
-      <c r="T18" s="522" t="s">
+      <c r="R18" s="526"/>
+      <c r="T18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="U18" s="524"/>
-      <c r="W18" s="522" t="s">
+      <c r="U18" s="526"/>
+      <c r="W18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="X18" s="524"/>
-      <c r="Z18" s="522" t="s">
+      <c r="X18" s="526"/>
+      <c r="Z18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AA18" s="524"/>
-      <c r="AC18" s="522" t="s">
+      <c r="AA18" s="526"/>
+      <c r="AC18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AD18" s="524"/>
-      <c r="AF18" s="522" t="s">
+      <c r="AD18" s="526"/>
+      <c r="AF18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AG18" s="524"/>
-      <c r="AI18" s="522" t="s">
+      <c r="AG18" s="526"/>
+      <c r="AI18" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AJ18" s="524"/>
+      <c r="AJ18" s="526"/>
     </row>
     <row r="19" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="525">
+      <c r="B19" s="527">
         <v>336</v>
       </c>
-      <c r="C19" s="526"/>
+      <c r="C19" s="528"/>
       <c r="D19" s="374"/>
       <c r="E19" s="374"/>
       <c r="F19" s="401"/>
       <c r="G19" s="374"/>
-      <c r="H19" s="525"/>
-      <c r="I19" s="532"/>
-      <c r="K19" s="527">
+      <c r="H19" s="527"/>
+      <c r="I19" s="529"/>
+      <c r="K19" s="530">
         <v>941</v>
       </c>
-      <c r="L19" s="528"/>
+      <c r="L19" s="531"/>
       <c r="M19" s="374"/>
-      <c r="N19" s="527">
+      <c r="N19" s="530">
         <v>417</v>
       </c>
-      <c r="O19" s="528"/>
+      <c r="O19" s="531"/>
       <c r="P19" s="374"/>
-      <c r="Q19" s="527">
+      <c r="Q19" s="530">
         <v>1610</v>
       </c>
-      <c r="R19" s="528"/>
+      <c r="R19" s="531"/>
       <c r="S19" s="374"/>
-      <c r="T19" s="525">
+      <c r="T19" s="527">
         <v>480</v>
       </c>
-      <c r="U19" s="526"/>
+      <c r="U19" s="528"/>
       <c r="V19" s="374"/>
-      <c r="W19" s="525">
+      <c r="W19" s="527">
         <v>342</v>
       </c>
-      <c r="X19" s="526"/>
+      <c r="X19" s="528"/>
       <c r="Y19" s="374"/>
-      <c r="Z19" s="525">
+      <c r="Z19" s="527">
         <v>59</v>
       </c>
-      <c r="AA19" s="526"/>
+      <c r="AA19" s="528"/>
       <c r="AB19" s="374"/>
-      <c r="AC19" s="525">
+      <c r="AC19" s="527">
         <v>143</v>
       </c>
-      <c r="AD19" s="526"/>
+      <c r="AD19" s="528"/>
       <c r="AE19" s="374"/>
-      <c r="AF19" s="525">
+      <c r="AF19" s="527">
         <v>111</v>
       </c>
-      <c r="AG19" s="526"/>
-      <c r="AI19" s="525">
+      <c r="AG19" s="528"/>
+      <c r="AI19" s="527">
         <v>371</v>
       </c>
-      <c r="AJ19" s="526"/>
+      <c r="AJ19" s="528"/>
     </row>
     <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="522" t="s">
+      <c r="B20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="524"/>
+      <c r="C20" s="526"/>
       <c r="D20" s="374"/>
       <c r="E20" s="374"/>
       <c r="F20" s="401"/>
       <c r="G20" s="374"/>
-      <c r="H20" s="522" t="s">
+      <c r="H20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="524"/>
+      <c r="I20" s="526"/>
       <c r="J20" s="374"/>
-      <c r="K20" s="522" t="s">
+      <c r="K20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="L20" s="524"/>
+      <c r="L20" s="526"/>
       <c r="M20" s="374"/>
-      <c r="N20" s="522" t="s">
+      <c r="N20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="O20" s="524"/>
+      <c r="O20" s="526"/>
       <c r="P20" s="374"/>
-      <c r="Q20" s="522" t="s">
+      <c r="Q20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="R20" s="524"/>
+      <c r="R20" s="526"/>
       <c r="S20" s="374"/>
-      <c r="T20" s="522" t="s">
+      <c r="T20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="U20" s="524"/>
+      <c r="U20" s="526"/>
       <c r="V20" s="374"/>
-      <c r="W20" s="522" t="s">
+      <c r="W20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="X20" s="524"/>
+      <c r="X20" s="526"/>
       <c r="Y20" s="374"/>
-      <c r="Z20" s="522" t="s">
+      <c r="Z20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AA20" s="524"/>
+      <c r="AA20" s="526"/>
       <c r="AB20" s="374"/>
-      <c r="AC20" s="522" t="s">
+      <c r="AC20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AD20" s="524"/>
+      <c r="AD20" s="526"/>
       <c r="AE20" s="374"/>
-      <c r="AF20" s="522" t="s">
+      <c r="AF20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AG20" s="524"/>
-      <c r="AI20" s="522" t="s">
+      <c r="AG20" s="526"/>
+      <c r="AI20" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AJ20" s="524"/>
+      <c r="AJ20" s="526"/>
     </row>
     <row r="21" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="527">
+      <c r="B21" s="530">
         <f>B19-B70</f>
         <v>175</v>
       </c>
-      <c r="C21" s="528"/>
+      <c r="C21" s="531"/>
       <c r="D21" s="374"/>
       <c r="F21" s="401"/>
       <c r="G21" s="374"/>
-      <c r="H21" s="527"/>
-      <c r="I21" s="528"/>
+      <c r="H21" s="530"/>
+      <c r="I21" s="531"/>
       <c r="J21" s="374"/>
-      <c r="K21" s="527">
+      <c r="K21" s="530">
         <f>K19-E70</f>
         <v>833</v>
       </c>
-      <c r="L21" s="528"/>
+      <c r="L21" s="531"/>
       <c r="M21" s="374"/>
-      <c r="N21" s="527">
+      <c r="N21" s="530">
         <f>N19-H70</f>
         <v>327</v>
       </c>
-      <c r="O21" s="528"/>
+      <c r="O21" s="531"/>
       <c r="P21" s="374"/>
-      <c r="Q21" s="527">
+      <c r="Q21" s="530">
         <f>Q19-K70</f>
         <v>440</v>
       </c>
-      <c r="R21" s="526"/>
+      <c r="R21" s="528"/>
       <c r="S21" s="374"/>
-      <c r="T21" s="525">
+      <c r="T21" s="527">
         <f>T19-N70</f>
         <v>-20</v>
       </c>
-      <c r="U21" s="526"/>
+      <c r="U21" s="528"/>
       <c r="V21" s="374"/>
-      <c r="W21" s="525">
+      <c r="W21" s="527">
         <f>W19-Q70</f>
         <v>47</v>
       </c>
-      <c r="X21" s="526"/>
+      <c r="X21" s="528"/>
       <c r="Y21" s="374"/>
-      <c r="Z21" s="525">
+      <c r="Z21" s="527">
         <f>Z19-T70</f>
         <v>58</v>
       </c>
-      <c r="AA21" s="526"/>
+      <c r="AA21" s="528"/>
       <c r="AB21" s="374"/>
-      <c r="AC21" s="525">
+      <c r="AC21" s="527">
         <f>AC19-W70</f>
         <v>111</v>
       </c>
-      <c r="AD21" s="526"/>
-      <c r="AF21" s="525">
+      <c r="AD21" s="528"/>
+      <c r="AF21" s="527">
         <f>AF19-Z70</f>
         <v>6</v>
       </c>
-      <c r="AG21" s="526"/>
-      <c r="AI21" s="525">
+      <c r="AG21" s="528"/>
+      <c r="AI21" s="527">
         <f>AI19-AC70</f>
         <v>281</v>
       </c>
-      <c r="AJ21" s="526"/>
+      <c r="AJ21" s="528"/>
     </row>
     <row r="22" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AZ22" s="374"/>
@@ -27568,60 +27568,60 @@
       <c r="BJ22" s="374"/>
     </row>
     <row r="23" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="522" t="s">
+      <c r="B23" s="524" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="523"/>
+      <c r="C23" s="525"/>
       <c r="D23" s="374"/>
-      <c r="E23" s="522" t="s">
+      <c r="E23" s="524" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="524"/>
+      <c r="F23" s="526"/>
       <c r="G23" s="374"/>
-      <c r="H23" s="522" t="s">
+      <c r="H23" s="524" t="s">
         <v>189</v>
       </c>
-      <c r="I23" s="523"/>
+      <c r="I23" s="525"/>
       <c r="J23" s="374"/>
-      <c r="K23" s="522" t="s">
+      <c r="K23" s="524" t="s">
         <v>190</v>
       </c>
-      <c r="L23" s="523"/>
+      <c r="L23" s="525"/>
       <c r="M23" s="374"/>
-      <c r="N23" s="522" t="s">
+      <c r="N23" s="524" t="s">
         <v>191</v>
       </c>
-      <c r="O23" s="523"/>
+      <c r="O23" s="525"/>
       <c r="P23" s="374"/>
-      <c r="Q23" s="522" t="s">
+      <c r="Q23" s="524" t="s">
         <v>192</v>
       </c>
-      <c r="R23" s="523"/>
+      <c r="R23" s="525"/>
       <c r="S23" s="374"/>
-      <c r="T23" s="522" t="s">
+      <c r="T23" s="524" t="s">
         <v>193</v>
       </c>
-      <c r="U23" s="523"/>
+      <c r="U23" s="525"/>
       <c r="V23" s="374"/>
-      <c r="W23" s="522" t="s">
+      <c r="W23" s="524" t="s">
         <v>194</v>
       </c>
-      <c r="X23" s="523"/>
+      <c r="X23" s="525"/>
       <c r="Y23" s="374"/>
-      <c r="Z23" s="522" t="s">
+      <c r="Z23" s="524" t="s">
         <v>195</v>
       </c>
-      <c r="AA23" s="523"/>
+      <c r="AA23" s="525"/>
       <c r="AB23" s="374"/>
-      <c r="AC23" s="522" t="s">
+      <c r="AC23" s="524" t="s">
         <v>196</v>
       </c>
-      <c r="AD23" s="523"/>
+      <c r="AD23" s="525"/>
       <c r="AE23" s="374"/>
-      <c r="AF23" s="522" t="s">
+      <c r="AF23" s="524" t="s">
         <v>197</v>
       </c>
-      <c r="AG23" s="523"/>
+      <c r="AG23" s="525"/>
       <c r="AZ23" s="374"/>
       <c r="BA23" s="374"/>
       <c r="BB23" s="374"/>
@@ -28920,219 +28920,219 @@
       <c r="BJ35" s="374"/>
     </row>
     <row r="36" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="522" t="s">
+      <c r="B36" s="524" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="524"/>
+      <c r="C36" s="526"/>
       <c r="D36" s="374"/>
-      <c r="E36" s="522" t="s">
+      <c r="E36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="524"/>
+      <c r="F36" s="526"/>
       <c r="G36" s="374"/>
-      <c r="H36" s="522" t="s">
+      <c r="H36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="524"/>
+      <c r="I36" s="526"/>
       <c r="J36" s="374"/>
-      <c r="K36" s="522" t="s">
+      <c r="K36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="L36" s="524"/>
+      <c r="L36" s="526"/>
       <c r="M36" s="374"/>
-      <c r="N36" s="522" t="s">
+      <c r="N36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="O36" s="524"/>
+      <c r="O36" s="526"/>
       <c r="P36" s="374"/>
-      <c r="Q36" s="522" t="s">
+      <c r="Q36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="524"/>
+      <c r="R36" s="526"/>
       <c r="S36" s="374"/>
-      <c r="T36" s="522" t="s">
+      <c r="T36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="U36" s="524"/>
+      <c r="U36" s="526"/>
       <c r="V36" s="374"/>
-      <c r="W36" s="522" t="s">
+      <c r="W36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="X36" s="524"/>
+      <c r="X36" s="526"/>
       <c r="Y36" s="374"/>
-      <c r="Z36" s="522" t="s">
+      <c r="Z36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AA36" s="524"/>
+      <c r="AA36" s="526"/>
       <c r="AB36" s="374"/>
-      <c r="AC36" s="522" t="s">
+      <c r="AC36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AD36" s="524"/>
+      <c r="AD36" s="526"/>
       <c r="AE36" s="374"/>
-      <c r="AF36" s="522" t="s">
+      <c r="AF36" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AG36" s="524"/>
+      <c r="AG36" s="526"/>
     </row>
     <row r="37" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="527">
+      <c r="B37" s="530">
         <v>1150</v>
       </c>
-      <c r="C37" s="528"/>
+      <c r="C37" s="531"/>
       <c r="D37" s="374"/>
-      <c r="E37" s="527">
+      <c r="E37" s="530">
         <v>764</v>
       </c>
-      <c r="F37" s="528"/>
+      <c r="F37" s="531"/>
       <c r="G37" s="374"/>
-      <c r="H37" s="527">
+      <c r="H37" s="530">
         <v>115</v>
       </c>
-      <c r="I37" s="528"/>
+      <c r="I37" s="531"/>
       <c r="J37" s="374"/>
-      <c r="K37" s="525">
+      <c r="K37" s="527">
         <v>96</v>
       </c>
-      <c r="L37" s="526"/>
+      <c r="L37" s="528"/>
       <c r="M37" s="374"/>
-      <c r="N37" s="525"/>
-      <c r="O37" s="526"/>
+      <c r="N37" s="527"/>
+      <c r="O37" s="528"/>
       <c r="P37" s="374"/>
-      <c r="Q37" s="525">
+      <c r="Q37" s="527">
         <v>35</v>
       </c>
-      <c r="R37" s="526"/>
+      <c r="R37" s="528"/>
       <c r="S37" s="374"/>
-      <c r="T37" s="525">
+      <c r="T37" s="527">
         <v>0</v>
       </c>
-      <c r="U37" s="526"/>
+      <c r="U37" s="528"/>
       <c r="V37" s="374"/>
-      <c r="W37" s="525"/>
-      <c r="X37" s="526"/>
+      <c r="W37" s="527"/>
+      <c r="X37" s="528"/>
       <c r="Y37" s="374"/>
-      <c r="Z37" s="525">
+      <c r="Z37" s="527">
         <v>50</v>
       </c>
-      <c r="AA37" s="526"/>
+      <c r="AA37" s="528"/>
       <c r="AB37" s="374"/>
-      <c r="AC37" s="525"/>
-      <c r="AD37" s="526"/>
+      <c r="AC37" s="527"/>
+      <c r="AD37" s="528"/>
       <c r="AE37" s="374"/>
-      <c r="AF37" s="525"/>
-      <c r="AG37" s="526"/>
+      <c r="AF37" s="527"/>
+      <c r="AG37" s="528"/>
     </row>
     <row r="38" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="522" t="s">
+      <c r="B38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="524"/>
+      <c r="C38" s="526"/>
       <c r="D38" s="374"/>
-      <c r="E38" s="522" t="s">
+      <c r="E38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="524"/>
+      <c r="F38" s="526"/>
       <c r="G38" s="374"/>
-      <c r="H38" s="522" t="s">
+      <c r="H38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="524"/>
+      <c r="I38" s="526"/>
       <c r="J38" s="374"/>
-      <c r="K38" s="522" t="s">
+      <c r="K38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="L38" s="524"/>
+      <c r="L38" s="526"/>
       <c r="M38" s="374"/>
-      <c r="N38" s="522" t="s">
+      <c r="N38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="O38" s="524"/>
+      <c r="O38" s="526"/>
       <c r="P38" s="374"/>
-      <c r="Q38" s="522" t="s">
+      <c r="Q38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="R38" s="524"/>
+      <c r="R38" s="526"/>
       <c r="S38" s="374"/>
-      <c r="T38" s="522" t="s">
+      <c r="T38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="U38" s="524"/>
+      <c r="U38" s="526"/>
       <c r="V38" s="374"/>
-      <c r="W38" s="522" t="s">
+      <c r="W38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="X38" s="524"/>
+      <c r="X38" s="526"/>
       <c r="Y38" s="374"/>
-      <c r="Z38" s="522" t="s">
+      <c r="Z38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AA38" s="524"/>
+      <c r="AA38" s="526"/>
       <c r="AB38" s="374"/>
-      <c r="AC38" s="522" t="s">
+      <c r="AC38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AD38" s="524"/>
+      <c r="AD38" s="526"/>
       <c r="AE38" s="374"/>
-      <c r="AF38" s="522" t="s">
+      <c r="AF38" s="524" t="s">
         <v>186</v>
       </c>
-      <c r="AG38" s="524"/>
+      <c r="AG38" s="526"/>
     </row>
     <row r="39" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="527">
+      <c r="B39" s="530">
         <f>B37-B62</f>
         <v>436</v>
       </c>
-      <c r="C39" s="528"/>
+      <c r="C39" s="531"/>
       <c r="D39" s="374"/>
-      <c r="E39" s="527">
+      <c r="E39" s="530">
         <f>E37-E62</f>
         <v>379</v>
       </c>
-      <c r="F39" s="528"/>
+      <c r="F39" s="531"/>
       <c r="G39" s="374"/>
-      <c r="H39" s="527">
+      <c r="H39" s="530">
         <f>H37-H62</f>
         <v>115</v>
       </c>
-      <c r="I39" s="528"/>
+      <c r="I39" s="531"/>
       <c r="J39" s="374"/>
-      <c r="K39" s="525">
+      <c r="K39" s="527">
         <f>K37-K62</f>
         <v>57</v>
       </c>
-      <c r="L39" s="526"/>
+      <c r="L39" s="528"/>
       <c r="M39" s="374"/>
-      <c r="N39" s="525"/>
-      <c r="O39" s="526"/>
+      <c r="N39" s="527"/>
+      <c r="O39" s="528"/>
       <c r="P39" s="374"/>
-      <c r="Q39" s="525">
+      <c r="Q39" s="527">
         <f>Q37-Q62</f>
         <v>-167</v>
       </c>
-      <c r="R39" s="526"/>
+      <c r="R39" s="528"/>
       <c r="S39" s="374"/>
-      <c r="T39" s="525">
+      <c r="T39" s="527">
         <f>T37-T62</f>
         <v>-187</v>
       </c>
-      <c r="U39" s="526"/>
+      <c r="U39" s="528"/>
       <c r="V39" s="374"/>
-      <c r="W39" s="525"/>
-      <c r="X39" s="526"/>
+      <c r="W39" s="527"/>
+      <c r="X39" s="528"/>
       <c r="Y39" s="374"/>
-      <c r="Z39" s="525">
+      <c r="Z39" s="527">
         <f>Z37-Z62</f>
         <v>0</v>
       </c>
-      <c r="AA39" s="526"/>
+      <c r="AA39" s="528"/>
       <c r="AB39" s="374"/>
-      <c r="AC39" s="525"/>
-      <c r="AD39" s="526"/>
+      <c r="AC39" s="527"/>
+      <c r="AD39" s="528"/>
       <c r="AE39" s="374"/>
-      <c r="AF39" s="525"/>
-      <c r="AG39" s="526"/>
+      <c r="AF39" s="527"/>
+      <c r="AG39" s="528"/>
     </row>
     <row r="40" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B40" s="411"/>
@@ -29169,10 +29169,10 @@
       <c r="AG40" s="374"/>
     </row>
     <row r="41" spans="2:62" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="531" t="s">
+      <c r="B41" s="532" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="531"/>
+      <c r="C41" s="532"/>
       <c r="D41" s="374"/>
       <c r="E41" s="374"/>
       <c r="F41" s="374"/>
@@ -29204,59 +29204,59 @@
       <c r="AG41" s="374"/>
     </row>
     <row r="42" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="522" t="s">
+      <c r="B42" s="524" t="s">
         <v>170</v>
       </c>
-      <c r="C42" s="523"/>
+      <c r="C42" s="525"/>
       <c r="D42" s="374"/>
-      <c r="E42" s="522" t="s">
+      <c r="E42" s="524" t="s">
         <v>173</v>
       </c>
-      <c r="F42" s="523"/>
+      <c r="F42" s="525"/>
       <c r="G42" s="374"/>
-      <c r="H42" s="522" t="s">
+      <c r="H42" s="524" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="523"/>
+      <c r="I42" s="525"/>
       <c r="J42" s="374"/>
-      <c r="K42" s="522" t="s">
+      <c r="K42" s="524" t="s">
         <v>175</v>
       </c>
-      <c r="L42" s="523"/>
+      <c r="L42" s="525"/>
       <c r="M42" s="374"/>
-      <c r="N42" s="522" t="s">
+      <c r="N42" s="524" t="s">
         <v>176</v>
       </c>
-      <c r="O42" s="523"/>
+      <c r="O42" s="525"/>
       <c r="P42" s="374"/>
-      <c r="Q42" s="522" t="s">
+      <c r="Q42" s="524" t="s">
         <v>177</v>
       </c>
-      <c r="R42" s="523"/>
-      <c r="T42" s="522" t="s">
+      <c r="R42" s="525"/>
+      <c r="T42" s="524" t="s">
         <v>178</v>
       </c>
-      <c r="U42" s="523"/>
+      <c r="U42" s="525"/>
       <c r="V42" s="374"/>
-      <c r="W42" s="522" t="s">
+      <c r="W42" s="524" t="s">
         <v>179</v>
       </c>
-      <c r="X42" s="523"/>
+      <c r="X42" s="525"/>
       <c r="Y42" s="374"/>
-      <c r="Z42" s="529" t="s">
+      <c r="Z42" s="533" t="s">
         <v>239</v>
       </c>
-      <c r="AA42" s="530"/>
+      <c r="AA42" s="534"/>
       <c r="AB42" s="374"/>
-      <c r="AC42" s="522" t="s">
+      <c r="AC42" s="524" t="s">
         <v>180</v>
       </c>
-      <c r="AD42" s="523"/>
+      <c r="AD42" s="525"/>
       <c r="AE42" s="374"/>
-      <c r="AF42" s="522" t="s">
+      <c r="AF42" s="524" t="s">
         <v>197</v>
       </c>
-      <c r="AG42" s="523"/>
+      <c r="AG42" s="525"/>
     </row>
     <row r="43" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="378">
@@ -29798,50 +29798,50 @@
       </c>
     </row>
     <row r="49" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="522" t="s">
+      <c r="B49" s="524" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="524"/>
+      <c r="C49" s="526"/>
       <c r="D49" s="444"/>
-      <c r="E49" s="522" t="s">
+      <c r="E49" s="524" t="s">
         <v>185</v>
       </c>
-      <c r="F49" s="524"/>
+      <c r="F49" s="526"/>
       <c r="G49" s="374"/>
-      <c r="H49" s="522" t="s">
+      <c r="H49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="I49" s="524"/>
+      <c r="I49" s="526"/>
       <c r="J49" s="374"/>
-      <c r="K49" s="522" t="s">
+      <c r="K49" s="524" t="s">
         <v>185</v>
       </c>
-      <c r="L49" s="524"/>
+      <c r="L49" s="526"/>
       <c r="M49" s="444"/>
-      <c r="N49" s="522" t="s">
+      <c r="N49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="O49" s="524"/>
+      <c r="O49" s="526"/>
       <c r="P49" s="444"/>
-      <c r="Q49" s="522" t="s">
+      <c r="Q49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="R49" s="524"/>
+      <c r="R49" s="526"/>
       <c r="S49" s="155"/>
-      <c r="T49" s="522" t="s">
+      <c r="T49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="U49" s="524"/>
+      <c r="U49" s="526"/>
       <c r="V49" s="444"/>
-      <c r="W49" s="522" t="s">
+      <c r="W49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="X49" s="524"/>
+      <c r="X49" s="526"/>
       <c r="Y49" s="444"/>
-      <c r="Z49" s="522" t="s">
+      <c r="Z49" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AA49" s="524"/>
+      <c r="AA49" s="526"/>
       <c r="AB49" s="444"/>
       <c r="AC49" s="446" t="str">
         <f>E33</f>
@@ -29861,32 +29861,32 @@
       </c>
     </row>
     <row r="50" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="525"/>
-      <c r="C50" s="526"/>
+      <c r="B50" s="527"/>
+      <c r="C50" s="528"/>
       <c r="D50" s="364"/>
-      <c r="E50" s="525"/>
-      <c r="F50" s="526"/>
+      <c r="E50" s="527"/>
+      <c r="F50" s="528"/>
       <c r="G50" s="374"/>
-      <c r="H50" s="527"/>
-      <c r="I50" s="528"/>
+      <c r="H50" s="530"/>
+      <c r="I50" s="531"/>
       <c r="J50" s="374"/>
-      <c r="K50" s="525"/>
-      <c r="L50" s="526"/>
+      <c r="K50" s="527"/>
+      <c r="L50" s="528"/>
       <c r="M50" s="374"/>
-      <c r="N50" s="525"/>
-      <c r="O50" s="526"/>
+      <c r="N50" s="527"/>
+      <c r="O50" s="528"/>
       <c r="P50" s="374"/>
-      <c r="Q50" s="525"/>
-      <c r="R50" s="526"/>
+      <c r="Q50" s="527"/>
+      <c r="R50" s="528"/>
       <c r="S50" s="374"/>
-      <c r="T50" s="525"/>
-      <c r="U50" s="526"/>
+      <c r="T50" s="527"/>
+      <c r="U50" s="528"/>
       <c r="V50" s="374"/>
-      <c r="W50" s="525"/>
-      <c r="X50" s="526"/>
+      <c r="W50" s="527"/>
+      <c r="X50" s="528"/>
       <c r="Y50" s="374"/>
-      <c r="Z50" s="525"/>
-      <c r="AA50" s="526"/>
+      <c r="Z50" s="527"/>
+      <c r="AA50" s="528"/>
       <c r="AB50" s="374"/>
       <c r="AC50" s="446" t="str">
         <f t="shared" ref="AC50:AC51" si="34">E34</f>
@@ -29971,15 +29971,15 @@
       <c r="Z52" s="412"/>
       <c r="AA52" s="412"/>
       <c r="AB52" s="412"/>
-      <c r="AC52" s="522" t="s">
+      <c r="AC52" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AD52" s="524"/>
+      <c r="AD52" s="526"/>
       <c r="AE52" s="412"/>
-      <c r="AF52" s="522" t="s">
+      <c r="AF52" s="524" t="s">
         <v>184</v>
       </c>
-      <c r="AG52" s="524"/>
+      <c r="AG52" s="526"/>
     </row>
     <row r="53" spans="2:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="412"/>
@@ -30008,8 +30008,8 @@
       <c r="Z53" s="412"/>
       <c r="AA53" s="412"/>
       <c r="AB53" s="374"/>
-      <c r="AC53" s="525"/>
-      <c r="AD53" s="526"/>
+      <c r="AC53" s="527"/>
+      <c r="AD53" s="528"/>
       <c r="AE53" s="374"/>
       <c r="AF53" s="438"/>
       <c r="AG53" s="439"/>
@@ -30114,157 +30114,157 @@
       </c>
     </row>
     <row r="60" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="522" t="s">
+      <c r="B60" s="524" t="s">
         <v>209</v>
       </c>
-      <c r="C60" s="523"/>
+      <c r="C60" s="525"/>
       <c r="D60" s="374"/>
-      <c r="E60" s="522" t="s">
+      <c r="E60" s="524" t="s">
         <v>210</v>
       </c>
-      <c r="F60" s="524"/>
+      <c r="F60" s="526"/>
       <c r="G60" s="374"/>
-      <c r="H60" s="522" t="s">
+      <c r="H60" s="524" t="s">
         <v>211</v>
       </c>
-      <c r="I60" s="523"/>
+      <c r="I60" s="525"/>
       <c r="J60" s="374"/>
-      <c r="K60" s="522" t="s">
+      <c r="K60" s="524" t="s">
         <v>190</v>
       </c>
-      <c r="L60" s="523"/>
+      <c r="L60" s="525"/>
       <c r="M60" s="374"/>
-      <c r="N60" s="522" t="s">
+      <c r="N60" s="524" t="s">
         <v>191</v>
       </c>
-      <c r="O60" s="523"/>
+      <c r="O60" s="525"/>
       <c r="P60" s="374"/>
-      <c r="Q60" s="522" t="s">
+      <c r="Q60" s="524" t="s">
         <v>192</v>
       </c>
-      <c r="R60" s="523"/>
+      <c r="R60" s="525"/>
       <c r="S60" s="374"/>
-      <c r="T60" s="522" t="s">
+      <c r="T60" s="524" t="s">
         <v>193</v>
       </c>
-      <c r="U60" s="523"/>
+      <c r="U60" s="525"/>
       <c r="V60" s="374"/>
-      <c r="W60" s="522" t="s">
+      <c r="W60" s="524" t="s">
         <v>194</v>
       </c>
-      <c r="X60" s="523"/>
+      <c r="X60" s="525"/>
       <c r="Y60" s="374"/>
-      <c r="Z60" s="522" t="s">
+      <c r="Z60" s="524" t="s">
         <v>195</v>
       </c>
-      <c r="AA60" s="523"/>
+      <c r="AA60" s="525"/>
       <c r="AB60" s="374"/>
-      <c r="AC60" s="522" t="s">
+      <c r="AC60" s="524" t="s">
         <v>196</v>
       </c>
-      <c r="AD60" s="523"/>
+      <c r="AD60" s="525"/>
       <c r="AF60" s="374">
         <v>66.680000000000007</v>
       </c>
     </row>
     <row r="61" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="522" t="s">
+      <c r="B61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="C61" s="524"/>
+      <c r="C61" s="526"/>
       <c r="D61" s="374"/>
-      <c r="E61" s="522" t="s">
+      <c r="E61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="524"/>
+      <c r="F61" s="526"/>
       <c r="G61" s="374"/>
-      <c r="H61" s="522" t="s">
+      <c r="H61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="I61" s="524"/>
+      <c r="I61" s="526"/>
       <c r="J61" s="374"/>
-      <c r="K61" s="522" t="s">
+      <c r="K61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="L61" s="524"/>
+      <c r="L61" s="526"/>
       <c r="M61" s="374"/>
-      <c r="N61" s="522" t="s">
+      <c r="N61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="O61" s="524"/>
+      <c r="O61" s="526"/>
       <c r="P61" s="374"/>
-      <c r="Q61" s="522" t="s">
+      <c r="Q61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="R61" s="524"/>
+      <c r="R61" s="526"/>
       <c r="S61" s="374"/>
-      <c r="T61" s="522" t="s">
+      <c r="T61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="U61" s="524"/>
+      <c r="U61" s="526"/>
       <c r="V61" s="374"/>
-      <c r="W61" s="522" t="s">
+      <c r="W61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="X61" s="524"/>
+      <c r="X61" s="526"/>
       <c r="Y61" s="374"/>
-      <c r="Z61" s="522" t="s">
+      <c r="Z61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="AA61" s="524"/>
+      <c r="AA61" s="526"/>
       <c r="AB61" s="374"/>
-      <c r="AC61" s="522" t="s">
+      <c r="AC61" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="AD61" s="524"/>
+      <c r="AD61" s="526"/>
       <c r="AF61" s="364">
         <v>66.260000000000005</v>
       </c>
     </row>
     <row r="62" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="527">
+      <c r="B62" s="530">
         <v>714</v>
       </c>
-      <c r="C62" s="528"/>
+      <c r="C62" s="531"/>
       <c r="D62" s="374"/>
-      <c r="E62" s="527">
+      <c r="E62" s="530">
         <v>385</v>
       </c>
-      <c r="F62" s="528"/>
+      <c r="F62" s="531"/>
       <c r="G62" s="374"/>
-      <c r="H62" s="527">
+      <c r="H62" s="530">
         <v>0</v>
       </c>
-      <c r="I62" s="528"/>
+      <c r="I62" s="531"/>
       <c r="J62" s="374"/>
-      <c r="K62" s="525">
+      <c r="K62" s="527">
         <v>39</v>
       </c>
-      <c r="L62" s="526"/>
+      <c r="L62" s="528"/>
       <c r="M62" s="374"/>
-      <c r="N62" s="525"/>
-      <c r="O62" s="526"/>
+      <c r="N62" s="527"/>
+      <c r="O62" s="528"/>
       <c r="P62" s="374"/>
-      <c r="Q62" s="525">
+      <c r="Q62" s="527">
         <v>202</v>
       </c>
-      <c r="R62" s="526"/>
+      <c r="R62" s="528"/>
       <c r="S62" s="374"/>
-      <c r="T62" s="525">
+      <c r="T62" s="527">
         <v>187</v>
       </c>
-      <c r="U62" s="526"/>
+      <c r="U62" s="528"/>
       <c r="V62" s="374"/>
-      <c r="W62" s="525"/>
-      <c r="X62" s="526"/>
+      <c r="W62" s="527"/>
+      <c r="X62" s="528"/>
       <c r="Y62" s="374"/>
-      <c r="Z62" s="525">
+      <c r="Z62" s="527">
         <v>50</v>
       </c>
-      <c r="AA62" s="526"/>
+      <c r="AA62" s="528"/>
       <c r="AB62" s="374"/>
-      <c r="AC62" s="525"/>
-      <c r="AD62" s="526"/>
+      <c r="AC62" s="527"/>
+      <c r="AD62" s="528"/>
       <c r="AE62" s="374"/>
       <c r="AF62" s="374">
         <v>66</v>
@@ -30362,144 +30362,327 @@
       </c>
     </row>
     <row r="68" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="522" t="s">
+      <c r="B68" s="524" t="s">
         <v>170</v>
       </c>
-      <c r="C68" s="523"/>
-      <c r="E68" s="522" t="s">
+      <c r="C68" s="525"/>
+      <c r="E68" s="524" t="s">
         <v>173</v>
       </c>
-      <c r="F68" s="523"/>
-      <c r="H68" s="522" t="s">
+      <c r="F68" s="525"/>
+      <c r="H68" s="524" t="s">
         <v>174</v>
       </c>
-      <c r="I68" s="523"/>
-      <c r="K68" s="522" t="s">
+      <c r="I68" s="525"/>
+      <c r="K68" s="524" t="s">
         <v>175</v>
       </c>
-      <c r="L68" s="523"/>
-      <c r="N68" s="522" t="s">
+      <c r="L68" s="525"/>
+      <c r="N68" s="524" t="s">
         <v>176</v>
       </c>
-      <c r="O68" s="523"/>
-      <c r="Q68" s="522" t="s">
+      <c r="O68" s="525"/>
+      <c r="Q68" s="524" t="s">
         <v>177</v>
       </c>
-      <c r="R68" s="523"/>
-      <c r="T68" s="522" t="s">
+      <c r="R68" s="525"/>
+      <c r="T68" s="524" t="s">
         <v>178</v>
       </c>
-      <c r="U68" s="523"/>
-      <c r="W68" s="522" t="s">
+      <c r="U68" s="525"/>
+      <c r="W68" s="524" t="s">
         <v>179</v>
       </c>
-      <c r="X68" s="523"/>
-      <c r="Z68" s="522" t="s">
+      <c r="X68" s="525"/>
+      <c r="Z68" s="524" t="s">
         <v>239</v>
       </c>
-      <c r="AA68" s="523"/>
-      <c r="AC68" s="522" t="s">
+      <c r="AA68" s="525"/>
+      <c r="AC68" s="524" t="s">
         <v>180</v>
       </c>
-      <c r="AD68" s="523"/>
+      <c r="AD68" s="525"/>
     </row>
     <row r="69" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="522" t="s">
+      <c r="B69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="C69" s="523"/>
-      <c r="E69" s="522" t="s">
+      <c r="C69" s="525"/>
+      <c r="E69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="F69" s="524"/>
-      <c r="H69" s="522" t="s">
+      <c r="F69" s="526"/>
+      <c r="H69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="I69" s="524"/>
-      <c r="K69" s="522" t="s">
+      <c r="I69" s="526"/>
+      <c r="K69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="L69" s="524"/>
-      <c r="N69" s="522" t="s">
+      <c r="L69" s="526"/>
+      <c r="N69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="O69" s="524"/>
-      <c r="Q69" s="522" t="s">
+      <c r="O69" s="526"/>
+      <c r="Q69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="R69" s="524"/>
-      <c r="T69" s="522" t="s">
+      <c r="R69" s="526"/>
+      <c r="T69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="U69" s="524"/>
-      <c r="W69" s="522" t="s">
+      <c r="U69" s="526"/>
+      <c r="W69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="X69" s="524"/>
-      <c r="Z69" s="522" t="s">
+      <c r="X69" s="526"/>
+      <c r="Z69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="AA69" s="524"/>
-      <c r="AC69" s="522" t="s">
+      <c r="AA69" s="526"/>
+      <c r="AC69" s="524" t="s">
         <v>212</v>
       </c>
-      <c r="AD69" s="524"/>
+      <c r="AD69" s="526"/>
     </row>
     <row r="70" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="525">
+      <c r="B70" s="527">
         <v>161</v>
       </c>
-      <c r="C70" s="526"/>
+      <c r="C70" s="528"/>
       <c r="D70" s="374"/>
-      <c r="E70" s="527">
+      <c r="E70" s="530">
         <v>108</v>
       </c>
-      <c r="F70" s="528"/>
+      <c r="F70" s="531"/>
       <c r="G70" s="374"/>
-      <c r="H70" s="527">
+      <c r="H70" s="530">
         <v>90</v>
       </c>
-      <c r="I70" s="528"/>
+      <c r="I70" s="531"/>
       <c r="J70" s="374"/>
-      <c r="K70" s="527">
+      <c r="K70" s="530">
         <v>1170</v>
       </c>
-      <c r="L70" s="528"/>
+      <c r="L70" s="531"/>
       <c r="M70" s="374"/>
-      <c r="N70" s="525">
+      <c r="N70" s="527">
         <v>500</v>
       </c>
-      <c r="O70" s="526"/>
+      <c r="O70" s="528"/>
       <c r="P70" s="374"/>
-      <c r="Q70" s="525">
+      <c r="Q70" s="527">
         <v>295</v>
       </c>
-      <c r="R70" s="526"/>
+      <c r="R70" s="528"/>
       <c r="S70" s="374"/>
-      <c r="T70" s="525">
+      <c r="T70" s="527">
         <v>1</v>
       </c>
-      <c r="U70" s="526"/>
+      <c r="U70" s="528"/>
       <c r="V70" s="374"/>
-      <c r="W70" s="525">
+      <c r="W70" s="527">
         <v>32</v>
       </c>
-      <c r="X70" s="526"/>
+      <c r="X70" s="528"/>
       <c r="Y70" s="374"/>
-      <c r="Z70" s="525">
+      <c r="Z70" s="527">
         <v>105</v>
       </c>
-      <c r="AA70" s="526"/>
-      <c r="AC70" s="525">
+      <c r="AA70" s="528"/>
+      <c r="AC70" s="527">
         <v>90</v>
       </c>
-      <c r="AD70" s="526"/>
+      <c r="AD70" s="528"/>
     </row>
     <row r="86" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M86" s="364"/>
     </row>
   </sheetData>
   <mergeCells count="207">
+    <mergeCell ref="AC68:AD68"/>
+    <mergeCell ref="AC69:AD69"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="AI20:AJ20"/>
+    <mergeCell ref="AI21:AJ21"/>
+    <mergeCell ref="AF42:AG42"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="Z50:AA50"/>
+    <mergeCell ref="AF52:AG52"/>
+    <mergeCell ref="AC61:AD61"/>
+    <mergeCell ref="AC62:AD62"/>
+    <mergeCell ref="AC52:AD52"/>
+    <mergeCell ref="AC53:AD53"/>
+    <mergeCell ref="AC60:AD60"/>
+    <mergeCell ref="Z42:AA42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="AC70:AD70"/>
+    <mergeCell ref="W69:X69"/>
+    <mergeCell ref="Z69:AA69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="Q68:R68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="W68:X68"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="Q62:R62"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="W62:X62"/>
+    <mergeCell ref="Z62:AA62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="W61:X61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="W60:X60"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AF39:AG39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AF38:AG38"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AF36:AG36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="AF21:AG21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AF23:AG23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AF20:AG20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
@@ -30524,189 +30707,6 @@
     <mergeCell ref="AC5:AD5"/>
     <mergeCell ref="AC18:AD18"/>
     <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AF20:AG20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="AF21:AG21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="AF23:AG23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="AC36:AD36"/>
-    <mergeCell ref="AF36:AG36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AF38:AG38"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="AF37:AG37"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AF39:AG39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="W60:X60"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="Q61:R61"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="W61:X61"/>
-    <mergeCell ref="Z61:AA61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="Q62:R62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="W62:X62"/>
-    <mergeCell ref="Z62:AA62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="Q68:R68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="W68:X68"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="Q69:R69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="Z70:AA70"/>
-    <mergeCell ref="AC70:AD70"/>
-    <mergeCell ref="W69:X69"/>
-    <mergeCell ref="Z69:AA69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="W70:X70"/>
-    <mergeCell ref="AC68:AD68"/>
-    <mergeCell ref="AC69:AD69"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="AI20:AJ20"/>
-    <mergeCell ref="AI21:AJ21"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="Z50:AA50"/>
-    <mergeCell ref="AF52:AG52"/>
-    <mergeCell ref="AC61:AD61"/>
-    <mergeCell ref="AC62:AD62"/>
-    <mergeCell ref="AC52:AD52"/>
-    <mergeCell ref="AC53:AD53"/>
-    <mergeCell ref="AC60:AD60"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AC42:AD42"/>
   </mergeCells>
   <conditionalFormatting sqref="F9">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
@@ -32477,74 +32477,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="513"/>
-      <c r="G3" s="512" t="s">
+      <c r="F3" s="503"/>
+      <c r="G3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="513"/>
-      <c r="I3" s="512" t="s">
+      <c r="H3" s="503"/>
+      <c r="I3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="513"/>
-      <c r="P3" s="512" t="s">
+      <c r="J3" s="503"/>
+      <c r="P3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="513"/>
-      <c r="R3" s="512" t="s">
+      <c r="Q3" s="503"/>
+      <c r="R3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="513"/>
-      <c r="T3" s="512" t="s">
+      <c r="S3" s="503"/>
+      <c r="T3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="513"/>
+      <c r="U3" s="503"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="510" t="s">
+      <c r="A4" s="504" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="511"/>
-      <c r="C4" s="511"/>
-      <c r="D4" s="511"/>
-      <c r="E4" s="509">
+      <c r="B4" s="505"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="506">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="503"/>
-      <c r="G4" s="502">
+      <c r="F4" s="507"/>
+      <c r="G4" s="508">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="503"/>
-      <c r="I4" s="502">
+      <c r="H4" s="507"/>
+      <c r="I4" s="508">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="503"/>
-      <c r="L4" s="510" t="s">
+      <c r="J4" s="507"/>
+      <c r="L4" s="504" t="s">
         <v>216</v>
       </c>
-      <c r="M4" s="511"/>
-      <c r="N4" s="511"/>
-      <c r="O4" s="511"/>
-      <c r="P4" s="509">
+      <c r="M4" s="505"/>
+      <c r="N4" s="505"/>
+      <c r="O4" s="505"/>
+      <c r="P4" s="506">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="503"/>
-      <c r="R4" s="502">
+      <c r="Q4" s="507"/>
+      <c r="R4" s="508">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="503"/>
-      <c r="T4" s="502">
+      <c r="S4" s="507"/>
+      <c r="T4" s="508">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="503"/>
+      <c r="U4" s="507"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -33827,56 +33827,45 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="504">
+      <c r="E25" s="509">
         <f ca="1">'Loading Arrival'!G9</f>
         <v>45918</v>
       </c>
-      <c r="F25" s="505"/>
-      <c r="G25" s="506">
+      <c r="F25" s="510"/>
+      <c r="G25" s="511">
         <f ca="1">'Loading Arrival'!H9</f>
         <v>45932</v>
       </c>
-      <c r="H25" s="507"/>
-      <c r="I25" s="508">
+      <c r="H25" s="512"/>
+      <c r="I25" s="513">
         <f ca="1">'Loading Arrival'!I9</f>
         <v>45946</v>
       </c>
-      <c r="J25" s="505"/>
+      <c r="J25" s="510"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="504">
+      <c r="P25" s="509">
         <f ca="1">E25</f>
         <v>45918</v>
       </c>
-      <c r="Q25" s="505"/>
-      <c r="R25" s="506">
+      <c r="Q25" s="510"/>
+      <c r="R25" s="511">
         <f ca="1">G25</f>
         <v>45932</v>
       </c>
-      <c r="S25" s="507"/>
-      <c r="T25" s="508">
+      <c r="S25" s="512"/>
+      <c r="T25" s="513">
         <f ca="1">I25</f>
         <v>45946</v>
       </c>
-      <c r="U25" s="505"/>
+      <c r="U25" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -33886,6 +33875,17 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33918,38 +33918,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="513"/>
-      <c r="G3" s="512" t="s">
+      <c r="F3" s="503"/>
+      <c r="G3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="513"/>
-      <c r="N3" s="512" t="s">
+      <c r="H3" s="503"/>
+      <c r="N3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="513"/>
-      <c r="P3" s="512" t="s">
+      <c r="O3" s="503"/>
+      <c r="P3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="513"/>
-      <c r="R3" s="512" t="s">
+      <c r="Q3" s="503"/>
+      <c r="R3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="513"/>
-      <c r="Y3" s="512" t="s">
+      <c r="S3" s="503"/>
+      <c r="Y3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="513"/>
-      <c r="AA3" s="512" t="s">
+      <c r="Z3" s="503"/>
+      <c r="AA3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="AB3" s="513"/>
-      <c r="AC3" s="512" t="s">
+      <c r="AB3" s="503"/>
+      <c r="AC3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="513"/>
+      <c r="AD3" s="503"/>
     </row>
     <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="341" t="s">
@@ -35898,61 +35898,69 @@
       <c r="B27" s="108"/>
       <c r="C27" s="105"/>
       <c r="D27" s="105"/>
-      <c r="E27" s="504">
+      <c r="E27" s="509">
         <f ca="1">'Loading Arrival'!B9</f>
         <v>45955</v>
       </c>
-      <c r="F27" s="505"/>
-      <c r="G27" s="504">
+      <c r="F27" s="510"/>
+      <c r="G27" s="509">
         <f ca="1">'Loading Arrival'!C9</f>
         <v>45969</v>
       </c>
-      <c r="H27" s="505"/>
+      <c r="H27" s="510"/>
       <c r="J27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K27" s="108"/>
       <c r="L27" s="105"/>
       <c r="M27" s="105"/>
-      <c r="N27" s="504">
+      <c r="N27" s="509">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="O27" s="505"/>
-      <c r="P27" s="506">
+      <c r="O27" s="510"/>
+      <c r="P27" s="511">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="Q27" s="507"/>
-      <c r="R27" s="508">
+      <c r="Q27" s="512"/>
+      <c r="R27" s="513">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="S27" s="505"/>
+      <c r="S27" s="510"/>
       <c r="U27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V27" s="108"/>
       <c r="W27" s="105"/>
       <c r="X27" s="105"/>
-      <c r="Y27" s="504">
+      <c r="Y27" s="509">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="Z27" s="505"/>
-      <c r="AA27" s="506">
+      <c r="Z27" s="510"/>
+      <c r="AA27" s="511">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="AB27" s="507"/>
-      <c r="AC27" s="508">
+      <c r="AB27" s="512"/>
+      <c r="AC27" s="513">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="AD27" s="505"/>
+      <c r="AD27" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="Y27:Z27"/>
     <mergeCell ref="AA27:AB27"/>
     <mergeCell ref="AC27:AD27"/>
@@ -35961,14 +35969,6 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="R27:S27"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -36007,74 +36007,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="513"/>
-      <c r="G3" s="512" t="s">
+      <c r="F3" s="503"/>
+      <c r="G3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="513"/>
-      <c r="I3" s="512" t="s">
+      <c r="H3" s="503"/>
+      <c r="I3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="513"/>
-      <c r="P3" s="512" t="s">
+      <c r="J3" s="503"/>
+      <c r="P3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="513"/>
-      <c r="R3" s="512" t="s">
+      <c r="Q3" s="503"/>
+      <c r="R3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="513"/>
-      <c r="T3" s="512" t="s">
+      <c r="S3" s="503"/>
+      <c r="T3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="513"/>
+      <c r="U3" s="503"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="510" t="s">
+      <c r="A4" s="504" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="511"/>
-      <c r="C4" s="511"/>
-      <c r="D4" s="511"/>
-      <c r="E4" s="509">
+      <c r="B4" s="505"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="506">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="503"/>
-      <c r="G4" s="502">
+      <c r="F4" s="507"/>
+      <c r="G4" s="508">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="503"/>
-      <c r="I4" s="502">
+      <c r="H4" s="507"/>
+      <c r="I4" s="508">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="503"/>
-      <c r="L4" s="510" t="s">
+      <c r="J4" s="507"/>
+      <c r="L4" s="504" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="511"/>
-      <c r="N4" s="511"/>
-      <c r="O4" s="511"/>
-      <c r="P4" s="509">
+      <c r="M4" s="505"/>
+      <c r="N4" s="505"/>
+      <c r="O4" s="505"/>
+      <c r="P4" s="506">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="503"/>
-      <c r="R4" s="502">
+      <c r="Q4" s="507"/>
+      <c r="R4" s="508">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="503"/>
-      <c r="T4" s="502">
+      <c r="S4" s="507"/>
+      <c r="T4" s="508">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="503"/>
+      <c r="U4" s="507"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -37357,51 +37357,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="504">
+      <c r="E25" s="509">
         <f ca="1">'Loading Arrival'!B35</f>
         <v>45923</v>
       </c>
-      <c r="F25" s="505"/>
-      <c r="G25" s="506">
+      <c r="F25" s="510"/>
+      <c r="G25" s="511">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="507"/>
-      <c r="I25" s="508">
+      <c r="H25" s="512"/>
+      <c r="I25" s="513">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="505"/>
+      <c r="J25" s="510"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="504">
+      <c r="P25" s="509">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="505"/>
-      <c r="R25" s="506">
+      <c r="Q25" s="510"/>
+      <c r="R25" s="511">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="507"/>
-      <c r="T25" s="508">
+      <c r="S25" s="512"/>
+      <c r="T25" s="513">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="505"/>
+      <c r="U25" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -37410,12 +37410,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -37454,74 +37454,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="513"/>
-      <c r="G3" s="512" t="s">
+      <c r="F3" s="503"/>
+      <c r="G3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="513"/>
-      <c r="I3" s="512" t="s">
+      <c r="H3" s="503"/>
+      <c r="I3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="513"/>
-      <c r="P3" s="512" t="s">
+      <c r="J3" s="503"/>
+      <c r="P3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="513"/>
-      <c r="R3" s="512" t="s">
+      <c r="Q3" s="503"/>
+      <c r="R3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="513"/>
-      <c r="T3" s="512" t="s">
+      <c r="S3" s="503"/>
+      <c r="T3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="513"/>
+      <c r="U3" s="503"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="510" t="s">
+      <c r="A4" s="504" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="511"/>
-      <c r="C4" s="511"/>
-      <c r="D4" s="511"/>
-      <c r="E4" s="509">
+      <c r="B4" s="505"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="506">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="503"/>
-      <c r="G4" s="502">
+      <c r="F4" s="507"/>
+      <c r="G4" s="508">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="503"/>
-      <c r="I4" s="502">
+      <c r="H4" s="507"/>
+      <c r="I4" s="508">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="503"/>
-      <c r="L4" s="510" t="s">
+      <c r="J4" s="507"/>
+      <c r="L4" s="504" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="511"/>
-      <c r="N4" s="511"/>
-      <c r="O4" s="511"/>
-      <c r="P4" s="509">
+      <c r="M4" s="505"/>
+      <c r="N4" s="505"/>
+      <c r="O4" s="505"/>
+      <c r="P4" s="506">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="503"/>
-      <c r="R4" s="502">
+      <c r="Q4" s="507"/>
+      <c r="R4" s="508">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="503"/>
-      <c r="T4" s="502">
+      <c r="S4" s="507"/>
+      <c r="T4" s="508">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="503"/>
+      <c r="U4" s="507"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -38804,51 +38804,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="504">
+      <c r="E25" s="509">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="505"/>
-      <c r="G25" s="506">
+      <c r="F25" s="510"/>
+      <c r="G25" s="511">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="507"/>
-      <c r="I25" s="508">
+      <c r="H25" s="512"/>
+      <c r="I25" s="513">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="505"/>
+      <c r="J25" s="510"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="504">
+      <c r="P25" s="509">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="505"/>
-      <c r="R25" s="506">
+      <c r="Q25" s="510"/>
+      <c r="R25" s="511">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="507"/>
-      <c r="T25" s="508">
+      <c r="S25" s="512"/>
+      <c r="T25" s="513">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="505"/>
+      <c r="U25" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -38857,12 +38857,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -38901,74 +38901,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="512" t="s">
+      <c r="E3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="513"/>
-      <c r="G3" s="512" t="s">
+      <c r="F3" s="503"/>
+      <c r="G3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="513"/>
-      <c r="I3" s="512" t="s">
+      <c r="H3" s="503"/>
+      <c r="I3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="513"/>
-      <c r="P3" s="512" t="s">
+      <c r="J3" s="503"/>
+      <c r="P3" s="502" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="513"/>
-      <c r="R3" s="512" t="s">
+      <c r="Q3" s="503"/>
+      <c r="R3" s="502" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="513"/>
-      <c r="T3" s="512" t="s">
+      <c r="S3" s="503"/>
+      <c r="T3" s="502" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="513"/>
+      <c r="U3" s="503"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="510" t="s">
+      <c r="A4" s="504" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="511"/>
-      <c r="C4" s="511"/>
-      <c r="D4" s="511"/>
-      <c r="E4" s="509">
+      <c r="B4" s="505"/>
+      <c r="C4" s="505"/>
+      <c r="D4" s="505"/>
+      <c r="E4" s="506">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="503"/>
-      <c r="G4" s="502">
+      <c r="F4" s="507"/>
+      <c r="G4" s="508">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="503"/>
-      <c r="I4" s="502">
+      <c r="H4" s="507"/>
+      <c r="I4" s="508">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="503"/>
-      <c r="L4" s="510" t="s">
+      <c r="J4" s="507"/>
+      <c r="L4" s="504" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="511"/>
-      <c r="N4" s="511"/>
-      <c r="O4" s="511"/>
-      <c r="P4" s="509">
+      <c r="M4" s="505"/>
+      <c r="N4" s="505"/>
+      <c r="O4" s="505"/>
+      <c r="P4" s="506">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="503"/>
-      <c r="R4" s="502">
+      <c r="Q4" s="507"/>
+      <c r="R4" s="508">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="503"/>
-      <c r="T4" s="502">
+      <c r="S4" s="507"/>
+      <c r="T4" s="508">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="503"/>
+      <c r="U4" s="507"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -40251,50 +40251,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="504">
+      <c r="E25" s="509">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="505"/>
-      <c r="G25" s="506">
+      <c r="F25" s="510"/>
+      <c r="G25" s="511">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="507"/>
-      <c r="I25" s="508">
+      <c r="H25" s="512"/>
+      <c r="I25" s="513">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="505"/>
+      <c r="J25" s="510"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="504">
+      <c r="P25" s="509">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="505"/>
-      <c r="R25" s="506">
+      <c r="Q25" s="510"/>
+      <c r="R25" s="511">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="507"/>
-      <c r="T25" s="508">
+      <c r="S25" s="512"/>
+      <c r="T25" s="513">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="505"/>
+      <c r="U25" s="510"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -40304,12 +40305,11 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/Arbs/Arbsheet updated.xlsx
+++ b/Arbs/Arbsheet updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\gvaps1\USR6\CHGE\desktop\Fuel dashboard\Arbs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F1649E9-3661-4A55-A4E0-FB8B2881D08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA5844D2-A161-4BF7-B0E5-66B3FBAAF474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="807" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3249,6 +3249,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3261,12 +3267,6 @@
     <xf numFmtId="16" fontId="0" fillId="25" borderId="25" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3276,11 +3276,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3297,16 +3303,16 @@
     <xf numFmtId="0" fontId="0" fillId="23" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="16" fontId="0" fillId="25" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="25" borderId="27" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="25" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3411,10 +3417,25 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -3430,21 +3451,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3471,6 +3477,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3486,10 +3498,7 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3501,20 +3510,11 @@
     <xf numFmtId="0" fontId="15" fillId="26" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -4343,6 +4343,60 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="2">
+    <pivotField numFmtId="14" showAll="0"/>
+    <pivotField axis="axisRow" numFmtId="14" showAll="0">
+      <items count="12">
+        <item m="1" x="8"/>
+        <item m="1" x="10"/>
+        <item m="1" x="4"/>
+        <item m="1" x="6"/>
+        <item m="1" x="3"/>
+        <item m="1" x="9"/>
+        <item m="1" x="7"/>
+        <item m="1" x="5"/>
+        <item n="01.11.2024" x="0"/>
+        <item n="01.12.2024" x="1"/>
+        <item n="01.01.2025" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000001000000}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="O2:O5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
@@ -4768,60 +4822,6 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0D00-000000000000}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="O11:O15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
-    <pivotField numFmtId="14" showAll="0"/>
-    <pivotField axis="axisRow" numFmtId="14" showAll="0">
-      <items count="12">
-        <item m="1" x="8"/>
-        <item m="1" x="10"/>
-        <item m="1" x="4"/>
-        <item m="1" x="6"/>
-        <item m="1" x="3"/>
-        <item m="1" x="9"/>
-        <item m="1" x="7"/>
-        <item m="1" x="5"/>
-        <item n="01.11.2024" x="0"/>
-        <item n="01.12.2024" x="1"/>
-        <item n="01.01.2025" x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5146,7 +5146,7 @@
       <c r="M3" s="154"/>
     </row>
     <row r="4" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="456" t="s">
+      <c r="A4" s="457" t="s">
         <v>126</v>
       </c>
       <c r="B4" s="154"/>
@@ -5167,7 +5167,7 @@
       <c r="M4" s="154"/>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="456"/>
+      <c r="A5" s="457"/>
       <c r="B5" s="198" t="s">
         <v>134</v>
       </c>
@@ -8305,7 +8305,7 @@
       <c r="M75" s="154"/>
     </row>
     <row r="76" spans="1:13" collapsed="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="535">
+      <c r="A76" s="448">
         <v>0.5</v>
       </c>
       <c r="B76" s="170"/>
@@ -9322,28 +9322,28 @@
       <c r="M99" s="154"/>
     </row>
     <row r="100" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="457" t="s">
+      <c r="A100" s="456" t="s">
         <v>138</v>
       </c>
       <c r="B100" s="154"/>
-      <c r="C100" s="458"/>
-      <c r="D100" s="459"/>
+      <c r="C100" s="460"/>
+      <c r="D100" s="461"/>
       <c r="E100" s="139"/>
-      <c r="F100" s="460" t="s">
+      <c r="F100" s="462" t="s">
         <v>132</v>
       </c>
-      <c r="G100" s="461"/>
-      <c r="H100" s="462"/>
+      <c r="G100" s="463"/>
+      <c r="H100" s="464"/>
       <c r="I100" s="139"/>
-      <c r="J100" s="460" t="s">
+      <c r="J100" s="462" t="s">
         <v>133</v>
       </c>
-      <c r="K100" s="461"/>
-      <c r="L100" s="462"/>
+      <c r="K100" s="463"/>
+      <c r="L100" s="464"/>
       <c r="M100" s="154"/>
     </row>
     <row r="101" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="457"/>
+      <c r="A101" s="456"/>
       <c r="B101" s="198" t="s">
         <v>134</v>
       </c>
@@ -9420,8 +9420,8 @@
         <v>139</v>
       </c>
       <c r="B103" s="167"/>
-      <c r="C103" s="449"/>
-      <c r="D103" s="450"/>
+      <c r="C103" s="451"/>
+      <c r="D103" s="452"/>
       <c r="E103" s="10"/>
       <c r="F103" s="158">
         <f ca="1">F123+F104-F105</f>
@@ -9455,8 +9455,8 @@
       <c r="B104" s="168" t="s">
         <v>136</v>
       </c>
-      <c r="C104" s="449"/>
-      <c r="D104" s="450"/>
+      <c r="C104" s="451"/>
+      <c r="D104" s="452"/>
       <c r="E104" s="176" t="s">
         <v>131</v>
       </c>
@@ -9494,8 +9494,8 @@
       <c r="B105" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C105" s="449"/>
-      <c r="D105" s="450"/>
+      <c r="C105" s="451"/>
+      <c r="D105" s="452"/>
       <c r="E105" s="176" t="s">
         <v>130</v>
       </c>
@@ -9533,8 +9533,8 @@
       <c r="B106" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C106" s="449"/>
-      <c r="D106" s="450"/>
+      <c r="C106" s="451"/>
+      <c r="D106" s="452"/>
       <c r="E106" s="6" t="s">
         <v>55</v>
       </c>
@@ -9572,8 +9572,8 @@
       <c r="B107" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C107" s="449"/>
-      <c r="D107" s="450"/>
+      <c r="C107" s="451"/>
+      <c r="D107" s="452"/>
       <c r="E107" s="6" t="s">
         <v>56</v>
       </c>
@@ -9611,8 +9611,8 @@
       <c r="B108" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C108" s="449"/>
-      <c r="D108" s="450"/>
+      <c r="C108" s="451"/>
+      <c r="D108" s="452"/>
       <c r="E108" s="6" t="s">
         <v>57</v>
       </c>
@@ -9650,8 +9650,8 @@
       <c r="B109" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C109" s="449"/>
-      <c r="D109" s="450"/>
+      <c r="C109" s="451"/>
+      <c r="D109" s="452"/>
       <c r="E109" s="6" t="s">
         <v>58</v>
       </c>
@@ -9689,8 +9689,8 @@
       <c r="B110" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C110" s="449"/>
-      <c r="D110" s="450"/>
+      <c r="C110" s="451"/>
+      <c r="D110" s="452"/>
       <c r="E110" s="6" t="s">
         <v>127</v>
       </c>
@@ -9728,8 +9728,8 @@
       <c r="B111" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C111" s="449"/>
-      <c r="D111" s="450"/>
+      <c r="C111" s="451"/>
+      <c r="D111" s="452"/>
       <c r="E111" s="6" t="s">
         <v>128</v>
       </c>
@@ -9767,8 +9767,8 @@
       <c r="B112" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C112" s="449"/>
-      <c r="D112" s="450"/>
+      <c r="C112" s="451"/>
+      <c r="D112" s="452"/>
       <c r="E112" s="6" t="s">
         <v>83</v>
       </c>
@@ -9806,8 +9806,8 @@
       <c r="B113" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C113" s="449"/>
-      <c r="D113" s="450"/>
+      <c r="C113" s="451"/>
+      <c r="D113" s="452"/>
       <c r="E113" s="6" t="s">
         <v>59</v>
       </c>
@@ -9845,8 +9845,8 @@
       <c r="B114" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C114" s="449"/>
-      <c r="D114" s="450"/>
+      <c r="C114" s="451"/>
+      <c r="D114" s="452"/>
       <c r="E114" s="6" t="s">
         <v>60</v>
       </c>
@@ -9884,8 +9884,8 @@
       <c r="B115" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C115" s="449"/>
-      <c r="D115" s="450"/>
+      <c r="C115" s="451"/>
+      <c r="D115" s="452"/>
       <c r="E115" s="6" t="s">
         <v>61</v>
       </c>
@@ -9923,8 +9923,8 @@
       <c r="B116" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C116" s="449"/>
-      <c r="D116" s="450"/>
+      <c r="C116" s="451"/>
+      <c r="D116" s="452"/>
       <c r="E116" s="6" t="s">
         <v>62</v>
       </c>
@@ -9962,8 +9962,8 @@
       <c r="B117" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C117" s="449"/>
-      <c r="D117" s="450"/>
+      <c r="C117" s="451"/>
+      <c r="D117" s="452"/>
       <c r="E117" s="6" t="s">
         <v>63</v>
       </c>
@@ -10001,8 +10001,8 @@
       <c r="B118" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C118" s="449"/>
-      <c r="D118" s="450"/>
+      <c r="C118" s="451"/>
+      <c r="D118" s="452"/>
       <c r="E118" s="6" t="s">
         <v>64</v>
       </c>
@@ -10040,8 +10040,8 @@
       <c r="B119" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C119" s="449"/>
-      <c r="D119" s="450"/>
+      <c r="C119" s="451"/>
+      <c r="D119" s="452"/>
       <c r="E119" s="6" t="s">
         <v>65</v>
       </c>
@@ -10079,8 +10079,8 @@
       <c r="B120" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C120" s="449"/>
-      <c r="D120" s="450"/>
+      <c r="C120" s="451"/>
+      <c r="D120" s="452"/>
       <c r="E120" s="6" t="s">
         <v>66</v>
       </c>
@@ -10118,8 +10118,8 @@
       <c r="B121" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C121" s="449"/>
-      <c r="D121" s="450"/>
+      <c r="C121" s="451"/>
+      <c r="D121" s="452"/>
       <c r="E121" s="6" t="s">
         <v>102</v>
       </c>
@@ -10157,8 +10157,8 @@
       <c r="B122" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C122" s="449"/>
-      <c r="D122" s="450"/>
+      <c r="C122" s="451"/>
+      <c r="D122" s="452"/>
       <c r="E122" s="6" t="s">
         <v>103</v>
       </c>
@@ -10196,8 +10196,8 @@
       <c r="B123" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C123" s="449"/>
-      <c r="D123" s="450"/>
+      <c r="C123" s="451"/>
+      <c r="D123" s="452"/>
       <c r="E123" s="6" t="s">
         <v>115</v>
       </c>
@@ -10235,8 +10235,8 @@
       <c r="B124" s="256" t="s">
         <v>129</v>
       </c>
-      <c r="C124" s="449"/>
-      <c r="D124" s="450"/>
+      <c r="C124" s="451"/>
+      <c r="D124" s="452"/>
       <c r="E124" s="6" t="s">
         <v>129</v>
       </c>
@@ -10309,7 +10309,7 @@
       <c r="B126" s="168" t="s">
         <v>131</v>
       </c>
-      <c r="C126" s="449"/>
+      <c r="C126" s="451"/>
       <c r="D126" s="465"/>
       <c r="E126" s="176" t="s">
         <v>131</v>
@@ -10347,7 +10347,7 @@
       <c r="B127" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C127" s="449"/>
+      <c r="C127" s="451"/>
       <c r="D127" s="465"/>
       <c r="E127" s="176" t="s">
         <v>130</v>
@@ -10387,7 +10387,7 @@
       <c r="B128" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C128" s="449"/>
+      <c r="C128" s="451"/>
       <c r="D128" s="465"/>
       <c r="E128" s="231" t="s">
         <v>55</v>
@@ -10426,7 +10426,7 @@
       <c r="B129" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C129" s="449"/>
+      <c r="C129" s="451"/>
       <c r="D129" s="465"/>
       <c r="E129" s="176" t="s">
         <v>56</v>
@@ -10465,7 +10465,7 @@
       <c r="B130" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C130" s="449"/>
+      <c r="C130" s="451"/>
       <c r="D130" s="465"/>
       <c r="E130" s="176" t="s">
         <v>57</v>
@@ -10504,7 +10504,7 @@
       <c r="B131" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C131" s="449"/>
+      <c r="C131" s="451"/>
       <c r="D131" s="465"/>
       <c r="E131" s="176" t="s">
         <v>58</v>
@@ -10543,7 +10543,7 @@
       <c r="B132" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C132" s="449"/>
+      <c r="C132" s="451"/>
       <c r="D132" s="465"/>
       <c r="E132" s="176" t="s">
         <v>127</v>
@@ -10582,7 +10582,7 @@
       <c r="B133" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C133" s="449"/>
+      <c r="C133" s="451"/>
       <c r="D133" s="465"/>
       <c r="E133" s="176" t="s">
         <v>128</v>
@@ -10621,7 +10621,7 @@
       <c r="B134" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C134" s="449"/>
+      <c r="C134" s="451"/>
       <c r="D134" s="465"/>
       <c r="E134" s="176" t="s">
         <v>83</v>
@@ -10660,7 +10660,7 @@
       <c r="B135" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C135" s="449"/>
+      <c r="C135" s="451"/>
       <c r="D135" s="465"/>
       <c r="E135" s="176" t="s">
         <v>59</v>
@@ -10699,7 +10699,7 @@
       <c r="B136" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C136" s="449"/>
+      <c r="C136" s="451"/>
       <c r="D136" s="465"/>
       <c r="E136" s="176" t="s">
         <v>60</v>
@@ -10738,7 +10738,7 @@
       <c r="B137" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C137" s="449"/>
+      <c r="C137" s="451"/>
       <c r="D137" s="465"/>
       <c r="E137" s="176" t="s">
         <v>61</v>
@@ -10777,7 +10777,7 @@
       <c r="B138" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C138" s="449"/>
+      <c r="C138" s="451"/>
       <c r="D138" s="465"/>
       <c r="E138" s="176" t="s">
         <v>62</v>
@@ -10816,7 +10816,7 @@
       <c r="B139" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C139" s="449"/>
+      <c r="C139" s="451"/>
       <c r="D139" s="465"/>
       <c r="E139" s="176" t="s">
         <v>63</v>
@@ -10855,7 +10855,7 @@
       <c r="B140" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C140" s="449"/>
+      <c r="C140" s="451"/>
       <c r="D140" s="465"/>
       <c r="E140" s="176" t="s">
         <v>64</v>
@@ -10894,7 +10894,7 @@
       <c r="B141" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C141" s="449"/>
+      <c r="C141" s="451"/>
       <c r="D141" s="465"/>
       <c r="E141" s="176" t="s">
         <v>65</v>
@@ -10933,7 +10933,7 @@
       <c r="B142" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C142" s="449"/>
+      <c r="C142" s="451"/>
       <c r="D142" s="465"/>
       <c r="E142" s="176" t="s">
         <v>66</v>
@@ -10972,7 +10972,7 @@
       <c r="B143" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C143" s="449"/>
+      <c r="C143" s="451"/>
       <c r="D143" s="465"/>
       <c r="E143" s="176" t="s">
         <v>102</v>
@@ -11011,7 +11011,7 @@
       <c r="B144" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C144" s="449"/>
+      <c r="C144" s="451"/>
       <c r="D144" s="465"/>
       <c r="E144" s="176" t="s">
         <v>103</v>
@@ -11050,7 +11050,7 @@
       <c r="B145" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C145" s="449"/>
+      <c r="C145" s="451"/>
       <c r="D145" s="465"/>
       <c r="E145" s="176" t="s">
         <v>115</v>
@@ -11089,8 +11089,8 @@
       <c r="B146" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="C146" s="463"/>
-      <c r="D146" s="466"/>
+      <c r="C146" s="466"/>
+      <c r="D146" s="467"/>
       <c r="E146" s="232" t="s">
         <v>129</v>
       </c>
@@ -11155,12 +11155,12 @@
       <c r="U148" s="435"/>
     </row>
     <row r="149" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="456" t="s">
+      <c r="A149" s="457" t="s">
         <v>141</v>
       </c>
       <c r="B149" s="154"/>
-      <c r="C149" s="451"/>
-      <c r="D149" s="452"/>
+      <c r="C149" s="458"/>
+      <c r="D149" s="459"/>
       <c r="E149" s="156"/>
       <c r="F149" s="453" t="s">
         <v>132</v>
@@ -11176,7 +11176,7 @@
       <c r="M149" s="154"/>
     </row>
     <row r="150" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="456"/>
+      <c r="A150" s="457"/>
       <c r="B150" s="198" t="s">
         <v>134</v>
       </c>
@@ -11218,8 +11218,8 @@
       <c r="B151" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="C151" s="447"/>
-      <c r="D151" s="448"/>
+      <c r="C151" s="449"/>
+      <c r="D151" s="450"/>
       <c r="E151" s="6"/>
       <c r="F151" s="157">
         <f ca="1">'Loading Arrival'!B26</f>
@@ -11256,8 +11256,8 @@
         <v>235</v>
       </c>
       <c r="B152" s="167"/>
-      <c r="C152" s="449"/>
-      <c r="D152" s="450"/>
+      <c r="C152" s="451"/>
+      <c r="D152" s="452"/>
       <c r="E152" s="10"/>
       <c r="F152" s="158">
         <f ca="1">F172+F153-F154</f>
@@ -11294,8 +11294,8 @@
       <c r="B153" s="168" t="s">
         <v>136</v>
       </c>
-      <c r="C153" s="449"/>
-      <c r="D153" s="450"/>
+      <c r="C153" s="451"/>
+      <c r="D153" s="452"/>
       <c r="E153" s="176" t="s">
         <v>131</v>
       </c>
@@ -11336,8 +11336,8 @@
       <c r="B154" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C154" s="449"/>
-      <c r="D154" s="450"/>
+      <c r="C154" s="451"/>
+      <c r="D154" s="452"/>
       <c r="E154" s="176" t="s">
         <v>130</v>
       </c>
@@ -11375,8 +11375,8 @@
       <c r="B155" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C155" s="449"/>
-      <c r="D155" s="450"/>
+      <c r="C155" s="451"/>
+      <c r="D155" s="452"/>
       <c r="E155" s="6" t="s">
         <v>55</v>
       </c>
@@ -11414,8 +11414,8 @@
       <c r="B156" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C156" s="449"/>
-      <c r="D156" s="450"/>
+      <c r="C156" s="451"/>
+      <c r="D156" s="452"/>
       <c r="E156" s="6" t="s">
         <v>56</v>
       </c>
@@ -11453,8 +11453,8 @@
       <c r="B157" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C157" s="449"/>
-      <c r="D157" s="450"/>
+      <c r="C157" s="451"/>
+      <c r="D157" s="452"/>
       <c r="E157" s="6" t="s">
         <v>57</v>
       </c>
@@ -11492,8 +11492,8 @@
       <c r="B158" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C158" s="449"/>
-      <c r="D158" s="450"/>
+      <c r="C158" s="451"/>
+      <c r="D158" s="452"/>
       <c r="E158" s="6" t="s">
         <v>58</v>
       </c>
@@ -11531,8 +11531,8 @@
       <c r="B159" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C159" s="449"/>
-      <c r="D159" s="450"/>
+      <c r="C159" s="451"/>
+      <c r="D159" s="452"/>
       <c r="E159" s="6" t="s">
         <v>127</v>
       </c>
@@ -11570,8 +11570,8 @@
       <c r="B160" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C160" s="449"/>
-      <c r="D160" s="450"/>
+      <c r="C160" s="451"/>
+      <c r="D160" s="452"/>
       <c r="E160" s="6" t="s">
         <v>128</v>
       </c>
@@ -11609,8 +11609,8 @@
       <c r="B161" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C161" s="449"/>
-      <c r="D161" s="450"/>
+      <c r="C161" s="451"/>
+      <c r="D161" s="452"/>
       <c r="E161" s="6" t="s">
         <v>83</v>
       </c>
@@ -11648,8 +11648,8 @@
       <c r="B162" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C162" s="449"/>
-      <c r="D162" s="450"/>
+      <c r="C162" s="451"/>
+      <c r="D162" s="452"/>
       <c r="E162" s="6" t="s">
         <v>59</v>
       </c>
@@ -11687,8 +11687,8 @@
       <c r="B163" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C163" s="449"/>
-      <c r="D163" s="450"/>
+      <c r="C163" s="451"/>
+      <c r="D163" s="452"/>
       <c r="E163" s="6" t="s">
         <v>60</v>
       </c>
@@ -11726,8 +11726,8 @@
       <c r="B164" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C164" s="449"/>
-      <c r="D164" s="450"/>
+      <c r="C164" s="451"/>
+      <c r="D164" s="452"/>
       <c r="E164" s="6" t="s">
         <v>61</v>
       </c>
@@ -11765,8 +11765,8 @@
       <c r="B165" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C165" s="449"/>
-      <c r="D165" s="450"/>
+      <c r="C165" s="451"/>
+      <c r="D165" s="452"/>
       <c r="E165" s="6" t="s">
         <v>62</v>
       </c>
@@ -11804,8 +11804,8 @@
       <c r="B166" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C166" s="449"/>
-      <c r="D166" s="450"/>
+      <c r="C166" s="451"/>
+      <c r="D166" s="452"/>
       <c r="E166" s="6" t="s">
         <v>63</v>
       </c>
@@ -11843,8 +11843,8 @@
       <c r="B167" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C167" s="449"/>
-      <c r="D167" s="450"/>
+      <c r="C167" s="451"/>
+      <c r="D167" s="452"/>
       <c r="E167" s="6" t="s">
         <v>64</v>
       </c>
@@ -11882,8 +11882,8 @@
       <c r="B168" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C168" s="449"/>
-      <c r="D168" s="450"/>
+      <c r="C168" s="451"/>
+      <c r="D168" s="452"/>
       <c r="E168" s="6" t="s">
         <v>65</v>
       </c>
@@ -11921,8 +11921,8 @@
       <c r="B169" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C169" s="449"/>
-      <c r="D169" s="450"/>
+      <c r="C169" s="451"/>
+      <c r="D169" s="452"/>
       <c r="E169" s="6" t="s">
         <v>66</v>
       </c>
@@ -11960,8 +11960,8 @@
       <c r="B170" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C170" s="449"/>
-      <c r="D170" s="450"/>
+      <c r="C170" s="451"/>
+      <c r="D170" s="452"/>
       <c r="E170" s="6" t="s">
         <v>102</v>
       </c>
@@ -11999,8 +11999,8 @@
       <c r="B171" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C171" s="449"/>
-      <c r="D171" s="450"/>
+      <c r="C171" s="451"/>
+      <c r="D171" s="452"/>
       <c r="E171" s="6" t="s">
         <v>103</v>
       </c>
@@ -12038,8 +12038,8 @@
       <c r="B172" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C172" s="449"/>
-      <c r="D172" s="450"/>
+      <c r="C172" s="451"/>
+      <c r="D172" s="452"/>
       <c r="E172" s="6" t="s">
         <v>115</v>
       </c>
@@ -12077,8 +12077,8 @@
       <c r="B173" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="C173" s="449"/>
-      <c r="D173" s="450"/>
+      <c r="C173" s="451"/>
+      <c r="D173" s="452"/>
       <c r="E173" s="6" t="s">
         <v>129</v>
       </c>
@@ -12128,28 +12128,28 @@
       <c r="M174" s="154"/>
     </row>
     <row r="175" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="457" t="s">
+      <c r="A175" s="456" t="s">
         <v>142</v>
       </c>
       <c r="B175" s="154"/>
-      <c r="C175" s="458"/>
-      <c r="D175" s="459"/>
+      <c r="C175" s="460"/>
+      <c r="D175" s="461"/>
       <c r="E175" s="213"/>
-      <c r="F175" s="460" t="s">
+      <c r="F175" s="462" t="s">
         <v>132</v>
       </c>
-      <c r="G175" s="461"/>
-      <c r="H175" s="462"/>
+      <c r="G175" s="463"/>
+      <c r="H175" s="464"/>
       <c r="I175" s="213"/>
-      <c r="J175" s="460" t="s">
+      <c r="J175" s="462" t="s">
         <v>133</v>
       </c>
-      <c r="K175" s="461"/>
-      <c r="L175" s="462"/>
+      <c r="K175" s="463"/>
+      <c r="L175" s="464"/>
       <c r="M175" s="154"/>
     </row>
     <row r="176" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="457"/>
+      <c r="A176" s="456"/>
       <c r="B176" s="198" t="s">
         <v>134</v>
       </c>
@@ -12191,8 +12191,8 @@
       <c r="B177" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="C177" s="447"/>
-      <c r="D177" s="448"/>
+      <c r="C177" s="449"/>
+      <c r="D177" s="450"/>
       <c r="E177" s="6"/>
       <c r="F177" s="251">
         <f ca="1">'Loading Arrival'!B44</f>
@@ -12229,8 +12229,8 @@
         <v>139</v>
       </c>
       <c r="B178" s="167"/>
-      <c r="C178" s="449"/>
-      <c r="D178" s="450"/>
+      <c r="C178" s="451"/>
+      <c r="D178" s="452"/>
       <c r="E178" s="10"/>
       <c r="F178" s="158">
         <f ca="1">F198+F179-F180</f>
@@ -12264,8 +12264,8 @@
       <c r="B179" s="168" t="s">
         <v>136</v>
       </c>
-      <c r="C179" s="449"/>
-      <c r="D179" s="450"/>
+      <c r="C179" s="451"/>
+      <c r="D179" s="452"/>
       <c r="E179" s="176" t="s">
         <v>131</v>
       </c>
@@ -12303,8 +12303,8 @@
       <c r="B180" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C180" s="449"/>
-      <c r="D180" s="450"/>
+      <c r="C180" s="451"/>
+      <c r="D180" s="452"/>
       <c r="E180" s="176" t="s">
         <v>130</v>
       </c>
@@ -12342,8 +12342,8 @@
       <c r="B181" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C181" s="449"/>
-      <c r="D181" s="450"/>
+      <c r="C181" s="451"/>
+      <c r="D181" s="452"/>
       <c r="E181" s="6" t="s">
         <v>55</v>
       </c>
@@ -12380,8 +12380,8 @@
       <c r="B182" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C182" s="449"/>
-      <c r="D182" s="450"/>
+      <c r="C182" s="451"/>
+      <c r="D182" s="452"/>
       <c r="E182" s="6" t="s">
         <v>56</v>
       </c>
@@ -12418,8 +12418,8 @@
       <c r="B183" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C183" s="449"/>
-      <c r="D183" s="450"/>
+      <c r="C183" s="451"/>
+      <c r="D183" s="452"/>
       <c r="E183" s="6" t="s">
         <v>57</v>
       </c>
@@ -12456,8 +12456,8 @@
       <c r="B184" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C184" s="449"/>
-      <c r="D184" s="450"/>
+      <c r="C184" s="451"/>
+      <c r="D184" s="452"/>
       <c r="E184" s="6" t="s">
         <v>58</v>
       </c>
@@ -12494,8 +12494,8 @@
       <c r="B185" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C185" s="449"/>
-      <c r="D185" s="450"/>
+      <c r="C185" s="451"/>
+      <c r="D185" s="452"/>
       <c r="E185" s="6" t="s">
         <v>127</v>
       </c>
@@ -12532,8 +12532,8 @@
       <c r="B186" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C186" s="449"/>
-      <c r="D186" s="450"/>
+      <c r="C186" s="451"/>
+      <c r="D186" s="452"/>
       <c r="E186" s="6" t="s">
         <v>128</v>
       </c>
@@ -12570,8 +12570,8 @@
       <c r="B187" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C187" s="449"/>
-      <c r="D187" s="450"/>
+      <c r="C187" s="451"/>
+      <c r="D187" s="452"/>
       <c r="E187" s="6" t="s">
         <v>83</v>
       </c>
@@ -12608,8 +12608,8 @@
       <c r="B188" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C188" s="449"/>
-      <c r="D188" s="450"/>
+      <c r="C188" s="451"/>
+      <c r="D188" s="452"/>
       <c r="E188" s="6" t="s">
         <v>59</v>
       </c>
@@ -12646,8 +12646,8 @@
       <c r="B189" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C189" s="449"/>
-      <c r="D189" s="450"/>
+      <c r="C189" s="451"/>
+      <c r="D189" s="452"/>
       <c r="E189" s="6" t="s">
         <v>60</v>
       </c>
@@ -12684,8 +12684,8 @@
       <c r="B190" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C190" s="449"/>
-      <c r="D190" s="450"/>
+      <c r="C190" s="451"/>
+      <c r="D190" s="452"/>
       <c r="E190" s="6" t="s">
         <v>61</v>
       </c>
@@ -12722,8 +12722,8 @@
       <c r="B191" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C191" s="449"/>
-      <c r="D191" s="450"/>
+      <c r="C191" s="451"/>
+      <c r="D191" s="452"/>
       <c r="E191" s="6" t="s">
         <v>62</v>
       </c>
@@ -12760,8 +12760,8 @@
       <c r="B192" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C192" s="449"/>
-      <c r="D192" s="450"/>
+      <c r="C192" s="451"/>
+      <c r="D192" s="452"/>
       <c r="E192" s="6" t="s">
         <v>63</v>
       </c>
@@ -12798,8 +12798,8 @@
       <c r="B193" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C193" s="449"/>
-      <c r="D193" s="450"/>
+      <c r="C193" s="451"/>
+      <c r="D193" s="452"/>
       <c r="E193" s="6" t="s">
         <v>64</v>
       </c>
@@ -12836,8 +12836,8 @@
       <c r="B194" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C194" s="449"/>
-      <c r="D194" s="450"/>
+      <c r="C194" s="451"/>
+      <c r="D194" s="452"/>
       <c r="E194" s="6" t="s">
         <v>65</v>
       </c>
@@ -12874,8 +12874,8 @@
       <c r="B195" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C195" s="449"/>
-      <c r="D195" s="450"/>
+      <c r="C195" s="451"/>
+      <c r="D195" s="452"/>
       <c r="E195" s="6" t="s">
         <v>66</v>
       </c>
@@ -12912,8 +12912,8 @@
       <c r="B196" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C196" s="449"/>
-      <c r="D196" s="450"/>
+      <c r="C196" s="451"/>
+      <c r="D196" s="452"/>
       <c r="E196" s="6" t="s">
         <v>102</v>
       </c>
@@ -12950,8 +12950,8 @@
       <c r="B197" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C197" s="449"/>
-      <c r="D197" s="450"/>
+      <c r="C197" s="451"/>
+      <c r="D197" s="452"/>
       <c r="E197" s="6" t="s">
         <v>103</v>
       </c>
@@ -12988,8 +12988,8 @@
       <c r="B198" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C198" s="449"/>
-      <c r="D198" s="450"/>
+      <c r="C198" s="451"/>
+      <c r="D198" s="452"/>
       <c r="E198" s="6" t="s">
         <v>115</v>
       </c>
@@ -13026,8 +13026,8 @@
       <c r="B199" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="C199" s="463"/>
-      <c r="D199" s="464"/>
+      <c r="C199" s="466"/>
+      <c r="D199" s="468"/>
       <c r="E199" s="105" t="s">
         <v>129</v>
       </c>
@@ -13109,8 +13109,8 @@
     <row r="204" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="154"/>
       <c r="B204" s="154"/>
-      <c r="C204" s="451"/>
-      <c r="D204" s="452"/>
+      <c r="C204" s="458"/>
+      <c r="D204" s="459"/>
       <c r="E204" s="156"/>
       <c r="F204" s="453" t="s">
         <v>132</v>
@@ -13126,12 +13126,12 @@
       <c r="M204" s="154"/>
     </row>
     <row r="205" spans="1:13" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="366">
-        <v>5.0000000000000001E-3</v>
+      <c r="A205" s="448">
+        <v>0.5</v>
       </c>
       <c r="B205" s="170"/>
-      <c r="C205" s="451"/>
-      <c r="D205" s="452">
+      <c r="C205" s="458"/>
+      <c r="D205" s="459">
         <f>D227+D208-D209</f>
         <v>0</v>
       </c>
@@ -13204,30 +13204,30 @@
       <c r="C207" s="369"/>
       <c r="D207" s="370"/>
       <c r="E207" s="6"/>
-      <c r="F207" s="158" t="e">
+      <c r="F207" s="158">
         <f ca="1">F227+F208-F209</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G207" s="159" t="e">
+        <v>-9.7322107565509288</v>
+      </c>
+      <c r="G207" s="159">
         <f ca="1">G227+G208-G209</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H207" s="160" t="e">
+        <v>-9.2307107565509288</v>
+      </c>
+      <c r="H207" s="160">
         <f ca="1">H227+H208-H209</f>
-        <v>#N/A</v>
+        <v>-7.9366508250440777</v>
       </c>
       <c r="I207" s="164"/>
-      <c r="J207" s="159" t="e">
+      <c r="J207" s="159">
         <f ca="1">J227+J208-J209</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K207" s="159" t="e">
+        <v>-20.458877423217601</v>
+      </c>
+      <c r="K207" s="159">
         <f ca="1">K227+K208-K209</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L207" s="160" t="e">
+        <v>-19.957377423217601</v>
+      </c>
+      <c r="L207" s="160">
         <f ca="1">L227+L208-L209</f>
-        <v>#N/A</v>
+        <v>-18.66331749171075</v>
       </c>
       <c r="M207" s="154"/>
     </row>
@@ -13236,38 +13236,38 @@
       <c r="B208" s="166" t="s">
         <v>131</v>
       </c>
-      <c r="C208" s="447"/>
-      <c r="D208" s="448"/>
+      <c r="C208" s="449"/>
+      <c r="D208" s="450"/>
       <c r="E208" s="176" t="s">
         <v>131</v>
       </c>
-      <c r="F208" s="174" t="e">
+      <c r="F208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!F206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="G208" s="174" t="e">
+        <v>2.6</v>
+      </c>
+      <c r="G208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!G206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="H208" s="174" t="e">
+        <v>2.6</v>
+      </c>
+      <c r="H208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!H206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
+        <v>2.6</v>
       </c>
       <c r="I208" s="178" t="e">
         <f>INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!I179,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="J208" s="174" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!J206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="K208" s="174" t="e">
+        <v>2.6</v>
+      </c>
+      <c r="K208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!K206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
-      </c>
-      <c r="L208" s="174" t="e">
+        <v>2.6</v>
+      </c>
+      <c r="L208" s="174">
         <f ca="1">INDEX(Premium!$A$2:$D$12,MATCH(MAIN!$A205,Premium!$A$2:$A$12,0),MATCH(EOMONTH(MAIN!L206,-1)+1,Premium!$A$2:$D$2,0))</f>
-        <v>#N/A</v>
+        <v>2.6</v>
       </c>
       <c r="M208" s="154"/>
     </row>
@@ -13276,8 +13276,8 @@
       <c r="B209" s="171" t="s">
         <v>130</v>
       </c>
-      <c r="C209" s="449"/>
-      <c r="D209" s="450"/>
+      <c r="C209" s="451"/>
+      <c r="D209" s="452"/>
       <c r="E209" s="176" t="s">
         <v>130</v>
       </c>
@@ -13315,8 +13315,8 @@
       <c r="B210" s="154" t="s">
         <v>55</v>
       </c>
-      <c r="C210" s="447"/>
-      <c r="D210" s="448"/>
+      <c r="C210" s="449"/>
+      <c r="D210" s="450"/>
       <c r="E210" s="6" t="s">
         <v>55</v>
       </c>
@@ -13354,8 +13354,8 @@
       <c r="B211" s="154" t="s">
         <v>56</v>
       </c>
-      <c r="C211" s="449"/>
-      <c r="D211" s="450"/>
+      <c r="C211" s="451"/>
+      <c r="D211" s="452"/>
       <c r="E211" t="s">
         <v>56</v>
       </c>
@@ -13393,8 +13393,8 @@
       <c r="B212" s="154" t="s">
         <v>57</v>
       </c>
-      <c r="C212" s="449"/>
-      <c r="D212" s="450"/>
+      <c r="C212" s="451"/>
+      <c r="D212" s="452"/>
       <c r="E212" t="s">
         <v>57</v>
       </c>
@@ -13432,8 +13432,8 @@
       <c r="B213" s="154" t="s">
         <v>58</v>
       </c>
-      <c r="C213" s="449"/>
-      <c r="D213" s="450"/>
+      <c r="C213" s="451"/>
+      <c r="D213" s="452"/>
       <c r="E213" t="s">
         <v>58</v>
       </c>
@@ -13471,8 +13471,8 @@
       <c r="B214" s="154" t="s">
         <v>127</v>
       </c>
-      <c r="C214" s="449"/>
-      <c r="D214" s="450"/>
+      <c r="C214" s="451"/>
+      <c r="D214" s="452"/>
       <c r="E214" t="s">
         <v>127</v>
       </c>
@@ -13509,8 +13509,8 @@
       <c r="B215" s="154" t="s">
         <v>128</v>
       </c>
-      <c r="C215" s="449"/>
-      <c r="D215" s="450"/>
+      <c r="C215" s="451"/>
+      <c r="D215" s="452"/>
       <c r="E215" t="s">
         <v>128</v>
       </c>
@@ -13547,8 +13547,8 @@
       <c r="B216" s="154" t="s">
         <v>83</v>
       </c>
-      <c r="C216" s="449"/>
-      <c r="D216" s="450"/>
+      <c r="C216" s="451"/>
+      <c r="D216" s="452"/>
       <c r="E216" t="s">
         <v>83</v>
       </c>
@@ -13585,8 +13585,8 @@
       <c r="B217" s="154" t="s">
         <v>59</v>
       </c>
-      <c r="C217" s="449"/>
-      <c r="D217" s="450"/>
+      <c r="C217" s="451"/>
+      <c r="D217" s="452"/>
       <c r="E217" t="s">
         <v>59</v>
       </c>
@@ -13623,8 +13623,8 @@
       <c r="B218" s="154" t="s">
         <v>60</v>
       </c>
-      <c r="C218" s="449"/>
-      <c r="D218" s="450"/>
+      <c r="C218" s="451"/>
+      <c r="D218" s="452"/>
       <c r="E218" t="s">
         <v>60</v>
       </c>
@@ -13661,8 +13661,8 @@
       <c r="B219" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="C219" s="449"/>
-      <c r="D219" s="450"/>
+      <c r="C219" s="451"/>
+      <c r="D219" s="452"/>
       <c r="E219" t="s">
         <v>61</v>
       </c>
@@ -13699,8 +13699,8 @@
       <c r="B220" s="154" t="s">
         <v>62</v>
       </c>
-      <c r="C220" s="449"/>
-      <c r="D220" s="450"/>
+      <c r="C220" s="451"/>
+      <c r="D220" s="452"/>
       <c r="E220" t="s">
         <v>62</v>
       </c>
@@ -13737,8 +13737,8 @@
       <c r="B221" s="154" t="s">
         <v>63</v>
       </c>
-      <c r="C221" s="449"/>
-      <c r="D221" s="450"/>
+      <c r="C221" s="451"/>
+      <c r="D221" s="452"/>
       <c r="E221" t="s">
         <v>63</v>
       </c>
@@ -13775,8 +13775,8 @@
       <c r="B222" s="154" t="s">
         <v>64</v>
       </c>
-      <c r="C222" s="449"/>
-      <c r="D222" s="450"/>
+      <c r="C222" s="451"/>
+      <c r="D222" s="452"/>
       <c r="E222" t="s">
         <v>64</v>
       </c>
@@ -13813,8 +13813,8 @@
       <c r="B223" s="154" t="s">
         <v>65</v>
       </c>
-      <c r="C223" s="449"/>
-      <c r="D223" s="450"/>
+      <c r="C223" s="451"/>
+      <c r="D223" s="452"/>
       <c r="E223" t="s">
         <v>65</v>
       </c>
@@ -13851,8 +13851,8 @@
       <c r="B224" s="154" t="s">
         <v>66</v>
       </c>
-      <c r="C224" s="449"/>
-      <c r="D224" s="450"/>
+      <c r="C224" s="451"/>
+      <c r="D224" s="452"/>
       <c r="E224" t="s">
         <v>66</v>
       </c>
@@ -13889,8 +13889,8 @@
       <c r="B225" s="154" t="s">
         <v>102</v>
       </c>
-      <c r="C225" s="449"/>
-      <c r="D225" s="450"/>
+      <c r="C225" s="451"/>
+      <c r="D225" s="452"/>
       <c r="E225" t="s">
         <v>102</v>
       </c>
@@ -13927,8 +13927,8 @@
       <c r="B226" s="154" t="s">
         <v>103</v>
       </c>
-      <c r="C226" s="449"/>
-      <c r="D226" s="450"/>
+      <c r="C226" s="451"/>
+      <c r="D226" s="452"/>
       <c r="E226" t="s">
         <v>103</v>
       </c>
@@ -13965,8 +13965,8 @@
       <c r="B227" s="154" t="s">
         <v>115</v>
       </c>
-      <c r="C227" s="449"/>
-      <c r="D227" s="450"/>
+      <c r="C227" s="451"/>
+      <c r="D227" s="452"/>
       <c r="E227" t="s">
         <v>115</v>
       </c>
@@ -14003,8 +14003,8 @@
       <c r="B228" s="154" t="s">
         <v>129</v>
       </c>
-      <c r="C228" s="449"/>
-      <c r="D228" s="450"/>
+      <c r="C228" s="451"/>
+      <c r="D228" s="452"/>
       <c r="E228" t="s">
         <v>129</v>
       </c>
@@ -14078,12 +14078,12 @@
       <c r="M231" s="154"/>
     </row>
     <row r="232" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="456" t="s">
+      <c r="A232" s="457" t="s">
         <v>214</v>
       </c>
       <c r="B232" s="154"/>
-      <c r="C232" s="451"/>
-      <c r="D232" s="452"/>
+      <c r="C232" s="458"/>
+      <c r="D232" s="459"/>
       <c r="E232" s="156"/>
       <c r="F232" s="453" t="s">
         <v>132</v>
@@ -14099,7 +14099,7 @@
       <c r="M232" s="154"/>
     </row>
     <row r="233" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="456"/>
+      <c r="A233" s="457"/>
       <c r="B233" s="198" t="s">
         <v>187</v>
       </c>
@@ -14137,8 +14137,8 @@
       <c r="M233" s="154"/>
     </row>
     <row r="234" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="C234" s="447"/>
-      <c r="D234" s="448"/>
+      <c r="C234" s="449"/>
+      <c r="D234" s="450"/>
       <c r="F234" s="157">
         <f ca="1">'Loading Arrival'!G9</f>
         <v>45918</v>
@@ -14174,8 +14174,8 @@
         <v>231</v>
       </c>
       <c r="B235" s="167"/>
-      <c r="C235" s="449"/>
-      <c r="D235" s="450"/>
+      <c r="C235" s="451"/>
+      <c r="D235" s="452"/>
       <c r="F235" s="158">
         <f ca="1">F255+F236-F237</f>
         <v>-53.505408333333307</v>
@@ -14208,8 +14208,8 @@
       <c r="B236" s="168" t="s">
         <v>136</v>
       </c>
-      <c r="C236" s="449"/>
-      <c r="D236" s="450"/>
+      <c r="C236" s="451"/>
+      <c r="D236" s="452"/>
       <c r="E236" s="176" t="s">
         <v>131</v>
       </c>
@@ -14247,8 +14247,8 @@
       <c r="B237" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C237" s="449"/>
-      <c r="D237" s="450"/>
+      <c r="C237" s="451"/>
+      <c r="D237" s="452"/>
       <c r="E237" s="176" t="s">
         <v>130</v>
       </c>
@@ -14286,8 +14286,8 @@
       <c r="B238" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C238" s="449"/>
-      <c r="D238" s="450"/>
+      <c r="C238" s="451"/>
+      <c r="D238" s="452"/>
       <c r="E238" s="6" t="s">
         <v>55</v>
       </c>
@@ -14325,8 +14325,8 @@
       <c r="B239" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C239" s="449"/>
-      <c r="D239" s="450"/>
+      <c r="C239" s="451"/>
+      <c r="D239" s="452"/>
       <c r="E239" t="s">
         <v>56</v>
       </c>
@@ -14364,8 +14364,8 @@
       <c r="B240" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C240" s="449"/>
-      <c r="D240" s="450"/>
+      <c r="C240" s="451"/>
+      <c r="D240" s="452"/>
       <c r="E240" t="s">
         <v>57</v>
       </c>
@@ -14403,8 +14403,8 @@
       <c r="B241" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C241" s="449"/>
-      <c r="D241" s="450"/>
+      <c r="C241" s="451"/>
+      <c r="D241" s="452"/>
       <c r="E241" t="s">
         <v>58</v>
       </c>
@@ -14442,8 +14442,8 @@
       <c r="B242" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C242" s="449"/>
-      <c r="D242" s="450"/>
+      <c r="C242" s="451"/>
+      <c r="D242" s="452"/>
       <c r="E242" t="s">
         <v>127</v>
       </c>
@@ -14481,8 +14481,8 @@
       <c r="B243" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C243" s="449"/>
-      <c r="D243" s="450"/>
+      <c r="C243" s="451"/>
+      <c r="D243" s="452"/>
       <c r="E243" t="s">
         <v>128</v>
       </c>
@@ -14520,8 +14520,8 @@
       <c r="B244" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C244" s="449"/>
-      <c r="D244" s="450"/>
+      <c r="C244" s="451"/>
+      <c r="D244" s="452"/>
       <c r="E244" t="s">
         <v>83</v>
       </c>
@@ -14559,8 +14559,8 @@
       <c r="B245" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C245" s="449"/>
-      <c r="D245" s="450"/>
+      <c r="C245" s="451"/>
+      <c r="D245" s="452"/>
       <c r="E245" t="s">
         <v>59</v>
       </c>
@@ -14598,8 +14598,8 @@
       <c r="B246" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C246" s="449"/>
-      <c r="D246" s="450"/>
+      <c r="C246" s="451"/>
+      <c r="D246" s="452"/>
       <c r="E246" t="s">
         <v>60</v>
       </c>
@@ -14637,8 +14637,8 @@
       <c r="B247" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C247" s="449"/>
-      <c r="D247" s="450"/>
+      <c r="C247" s="451"/>
+      <c r="D247" s="452"/>
       <c r="E247" t="s">
         <v>61</v>
       </c>
@@ -14676,8 +14676,8 @@
       <c r="B248" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C248" s="449"/>
-      <c r="D248" s="450"/>
+      <c r="C248" s="451"/>
+      <c r="D248" s="452"/>
       <c r="E248" t="s">
         <v>62</v>
       </c>
@@ -14715,8 +14715,8 @@
       <c r="B249" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C249" s="449"/>
-      <c r="D249" s="450"/>
+      <c r="C249" s="451"/>
+      <c r="D249" s="452"/>
       <c r="E249" t="s">
         <v>63</v>
       </c>
@@ -14754,8 +14754,8 @@
       <c r="B250" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C250" s="449"/>
-      <c r="D250" s="450"/>
+      <c r="C250" s="451"/>
+      <c r="D250" s="452"/>
       <c r="E250" t="s">
         <v>64</v>
       </c>
@@ -14793,8 +14793,8 @@
       <c r="B251" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C251" s="449"/>
-      <c r="D251" s="450"/>
+      <c r="C251" s="451"/>
+      <c r="D251" s="452"/>
       <c r="E251" t="s">
         <v>65</v>
       </c>
@@ -14832,8 +14832,8 @@
       <c r="B252" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C252" s="449"/>
-      <c r="D252" s="450"/>
+      <c r="C252" s="451"/>
+      <c r="D252" s="452"/>
       <c r="E252" t="s">
         <v>66</v>
       </c>
@@ -14871,8 +14871,8 @@
       <c r="B253" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C253" s="449"/>
-      <c r="D253" s="450"/>
+      <c r="C253" s="451"/>
+      <c r="D253" s="452"/>
       <c r="E253" t="s">
         <v>102</v>
       </c>
@@ -14910,8 +14910,8 @@
       <c r="B254" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C254" s="449"/>
-      <c r="D254" s="450"/>
+      <c r="C254" s="451"/>
+      <c r="D254" s="452"/>
       <c r="E254" t="s">
         <v>103</v>
       </c>
@@ -14949,8 +14949,8 @@
       <c r="B255" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C255" s="449"/>
-      <c r="D255" s="450"/>
+      <c r="C255" s="451"/>
+      <c r="D255" s="452"/>
       <c r="E255" t="s">
         <v>115</v>
       </c>
@@ -14988,8 +14988,8 @@
       <c r="B256" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="C256" s="449"/>
-      <c r="D256" s="450"/>
+      <c r="C256" s="451"/>
+      <c r="D256" s="452"/>
       <c r="E256" t="s">
         <v>129</v>
       </c>
@@ -15041,8 +15041,8 @@
     <row r="258" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A258" s="154"/>
       <c r="B258" s="154"/>
-      <c r="C258" s="447"/>
-      <c r="D258" s="448"/>
+      <c r="C258" s="449"/>
+      <c r="D258" s="450"/>
       <c r="F258" s="157">
         <f ca="1">F234</f>
         <v>45918</v>
@@ -15078,8 +15078,8 @@
         <v>232</v>
       </c>
       <c r="B259" s="167"/>
-      <c r="C259" s="449"/>
-      <c r="D259" s="450"/>
+      <c r="C259" s="451"/>
+      <c r="D259" s="452"/>
       <c r="F259" s="158">
         <f ca="1">F279+F260-F261</f>
         <v>-12.710598256550956</v>
@@ -15112,8 +15112,8 @@
       <c r="B260" s="168" t="s">
         <v>136</v>
       </c>
-      <c r="C260" s="449"/>
-      <c r="D260" s="450"/>
+      <c r="C260" s="451"/>
+      <c r="D260" s="452"/>
       <c r="E260" s="176" t="s">
         <v>131</v>
       </c>
@@ -15151,8 +15151,8 @@
       <c r="B261" s="169" t="s">
         <v>135</v>
       </c>
-      <c r="C261" s="449"/>
-      <c r="D261" s="450"/>
+      <c r="C261" s="451"/>
+      <c r="D261" s="452"/>
       <c r="E261" s="176" t="s">
         <v>130</v>
       </c>
@@ -15190,8 +15190,8 @@
       <c r="B262" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C262" s="449"/>
-      <c r="D262" s="450"/>
+      <c r="C262" s="451"/>
+      <c r="D262" s="452"/>
       <c r="E262" s="6" t="s">
         <v>55</v>
       </c>
@@ -15228,8 +15228,8 @@
       <c r="B263" s="255" t="s">
         <v>56</v>
       </c>
-      <c r="C263" s="449"/>
-      <c r="D263" s="450"/>
+      <c r="C263" s="451"/>
+      <c r="D263" s="452"/>
       <c r="E263" t="s">
         <v>56</v>
       </c>
@@ -15266,8 +15266,8 @@
       <c r="B264" s="255" t="s">
         <v>57</v>
       </c>
-      <c r="C264" s="449"/>
-      <c r="D264" s="450"/>
+      <c r="C264" s="451"/>
+      <c r="D264" s="452"/>
       <c r="E264" t="s">
         <v>57</v>
       </c>
@@ -15304,8 +15304,8 @@
       <c r="B265" s="255" t="s">
         <v>58</v>
       </c>
-      <c r="C265" s="449"/>
-      <c r="D265" s="450"/>
+      <c r="C265" s="451"/>
+      <c r="D265" s="452"/>
       <c r="E265" t="s">
         <v>58</v>
       </c>
@@ -15342,8 +15342,8 @@
       <c r="B266" s="255" t="s">
         <v>127</v>
       </c>
-      <c r="C266" s="449"/>
-      <c r="D266" s="450"/>
+      <c r="C266" s="451"/>
+      <c r="D266" s="452"/>
       <c r="E266" t="s">
         <v>127</v>
       </c>
@@ -15380,8 +15380,8 @@
       <c r="B267" s="255" t="s">
         <v>128</v>
       </c>
-      <c r="C267" s="449"/>
-      <c r="D267" s="450"/>
+      <c r="C267" s="451"/>
+      <c r="D267" s="452"/>
       <c r="E267" t="s">
         <v>128</v>
       </c>
@@ -15418,8 +15418,8 @@
       <c r="B268" s="255" t="s">
         <v>83</v>
       </c>
-      <c r="C268" s="449"/>
-      <c r="D268" s="450"/>
+      <c r="C268" s="451"/>
+      <c r="D268" s="452"/>
       <c r="E268" t="s">
         <v>83</v>
       </c>
@@ -15456,8 +15456,8 @@
       <c r="B269" s="255" t="s">
         <v>59</v>
       </c>
-      <c r="C269" s="449"/>
-      <c r="D269" s="450"/>
+      <c r="C269" s="451"/>
+      <c r="D269" s="452"/>
       <c r="E269" t="s">
         <v>59</v>
       </c>
@@ -15494,8 +15494,8 @@
       <c r="B270" s="255" t="s">
         <v>60</v>
       </c>
-      <c r="C270" s="449"/>
-      <c r="D270" s="450"/>
+      <c r="C270" s="451"/>
+      <c r="D270" s="452"/>
       <c r="E270" t="s">
         <v>60</v>
       </c>
@@ -15532,8 +15532,8 @@
       <c r="B271" s="255" t="s">
         <v>61</v>
       </c>
-      <c r="C271" s="449"/>
-      <c r="D271" s="450"/>
+      <c r="C271" s="451"/>
+      <c r="D271" s="452"/>
       <c r="E271" t="s">
         <v>61</v>
       </c>
@@ -15570,8 +15570,8 @@
       <c r="B272" s="255" t="s">
         <v>62</v>
       </c>
-      <c r="C272" s="449"/>
-      <c r="D272" s="450"/>
+      <c r="C272" s="451"/>
+      <c r="D272" s="452"/>
       <c r="E272" t="s">
         <v>62</v>
       </c>
@@ -15608,8 +15608,8 @@
       <c r="B273" s="255" t="s">
         <v>63</v>
       </c>
-      <c r="C273" s="449"/>
-      <c r="D273" s="450"/>
+      <c r="C273" s="451"/>
+      <c r="D273" s="452"/>
       <c r="E273" t="s">
         <v>63</v>
       </c>
@@ -15646,8 +15646,8 @@
       <c r="B274" s="255" t="s">
         <v>64</v>
       </c>
-      <c r="C274" s="449"/>
-      <c r="D274" s="450"/>
+      <c r="C274" s="451"/>
+      <c r="D274" s="452"/>
       <c r="E274" t="s">
         <v>64</v>
       </c>
@@ -15684,8 +15684,8 @@
       <c r="B275" s="255" t="s">
         <v>65</v>
       </c>
-      <c r="C275" s="449"/>
-      <c r="D275" s="450"/>
+      <c r="C275" s="451"/>
+      <c r="D275" s="452"/>
       <c r="E275" t="s">
         <v>65</v>
       </c>
@@ -15722,8 +15722,8 @@
       <c r="B276" s="255" t="s">
         <v>66</v>
       </c>
-      <c r="C276" s="449"/>
-      <c r="D276" s="450"/>
+      <c r="C276" s="451"/>
+      <c r="D276" s="452"/>
       <c r="E276" t="s">
         <v>66</v>
       </c>
@@ -15760,8 +15760,8 @@
       <c r="B277" s="255" t="s">
         <v>102</v>
       </c>
-      <c r="C277" s="449"/>
-      <c r="D277" s="450"/>
+      <c r="C277" s="451"/>
+      <c r="D277" s="452"/>
       <c r="E277" t="s">
         <v>102</v>
       </c>
@@ -15798,8 +15798,8 @@
       <c r="B278" s="255" t="s">
         <v>103</v>
       </c>
-      <c r="C278" s="449"/>
-      <c r="D278" s="450"/>
+      <c r="C278" s="451"/>
+      <c r="D278" s="452"/>
       <c r="E278" t="s">
         <v>103</v>
       </c>
@@ -15836,8 +15836,8 @@
       <c r="B279" s="255" t="s">
         <v>115</v>
       </c>
-      <c r="C279" s="449"/>
-      <c r="D279" s="450"/>
+      <c r="C279" s="451"/>
+      <c r="D279" s="452"/>
       <c r="E279" t="s">
         <v>115</v>
       </c>
@@ -15874,8 +15874,8 @@
       <c r="B280" s="255" t="s">
         <v>129</v>
       </c>
-      <c r="C280" s="449"/>
-      <c r="D280" s="450"/>
+      <c r="C280" s="451"/>
+      <c r="D280" s="452"/>
       <c r="E280" t="s">
         <v>129</v>
       </c>
@@ -15925,6 +15925,22 @@
   </sheetData>
   <dataConsolidate/>
   <mergeCells count="32">
+    <mergeCell ref="C234:D256"/>
+    <mergeCell ref="C204:D204"/>
+    <mergeCell ref="F204:H204"/>
+    <mergeCell ref="J204:L204"/>
+    <mergeCell ref="A232:A233"/>
+    <mergeCell ref="C232:D232"/>
+    <mergeCell ref="F232:H232"/>
+    <mergeCell ref="J232:L232"/>
+    <mergeCell ref="C210:D228"/>
+    <mergeCell ref="C208:D209"/>
+    <mergeCell ref="C205:D205"/>
+    <mergeCell ref="A175:A176"/>
+    <mergeCell ref="C175:D175"/>
+    <mergeCell ref="F175:H175"/>
+    <mergeCell ref="J175:L175"/>
+    <mergeCell ref="C177:D199"/>
     <mergeCell ref="C258:D280"/>
     <mergeCell ref="J149:L149"/>
     <mergeCell ref="C151:D173"/>
@@ -15941,22 +15957,6 @@
     <mergeCell ref="J100:L100"/>
     <mergeCell ref="C103:D124"/>
     <mergeCell ref="C126:D146"/>
-    <mergeCell ref="A175:A176"/>
-    <mergeCell ref="C175:D175"/>
-    <mergeCell ref="F175:H175"/>
-    <mergeCell ref="J175:L175"/>
-    <mergeCell ref="C177:D199"/>
-    <mergeCell ref="C234:D256"/>
-    <mergeCell ref="C204:D204"/>
-    <mergeCell ref="F204:H204"/>
-    <mergeCell ref="J204:L204"/>
-    <mergeCell ref="A232:A233"/>
-    <mergeCell ref="C232:D232"/>
-    <mergeCell ref="F232:H232"/>
-    <mergeCell ref="J232:L232"/>
-    <mergeCell ref="C210:D228"/>
-    <mergeCell ref="C208:D209"/>
-    <mergeCell ref="C205:D205"/>
   </mergeCells>
   <conditionalFormatting sqref="C7:L7 C29:L29">
     <cfRule type="cellIs" dxfId="29" priority="31" operator="between">
@@ -16136,10 +16136,10 @@
         <f ca="1">E2-B2</f>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I2" s="517" t="s">
+      <c r="I2" s="519" t="s">
         <v>52</v>
       </c>
-      <c r="J2" s="518" t="s">
+      <c r="J2" s="520" t="s">
         <v>46</v>
       </c>
       <c r="K2" s="3" t="s">
@@ -16175,8 +16175,8 @@
         <f t="shared" ref="F3:F66" ca="1" si="0">E3-B3</f>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I3" s="517"/>
-      <c r="J3" s="519"/>
+      <c r="I3" s="519"/>
+      <c r="J3" s="521"/>
       <c r="K3" s="5" t="s">
         <v>106</v>
       </c>
@@ -16210,8 +16210,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I4" s="517"/>
-      <c r="J4" s="519"/>
+      <c r="I4" s="519"/>
+      <c r="J4" s="521"/>
       <c r="K4" s="114" t="s">
         <v>107</v>
       </c>
@@ -16245,8 +16245,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I5" s="517"/>
-      <c r="J5" s="519"/>
+      <c r="I5" s="519"/>
+      <c r="J5" s="521"/>
       <c r="K5" s="3" t="s">
         <v>108</v>
       </c>
@@ -16280,8 +16280,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I6" s="517"/>
-      <c r="J6" s="519"/>
+      <c r="I6" s="519"/>
+      <c r="J6" s="521"/>
       <c r="K6" s="5" t="s">
         <v>106</v>
       </c>
@@ -16315,8 +16315,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I7" s="517"/>
-      <c r="J7" s="519"/>
+      <c r="I7" s="519"/>
+      <c r="J7" s="521"/>
       <c r="K7" s="7" t="s">
         <v>107</v>
       </c>
@@ -16350,8 +16350,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I8" s="517"/>
-      <c r="J8" s="519"/>
+      <c r="I8" s="519"/>
+      <c r="J8" s="521"/>
       <c r="K8" s="3" t="s">
         <v>109</v>
       </c>
@@ -16385,8 +16385,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I9" s="517"/>
-      <c r="J9" s="519"/>
+      <c r="I9" s="519"/>
+      <c r="J9" s="521"/>
       <c r="K9" s="5" t="s">
         <v>106</v>
       </c>
@@ -16420,8 +16420,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I10" s="517"/>
-      <c r="J10" s="520"/>
+      <c r="I10" s="519"/>
+      <c r="J10" s="522"/>
       <c r="K10" s="114" t="s">
         <v>107</v>
       </c>
@@ -16455,7 +16455,7 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I11" s="517"/>
+      <c r="I11" s="519"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -16482,8 +16482,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I12" s="517"/>
-      <c r="J12" s="514" t="s">
+      <c r="I12" s="519"/>
+      <c r="J12" s="516" t="s">
         <v>110</v>
       </c>
       <c r="K12" s="3" t="s">
@@ -16519,8 +16519,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I13" s="517"/>
-      <c r="J13" s="515"/>
+      <c r="I13" s="519"/>
+      <c r="J13" s="517"/>
       <c r="K13" s="5" t="s">
         <v>106</v>
       </c>
@@ -16554,8 +16554,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I14" s="517"/>
-      <c r="J14" s="515"/>
+      <c r="I14" s="519"/>
+      <c r="J14" s="517"/>
       <c r="K14" s="118" t="s">
         <v>107</v>
       </c>
@@ -16589,8 +16589,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I15" s="517"/>
-      <c r="J15" s="515"/>
+      <c r="I15" s="519"/>
+      <c r="J15" s="517"/>
       <c r="K15" s="3" t="s">
         <v>108</v>
       </c>
@@ -16627,8 +16627,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I16" s="517"/>
-      <c r="J16" s="515"/>
+      <c r="I16" s="519"/>
+      <c r="J16" s="517"/>
       <c r="K16" s="5" t="s">
         <v>106</v>
       </c>
@@ -16666,8 +16666,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I17" s="517"/>
-      <c r="J17" s="515"/>
+      <c r="I17" s="519"/>
+      <c r="J17" s="517"/>
       <c r="K17" s="114" t="s">
         <v>107</v>
       </c>
@@ -16704,8 +16704,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I18" s="517"/>
-      <c r="J18" s="515"/>
+      <c r="I18" s="519"/>
+      <c r="J18" s="517"/>
       <c r="K18" s="5" t="s">
         <v>109</v>
       </c>
@@ -16739,8 +16739,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I19" s="517"/>
-      <c r="J19" s="515"/>
+      <c r="I19" s="519"/>
+      <c r="J19" s="517"/>
       <c r="K19" s="5" t="s">
         <v>106</v>
       </c>
@@ -16774,8 +16774,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-16.537499999999966</v>
       </c>
-      <c r="I20" s="517"/>
-      <c r="J20" s="516"/>
+      <c r="I20" s="519"/>
+      <c r="J20" s="518"/>
       <c r="K20" s="114" t="s">
         <v>107</v>
       </c>
@@ -16835,10 +16835,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I22" s="513" t="s">
+      <c r="I22" s="515" t="s">
         <v>112</v>
       </c>
-      <c r="J22" s="514" t="s">
+      <c r="J22" s="516" t="s">
         <v>110</v>
       </c>
       <c r="K22" s="3" t="s">
@@ -16874,8 +16874,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I23" s="513"/>
-      <c r="J23" s="515"/>
+      <c r="I23" s="515"/>
+      <c r="J23" s="517"/>
       <c r="K23" s="5" t="s">
         <v>106</v>
       </c>
@@ -16909,8 +16909,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I24" s="513"/>
-      <c r="J24" s="515"/>
+      <c r="I24" s="515"/>
+      <c r="J24" s="517"/>
       <c r="K24" s="118" t="s">
         <v>107</v>
       </c>
@@ -16944,8 +16944,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I25" s="513"/>
-      <c r="J25" s="515"/>
+      <c r="I25" s="515"/>
+      <c r="J25" s="517"/>
       <c r="K25" s="3" t="s">
         <v>108</v>
       </c>
@@ -16979,8 +16979,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I26" s="513"/>
-      <c r="J26" s="515"/>
+      <c r="I26" s="515"/>
+      <c r="J26" s="517"/>
       <c r="K26" s="5" t="s">
         <v>106</v>
       </c>
@@ -17014,8 +17014,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I27" s="513"/>
-      <c r="J27" s="515"/>
+      <c r="I27" s="515"/>
+      <c r="J27" s="517"/>
       <c r="K27" s="114" t="s">
         <v>107</v>
       </c>
@@ -17049,8 +17049,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I28" s="513"/>
-      <c r="J28" s="515"/>
+      <c r="I28" s="515"/>
+      <c r="J28" s="517"/>
       <c r="K28" s="5" t="s">
         <v>109</v>
       </c>
@@ -17084,8 +17084,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I29" s="513"/>
-      <c r="J29" s="515"/>
+      <c r="I29" s="515"/>
+      <c r="J29" s="517"/>
       <c r="K29" s="5" t="s">
         <v>106</v>
       </c>
@@ -17119,8 +17119,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I30" s="513"/>
-      <c r="J30" s="516"/>
+      <c r="I30" s="515"/>
+      <c r="J30" s="518"/>
       <c r="K30" s="114" t="s">
         <v>107</v>
       </c>
@@ -17180,10 +17180,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I32" s="513" t="s">
+      <c r="I32" s="515" t="s">
         <v>113</v>
       </c>
-      <c r="J32" s="514" t="s">
+      <c r="J32" s="516" t="s">
         <v>110</v>
       </c>
       <c r="K32" s="3" t="s">
@@ -17219,8 +17219,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I33" s="513"/>
-      <c r="J33" s="515"/>
+      <c r="I33" s="515"/>
+      <c r="J33" s="517"/>
       <c r="K33" s="5" t="s">
         <v>106</v>
       </c>
@@ -17254,8 +17254,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I34" s="513"/>
-      <c r="J34" s="515"/>
+      <c r="I34" s="515"/>
+      <c r="J34" s="517"/>
       <c r="K34" s="118" t="s">
         <v>107</v>
       </c>
@@ -17289,8 +17289,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I35" s="513"/>
-      <c r="J35" s="515"/>
+      <c r="I35" s="515"/>
+      <c r="J35" s="517"/>
       <c r="K35" s="3" t="s">
         <v>108</v>
       </c>
@@ -17324,8 +17324,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I36" s="513"/>
-      <c r="J36" s="515"/>
+      <c r="I36" s="515"/>
+      <c r="J36" s="517"/>
       <c r="K36" s="5" t="s">
         <v>106</v>
       </c>
@@ -17359,8 +17359,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I37" s="513"/>
-      <c r="J37" s="515"/>
+      <c r="I37" s="515"/>
+      <c r="J37" s="517"/>
       <c r="K37" s="114" t="s">
         <v>107</v>
       </c>
@@ -17394,8 +17394,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I38" s="513"/>
-      <c r="J38" s="515"/>
+      <c r="I38" s="515"/>
+      <c r="J38" s="517"/>
       <c r="K38" s="5" t="s">
         <v>109</v>
       </c>
@@ -17429,8 +17429,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I39" s="513"/>
-      <c r="J39" s="515"/>
+      <c r="I39" s="515"/>
+      <c r="J39" s="517"/>
       <c r="K39" s="5" t="s">
         <v>106</v>
       </c>
@@ -17464,8 +17464,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I40" s="513"/>
-      <c r="J40" s="516"/>
+      <c r="I40" s="515"/>
+      <c r="J40" s="518"/>
       <c r="K40" s="114" t="s">
         <v>107</v>
       </c>
@@ -17525,10 +17525,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I42" s="513" t="s">
+      <c r="I42" s="515" t="s">
         <v>114</v>
       </c>
-      <c r="J42" s="514" t="s">
+      <c r="J42" s="516" t="s">
         <v>110</v>
       </c>
       <c r="K42" s="3" t="s">
@@ -17564,8 +17564,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I43" s="513"/>
-      <c r="J43" s="515"/>
+      <c r="I43" s="515"/>
+      <c r="J43" s="517"/>
       <c r="K43" s="5" t="s">
         <v>106</v>
       </c>
@@ -17599,8 +17599,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.77249999999998</v>
       </c>
-      <c r="I44" s="513"/>
-      <c r="J44" s="515"/>
+      <c r="I44" s="515"/>
+      <c r="J44" s="517"/>
       <c r="K44" s="118" t="s">
         <v>107</v>
       </c>
@@ -17634,8 +17634,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I45" s="513"/>
-      <c r="J45" s="515"/>
+      <c r="I45" s="515"/>
+      <c r="J45" s="517"/>
       <c r="K45" s="3" t="s">
         <v>108</v>
       </c>
@@ -17669,8 +17669,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I46" s="513"/>
-      <c r="J46" s="515"/>
+      <c r="I46" s="515"/>
+      <c r="J46" s="517"/>
       <c r="K46" s="5" t="s">
         <v>106</v>
       </c>
@@ -17704,8 +17704,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I47" s="513"/>
-      <c r="J47" s="515"/>
+      <c r="I47" s="515"/>
+      <c r="J47" s="517"/>
       <c r="K47" s="114" t="s">
         <v>107</v>
       </c>
@@ -17739,8 +17739,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I48" s="513"/>
-      <c r="J48" s="515"/>
+      <c r="I48" s="515"/>
+      <c r="J48" s="517"/>
       <c r="K48" s="5" t="s">
         <v>109</v>
       </c>
@@ -17774,8 +17774,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I49" s="513"/>
-      <c r="J49" s="515"/>
+      <c r="I49" s="515"/>
+      <c r="J49" s="517"/>
       <c r="K49" s="5" t="s">
         <v>106</v>
       </c>
@@ -17809,8 +17809,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I50" s="513"/>
-      <c r="J50" s="516"/>
+      <c r="I50" s="515"/>
+      <c r="J50" s="518"/>
       <c r="K50" s="114" t="s">
         <v>107</v>
       </c>
@@ -17870,10 +17870,10 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I52" s="513" t="s">
+      <c r="I52" s="515" t="s">
         <v>222</v>
       </c>
-      <c r="J52" s="514" t="s">
+      <c r="J52" s="516" t="s">
         <v>110</v>
       </c>
       <c r="K52" s="3" t="s">
@@ -17909,8 +17909,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I53" s="513"/>
-      <c r="J53" s="515"/>
+      <c r="I53" s="515"/>
+      <c r="J53" s="517"/>
       <c r="K53" s="5" t="s">
         <v>106</v>
       </c>
@@ -17944,8 +17944,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I54" s="513"/>
-      <c r="J54" s="515"/>
+      <c r="I54" s="515"/>
+      <c r="J54" s="517"/>
       <c r="K54" s="118" t="s">
         <v>107</v>
       </c>
@@ -17979,8 +17979,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I55" s="513"/>
-      <c r="J55" s="515"/>
+      <c r="I55" s="515"/>
+      <c r="J55" s="517"/>
       <c r="K55" s="3" t="s">
         <v>108</v>
       </c>
@@ -18014,8 +18014,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I56" s="513"/>
-      <c r="J56" s="515"/>
+      <c r="I56" s="515"/>
+      <c r="J56" s="517"/>
       <c r="K56" s="5" t="s">
         <v>106</v>
       </c>
@@ -18049,8 +18049,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I57" s="513"/>
-      <c r="J57" s="515"/>
+      <c r="I57" s="515"/>
+      <c r="J57" s="517"/>
       <c r="K57" s="114" t="s">
         <v>107</v>
       </c>
@@ -18084,8 +18084,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I58" s="513"/>
-      <c r="J58" s="515"/>
+      <c r="I58" s="515"/>
+      <c r="J58" s="517"/>
       <c r="K58" s="5" t="s">
         <v>109</v>
       </c>
@@ -18119,8 +18119,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I59" s="513"/>
-      <c r="J59" s="515"/>
+      <c r="I59" s="515"/>
+      <c r="J59" s="517"/>
       <c r="K59" s="5" t="s">
         <v>106</v>
       </c>
@@ -18154,8 +18154,8 @@
         <f t="shared" ca="1" si="0"/>
         <v>-19.649999999999977</v>
       </c>
-      <c r="I60" s="513"/>
-      <c r="J60" s="516"/>
+      <c r="I60" s="515"/>
+      <c r="J60" s="518"/>
       <c r="K60" s="114" t="s">
         <v>107</v>
       </c>
@@ -18392,10 +18392,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A2), MONTH(A2), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H2" s="517" t="s">
+      <c r="H2" s="519" t="s">
         <v>52</v>
       </c>
-      <c r="I2" s="518" t="s">
+      <c r="I2" s="520" t="s">
         <v>46</v>
       </c>
       <c r="J2" s="3" t="s">
@@ -18427,8 +18427,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A3), MONTH(A3), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H3" s="517"/>
-      <c r="I3" s="519"/>
+      <c r="H3" s="519"/>
+      <c r="I3" s="521"/>
       <c r="J3" s="5" t="s">
         <v>106</v>
       </c>
@@ -18458,8 +18458,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A4), MONTH(A4), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H4" s="517"/>
-      <c r="I4" s="519"/>
+      <c r="H4" s="519"/>
+      <c r="I4" s="521"/>
       <c r="J4" s="114" t="s">
         <v>107</v>
       </c>
@@ -18489,8 +18489,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A5), MONTH(A5), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H5" s="517"/>
-      <c r="I5" s="519"/>
+      <c r="H5" s="519"/>
+      <c r="I5" s="521"/>
       <c r="J5" s="3" t="s">
         <v>108</v>
       </c>
@@ -18520,8 +18520,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A6), MONTH(A6), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H6" s="517"/>
-      <c r="I6" s="519"/>
+      <c r="H6" s="519"/>
+      <c r="I6" s="521"/>
       <c r="J6" s="5" t="s">
         <v>106</v>
       </c>
@@ -18551,8 +18551,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A7), MONTH(A7), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H7" s="517"/>
-      <c r="I7" s="519"/>
+      <c r="H7" s="519"/>
+      <c r="I7" s="521"/>
       <c r="J7" s="7" t="s">
         <v>107</v>
       </c>
@@ -18582,8 +18582,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A8), MONTH(A8), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H8" s="517"/>
-      <c r="I8" s="519"/>
+      <c r="H8" s="519"/>
+      <c r="I8" s="521"/>
       <c r="J8" s="3" t="s">
         <v>109</v>
       </c>
@@ -18613,8 +18613,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A9), MONTH(A9), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H9" s="517"/>
-      <c r="I9" s="519"/>
+      <c r="H9" s="519"/>
+      <c r="I9" s="521"/>
       <c r="J9" s="5" t="s">
         <v>106</v>
       </c>
@@ -18644,8 +18644,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A10), MONTH(A10), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H10" s="517"/>
-      <c r="I10" s="520"/>
+      <c r="H10" s="519"/>
+      <c r="I10" s="522"/>
       <c r="J10" s="114" t="s">
         <v>107</v>
       </c>
@@ -18675,7 +18675,7 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A11), MONTH(A11), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H11" s="517"/>
+      <c r="H11" s="519"/>
       <c r="Q11" t="s">
         <v>153</v>
       </c>
@@ -18701,8 +18701,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A12), MONTH(A12), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H12" s="517"/>
-      <c r="I12" s="514" t="s">
+      <c r="H12" s="519"/>
+      <c r="I12" s="516" t="s">
         <v>110</v>
       </c>
       <c r="J12" s="3" t="s">
@@ -18740,8 +18740,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A13), MONTH(A13), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H13" s="517"/>
-      <c r="I13" s="515"/>
+      <c r="H13" s="519"/>
+      <c r="I13" s="517"/>
       <c r="J13" s="5" t="s">
         <v>106</v>
       </c>
@@ -18774,8 +18774,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A14), MONTH(A14), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H14" s="517"/>
-      <c r="I14" s="515"/>
+      <c r="H14" s="519"/>
+      <c r="I14" s="517"/>
       <c r="J14" s="118" t="s">
         <v>107</v>
       </c>
@@ -18805,8 +18805,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A15), MONTH(A15), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H15" s="517"/>
-      <c r="I15" s="515"/>
+      <c r="H15" s="519"/>
+      <c r="I15" s="517"/>
       <c r="J15" s="3" t="s">
         <v>108</v>
       </c>
@@ -18836,8 +18836,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A16), MONTH(A16), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H16" s="517"/>
-      <c r="I16" s="515"/>
+      <c r="H16" s="519"/>
+      <c r="I16" s="517"/>
       <c r="J16" s="5" t="s">
         <v>106</v>
       </c>
@@ -18867,8 +18867,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A17), MONTH(A17), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H17" s="517"/>
-      <c r="I17" s="515"/>
+      <c r="H17" s="519"/>
+      <c r="I17" s="517"/>
       <c r="J17" s="114" t="s">
         <v>107</v>
       </c>
@@ -18901,8 +18901,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A18), MONTH(A18), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H18" s="517"/>
-      <c r="I18" s="515"/>
+      <c r="H18" s="519"/>
+      <c r="I18" s="517"/>
       <c r="J18" s="5" t="s">
         <v>109</v>
       </c>
@@ -18932,8 +18932,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A19), MONTH(A19), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H19" s="517"/>
-      <c r="I19" s="515"/>
+      <c r="H19" s="519"/>
+      <c r="I19" s="517"/>
       <c r="J19" s="5" t="s">
         <v>106</v>
       </c>
@@ -18963,8 +18963,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A20), MONTH(A20), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>15.875</v>
       </c>
-      <c r="H20" s="517"/>
-      <c r="I20" s="516"/>
+      <c r="H20" s="519"/>
+      <c r="I20" s="518"/>
       <c r="J20" s="114" t="s">
         <v>107</v>
       </c>
@@ -19016,10 +19016,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A22), MONTH(A22), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H22" s="513" t="s">
+      <c r="H22" s="515" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="514" t="s">
+      <c r="I22" s="516" t="s">
         <v>110</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -19051,8 +19051,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A23), MONTH(A23), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H23" s="513"/>
-      <c r="I23" s="515"/>
+      <c r="H23" s="515"/>
+      <c r="I23" s="517"/>
       <c r="J23" s="5" t="s">
         <v>106</v>
       </c>
@@ -19082,8 +19082,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A24), MONTH(A24), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H24" s="513"/>
-      <c r="I24" s="515"/>
+      <c r="H24" s="515"/>
+      <c r="I24" s="517"/>
       <c r="J24" s="118" t="s">
         <v>107</v>
       </c>
@@ -19113,8 +19113,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A25), MONTH(A25), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H25" s="513"/>
-      <c r="I25" s="515"/>
+      <c r="H25" s="515"/>
+      <c r="I25" s="517"/>
       <c r="J25" s="3" t="s">
         <v>108</v>
       </c>
@@ -19144,8 +19144,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A26), MONTH(A26), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H26" s="513"/>
-      <c r="I26" s="515"/>
+      <c r="H26" s="515"/>
+      <c r="I26" s="517"/>
       <c r="J26" s="5" t="s">
         <v>106</v>
       </c>
@@ -19175,8 +19175,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A27), MONTH(A27), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H27" s="513"/>
-      <c r="I27" s="515"/>
+      <c r="H27" s="515"/>
+      <c r="I27" s="517"/>
       <c r="J27" s="114" t="s">
         <v>107</v>
       </c>
@@ -19206,8 +19206,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A28), MONTH(A28), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H28" s="513"/>
-      <c r="I28" s="515"/>
+      <c r="H28" s="515"/>
+      <c r="I28" s="517"/>
       <c r="J28" s="5" t="s">
         <v>109</v>
       </c>
@@ -19237,8 +19237,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A29), MONTH(A29), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H29" s="513"/>
-      <c r="I29" s="515"/>
+      <c r="H29" s="515"/>
+      <c r="I29" s="517"/>
       <c r="J29" s="5" t="s">
         <v>106</v>
       </c>
@@ -19268,8 +19268,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A30), MONTH(A30), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H30" s="513"/>
-      <c r="I30" s="516"/>
+      <c r="H30" s="515"/>
+      <c r="I30" s="518"/>
       <c r="J30" s="114" t="s">
         <v>107</v>
       </c>
@@ -19321,10 +19321,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A32), MONTH(A32), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H32" s="513" t="s">
+      <c r="H32" s="515" t="s">
         <v>113</v>
       </c>
-      <c r="I32" s="514" t="s">
+      <c r="I32" s="516" t="s">
         <v>110</v>
       </c>
       <c r="J32" s="3" t="s">
@@ -19356,8 +19356,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A33), MONTH(A33), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H33" s="513"/>
-      <c r="I33" s="515"/>
+      <c r="H33" s="515"/>
+      <c r="I33" s="517"/>
       <c r="J33" s="5" t="s">
         <v>106</v>
       </c>
@@ -19387,8 +19387,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A34), MONTH(A34), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H34" s="513"/>
-      <c r="I34" s="515"/>
+      <c r="H34" s="515"/>
+      <c r="I34" s="517"/>
       <c r="J34" s="118" t="s">
         <v>107</v>
       </c>
@@ -19418,8 +19418,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A35), MONTH(A35), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H35" s="513"/>
-      <c r="I35" s="515"/>
+      <c r="H35" s="515"/>
+      <c r="I35" s="517"/>
       <c r="J35" s="3" t="s">
         <v>108</v>
       </c>
@@ -19449,8 +19449,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A36), MONTH(A36), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H36" s="513"/>
-      <c r="I36" s="515"/>
+      <c r="H36" s="515"/>
+      <c r="I36" s="517"/>
       <c r="J36" s="5" t="s">
         <v>106</v>
       </c>
@@ -19480,8 +19480,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A37), MONTH(A37), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H37" s="513"/>
-      <c r="I37" s="515"/>
+      <c r="H37" s="515"/>
+      <c r="I37" s="517"/>
       <c r="J37" s="114" t="s">
         <v>107</v>
       </c>
@@ -19511,8 +19511,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A38), MONTH(A38), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H38" s="513"/>
-      <c r="I38" s="515"/>
+      <c r="H38" s="515"/>
+      <c r="I38" s="517"/>
       <c r="J38" s="5" t="s">
         <v>109</v>
       </c>
@@ -19542,8 +19542,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A39), MONTH(A39), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H39" s="513"/>
-      <c r="I39" s="515"/>
+      <c r="H39" s="515"/>
+      <c r="I39" s="517"/>
       <c r="J39" s="5" t="s">
         <v>106</v>
       </c>
@@ -19573,8 +19573,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A40), MONTH(A40), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H40" s="513"/>
-      <c r="I40" s="516"/>
+      <c r="H40" s="515"/>
+      <c r="I40" s="518"/>
       <c r="J40" s="114" t="s">
         <v>107</v>
       </c>
@@ -19626,10 +19626,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A42), MONTH(A42), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H42" s="513" t="s">
+      <c r="H42" s="515" t="s">
         <v>114</v>
       </c>
-      <c r="I42" s="514" t="s">
+      <c r="I42" s="516" t="s">
         <v>110</v>
       </c>
       <c r="J42" s="3" t="s">
@@ -19661,8 +19661,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A43), MONTH(A43), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H43" s="513"/>
-      <c r="I43" s="515"/>
+      <c r="H43" s="515"/>
+      <c r="I43" s="517"/>
       <c r="J43" s="5" t="s">
         <v>106</v>
       </c>
@@ -19692,8 +19692,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A44), MONTH(A44), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>13.97</v>
       </c>
-      <c r="H44" s="513"/>
-      <c r="I44" s="515"/>
+      <c r="H44" s="515"/>
+      <c r="I44" s="517"/>
       <c r="J44" s="118" t="s">
         <v>107</v>
       </c>
@@ -19723,8 +19723,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A45), MONTH(A45), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H45" s="513"/>
-      <c r="I45" s="515"/>
+      <c r="H45" s="515"/>
+      <c r="I45" s="517"/>
       <c r="J45" s="3" t="s">
         <v>108</v>
       </c>
@@ -19754,8 +19754,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A46), MONTH(A46), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H46" s="513"/>
-      <c r="I46" s="515"/>
+      <c r="H46" s="515"/>
+      <c r="I46" s="517"/>
       <c r="J46" s="5" t="s">
         <v>106</v>
       </c>
@@ -19785,8 +19785,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A47), MONTH(A47), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H47" s="513"/>
-      <c r="I47" s="515"/>
+      <c r="H47" s="515"/>
+      <c r="I47" s="517"/>
       <c r="J47" s="114" t="s">
         <v>107</v>
       </c>
@@ -19816,8 +19816,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A48), MONTH(A48), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H48" s="513"/>
-      <c r="I48" s="515"/>
+      <c r="H48" s="515"/>
+      <c r="I48" s="517"/>
       <c r="J48" s="5" t="s">
         <v>109</v>
       </c>
@@ -19847,8 +19847,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A49), MONTH(A49), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H49" s="513"/>
-      <c r="I49" s="515"/>
+      <c r="H49" s="515"/>
+      <c r="I49" s="517"/>
       <c r="J49" s="5" t="s">
         <v>106</v>
       </c>
@@ -19878,8 +19878,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A50), MONTH(A50), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H50" s="513"/>
-      <c r="I50" s="516"/>
+      <c r="H50" s="515"/>
+      <c r="I50" s="518"/>
       <c r="J50" s="114" t="s">
         <v>107</v>
       </c>
@@ -19931,10 +19931,10 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A52), MONTH(A52), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H52" s="513" t="s">
+      <c r="H52" s="515" t="s">
         <v>222</v>
       </c>
-      <c r="I52" s="514" t="s">
+      <c r="I52" s="516" t="s">
         <v>110</v>
       </c>
       <c r="J52" s="3" t="s">
@@ -19966,8 +19966,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A53), MONTH(A53), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H53" s="513"/>
-      <c r="I53" s="515"/>
+      <c r="H53" s="515"/>
+      <c r="I53" s="517"/>
       <c r="J53" s="5" t="s">
         <v>106</v>
       </c>
@@ -19997,8 +19997,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A54), MONTH(A54), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H54" s="513"/>
-      <c r="I54" s="515"/>
+      <c r="H54" s="515"/>
+      <c r="I54" s="517"/>
       <c r="J54" s="118" t="s">
         <v>107</v>
       </c>
@@ -20028,8 +20028,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A55), MONTH(A55), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H55" s="513"/>
-      <c r="I55" s="515"/>
+      <c r="H55" s="515"/>
+      <c r="I55" s="517"/>
       <c r="J55" s="3" t="s">
         <v>108</v>
       </c>
@@ -20059,8 +20059,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A56), MONTH(A56), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H56" s="513"/>
-      <c r="I56" s="515"/>
+      <c r="H56" s="515"/>
+      <c r="I56" s="517"/>
       <c r="J56" s="5" t="s">
         <v>106</v>
       </c>
@@ -20090,8 +20090,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A57), MONTH(A57), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H57" s="513"/>
-      <c r="I57" s="515"/>
+      <c r="H57" s="515"/>
+      <c r="I57" s="517"/>
       <c r="J57" s="114" t="s">
         <v>107</v>
       </c>
@@ -20121,8 +20121,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A58), MONTH(A58), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H58" s="513"/>
-      <c r="I58" s="515"/>
+      <c r="H58" s="515"/>
+      <c r="I58" s="517"/>
       <c r="J58" s="5" t="s">
         <v>109</v>
       </c>
@@ -20152,8 +20152,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A59), MONTH(A59), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H59" s="513"/>
-      <c r="I59" s="515"/>
+      <c r="H59" s="515"/>
+      <c r="I59" s="517"/>
       <c r="J59" s="5" t="s">
         <v>106</v>
       </c>
@@ -20183,8 +20183,8 @@
         <f ca="1">VLOOKUP(DATE(YEAR(A60), MONTH(A60), 1), 'Tullet US'!$V$24:$X$32, 3, FALSE)*6.35</f>
         <v>14.224</v>
       </c>
-      <c r="H60" s="513"/>
-      <c r="I60" s="516"/>
+      <c r="H60" s="515"/>
+      <c r="I60" s="518"/>
       <c r="J60" s="114" t="s">
         <v>107</v>
       </c>
@@ -26264,72 +26264,72 @@
   <sheetData>
     <row r="2" spans="1:36" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="371"/>
-      <c r="B2" s="532">
+      <c r="B2" s="523">
         <v>45895</v>
       </c>
-      <c r="C2" s="532"/>
+      <c r="C2" s="523"/>
     </row>
     <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="F3" s="372"/>
     </row>
     <row r="4" spans="1:36" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="533" t="s">
+      <c r="B4" s="524" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="533"/>
+      <c r="C4" s="524"/>
       <c r="R4" s="363"/>
     </row>
     <row r="5" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="521" t="s">
+      <c r="B5" s="525" t="s">
         <v>170</v>
       </c>
-      <c r="C5" s="522"/>
+      <c r="C5" s="526"/>
       <c r="D5" s="373"/>
-      <c r="E5" s="521" t="s">
+      <c r="E5" s="525" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="523"/>
+      <c r="F5" s="527"/>
       <c r="G5" s="373"/>
-      <c r="H5" s="521" t="s">
+      <c r="H5" s="525" t="s">
         <v>172</v>
       </c>
-      <c r="I5" s="522"/>
-      <c r="K5" s="521" t="s">
+      <c r="I5" s="526"/>
+      <c r="K5" s="525" t="s">
         <v>173</v>
       </c>
-      <c r="L5" s="522"/>
-      <c r="N5" s="521" t="s">
+      <c r="L5" s="526"/>
+      <c r="N5" s="525" t="s">
         <v>174</v>
       </c>
-      <c r="O5" s="522"/>
-      <c r="Q5" s="521" t="s">
+      <c r="O5" s="526"/>
+      <c r="Q5" s="525" t="s">
         <v>175</v>
       </c>
-      <c r="R5" s="522"/>
-      <c r="T5" s="521" t="s">
+      <c r="R5" s="526"/>
+      <c r="T5" s="525" t="s">
         <v>176</v>
       </c>
-      <c r="U5" s="522"/>
-      <c r="W5" s="521" t="s">
+      <c r="U5" s="526"/>
+      <c r="W5" s="525" t="s">
         <v>177</v>
       </c>
-      <c r="X5" s="522"/>
-      <c r="Z5" s="521" t="s">
+      <c r="X5" s="526"/>
+      <c r="Z5" s="525" t="s">
         <v>178</v>
       </c>
-      <c r="AA5" s="522"/>
-      <c r="AC5" s="521" t="s">
+      <c r="AA5" s="526"/>
+      <c r="AC5" s="525" t="s">
         <v>179</v>
       </c>
-      <c r="AD5" s="522"/>
-      <c r="AF5" s="521" t="s">
+      <c r="AD5" s="526"/>
+      <c r="AF5" s="525" t="s">
         <v>239</v>
       </c>
-      <c r="AG5" s="522"/>
-      <c r="AI5" s="521" t="s">
+      <c r="AG5" s="526"/>
+      <c r="AI5" s="525" t="s">
         <v>180</v>
       </c>
-      <c r="AJ5" s="522"/>
+      <c r="AJ5" s="526"/>
     </row>
     <row r="6" spans="1:36" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="374">
@@ -26509,10 +26509,10 @@
         <v>-6.67</v>
       </c>
       <c r="D8" s="373"/>
-      <c r="E8" s="521" t="s">
+      <c r="E8" s="525" t="s">
         <v>181</v>
       </c>
-      <c r="F8" s="523"/>
+      <c r="F8" s="527"/>
       <c r="G8" s="373"/>
       <c r="H8" s="377">
         <f t="shared" si="0"/>
@@ -27331,231 +27331,231 @@
       </c>
     </row>
     <row r="18" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="521" t="s">
+      <c r="B18" s="525" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="523"/>
+      <c r="C18" s="527"/>
       <c r="D18" s="373"/>
       <c r="E18" s="400"/>
       <c r="F18" s="400"/>
       <c r="G18" s="373"/>
-      <c r="H18" s="521" t="s">
+      <c r="H18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="I18" s="523"/>
-      <c r="K18" s="521" t="s">
+      <c r="I18" s="527"/>
+      <c r="K18" s="525" t="s">
         <v>185</v>
       </c>
-      <c r="L18" s="523"/>
-      <c r="N18" s="521" t="s">
+      <c r="L18" s="527"/>
+      <c r="N18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="O18" s="523"/>
-      <c r="Q18" s="521" t="s">
+      <c r="O18" s="527"/>
+      <c r="Q18" s="525" t="s">
         <v>185</v>
       </c>
-      <c r="R18" s="523"/>
-      <c r="T18" s="521" t="s">
+      <c r="R18" s="527"/>
+      <c r="T18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="U18" s="523"/>
-      <c r="W18" s="521" t="s">
+      <c r="U18" s="527"/>
+      <c r="W18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="X18" s="523"/>
-      <c r="Z18" s="521" t="s">
+      <c r="X18" s="527"/>
+      <c r="Z18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AA18" s="523"/>
-      <c r="AC18" s="521" t="s">
+      <c r="AA18" s="527"/>
+      <c r="AC18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AD18" s="523"/>
-      <c r="AF18" s="521" t="s">
+      <c r="AD18" s="527"/>
+      <c r="AF18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AG18" s="523"/>
-      <c r="AI18" s="521" t="s">
+      <c r="AG18" s="527"/>
+      <c r="AI18" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AJ18" s="523"/>
+      <c r="AJ18" s="527"/>
     </row>
     <row r="19" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="524">
+      <c r="B19" s="528">
         <v>336</v>
       </c>
-      <c r="C19" s="525"/>
+      <c r="C19" s="529"/>
       <c r="D19" s="373"/>
       <c r="E19" s="373"/>
       <c r="F19" s="400"/>
       <c r="G19" s="373"/>
-      <c r="H19" s="524"/>
-      <c r="I19" s="531"/>
-      <c r="K19" s="528">
+      <c r="H19" s="528"/>
+      <c r="I19" s="530"/>
+      <c r="K19" s="531">
         <v>941</v>
       </c>
-      <c r="L19" s="529"/>
+      <c r="L19" s="532"/>
       <c r="M19" s="373"/>
-      <c r="N19" s="528">
+      <c r="N19" s="531">
         <v>417</v>
       </c>
-      <c r="O19" s="529"/>
+      <c r="O19" s="532"/>
       <c r="P19" s="373"/>
-      <c r="Q19" s="528">
+      <c r="Q19" s="531">
         <v>1610</v>
       </c>
-      <c r="R19" s="529"/>
+      <c r="R19" s="532"/>
       <c r="S19" s="373"/>
-      <c r="T19" s="524">
+      <c r="T19" s="528">
         <v>480</v>
       </c>
-      <c r="U19" s="525"/>
+      <c r="U19" s="529"/>
       <c r="V19" s="373"/>
-      <c r="W19" s="524">
+      <c r="W19" s="528">
         <v>342</v>
       </c>
-      <c r="X19" s="525"/>
+      <c r="X19" s="529"/>
       <c r="Y19" s="373"/>
-      <c r="Z19" s="524">
+      <c r="Z19" s="528">
         <v>59</v>
       </c>
-      <c r="AA19" s="525"/>
+      <c r="AA19" s="529"/>
       <c r="AB19" s="373"/>
-      <c r="AC19" s="524">
+      <c r="AC19" s="528">
         <v>143</v>
       </c>
-      <c r="AD19" s="525"/>
+      <c r="AD19" s="529"/>
       <c r="AE19" s="373"/>
-      <c r="AF19" s="524">
+      <c r="AF19" s="528">
         <v>111</v>
       </c>
-      <c r="AG19" s="525"/>
-      <c r="AI19" s="524">
+      <c r="AG19" s="529"/>
+      <c r="AI19" s="528">
         <v>371</v>
       </c>
-      <c r="AJ19" s="525"/>
+      <c r="AJ19" s="529"/>
     </row>
     <row r="20" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="521" t="s">
+      <c r="B20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="523"/>
+      <c r="C20" s="527"/>
       <c r="D20" s="373"/>
       <c r="E20" s="373"/>
       <c r="F20" s="400"/>
       <c r="G20" s="373"/>
-      <c r="H20" s="521" t="s">
+      <c r="H20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="I20" s="523"/>
+      <c r="I20" s="527"/>
       <c r="J20" s="373"/>
-      <c r="K20" s="521" t="s">
+      <c r="K20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="L20" s="523"/>
+      <c r="L20" s="527"/>
       <c r="M20" s="373"/>
-      <c r="N20" s="521" t="s">
+      <c r="N20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="O20" s="523"/>
+      <c r="O20" s="527"/>
       <c r="P20" s="373"/>
-      <c r="Q20" s="521" t="s">
+      <c r="Q20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="R20" s="523"/>
+      <c r="R20" s="527"/>
       <c r="S20" s="373"/>
-      <c r="T20" s="521" t="s">
+      <c r="T20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="U20" s="523"/>
+      <c r="U20" s="527"/>
       <c r="V20" s="373"/>
-      <c r="W20" s="521" t="s">
+      <c r="W20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="X20" s="523"/>
+      <c r="X20" s="527"/>
       <c r="Y20" s="373"/>
-      <c r="Z20" s="521" t="s">
+      <c r="Z20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AA20" s="523"/>
+      <c r="AA20" s="527"/>
       <c r="AB20" s="373"/>
-      <c r="AC20" s="521" t="s">
+      <c r="AC20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AD20" s="523"/>
+      <c r="AD20" s="527"/>
       <c r="AE20" s="373"/>
-      <c r="AF20" s="521" t="s">
+      <c r="AF20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AG20" s="523"/>
-      <c r="AI20" s="521" t="s">
+      <c r="AG20" s="527"/>
+      <c r="AI20" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AJ20" s="523"/>
+      <c r="AJ20" s="527"/>
     </row>
     <row r="21" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="528">
+      <c r="B21" s="531">
         <f>B19-B70</f>
         <v>175</v>
       </c>
-      <c r="C21" s="529"/>
+      <c r="C21" s="532"/>
       <c r="D21" s="373"/>
       <c r="F21" s="400"/>
       <c r="G21" s="373"/>
-      <c r="H21" s="528"/>
-      <c r="I21" s="529"/>
+      <c r="H21" s="531"/>
+      <c r="I21" s="532"/>
       <c r="J21" s="373"/>
-      <c r="K21" s="528">
+      <c r="K21" s="531">
         <f>K19-E70</f>
         <v>833</v>
       </c>
-      <c r="L21" s="529"/>
+      <c r="L21" s="532"/>
       <c r="M21" s="373"/>
-      <c r="N21" s="528">
+      <c r="N21" s="531">
         <f>N19-H70</f>
         <v>327</v>
       </c>
-      <c r="O21" s="529"/>
+      <c r="O21" s="532"/>
       <c r="P21" s="373"/>
-      <c r="Q21" s="528">
+      <c r="Q21" s="531">
         <f>Q19-K70</f>
         <v>440</v>
       </c>
-      <c r="R21" s="525"/>
+      <c r="R21" s="529"/>
       <c r="S21" s="373"/>
-      <c r="T21" s="524">
+      <c r="T21" s="528">
         <f>T19-N70</f>
         <v>-20</v>
       </c>
-      <c r="U21" s="525"/>
+      <c r="U21" s="529"/>
       <c r="V21" s="373"/>
-      <c r="W21" s="524">
+      <c r="W21" s="528">
         <f>W19-Q70</f>
         <v>47</v>
       </c>
-      <c r="X21" s="525"/>
+      <c r="X21" s="529"/>
       <c r="Y21" s="373"/>
-      <c r="Z21" s="524">
+      <c r="Z21" s="528">
         <f>Z19-T70</f>
         <v>58</v>
       </c>
-      <c r="AA21" s="525"/>
+      <c r="AA21" s="529"/>
       <c r="AB21" s="373"/>
-      <c r="AC21" s="524">
+      <c r="AC21" s="528">
         <f>AC19-W70</f>
         <v>111</v>
       </c>
-      <c r="AD21" s="525"/>
-      <c r="AF21" s="524">
+      <c r="AD21" s="529"/>
+      <c r="AF21" s="528">
         <f>AF19-Z70</f>
         <v>6</v>
       </c>
-      <c r="AG21" s="525"/>
-      <c r="AI21" s="524">
+      <c r="AG21" s="529"/>
+      <c r="AI21" s="528">
         <f>AI19-AC70</f>
         <v>281</v>
       </c>
-      <c r="AJ21" s="525"/>
+      <c r="AJ21" s="529"/>
     </row>
     <row r="22" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="AZ22" s="373"/>
@@ -27571,60 +27571,60 @@
       <c r="BJ22" s="373"/>
     </row>
     <row r="23" spans="1:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B23" s="521" t="s">
+      <c r="B23" s="525" t="s">
         <v>187</v>
       </c>
-      <c r="C23" s="522"/>
+      <c r="C23" s="526"/>
       <c r="D23" s="373"/>
-      <c r="E23" s="521" t="s">
+      <c r="E23" s="525" t="s">
         <v>188</v>
       </c>
-      <c r="F23" s="523"/>
+      <c r="F23" s="527"/>
       <c r="G23" s="373"/>
-      <c r="H23" s="521" t="s">
+      <c r="H23" s="525" t="s">
         <v>189</v>
       </c>
-      <c r="I23" s="522"/>
+      <c r="I23" s="526"/>
       <c r="J23" s="373"/>
-      <c r="K23" s="521" t="s">
+      <c r="K23" s="525" t="s">
         <v>190</v>
       </c>
-      <c r="L23" s="522"/>
+      <c r="L23" s="526"/>
       <c r="M23" s="373"/>
-      <c r="N23" s="521" t="s">
+      <c r="N23" s="525" t="s">
         <v>191</v>
       </c>
-      <c r="O23" s="522"/>
+      <c r="O23" s="526"/>
       <c r="P23" s="373"/>
-      <c r="Q23" s="521" t="s">
+      <c r="Q23" s="525" t="s">
         <v>192</v>
       </c>
-      <c r="R23" s="522"/>
+      <c r="R23" s="526"/>
       <c r="S23" s="373"/>
-      <c r="T23" s="521" t="s">
+      <c r="T23" s="525" t="s">
         <v>193</v>
       </c>
-      <c r="U23" s="522"/>
+      <c r="U23" s="526"/>
       <c r="V23" s="373"/>
-      <c r="W23" s="521" t="s">
+      <c r="W23" s="525" t="s">
         <v>194</v>
       </c>
-      <c r="X23" s="522"/>
+      <c r="X23" s="526"/>
       <c r="Y23" s="373"/>
-      <c r="Z23" s="521" t="s">
+      <c r="Z23" s="525" t="s">
         <v>195</v>
       </c>
-      <c r="AA23" s="522"/>
+      <c r="AA23" s="526"/>
       <c r="AB23" s="373"/>
-      <c r="AC23" s="521" t="s">
+      <c r="AC23" s="525" t="s">
         <v>196</v>
       </c>
-      <c r="AD23" s="522"/>
+      <c r="AD23" s="526"/>
       <c r="AE23" s="373"/>
-      <c r="AF23" s="521" t="s">
+      <c r="AF23" s="525" t="s">
         <v>197</v>
       </c>
-      <c r="AG23" s="522"/>
+      <c r="AG23" s="526"/>
       <c r="AZ23" s="373"/>
       <c r="BA23" s="373"/>
       <c r="BB23" s="373"/>
@@ -28923,219 +28923,219 @@
       <c r="BJ35" s="373"/>
     </row>
     <row r="36" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B36" s="521" t="s">
+      <c r="B36" s="525" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="523"/>
+      <c r="C36" s="527"/>
       <c r="D36" s="373"/>
-      <c r="E36" s="521" t="s">
+      <c r="E36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="F36" s="523"/>
+      <c r="F36" s="527"/>
       <c r="G36" s="373"/>
-      <c r="H36" s="521" t="s">
+      <c r="H36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="I36" s="523"/>
+      <c r="I36" s="527"/>
       <c r="J36" s="373"/>
-      <c r="K36" s="521" t="s">
+      <c r="K36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="L36" s="523"/>
+      <c r="L36" s="527"/>
       <c r="M36" s="373"/>
-      <c r="N36" s="521" t="s">
+      <c r="N36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="O36" s="523"/>
+      <c r="O36" s="527"/>
       <c r="P36" s="373"/>
-      <c r="Q36" s="521" t="s">
+      <c r="Q36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="R36" s="523"/>
+      <c r="R36" s="527"/>
       <c r="S36" s="373"/>
-      <c r="T36" s="521" t="s">
+      <c r="T36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="U36" s="523"/>
+      <c r="U36" s="527"/>
       <c r="V36" s="373"/>
-      <c r="W36" s="521" t="s">
+      <c r="W36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="X36" s="523"/>
+      <c r="X36" s="527"/>
       <c r="Y36" s="373"/>
-      <c r="Z36" s="521" t="s">
+      <c r="Z36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AA36" s="523"/>
+      <c r="AA36" s="527"/>
       <c r="AB36" s="373"/>
-      <c r="AC36" s="521" t="s">
+      <c r="AC36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AD36" s="523"/>
+      <c r="AD36" s="527"/>
       <c r="AE36" s="373"/>
-      <c r="AF36" s="521" t="s">
+      <c r="AF36" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AG36" s="523"/>
+      <c r="AG36" s="527"/>
     </row>
     <row r="37" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B37" s="528">
+      <c r="B37" s="531">
         <v>1150</v>
       </c>
-      <c r="C37" s="529"/>
+      <c r="C37" s="532"/>
       <c r="D37" s="373"/>
-      <c r="E37" s="528">
+      <c r="E37" s="531">
         <v>764</v>
       </c>
-      <c r="F37" s="529"/>
+      <c r="F37" s="532"/>
       <c r="G37" s="373"/>
-      <c r="H37" s="528">
+      <c r="H37" s="531">
         <v>115</v>
       </c>
-      <c r="I37" s="529"/>
+      <c r="I37" s="532"/>
       <c r="J37" s="373"/>
-      <c r="K37" s="524">
+      <c r="K37" s="528">
         <v>96</v>
       </c>
-      <c r="L37" s="525"/>
+      <c r="L37" s="529"/>
       <c r="M37" s="373"/>
-      <c r="N37" s="524"/>
-      <c r="O37" s="525"/>
+      <c r="N37" s="528"/>
+      <c r="O37" s="529"/>
       <c r="P37" s="373"/>
-      <c r="Q37" s="524">
+      <c r="Q37" s="528">
         <v>35</v>
       </c>
-      <c r="R37" s="525"/>
+      <c r="R37" s="529"/>
       <c r="S37" s="373"/>
-      <c r="T37" s="524">
+      <c r="T37" s="528">
         <v>0</v>
       </c>
-      <c r="U37" s="525"/>
+      <c r="U37" s="529"/>
       <c r="V37" s="373"/>
-      <c r="W37" s="524"/>
-      <c r="X37" s="525"/>
+      <c r="W37" s="528"/>
+      <c r="X37" s="529"/>
       <c r="Y37" s="373"/>
-      <c r="Z37" s="524">
+      <c r="Z37" s="528">
         <v>50</v>
       </c>
-      <c r="AA37" s="525"/>
+      <c r="AA37" s="529"/>
       <c r="AB37" s="373"/>
-      <c r="AC37" s="524"/>
-      <c r="AD37" s="525"/>
+      <c r="AC37" s="528"/>
+      <c r="AD37" s="529"/>
       <c r="AE37" s="373"/>
-      <c r="AF37" s="524"/>
-      <c r="AG37" s="525"/>
+      <c r="AF37" s="528"/>
+      <c r="AG37" s="529"/>
     </row>
     <row r="38" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="521" t="s">
+      <c r="B38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="C38" s="523"/>
+      <c r="C38" s="527"/>
       <c r="D38" s="373"/>
-      <c r="E38" s="521" t="s">
+      <c r="E38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="F38" s="523"/>
+      <c r="F38" s="527"/>
       <c r="G38" s="373"/>
-      <c r="H38" s="521" t="s">
+      <c r="H38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="523"/>
+      <c r="I38" s="527"/>
       <c r="J38" s="373"/>
-      <c r="K38" s="521" t="s">
+      <c r="K38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="L38" s="523"/>
+      <c r="L38" s="527"/>
       <c r="M38" s="373"/>
-      <c r="N38" s="521" t="s">
+      <c r="N38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="O38" s="523"/>
+      <c r="O38" s="527"/>
       <c r="P38" s="373"/>
-      <c r="Q38" s="521" t="s">
+      <c r="Q38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="R38" s="523"/>
+      <c r="R38" s="527"/>
       <c r="S38" s="373"/>
-      <c r="T38" s="521" t="s">
+      <c r="T38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="U38" s="523"/>
+      <c r="U38" s="527"/>
       <c r="V38" s="373"/>
-      <c r="W38" s="521" t="s">
+      <c r="W38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="X38" s="523"/>
+      <c r="X38" s="527"/>
       <c r="Y38" s="373"/>
-      <c r="Z38" s="521" t="s">
+      <c r="Z38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AA38" s="523"/>
+      <c r="AA38" s="527"/>
       <c r="AB38" s="373"/>
-      <c r="AC38" s="521" t="s">
+      <c r="AC38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AD38" s="523"/>
+      <c r="AD38" s="527"/>
       <c r="AE38" s="373"/>
-      <c r="AF38" s="521" t="s">
+      <c r="AF38" s="525" t="s">
         <v>186</v>
       </c>
-      <c r="AG38" s="523"/>
+      <c r="AG38" s="527"/>
     </row>
     <row r="39" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B39" s="528">
+      <c r="B39" s="531">
         <f>B37-B62</f>
         <v>436</v>
       </c>
-      <c r="C39" s="529"/>
+      <c r="C39" s="532"/>
       <c r="D39" s="373"/>
-      <c r="E39" s="528">
+      <c r="E39" s="531">
         <f>E37-E62</f>
         <v>379</v>
       </c>
-      <c r="F39" s="529"/>
+      <c r="F39" s="532"/>
       <c r="G39" s="373"/>
-      <c r="H39" s="528">
+      <c r="H39" s="531">
         <f>H37-H62</f>
         <v>115</v>
       </c>
-      <c r="I39" s="529"/>
+      <c r="I39" s="532"/>
       <c r="J39" s="373"/>
-      <c r="K39" s="524">
+      <c r="K39" s="528">
         <f>K37-K62</f>
         <v>57</v>
       </c>
-      <c r="L39" s="525"/>
+      <c r="L39" s="529"/>
       <c r="M39" s="373"/>
-      <c r="N39" s="524"/>
-      <c r="O39" s="525"/>
+      <c r="N39" s="528"/>
+      <c r="O39" s="529"/>
       <c r="P39" s="373"/>
-      <c r="Q39" s="524">
+      <c r="Q39" s="528">
         <f>Q37-Q62</f>
         <v>-167</v>
       </c>
-      <c r="R39" s="525"/>
+      <c r="R39" s="529"/>
       <c r="S39" s="373"/>
-      <c r="T39" s="524">
+      <c r="T39" s="528">
         <f>T37-T62</f>
         <v>-187</v>
       </c>
-      <c r="U39" s="525"/>
+      <c r="U39" s="529"/>
       <c r="V39" s="373"/>
-      <c r="W39" s="524"/>
-      <c r="X39" s="525"/>
+      <c r="W39" s="528"/>
+      <c r="X39" s="529"/>
       <c r="Y39" s="373"/>
-      <c r="Z39" s="524">
+      <c r="Z39" s="528">
         <f>Z37-Z62</f>
         <v>0</v>
       </c>
-      <c r="AA39" s="525"/>
+      <c r="AA39" s="529"/>
       <c r="AB39" s="373"/>
-      <c r="AC39" s="524"/>
-      <c r="AD39" s="525"/>
+      <c r="AC39" s="528"/>
+      <c r="AD39" s="529"/>
       <c r="AE39" s="373"/>
-      <c r="AF39" s="524"/>
-      <c r="AG39" s="525"/>
+      <c r="AF39" s="528"/>
+      <c r="AG39" s="529"/>
     </row>
     <row r="40" spans="2:62" x14ac:dyDescent="0.25">
       <c r="B40" s="410"/>
@@ -29172,10 +29172,10 @@
       <c r="AG40" s="373"/>
     </row>
     <row r="41" spans="2:62" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="530" t="s">
+      <c r="B41" s="533" t="s">
         <v>207</v>
       </c>
-      <c r="C41" s="530"/>
+      <c r="C41" s="533"/>
       <c r="D41" s="373"/>
       <c r="E41" s="373"/>
       <c r="F41" s="373"/>
@@ -29207,59 +29207,59 @@
       <c r="AG41" s="373"/>
     </row>
     <row r="42" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B42" s="521" t="s">
+      <c r="B42" s="525" t="s">
         <v>170</v>
       </c>
-      <c r="C42" s="522"/>
+      <c r="C42" s="526"/>
       <c r="D42" s="373"/>
-      <c r="E42" s="521" t="s">
+      <c r="E42" s="525" t="s">
         <v>173</v>
       </c>
-      <c r="F42" s="522"/>
+      <c r="F42" s="526"/>
       <c r="G42" s="373"/>
-      <c r="H42" s="521" t="s">
+      <c r="H42" s="525" t="s">
         <v>174</v>
       </c>
-      <c r="I42" s="522"/>
+      <c r="I42" s="526"/>
       <c r="J42" s="373"/>
-      <c r="K42" s="521" t="s">
+      <c r="K42" s="525" t="s">
         <v>175</v>
       </c>
-      <c r="L42" s="522"/>
+      <c r="L42" s="526"/>
       <c r="M42" s="373"/>
-      <c r="N42" s="521" t="s">
+      <c r="N42" s="525" t="s">
         <v>176</v>
       </c>
-      <c r="O42" s="522"/>
+      <c r="O42" s="526"/>
       <c r="P42" s="373"/>
-      <c r="Q42" s="521" t="s">
+      <c r="Q42" s="525" t="s">
         <v>177</v>
       </c>
-      <c r="R42" s="522"/>
-      <c r="T42" s="521" t="s">
+      <c r="R42" s="526"/>
+      <c r="T42" s="525" t="s">
         <v>178</v>
       </c>
-      <c r="U42" s="522"/>
+      <c r="U42" s="526"/>
       <c r="V42" s="373"/>
-      <c r="W42" s="521" t="s">
+      <c r="W42" s="525" t="s">
         <v>179</v>
       </c>
-      <c r="X42" s="522"/>
+      <c r="X42" s="526"/>
       <c r="Y42" s="373"/>
-      <c r="Z42" s="526" t="s">
+      <c r="Z42" s="534" t="s">
         <v>239</v>
       </c>
-      <c r="AA42" s="527"/>
+      <c r="AA42" s="535"/>
       <c r="AB42" s="373"/>
-      <c r="AC42" s="521" t="s">
+      <c r="AC42" s="525" t="s">
         <v>180</v>
       </c>
-      <c r="AD42" s="522"/>
+      <c r="AD42" s="526"/>
       <c r="AE42" s="373"/>
-      <c r="AF42" s="521" t="s">
+      <c r="AF42" s="525" t="s">
         <v>197</v>
       </c>
-      <c r="AG42" s="522"/>
+      <c r="AG42" s="526"/>
     </row>
     <row r="43" spans="2:62" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="377">
@@ -29801,50 +29801,50 @@
       </c>
     </row>
     <row r="49" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B49" s="521" t="s">
+      <c r="B49" s="525" t="s">
         <v>183</v>
       </c>
-      <c r="C49" s="523"/>
+      <c r="C49" s="527"/>
       <c r="D49" s="443"/>
-      <c r="E49" s="521" t="s">
+      <c r="E49" s="525" t="s">
         <v>185</v>
       </c>
-      <c r="F49" s="523"/>
+      <c r="F49" s="527"/>
       <c r="G49" s="373"/>
-      <c r="H49" s="521" t="s">
+      <c r="H49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="I49" s="523"/>
+      <c r="I49" s="527"/>
       <c r="J49" s="373"/>
-      <c r="K49" s="521" t="s">
+      <c r="K49" s="525" t="s">
         <v>185</v>
       </c>
-      <c r="L49" s="523"/>
+      <c r="L49" s="527"/>
       <c r="M49" s="443"/>
-      <c r="N49" s="521" t="s">
+      <c r="N49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="O49" s="523"/>
+      <c r="O49" s="527"/>
       <c r="P49" s="443"/>
-      <c r="Q49" s="521" t="s">
+      <c r="Q49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="R49" s="523"/>
+      <c r="R49" s="527"/>
       <c r="S49" s="154"/>
-      <c r="T49" s="521" t="s">
+      <c r="T49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="U49" s="523"/>
+      <c r="U49" s="527"/>
       <c r="V49" s="443"/>
-      <c r="W49" s="521" t="s">
+      <c r="W49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="X49" s="523"/>
+      <c r="X49" s="527"/>
       <c r="Y49" s="443"/>
-      <c r="Z49" s="521" t="s">
+      <c r="Z49" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AA49" s="523"/>
+      <c r="AA49" s="527"/>
       <c r="AB49" s="443"/>
       <c r="AC49" s="445" t="str">
         <f>E33</f>
@@ -29864,32 +29864,32 @@
       </c>
     </row>
     <row r="50" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="524"/>
-      <c r="C50" s="525"/>
+      <c r="B50" s="528"/>
+      <c r="C50" s="529"/>
       <c r="D50" s="363"/>
-      <c r="E50" s="524"/>
-      <c r="F50" s="525"/>
+      <c r="E50" s="528"/>
+      <c r="F50" s="529"/>
       <c r="G50" s="373"/>
-      <c r="H50" s="528"/>
-      <c r="I50" s="529"/>
+      <c r="H50" s="531"/>
+      <c r="I50" s="532"/>
       <c r="J50" s="373"/>
-      <c r="K50" s="524"/>
-      <c r="L50" s="525"/>
+      <c r="K50" s="528"/>
+      <c r="L50" s="529"/>
       <c r="M50" s="373"/>
-      <c r="N50" s="524"/>
-      <c r="O50" s="525"/>
+      <c r="N50" s="528"/>
+      <c r="O50" s="529"/>
       <c r="P50" s="373"/>
-      <c r="Q50" s="524"/>
-      <c r="R50" s="525"/>
+      <c r="Q50" s="528"/>
+      <c r="R50" s="529"/>
       <c r="S50" s="373"/>
-      <c r="T50" s="524"/>
-      <c r="U50" s="525"/>
+      <c r="T50" s="528"/>
+      <c r="U50" s="529"/>
       <c r="V50" s="373"/>
-      <c r="W50" s="524"/>
-      <c r="X50" s="525"/>
+      <c r="W50" s="528"/>
+      <c r="X50" s="529"/>
       <c r="Y50" s="373"/>
-      <c r="Z50" s="524"/>
-      <c r="AA50" s="525"/>
+      <c r="Z50" s="528"/>
+      <c r="AA50" s="529"/>
       <c r="AB50" s="373"/>
       <c r="AC50" s="445" t="str">
         <f t="shared" ref="AC50:AC51" si="34">E34</f>
@@ -29974,15 +29974,15 @@
       <c r="Z52" s="411"/>
       <c r="AA52" s="411"/>
       <c r="AB52" s="411"/>
-      <c r="AC52" s="521" t="s">
+      <c r="AC52" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AD52" s="523"/>
+      <c r="AD52" s="527"/>
       <c r="AE52" s="411"/>
-      <c r="AF52" s="521" t="s">
+      <c r="AF52" s="525" t="s">
         <v>184</v>
       </c>
-      <c r="AG52" s="523"/>
+      <c r="AG52" s="527"/>
     </row>
     <row r="53" spans="2:35" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="411"/>
@@ -30011,8 +30011,8 @@
       <c r="Z53" s="411"/>
       <c r="AA53" s="411"/>
       <c r="AB53" s="373"/>
-      <c r="AC53" s="524"/>
-      <c r="AD53" s="525"/>
+      <c r="AC53" s="528"/>
+      <c r="AD53" s="529"/>
       <c r="AE53" s="373"/>
       <c r="AF53" s="437"/>
       <c r="AG53" s="438"/>
@@ -30117,157 +30117,157 @@
       </c>
     </row>
     <row r="60" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B60" s="521" t="s">
+      <c r="B60" s="525" t="s">
         <v>209</v>
       </c>
-      <c r="C60" s="522"/>
+      <c r="C60" s="526"/>
       <c r="D60" s="373"/>
-      <c r="E60" s="521" t="s">
+      <c r="E60" s="525" t="s">
         <v>210</v>
       </c>
-      <c r="F60" s="523"/>
+      <c r="F60" s="527"/>
       <c r="G60" s="373"/>
-      <c r="H60" s="521" t="s">
+      <c r="H60" s="525" t="s">
         <v>211</v>
       </c>
-      <c r="I60" s="522"/>
+      <c r="I60" s="526"/>
       <c r="J60" s="373"/>
-      <c r="K60" s="521" t="s">
+      <c r="K60" s="525" t="s">
         <v>190</v>
       </c>
-      <c r="L60" s="522"/>
+      <c r="L60" s="526"/>
       <c r="M60" s="373"/>
-      <c r="N60" s="521" t="s">
+      <c r="N60" s="525" t="s">
         <v>191</v>
       </c>
-      <c r="O60" s="522"/>
+      <c r="O60" s="526"/>
       <c r="P60" s="373"/>
-      <c r="Q60" s="521" t="s">
+      <c r="Q60" s="525" t="s">
         <v>192</v>
       </c>
-      <c r="R60" s="522"/>
+      <c r="R60" s="526"/>
       <c r="S60" s="373"/>
-      <c r="T60" s="521" t="s">
+      <c r="T60" s="525" t="s">
         <v>193</v>
       </c>
-      <c r="U60" s="522"/>
+      <c r="U60" s="526"/>
       <c r="V60" s="373"/>
-      <c r="W60" s="521" t="s">
+      <c r="W60" s="525" t="s">
         <v>194</v>
       </c>
-      <c r="X60" s="522"/>
+      <c r="X60" s="526"/>
       <c r="Y60" s="373"/>
-      <c r="Z60" s="521" t="s">
+      <c r="Z60" s="525" t="s">
         <v>195</v>
       </c>
-      <c r="AA60" s="522"/>
+      <c r="AA60" s="526"/>
       <c r="AB60" s="373"/>
-      <c r="AC60" s="521" t="s">
+      <c r="AC60" s="525" t="s">
         <v>196</v>
       </c>
-      <c r="AD60" s="522"/>
+      <c r="AD60" s="526"/>
       <c r="AF60" s="373">
         <v>66.680000000000007</v>
       </c>
     </row>
     <row r="61" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="521" t="s">
+      <c r="B61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="C61" s="523"/>
+      <c r="C61" s="527"/>
       <c r="D61" s="373"/>
-      <c r="E61" s="521" t="s">
+      <c r="E61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="F61" s="523"/>
+      <c r="F61" s="527"/>
       <c r="G61" s="373"/>
-      <c r="H61" s="521" t="s">
+      <c r="H61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="I61" s="523"/>
+      <c r="I61" s="527"/>
       <c r="J61" s="373"/>
-      <c r="K61" s="521" t="s">
+      <c r="K61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="L61" s="523"/>
+      <c r="L61" s="527"/>
       <c r="M61" s="373"/>
-      <c r="N61" s="521" t="s">
+      <c r="N61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="O61" s="523"/>
+      <c r="O61" s="527"/>
       <c r="P61" s="373"/>
-      <c r="Q61" s="521" t="s">
+      <c r="Q61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="R61" s="523"/>
+      <c r="R61" s="527"/>
       <c r="S61" s="373"/>
-      <c r="T61" s="521" t="s">
+      <c r="T61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="U61" s="523"/>
+      <c r="U61" s="527"/>
       <c r="V61" s="373"/>
-      <c r="W61" s="521" t="s">
+      <c r="W61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="X61" s="523"/>
+      <c r="X61" s="527"/>
       <c r="Y61" s="373"/>
-      <c r="Z61" s="521" t="s">
+      <c r="Z61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="AA61" s="523"/>
+      <c r="AA61" s="527"/>
       <c r="AB61" s="373"/>
-      <c r="AC61" s="521" t="s">
+      <c r="AC61" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="AD61" s="523"/>
+      <c r="AD61" s="527"/>
       <c r="AF61" s="363">
         <v>66.260000000000005</v>
       </c>
     </row>
     <row r="62" spans="2:35" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B62" s="528">
+      <c r="B62" s="531">
         <v>714</v>
       </c>
-      <c r="C62" s="529"/>
+      <c r="C62" s="532"/>
       <c r="D62" s="373"/>
-      <c r="E62" s="528">
+      <c r="E62" s="531">
         <v>385</v>
       </c>
-      <c r="F62" s="529"/>
+      <c r="F62" s="532"/>
       <c r="G62" s="373"/>
-      <c r="H62" s="528">
+      <c r="H62" s="531">
         <v>0</v>
       </c>
-      <c r="I62" s="529"/>
+      <c r="I62" s="532"/>
       <c r="J62" s="373"/>
-      <c r="K62" s="524">
+      <c r="K62" s="528">
         <v>39</v>
       </c>
-      <c r="L62" s="525"/>
+      <c r="L62" s="529"/>
       <c r="M62" s="373"/>
-      <c r="N62" s="524"/>
-      <c r="O62" s="525"/>
+      <c r="N62" s="528"/>
+      <c r="O62" s="529"/>
       <c r="P62" s="373"/>
-      <c r="Q62" s="524">
+      <c r="Q62" s="528">
         <v>202</v>
       </c>
-      <c r="R62" s="525"/>
+      <c r="R62" s="529"/>
       <c r="S62" s="373"/>
-      <c r="T62" s="524">
+      <c r="T62" s="528">
         <v>187</v>
       </c>
-      <c r="U62" s="525"/>
+      <c r="U62" s="529"/>
       <c r="V62" s="373"/>
-      <c r="W62" s="524"/>
-      <c r="X62" s="525"/>
+      <c r="W62" s="528"/>
+      <c r="X62" s="529"/>
       <c r="Y62" s="373"/>
-      <c r="Z62" s="524">
+      <c r="Z62" s="528">
         <v>50</v>
       </c>
-      <c r="AA62" s="525"/>
+      <c r="AA62" s="529"/>
       <c r="AB62" s="373"/>
-      <c r="AC62" s="524"/>
-      <c r="AD62" s="525"/>
+      <c r="AC62" s="528"/>
+      <c r="AD62" s="529"/>
       <c r="AE62" s="373"/>
       <c r="AF62" s="373">
         <v>66</v>
@@ -30365,144 +30365,327 @@
       </c>
     </row>
     <row r="68" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B68" s="521" t="s">
+      <c r="B68" s="525" t="s">
         <v>170</v>
       </c>
-      <c r="C68" s="522"/>
-      <c r="E68" s="521" t="s">
+      <c r="C68" s="526"/>
+      <c r="E68" s="525" t="s">
         <v>173</v>
       </c>
-      <c r="F68" s="522"/>
-      <c r="H68" s="521" t="s">
+      <c r="F68" s="526"/>
+      <c r="H68" s="525" t="s">
         <v>174</v>
       </c>
-      <c r="I68" s="522"/>
-      <c r="K68" s="521" t="s">
+      <c r="I68" s="526"/>
+      <c r="K68" s="525" t="s">
         <v>175</v>
       </c>
-      <c r="L68" s="522"/>
-      <c r="N68" s="521" t="s">
+      <c r="L68" s="526"/>
+      <c r="N68" s="525" t="s">
         <v>176</v>
       </c>
-      <c r="O68" s="522"/>
-      <c r="Q68" s="521" t="s">
+      <c r="O68" s="526"/>
+      <c r="Q68" s="525" t="s">
         <v>177</v>
       </c>
-      <c r="R68" s="522"/>
-      <c r="T68" s="521" t="s">
+      <c r="R68" s="526"/>
+      <c r="T68" s="525" t="s">
         <v>178</v>
       </c>
-      <c r="U68" s="522"/>
-      <c r="W68" s="521" t="s">
+      <c r="U68" s="526"/>
+      <c r="W68" s="525" t="s">
         <v>179</v>
       </c>
-      <c r="X68" s="522"/>
-      <c r="Z68" s="521" t="s">
+      <c r="X68" s="526"/>
+      <c r="Z68" s="525" t="s">
         <v>239</v>
       </c>
-      <c r="AA68" s="522"/>
-      <c r="AC68" s="521" t="s">
+      <c r="AA68" s="526"/>
+      <c r="AC68" s="525" t="s">
         <v>180</v>
       </c>
-      <c r="AD68" s="522"/>
+      <c r="AD68" s="526"/>
     </row>
     <row r="69" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B69" s="521" t="s">
+      <c r="B69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="C69" s="522"/>
-      <c r="E69" s="521" t="s">
+      <c r="C69" s="526"/>
+      <c r="E69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="F69" s="523"/>
-      <c r="H69" s="521" t="s">
+      <c r="F69" s="527"/>
+      <c r="H69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="I69" s="523"/>
-      <c r="K69" s="521" t="s">
+      <c r="I69" s="527"/>
+      <c r="K69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="L69" s="523"/>
-      <c r="N69" s="521" t="s">
+      <c r="L69" s="527"/>
+      <c r="N69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="O69" s="523"/>
-      <c r="Q69" s="521" t="s">
+      <c r="O69" s="527"/>
+      <c r="Q69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="R69" s="523"/>
-      <c r="T69" s="521" t="s">
+      <c r="R69" s="527"/>
+      <c r="T69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="U69" s="523"/>
-      <c r="W69" s="521" t="s">
+      <c r="U69" s="527"/>
+      <c r="W69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="X69" s="523"/>
-      <c r="Z69" s="521" t="s">
+      <c r="X69" s="527"/>
+      <c r="Z69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="AA69" s="523"/>
-      <c r="AC69" s="521" t="s">
+      <c r="AA69" s="527"/>
+      <c r="AC69" s="525" t="s">
         <v>212</v>
       </c>
-      <c r="AD69" s="523"/>
+      <c r="AD69" s="527"/>
     </row>
     <row r="70" spans="2:32" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B70" s="524">
+      <c r="B70" s="528">
         <v>161</v>
       </c>
-      <c r="C70" s="525"/>
+      <c r="C70" s="529"/>
       <c r="D70" s="373"/>
-      <c r="E70" s="528">
+      <c r="E70" s="531">
         <v>108</v>
       </c>
-      <c r="F70" s="529"/>
+      <c r="F70" s="532"/>
       <c r="G70" s="373"/>
-      <c r="H70" s="528">
+      <c r="H70" s="531">
         <v>90</v>
       </c>
-      <c r="I70" s="529"/>
+      <c r="I70" s="532"/>
       <c r="J70" s="373"/>
-      <c r="K70" s="528">
+      <c r="K70" s="531">
         <v>1170</v>
       </c>
-      <c r="L70" s="529"/>
+      <c r="L70" s="532"/>
       <c r="M70" s="373"/>
-      <c r="N70" s="524">
+      <c r="N70" s="528">
         <v>500</v>
       </c>
-      <c r="O70" s="525"/>
+      <c r="O70" s="529"/>
       <c r="P70" s="373"/>
-      <c r="Q70" s="524">
+      <c r="Q70" s="528">
         <v>295</v>
       </c>
-      <c r="R70" s="525"/>
+      <c r="R70" s="529"/>
       <c r="S70" s="373"/>
-      <c r="T70" s="524">
+      <c r="T70" s="528">
         <v>1</v>
       </c>
-      <c r="U70" s="525"/>
+      <c r="U70" s="529"/>
       <c r="V70" s="373"/>
-      <c r="W70" s="524">
+      <c r="W70" s="528">
         <v>32</v>
       </c>
-      <c r="X70" s="525"/>
+      <c r="X70" s="529"/>
       <c r="Y70" s="373"/>
-      <c r="Z70" s="524">
+      <c r="Z70" s="528">
         <v>105</v>
       </c>
-      <c r="AA70" s="525"/>
-      <c r="AC70" s="524">
+      <c r="AA70" s="529"/>
+      <c r="AC70" s="528">
         <v>90</v>
       </c>
-      <c r="AD70" s="525"/>
+      <c r="AD70" s="529"/>
     </row>
     <row r="86" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M86" s="363"/>
     </row>
   </sheetData>
   <mergeCells count="207">
+    <mergeCell ref="AC68:AD68"/>
+    <mergeCell ref="AC69:AD69"/>
+    <mergeCell ref="AI5:AJ5"/>
+    <mergeCell ref="AI18:AJ18"/>
+    <mergeCell ref="AI19:AJ19"/>
+    <mergeCell ref="AI20:AJ20"/>
+    <mergeCell ref="AI21:AJ21"/>
+    <mergeCell ref="AF42:AG42"/>
+    <mergeCell ref="Z49:AA49"/>
+    <mergeCell ref="Z50:AA50"/>
+    <mergeCell ref="AF52:AG52"/>
+    <mergeCell ref="AC61:AD61"/>
+    <mergeCell ref="AC62:AD62"/>
+    <mergeCell ref="AC52:AD52"/>
+    <mergeCell ref="AC53:AD53"/>
+    <mergeCell ref="AC60:AD60"/>
+    <mergeCell ref="Z42:AA42"/>
+    <mergeCell ref="AC42:AD42"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="E69:F69"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="K69:L69"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="Q69:R69"/>
+    <mergeCell ref="T69:U69"/>
+    <mergeCell ref="Z70:AA70"/>
+    <mergeCell ref="AC70:AD70"/>
+    <mergeCell ref="W69:X69"/>
+    <mergeCell ref="Z69:AA69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="E70:F70"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="K70:L70"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="Q70:R70"/>
+    <mergeCell ref="T70:U70"/>
+    <mergeCell ref="W70:X70"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="E68:F68"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="K68:L68"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="Q68:R68"/>
+    <mergeCell ref="T68:U68"/>
+    <mergeCell ref="W68:X68"/>
+    <mergeCell ref="Z68:AA68"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="E62:F62"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="K62:L62"/>
+    <mergeCell ref="N62:O62"/>
+    <mergeCell ref="Q62:R62"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="W62:X62"/>
+    <mergeCell ref="Z62:AA62"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="E61:F61"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="K61:L61"/>
+    <mergeCell ref="N61:O61"/>
+    <mergeCell ref="Q61:R61"/>
+    <mergeCell ref="T61:U61"/>
+    <mergeCell ref="W61:X61"/>
+    <mergeCell ref="Z61:AA61"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="E60:F60"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="K60:L60"/>
+    <mergeCell ref="N60:O60"/>
+    <mergeCell ref="Q60:R60"/>
+    <mergeCell ref="T60:U60"/>
+    <mergeCell ref="W60:X60"/>
+    <mergeCell ref="Z60:AA60"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="E50:F50"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="K50:L50"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="Q50:R50"/>
+    <mergeCell ref="T50:U50"/>
+    <mergeCell ref="W50:X50"/>
+    <mergeCell ref="T42:U42"/>
+    <mergeCell ref="W42:X42"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="Q49:R49"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="Q42:R42"/>
+    <mergeCell ref="T49:U49"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="T39:U39"/>
+    <mergeCell ref="W39:X39"/>
+    <mergeCell ref="Z39:AA39"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AF39:AG39"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="E39:F39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="N39:O39"/>
+    <mergeCell ref="Q39:R39"/>
+    <mergeCell ref="W38:X38"/>
+    <mergeCell ref="Z38:AA38"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AF38:AG38"/>
+    <mergeCell ref="T37:U37"/>
+    <mergeCell ref="W37:X37"/>
+    <mergeCell ref="Z37:AA37"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="W36:X36"/>
+    <mergeCell ref="Z36:AA36"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AF36:AG36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="E37:F37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="Q37:R37"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="E36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="Q36:R36"/>
+    <mergeCell ref="T36:U36"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="N38:O38"/>
+    <mergeCell ref="Q38:R38"/>
+    <mergeCell ref="T38:U38"/>
+    <mergeCell ref="AF21:AG21"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="N23:O23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="T23:U23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="Z23:AA23"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AF23:AG23"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="T21:U21"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="Z21:AA21"/>
+    <mergeCell ref="AC21:AD21"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="N20:O20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="T20:U20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="Z20:AA20"/>
+    <mergeCell ref="AC20:AD20"/>
+    <mergeCell ref="AF20:AG20"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="N19:O19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="Z19:AA19"/>
+    <mergeCell ref="AC19:AD19"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
@@ -30527,189 +30710,6 @@
     <mergeCell ref="AC5:AD5"/>
     <mergeCell ref="AC18:AD18"/>
     <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="T21:U21"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="Z21:AA21"/>
-    <mergeCell ref="AC21:AD21"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="N20:O20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="T20:U20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="Z20:AA20"/>
-    <mergeCell ref="AC20:AD20"/>
-    <mergeCell ref="AF20:AG20"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="T19:U19"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="Z19:AA19"/>
-    <mergeCell ref="AC19:AD19"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="E38:F38"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="N38:O38"/>
-    <mergeCell ref="Q38:R38"/>
-    <mergeCell ref="T38:U38"/>
-    <mergeCell ref="AF21:AG21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="N23:O23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="T23:U23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="Z23:AA23"/>
-    <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="AF23:AG23"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="N21:O21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="W36:X36"/>
-    <mergeCell ref="Z36:AA36"/>
-    <mergeCell ref="AC36:AD36"/>
-    <mergeCell ref="AF36:AG36"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="E37:F37"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="Q37:R37"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="E36:F36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="Q36:R36"/>
-    <mergeCell ref="T36:U36"/>
-    <mergeCell ref="W38:X38"/>
-    <mergeCell ref="Z38:AA38"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AF38:AG38"/>
-    <mergeCell ref="T37:U37"/>
-    <mergeCell ref="W37:X37"/>
-    <mergeCell ref="Z37:AA37"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="AF37:AG37"/>
-    <mergeCell ref="T39:U39"/>
-    <mergeCell ref="W39:X39"/>
-    <mergeCell ref="Z39:AA39"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AF39:AG39"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="E39:F39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="N39:O39"/>
-    <mergeCell ref="Q39:R39"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="E50:F50"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="K50:L50"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="Q50:R50"/>
-    <mergeCell ref="T50:U50"/>
-    <mergeCell ref="W50:X50"/>
-    <mergeCell ref="T42:U42"/>
-    <mergeCell ref="W42:X42"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="E49:F49"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="Q49:R49"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="E42:F42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="Q42:R42"/>
-    <mergeCell ref="T49:U49"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="E60:F60"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="K60:L60"/>
-    <mergeCell ref="N60:O60"/>
-    <mergeCell ref="Q60:R60"/>
-    <mergeCell ref="T60:U60"/>
-    <mergeCell ref="W60:X60"/>
-    <mergeCell ref="Z60:AA60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="E61:F61"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="K61:L61"/>
-    <mergeCell ref="N61:O61"/>
-    <mergeCell ref="Q61:R61"/>
-    <mergeCell ref="T61:U61"/>
-    <mergeCell ref="W61:X61"/>
-    <mergeCell ref="Z61:AA61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="E62:F62"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="K62:L62"/>
-    <mergeCell ref="N62:O62"/>
-    <mergeCell ref="Q62:R62"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="W62:X62"/>
-    <mergeCell ref="Z62:AA62"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="E68:F68"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="K68:L68"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="Q68:R68"/>
-    <mergeCell ref="T68:U68"/>
-    <mergeCell ref="W68:X68"/>
-    <mergeCell ref="Z68:AA68"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="E69:F69"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="K69:L69"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="Q69:R69"/>
-    <mergeCell ref="T69:U69"/>
-    <mergeCell ref="Z70:AA70"/>
-    <mergeCell ref="AC70:AD70"/>
-    <mergeCell ref="W69:X69"/>
-    <mergeCell ref="Z69:AA69"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="E70:F70"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="K70:L70"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="Q70:R70"/>
-    <mergeCell ref="T70:U70"/>
-    <mergeCell ref="W70:X70"/>
-    <mergeCell ref="AC68:AD68"/>
-    <mergeCell ref="AC69:AD69"/>
-    <mergeCell ref="AI5:AJ5"/>
-    <mergeCell ref="AI18:AJ18"/>
-    <mergeCell ref="AI19:AJ19"/>
-    <mergeCell ref="AI20:AJ20"/>
-    <mergeCell ref="AI21:AJ21"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="Z49:AA49"/>
-    <mergeCell ref="Z50:AA50"/>
-    <mergeCell ref="AF52:AG52"/>
-    <mergeCell ref="AC61:AD61"/>
-    <mergeCell ref="AC62:AD62"/>
-    <mergeCell ref="AC52:AD52"/>
-    <mergeCell ref="AC53:AD53"/>
-    <mergeCell ref="AC60:AD60"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AC42:AD42"/>
   </mergeCells>
   <conditionalFormatting sqref="F9">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
@@ -30746,15 +30746,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="467" t="s">
+      <c r="A1" s="469" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="467"/>
-      <c r="C1" s="467"/>
-      <c r="J1" s="468" t="s">
+      <c r="B1" s="469"/>
+      <c r="C1" s="469"/>
+      <c r="J1" s="470" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="468"/>
+      <c r="K1" s="470"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" s="136"/>
@@ -30908,7 +30908,7 @@
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="534">
+      <c r="A9" s="447">
         <v>0.5</v>
       </c>
       <c r="B9" s="141">
@@ -30926,10 +30926,10 @@
         <v>45</v>
       </c>
       <c r="B10" s="141"/>
-      <c r="J10" s="468" t="s">
+      <c r="J10" s="470" t="s">
         <v>125</v>
       </c>
-      <c r="K10" s="468"/>
+      <c r="K10" s="470"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -31166,11 +31166,11 @@
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="467" t="s">
+      <c r="A20" s="469" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="467"/>
-      <c r="C20" s="467"/>
+      <c r="B20" s="469"/>
+      <c r="C20" s="469"/>
       <c r="J20" s="2">
         <f ca="1">'Loading Arrival'!B35</f>
         <v>45923</v>
@@ -31311,7 +31311,7 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="534">
+      <c r="A28" s="447">
         <v>0.5</v>
       </c>
       <c r="B28" s="141">
@@ -31694,18 +31694,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="484" t="s">
+      <c r="A1" s="486" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="485"/>
-      <c r="C1" s="485"/>
-      <c r="D1" s="486"/>
-      <c r="F1" s="469" t="s">
+      <c r="B1" s="487"/>
+      <c r="C1" s="487"/>
+      <c r="D1" s="488"/>
+      <c r="F1" s="471" t="s">
         <v>215</v>
       </c>
-      <c r="G1" s="470"/>
-      <c r="H1" s="470"/>
-      <c r="I1" s="471"/>
+      <c r="G1" s="472"/>
+      <c r="H1" s="472"/>
+      <c r="I1" s="473"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="32"/>
@@ -31730,7 +31730,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="496" t="s">
+      <c r="A3" s="498" t="s">
         <v>46</v>
       </c>
       <c r="B3" s="23">
@@ -31745,7 +31745,7 @@
         <f ca="1">C3+14</f>
         <v>45938</v>
       </c>
-      <c r="F3" s="472" t="s">
+      <c r="F3" s="474" t="s">
         <v>50</v>
       </c>
       <c r="G3" s="417">
@@ -31762,7 +31762,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="496"/>
+      <c r="A4" s="498"/>
       <c r="B4" s="26">
         <f ca="1">B5-B3</f>
         <v>21</v>
@@ -31775,7 +31775,7 @@
         <f ca="1">D5-D3</f>
         <v>24</v>
       </c>
-      <c r="F4" s="473"/>
+      <c r="F4" s="475"/>
       <c r="G4" s="420">
         <f ca="1">G5-G3</f>
         <v>28</v>
@@ -31790,7 +31790,7 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="496"/>
+      <c r="A5" s="498"/>
       <c r="B5" s="29">
         <f ca="1">EOMONTH(B3,0)+1</f>
         <v>45931</v>
@@ -31803,7 +31803,7 @@
         <f ca="1">EOMONTH(D3,0)+1</f>
         <v>45962</v>
       </c>
-      <c r="F5" s="473"/>
+      <c r="F5" s="475"/>
       <c r="G5" s="423">
         <f ca="1">EOMONTH(G3,0)+1</f>
         <v>45931</v>
@@ -31818,7 +31818,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="496"/>
+      <c r="A6" s="498"/>
       <c r="B6" s="26">
         <f ca="1">IF(45-B4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),45-B4)</f>
         <v>24</v>
@@ -31831,7 +31831,7 @@
         <f ca="1">IF(45-D4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),45-D4)</f>
         <v>21</v>
       </c>
-      <c r="F6" s="473"/>
+      <c r="F6" s="475"/>
       <c r="G6" s="420">
         <f ca="1">IF(15-G4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),15-G4)</f>
         <v>-13</v>
@@ -31846,7 +31846,7 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="496"/>
+      <c r="A7" s="498"/>
       <c r="B7" s="29">
         <f ca="1">B5+B6</f>
         <v>45955</v>
@@ -31859,7 +31859,7 @@
         <f ca="1">D5+D6</f>
         <v>45983</v>
       </c>
-      <c r="F7" s="473"/>
+      <c r="F7" s="475"/>
       <c r="G7" s="423">
         <f ca="1">G5+G6</f>
         <v>45918</v>
@@ -31874,7 +31874,7 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="496"/>
+      <c r="A8" s="498"/>
       <c r="B8" s="26">
         <f ca="1">IF(45-B4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B5,0))),45-B4-B6,0)</f>
         <v>0</v>
@@ -31887,7 +31887,7 @@
         <f ca="1">IF(45-D4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(D5,0))),45-D4-D6,0)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="473"/>
+      <c r="F8" s="475"/>
       <c r="G8" s="420">
         <f ca="1">IF(15-G4&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(G5,0))),15-G4-G6,0)</f>
         <v>0</v>
@@ -31902,7 +31902,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="497"/>
+      <c r="A9" s="499"/>
       <c r="B9" s="29">
         <f ca="1">B7+B8</f>
         <v>45955</v>
@@ -31915,7 +31915,7 @@
         <f ca="1">D7+D8</f>
         <v>45983</v>
       </c>
-      <c r="F9" s="474"/>
+      <c r="F9" s="476"/>
       <c r="G9" s="426">
         <f ca="1">G7+G8</f>
         <v>45918</v>
@@ -31942,7 +31942,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="498" t="s">
+      <c r="A11" s="500" t="s">
         <v>50</v>
       </c>
       <c r="B11" s="51">
@@ -31959,7 +31959,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="499"/>
+      <c r="A12" s="501"/>
       <c r="B12" s="54">
         <f ca="1">B13-B11</f>
         <v>28</v>
@@ -31974,7 +31974,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="499"/>
+      <c r="A13" s="501"/>
       <c r="B13" s="57">
         <f ca="1">EOMONTH(B11,0)+1</f>
         <v>45931</v>
@@ -31989,7 +31989,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="499"/>
+      <c r="A14" s="501"/>
       <c r="B14" s="54">
         <f ca="1">IF(27-B12&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),27-B12)</f>
         <v>-1</v>
@@ -32004,7 +32004,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="499"/>
+      <c r="A15" s="501"/>
       <c r="B15" s="57">
         <f ca="1">B13+B14</f>
         <v>45930</v>
@@ -32020,7 +32020,7 @@
       <c r="H15" s="363"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="499"/>
+      <c r="A16" s="501"/>
       <c r="B16" s="54">
         <f ca="1">IF(27-B12&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B13,0))),30-B12-B14,0)</f>
         <v>0</v>
@@ -32035,7 +32035,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="500"/>
+      <c r="A17" s="502"/>
       <c r="B17" s="60">
         <f ca="1">B15+B16</f>
         <v>45930</v>
@@ -32050,12 +32050,12 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="487" t="s">
+      <c r="A18" s="489" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="488"/>
-      <c r="C18" s="488"/>
-      <c r="D18" s="489"/>
+      <c r="B18" s="490"/>
+      <c r="C18" s="490"/>
+      <c r="D18" s="491"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="63"/>
@@ -32070,7 +32070,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="475" t="s">
+      <c r="A20" s="477" t="s">
         <v>50</v>
       </c>
       <c r="B20" s="67">
@@ -32087,7 +32087,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="476"/>
+      <c r="A21" s="478"/>
       <c r="B21" s="70">
         <f ca="1">B22-B20</f>
         <v>28</v>
@@ -32102,7 +32102,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="476"/>
+      <c r="A22" s="478"/>
       <c r="B22" s="71">
         <f ca="1">EOMONTH(B20,0)+1</f>
         <v>45931</v>
@@ -32117,7 +32117,7 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="476"/>
+      <c r="A23" s="478"/>
       <c r="B23" s="70">
         <f ca="1">IF(19-B21&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),19-B21)</f>
         <v>-9</v>
@@ -32132,7 +32132,7 @@
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="476"/>
+      <c r="A24" s="478"/>
       <c r="B24" s="71">
         <f ca="1">B22+B23</f>
         <v>45922</v>
@@ -32147,7 +32147,7 @@
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="476"/>
+      <c r="A25" s="478"/>
       <c r="B25" s="70">
         <f ca="1">IF(19-B21&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B22,0))),19-B21-B23,0)</f>
         <v>0</v>
@@ -32162,7 +32162,7 @@
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="477"/>
+      <c r="A26" s="479"/>
       <c r="B26" s="72">
         <f ca="1">B24+B25</f>
         <v>45922</v>
@@ -32177,12 +32177,12 @@
       </c>
     </row>
     <row r="27" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="490" t="s">
+      <c r="A27" s="492" t="s">
         <v>54</v>
       </c>
-      <c r="B27" s="491"/>
-      <c r="C27" s="491"/>
-      <c r="D27" s="492"/>
+      <c r="B27" s="493"/>
+      <c r="C27" s="493"/>
+      <c r="D27" s="494"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="73"/>
@@ -32197,7 +32197,7 @@
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="478" t="s">
+      <c r="A29" s="480" t="s">
         <v>50</v>
       </c>
       <c r="B29" s="17">
@@ -32214,7 +32214,7 @@
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="479"/>
+      <c r="A30" s="481"/>
       <c r="B30" s="11">
         <f ca="1">B31-B29</f>
         <v>28</v>
@@ -32229,7 +32229,7 @@
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="479"/>
+      <c r="A31" s="481"/>
       <c r="B31" s="14">
         <f ca="1">EOMONTH(B29,0)+1</f>
         <v>45931</v>
@@ -32244,7 +32244,7 @@
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="479"/>
+      <c r="A32" s="481"/>
       <c r="B32" s="11">
         <f ca="1">IF(20-B30&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),20-B30)</f>
         <v>-8</v>
@@ -32259,7 +32259,7 @@
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="479"/>
+      <c r="A33" s="481"/>
       <c r="B33" s="14">
         <f ca="1">B31+B32</f>
         <v>45923</v>
@@ -32274,7 +32274,7 @@
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="479"/>
+      <c r="A34" s="481"/>
       <c r="B34" s="11">
         <f ca="1">IF(20-B30&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B31,0))),20-B30-B32,0)</f>
         <v>0</v>
@@ -32289,7 +32289,7 @@
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="480"/>
+      <c r="A35" s="482"/>
       <c r="B35" s="20">
         <f ca="1">B33+B34</f>
         <v>45923</v>
@@ -32304,12 +32304,12 @@
       </c>
     </row>
     <row r="36" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="493" t="s">
+      <c r="A36" s="495" t="s">
         <v>53</v>
       </c>
-      <c r="B36" s="494"/>
-      <c r="C36" s="494"/>
-      <c r="D36" s="495"/>
+      <c r="B36" s="496"/>
+      <c r="C36" s="496"/>
+      <c r="D36" s="497"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="83"/>
@@ -32324,7 +32324,7 @@
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="481" t="s">
+      <c r="A38" s="483" t="s">
         <v>50</v>
       </c>
       <c r="B38" s="77">
@@ -32341,7 +32341,7 @@
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="482"/>
+      <c r="A39" s="484"/>
       <c r="B39" s="80">
         <f ca="1">B40-B38</f>
         <v>12</v>
@@ -32356,7 +32356,7 @@
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="482"/>
+      <c r="A40" s="484"/>
       <c r="B40" s="81">
         <f ca="1">IF(EOMONTH(B38,0)+1-B38&gt;12,B38+12,EOMONTH(B38,0)+1)</f>
         <v>45915</v>
@@ -32371,7 +32371,7 @@
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="482"/>
+      <c r="A41" s="484"/>
       <c r="B41" s="80">
         <f ca="1">IF(12-B39&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),12-B39)</f>
         <v>0</v>
@@ -32386,7 +32386,7 @@
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="482"/>
+      <c r="A42" s="484"/>
       <c r="B42" s="81">
         <f ca="1">B40+B41</f>
         <v>45915</v>
@@ -32401,7 +32401,7 @@
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="482"/>
+      <c r="A43" s="484"/>
       <c r="B43" s="80">
         <f ca="1">IF(12-B39&gt;_xlfn.NUMBERVALUE(DAY(EOMONTH(B40,0))),20-B39-B41,0)</f>
         <v>0</v>
@@ -32416,7 +32416,7 @@
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="483"/>
+      <c r="A44" s="485"/>
       <c r="B44" s="82">
         <f ca="1">B42+B43</f>
         <v>45915</v>
@@ -32480,74 +32480,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="511" t="s">
+      <c r="E3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="512"/>
-      <c r="G3" s="511" t="s">
+      <c r="F3" s="504"/>
+      <c r="G3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="512"/>
-      <c r="I3" s="511" t="s">
+      <c r="H3" s="504"/>
+      <c r="I3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="512"/>
-      <c r="P3" s="511" t="s">
+      <c r="J3" s="504"/>
+      <c r="P3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="511" t="s">
+      <c r="Q3" s="504"/>
+      <c r="R3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="512"/>
-      <c r="T3" s="511" t="s">
+      <c r="S3" s="504"/>
+      <c r="T3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="512"/>
+      <c r="U3" s="504"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="509" t="s">
+      <c r="A4" s="505" t="s">
         <v>217</v>
       </c>
-      <c r="B4" s="510"/>
-      <c r="C4" s="510"/>
-      <c r="D4" s="510"/>
-      <c r="E4" s="508">
+      <c r="B4" s="506"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="507">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="502"/>
-      <c r="G4" s="501">
+      <c r="F4" s="508"/>
+      <c r="G4" s="509">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="502"/>
-      <c r="I4" s="501">
+      <c r="H4" s="508"/>
+      <c r="I4" s="509">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="502"/>
-      <c r="L4" s="509" t="s">
+      <c r="J4" s="508"/>
+      <c r="L4" s="505" t="s">
         <v>216</v>
       </c>
-      <c r="M4" s="510"/>
-      <c r="N4" s="510"/>
-      <c r="O4" s="510"/>
-      <c r="P4" s="508">
+      <c r="M4" s="506"/>
+      <c r="N4" s="506"/>
+      <c r="O4" s="506"/>
+      <c r="P4" s="507">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="502"/>
-      <c r="R4" s="501">
+      <c r="Q4" s="508"/>
+      <c r="R4" s="509">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="502"/>
-      <c r="T4" s="501">
+      <c r="S4" s="508"/>
+      <c r="T4" s="509">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="502"/>
+      <c r="U4" s="508"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -33830,56 +33830,45 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="503">
+      <c r="E25" s="510">
         <f ca="1">'Loading Arrival'!G9</f>
         <v>45918</v>
       </c>
-      <c r="F25" s="504"/>
-      <c r="G25" s="505">
+      <c r="F25" s="511"/>
+      <c r="G25" s="512">
         <f ca="1">'Loading Arrival'!H9</f>
         <v>45932</v>
       </c>
-      <c r="H25" s="506"/>
-      <c r="I25" s="507">
+      <c r="H25" s="513"/>
+      <c r="I25" s="514">
         <f ca="1">'Loading Arrival'!I9</f>
         <v>45946</v>
       </c>
-      <c r="J25" s="504"/>
+      <c r="J25" s="511"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="503">
+      <c r="P25" s="510">
         <f ca="1">E25</f>
         <v>45918</v>
       </c>
-      <c r="Q25" s="504"/>
-      <c r="R25" s="505">
+      <c r="Q25" s="511"/>
+      <c r="R25" s="512">
         <f ca="1">G25</f>
         <v>45932</v>
       </c>
-      <c r="S25" s="506"/>
-      <c r="T25" s="507">
+      <c r="S25" s="513"/>
+      <c r="T25" s="514">
         <f ca="1">I25</f>
         <v>45946</v>
       </c>
-      <c r="U25" s="504"/>
+      <c r="U25" s="511"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -33889,6 +33878,17 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -33921,38 +33921,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="511" t="s">
+      <c r="E3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="512"/>
-      <c r="G3" s="511" t="s">
+      <c r="F3" s="504"/>
+      <c r="G3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="512"/>
-      <c r="N3" s="511" t="s">
+      <c r="H3" s="504"/>
+      <c r="N3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="O3" s="512"/>
-      <c r="P3" s="511" t="s">
+      <c r="O3" s="504"/>
+      <c r="P3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="511" t="s">
+      <c r="Q3" s="504"/>
+      <c r="R3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="S3" s="512"/>
-      <c r="Y3" s="511" t="s">
+      <c r="S3" s="504"/>
+      <c r="Y3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="Z3" s="512"/>
-      <c r="AA3" s="511" t="s">
+      <c r="Z3" s="504"/>
+      <c r="AA3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="AB3" s="512"/>
-      <c r="AC3" s="511" t="s">
+      <c r="AB3" s="504"/>
+      <c r="AC3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="AD3" s="512"/>
+      <c r="AD3" s="504"/>
     </row>
     <row r="4" spans="1:30" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="340" t="s">
@@ -35901,61 +35901,69 @@
       <c r="B27" s="108"/>
       <c r="C27" s="105"/>
       <c r="D27" s="105"/>
-      <c r="E27" s="503">
+      <c r="E27" s="510">
         <f ca="1">'Loading Arrival'!B9</f>
         <v>45955</v>
       </c>
-      <c r="F27" s="504"/>
-      <c r="G27" s="503">
+      <c r="F27" s="511"/>
+      <c r="G27" s="510">
         <f ca="1">'Loading Arrival'!C9</f>
         <v>45969</v>
       </c>
-      <c r="H27" s="504"/>
+      <c r="H27" s="511"/>
       <c r="J27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="K27" s="108"/>
       <c r="L27" s="105"/>
       <c r="M27" s="105"/>
-      <c r="N27" s="503">
+      <c r="N27" s="510">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="O27" s="504"/>
-      <c r="P27" s="505">
+      <c r="O27" s="511"/>
+      <c r="P27" s="512">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="Q27" s="506"/>
-      <c r="R27" s="507">
+      <c r="Q27" s="513"/>
+      <c r="R27" s="514">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="S27" s="504"/>
+      <c r="S27" s="511"/>
       <c r="U27" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V27" s="108"/>
       <c r="W27" s="105"/>
       <c r="X27" s="105"/>
-      <c r="Y27" s="503">
+      <c r="Y27" s="510">
         <f ca="1">'Loading Arrival'!B17</f>
         <v>45930</v>
       </c>
-      <c r="Z27" s="504"/>
-      <c r="AA27" s="505">
+      <c r="Z27" s="511"/>
+      <c r="AA27" s="512">
         <f ca="1">'Loading Arrival'!C17</f>
         <v>45944</v>
       </c>
-      <c r="AB27" s="506"/>
-      <c r="AC27" s="507">
+      <c r="AB27" s="513"/>
+      <c r="AC27" s="514">
         <f ca="1">'Loading Arrival'!D17</f>
         <v>45958</v>
       </c>
-      <c r="AD27" s="504"/>
+      <c r="AD27" s="511"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="Y3:Z3"/>
+    <mergeCell ref="AA3:AB3"/>
+    <mergeCell ref="AC3:AD3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="Y27:Z27"/>
     <mergeCell ref="AA27:AB27"/>
     <mergeCell ref="AC27:AD27"/>
@@ -35964,14 +35972,6 @@
     <mergeCell ref="N27:O27"/>
     <mergeCell ref="P27:Q27"/>
     <mergeCell ref="R27:S27"/>
-    <mergeCell ref="Y3:Z3"/>
-    <mergeCell ref="AA3:AB3"/>
-    <mergeCell ref="AC3:AD3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="N3:O3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -36010,74 +36010,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="511" t="s">
+      <c r="E3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="512"/>
-      <c r="G3" s="511" t="s">
+      <c r="F3" s="504"/>
+      <c r="G3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="512"/>
-      <c r="I3" s="511" t="s">
+      <c r="H3" s="504"/>
+      <c r="I3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="512"/>
-      <c r="P3" s="511" t="s">
+      <c r="J3" s="504"/>
+      <c r="P3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="511" t="s">
+      <c r="Q3" s="504"/>
+      <c r="R3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="512"/>
-      <c r="T3" s="511" t="s">
+      <c r="S3" s="504"/>
+      <c r="T3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="512"/>
+      <c r="U3" s="504"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="509" t="s">
+      <c r="A4" s="505" t="s">
         <v>77</v>
       </c>
-      <c r="B4" s="510"/>
-      <c r="C4" s="510"/>
-      <c r="D4" s="510"/>
-      <c r="E4" s="508">
+      <c r="B4" s="506"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="507">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="502"/>
-      <c r="G4" s="501">
+      <c r="F4" s="508"/>
+      <c r="G4" s="509">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="502"/>
-      <c r="I4" s="501">
+      <c r="H4" s="508"/>
+      <c r="I4" s="509">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="502"/>
-      <c r="L4" s="509" t="s">
+      <c r="J4" s="508"/>
+      <c r="L4" s="505" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="510"/>
-      <c r="N4" s="510"/>
-      <c r="O4" s="510"/>
-      <c r="P4" s="508">
+      <c r="M4" s="506"/>
+      <c r="N4" s="506"/>
+      <c r="O4" s="506"/>
+      <c r="P4" s="507">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="502"/>
-      <c r="R4" s="501">
+      <c r="Q4" s="508"/>
+      <c r="R4" s="509">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="502"/>
-      <c r="T4" s="501">
+      <c r="S4" s="508"/>
+      <c r="T4" s="509">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="502"/>
+      <c r="U4" s="508"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -37360,51 +37360,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="503">
+      <c r="E25" s="510">
         <f ca="1">'Loading Arrival'!B35</f>
         <v>45923</v>
       </c>
-      <c r="F25" s="504"/>
-      <c r="G25" s="505">
+      <c r="F25" s="511"/>
+      <c r="G25" s="512">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="506"/>
-      <c r="I25" s="507">
+      <c r="H25" s="513"/>
+      <c r="I25" s="514">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="504"/>
+      <c r="J25" s="511"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="503">
+      <c r="P25" s="510">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="504"/>
-      <c r="R25" s="505">
+      <c r="Q25" s="511"/>
+      <c r="R25" s="512">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="506"/>
-      <c r="T25" s="507">
+      <c r="S25" s="513"/>
+      <c r="T25" s="514">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="504"/>
+      <c r="U25" s="511"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -37413,12 +37413,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -37457,74 +37457,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="511" t="s">
+      <c r="E3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="512"/>
-      <c r="G3" s="511" t="s">
+      <c r="F3" s="504"/>
+      <c r="G3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="512"/>
-      <c r="I3" s="511" t="s">
+      <c r="H3" s="504"/>
+      <c r="I3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="512"/>
-      <c r="P3" s="511" t="s">
+      <c r="J3" s="504"/>
+      <c r="P3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="511" t="s">
+      <c r="Q3" s="504"/>
+      <c r="R3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="512"/>
-      <c r="T3" s="511" t="s">
+      <c r="S3" s="504"/>
+      <c r="T3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="512"/>
+      <c r="U3" s="504"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="509" t="s">
+      <c r="A4" s="505" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="510"/>
-      <c r="C4" s="510"/>
-      <c r="D4" s="510"/>
-      <c r="E4" s="508">
+      <c r="B4" s="506"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="507">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="502"/>
-      <c r="G4" s="501">
+      <c r="F4" s="508"/>
+      <c r="G4" s="509">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="502"/>
-      <c r="I4" s="501">
+      <c r="H4" s="508"/>
+      <c r="I4" s="509">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="502"/>
-      <c r="L4" s="509" t="s">
+      <c r="J4" s="508"/>
+      <c r="L4" s="505" t="s">
         <v>74</v>
       </c>
-      <c r="M4" s="510"/>
-      <c r="N4" s="510"/>
-      <c r="O4" s="510"/>
-      <c r="P4" s="508">
+      <c r="M4" s="506"/>
+      <c r="N4" s="506"/>
+      <c r="O4" s="506"/>
+      <c r="P4" s="507">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="502"/>
-      <c r="R4" s="501">
+      <c r="Q4" s="508"/>
+      <c r="R4" s="509">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="502"/>
-      <c r="T4" s="501">
+      <c r="S4" s="508"/>
+      <c r="T4" s="509">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="502"/>
+      <c r="U4" s="508"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -38807,51 +38807,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="503">
+      <c r="E25" s="510">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="504"/>
-      <c r="G25" s="505">
+      <c r="F25" s="511"/>
+      <c r="G25" s="512">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="506"/>
-      <c r="I25" s="507">
+      <c r="H25" s="513"/>
+      <c r="I25" s="514">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="504"/>
+      <c r="J25" s="511"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="503">
+      <c r="P25" s="510">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="504"/>
-      <c r="R25" s="505">
+      <c r="Q25" s="511"/>
+      <c r="R25" s="512">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="506"/>
-      <c r="T25" s="507">
+      <c r="S25" s="513"/>
+      <c r="T25" s="514">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="504"/>
+      <c r="U25" s="511"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="P25:Q25"/>
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
@@ -38860,12 +38860,12 @@
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -38904,74 +38904,74 @@
   </cols>
   <sheetData>
     <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="E3" s="511" t="s">
+      <c r="E3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="512"/>
-      <c r="G3" s="511" t="s">
+      <c r="F3" s="504"/>
+      <c r="G3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="H3" s="512"/>
-      <c r="I3" s="511" t="s">
+      <c r="H3" s="504"/>
+      <c r="I3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="512"/>
-      <c r="P3" s="511" t="s">
+      <c r="J3" s="504"/>
+      <c r="P3" s="503" t="s">
         <v>47</v>
       </c>
-      <c r="Q3" s="512"/>
-      <c r="R3" s="511" t="s">
+      <c r="Q3" s="504"/>
+      <c r="R3" s="503" t="s">
         <v>48</v>
       </c>
-      <c r="S3" s="512"/>
-      <c r="T3" s="511" t="s">
+      <c r="S3" s="504"/>
+      <c r="T3" s="503" t="s">
         <v>49</v>
       </c>
-      <c r="U3" s="512"/>
+      <c r="U3" s="504"/>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="509" t="s">
+      <c r="A4" s="505" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="510"/>
-      <c r="C4" s="510"/>
-      <c r="D4" s="510"/>
-      <c r="E4" s="508">
+      <c r="B4" s="506"/>
+      <c r="C4" s="506"/>
+      <c r="D4" s="506"/>
+      <c r="E4" s="507">
         <f ca="1">'Loading Arrival'!B11</f>
         <v>45903</v>
       </c>
-      <c r="F4" s="502"/>
-      <c r="G4" s="501">
+      <c r="F4" s="508"/>
+      <c r="G4" s="509">
         <f ca="1">'Loading Arrival'!C11</f>
         <v>45917</v>
       </c>
-      <c r="H4" s="502"/>
-      <c r="I4" s="501">
+      <c r="H4" s="508"/>
+      <c r="I4" s="509">
         <f ca="1">'Loading Arrival'!D11</f>
         <v>45931</v>
       </c>
-      <c r="J4" s="502"/>
-      <c r="L4" s="509" t="s">
+      <c r="J4" s="508"/>
+      <c r="L4" s="505" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="510"/>
-      <c r="N4" s="510"/>
-      <c r="O4" s="510"/>
-      <c r="P4" s="508">
+      <c r="M4" s="506"/>
+      <c r="N4" s="506"/>
+      <c r="O4" s="506"/>
+      <c r="P4" s="507">
         <f ca="1">E4</f>
         <v>45903</v>
       </c>
-      <c r="Q4" s="502"/>
-      <c r="R4" s="501">
+      <c r="Q4" s="508"/>
+      <c r="R4" s="509">
         <f ca="1">G4</f>
         <v>45917</v>
       </c>
-      <c r="S4" s="502"/>
-      <c r="T4" s="501">
+      <c r="S4" s="508"/>
+      <c r="T4" s="509">
         <f ca="1">I4</f>
         <v>45931</v>
       </c>
-      <c r="U4" s="502"/>
+      <c r="U4" s="508"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="131"/>
@@ -40254,50 +40254,51 @@
       <c r="B25" s="108"/>
       <c r="C25" s="105"/>
       <c r="D25" s="105"/>
-      <c r="E25" s="503">
+      <c r="E25" s="510">
         <f>'Loading Arrival'!K9</f>
         <v>0</v>
       </c>
-      <c r="F25" s="504"/>
-      <c r="G25" s="505">
+      <c r="F25" s="511"/>
+      <c r="G25" s="512">
         <f>'Loading Arrival'!L9</f>
         <v>0</v>
       </c>
-      <c r="H25" s="506"/>
-      <c r="I25" s="507">
+      <c r="H25" s="513"/>
+      <c r="I25" s="514">
         <f>'Loading Arrival'!N9</f>
         <v>0</v>
       </c>
-      <c r="J25" s="504"/>
+      <c r="J25" s="511"/>
       <c r="L25" s="7" t="s">
         <v>101</v>
       </c>
       <c r="M25" s="108"/>
       <c r="N25" s="105"/>
       <c r="O25" s="105"/>
-      <c r="P25" s="503">
+      <c r="P25" s="510">
         <f>'Loading Arrival'!V9</f>
         <v>0</v>
       </c>
-      <c r="Q25" s="504"/>
-      <c r="R25" s="505">
+      <c r="Q25" s="511"/>
+      <c r="R25" s="512">
         <f>'Loading Arrival'!W9</f>
         <v>0</v>
       </c>
-      <c r="S25" s="506"/>
-      <c r="T25" s="507">
+      <c r="S25" s="513"/>
+      <c r="T25" s="514">
         <f>'Loading Arrival'!Y9</f>
         <v>0</v>
       </c>
-      <c r="U25" s="504"/>
+      <c r="U25" s="511"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="L4:O4"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R3:S3"/>
     <mergeCell ref="R4:S4"/>
     <mergeCell ref="T4:U4"/>
     <mergeCell ref="E25:F25"/>
@@ -40307,12 +40308,11 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="T25:U25"/>
     <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="L4:O4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
